--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3186" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="684">
   <si>
     <t>trade_time</t>
   </si>
@@ -1495,7 +1495,7 @@
     <t>2021-07-15</t>
   </si>
   <si>
-    <t>2021-07-22</t>
+    <t>2021-07-23</t>
   </si>
   <si>
     <t>2016-07-13</t>
@@ -2423,7 +2423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1058"/>
+  <dimension ref="A1:P1059"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -55087,7 +55087,7 @@
         <v>493</v>
       </c>
       <c r="E1054">
-        <v>0.07463214968953125</v>
+        <v>0.04205452336554494</v>
       </c>
       <c r="F1054">
         <v>-1</v>
@@ -55096,10 +55096,10 @@
         <v>0.01574897057647875</v>
       </c>
       <c r="H1054">
-        <v>0.01628536785031047</v>
+        <v>0.01629794547663445</v>
       </c>
       <c r="I1054">
-        <v>0.2763972738317229</v>
+        <v>0.3089749001557092</v>
       </c>
       <c r="J1054">
         <v>1.12888131619923</v>
@@ -55111,10 +55111,10 @@
         <v>8.050000000000001</v>
       </c>
       <c r="M1054">
-        <v>7.18</v>
+        <v>7.2</v>
       </c>
       <c r="N1054">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="O1054">
         <v>1</v>
@@ -55128,43 +55128,43 @@
         <v>0</v>
       </c>
       <c r="B1055" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1055">
-        <v>0.1371988614513491</v>
+        <v>-0.4293866076767205</v>
       </c>
       <c r="D1055" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E1055">
-        <v>-0.1504856561259995</v>
+        <v>-0.08369035154696292</v>
       </c>
       <c r="F1055">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1055">
-        <v>0.01596280113854865</v>
+        <v>0.01722938660767672</v>
       </c>
       <c r="H1055">
-        <v>0.016510485656126</v>
+        <v>0.01662369035154696</v>
       </c>
       <c r="I1055">
-        <v>0.2876845175773486</v>
+        <v>0.3456962561297576</v>
       </c>
       <c r="J1055">
         <v>1.160234771048189</v>
       </c>
       <c r="K1055">
-        <v>6.82</v>
+        <v>7.61</v>
       </c>
       <c r="L1055">
-        <v>8.050000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M1055">
-        <v>7.18</v>
+        <v>7.2</v>
       </c>
       <c r="N1055">
-        <v>8.18</v>
+        <v>8.27</v>
       </c>
       <c r="O1055">
         <v>1</v>
@@ -55175,34 +55175,34 @@
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1056" t="s">
         <v>256</v>
       </c>
       <c r="C1056">
-        <v>-0.2189357835067671</v>
+        <v>0.1371988614513491</v>
       </c>
       <c r="D1056" t="s">
         <v>493</v>
       </c>
       <c r="E1056">
-        <v>-0.5254191972989144</v>
+        <v>-0.1836903515469626</v>
       </c>
       <c r="F1056">
         <v>-1</v>
       </c>
       <c r="G1056">
-        <v>0.01631893578350677</v>
+        <v>0.01596280113854865</v>
       </c>
       <c r="H1056">
-        <v>0.01688541919729892</v>
+        <v>0.01652369035154696</v>
       </c>
       <c r="I1056">
-        <v>0.3064834137921473</v>
+        <v>0.3208892129983116</v>
       </c>
       <c r="J1056">
-        <v>1.212453927200406</v>
+        <v>1.160234771048189</v>
       </c>
       <c r="K1056">
         <v>6.82</v>
@@ -55211,16 +55211,16 @@
         <v>8.050000000000001</v>
       </c>
       <c r="M1056">
-        <v>7.18</v>
+        <v>7.2</v>
       </c>
       <c r="N1056">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="O1056">
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>489</v>
+        <v>253</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
@@ -55231,28 +55231,28 @@
         <v>256</v>
       </c>
       <c r="C1057">
-        <v>-0.6993263373634928</v>
+        <v>-0.2189357835067671</v>
       </c>
       <c r="D1057" t="s">
         <v>493</v>
       </c>
       <c r="E1057">
-        <v>-1.031167610303502</v>
+        <v>-0.5596682758429221</v>
       </c>
       <c r="F1057">
         <v>-1</v>
       </c>
       <c r="G1057">
-        <v>0.0167993263373635</v>
+        <v>0.01631893578350677</v>
       </c>
       <c r="H1057">
-        <v>0.0173911676103035</v>
+        <v>0.01689966827584292</v>
       </c>
       <c r="I1057">
-        <v>0.3318412729400091</v>
+        <v>0.340732492336155</v>
       </c>
       <c r="J1057">
-        <v>1.282892424833357</v>
+        <v>1.212453927200406</v>
       </c>
       <c r="K1057">
         <v>6.82</v>
@@ -55261,16 +55261,16 @@
         <v>8.050000000000001</v>
       </c>
       <c r="M1057">
-        <v>7.18</v>
+        <v>7.2</v>
       </c>
       <c r="N1057">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="O1057">
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
@@ -55278,48 +55278,98 @@
         <v>0</v>
       </c>
       <c r="B1058" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1058">
-        <v>-1.416234245524462</v>
+        <v>-0.6993263373634928</v>
       </c>
       <c r="D1058" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E1058">
-        <v>-1.141660242826392</v>
+        <v>-1.066825458800169</v>
       </c>
       <c r="F1058">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1058">
-        <v>0.01761623424552446</v>
+        <v>0.0167993263373635</v>
       </c>
       <c r="H1058">
-        <v>0.01768166024282639</v>
+        <v>0.01740682545880017</v>
       </c>
       <c r="I1058">
-        <v>0.2745740026980705</v>
+        <v>0.3674991214366763</v>
       </c>
       <c r="J1058">
-        <v>1.307175033725888</v>
+        <v>1.282892424833357</v>
       </c>
       <c r="K1058">
-        <v>7.28</v>
+        <v>6.82</v>
       </c>
       <c r="L1058">
-        <v>8.1</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M1058">
         <v>7.2</v>
       </c>
       <c r="N1058">
+        <v>8.17</v>
+      </c>
+      <c r="O1058">
+        <v>1</v>
+      </c>
+      <c r="P1058" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:16">
+      <c r="A1059" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1059">
+        <v>-1.416234245524462</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>492</v>
+      </c>
+      <c r="E1059">
+        <v>-1.141660242826392</v>
+      </c>
+      <c r="F1059">
+        <v>1</v>
+      </c>
+      <c r="G1059">
+        <v>0.01761623424552446</v>
+      </c>
+      <c r="H1059">
+        <v>0.01768166024282639</v>
+      </c>
+      <c r="I1059">
+        <v>0.2745740026980705</v>
+      </c>
+      <c r="J1059">
+        <v>1.307175033725888</v>
+      </c>
+      <c r="K1059">
+        <v>7.28</v>
+      </c>
+      <c r="L1059">
+        <v>8.1</v>
+      </c>
+      <c r="M1059">
+        <v>7.2</v>
+      </c>
+      <c r="N1059">
         <v>8.27</v>
       </c>
-      <c r="O1058">
-        <v>1</v>
-      </c>
-      <c r="P1058" t="s">
+      <c r="O1059">
+        <v>1</v>
+      </c>
+      <c r="P1059" t="s">
         <v>255</v>
       </c>
     </row>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3210" uniqueCount="688">
   <si>
     <t>trade_time</t>
   </si>
@@ -781,1291 +781,1303 @@
     <t>2021-06-18</t>
   </si>
   <si>
+    <t>2021-07-20</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
+    <t>2021-07-14</t>
+  </si>
+  <si>
+    <t>2016-07-27</t>
+  </si>
+  <si>
+    <t>2016-08-10</t>
+  </si>
+  <si>
+    <t>2016-08-15</t>
+  </si>
+  <si>
+    <t>2016-08-22</t>
+  </si>
+  <si>
+    <t>2016-08-23</t>
+  </si>
+  <si>
+    <t>2016-08-24</t>
+  </si>
+  <si>
+    <t>2016-08-25</t>
+  </si>
+  <si>
+    <t>2016-08-26</t>
+  </si>
+  <si>
+    <t>2016-09-02</t>
+  </si>
+  <si>
+    <t>2016-09-05</t>
+  </si>
+  <si>
+    <t>2016-09-06</t>
+  </si>
+  <si>
+    <t>2016-09-28</t>
+  </si>
+  <si>
+    <t>2016-09-29</t>
+  </si>
+  <si>
+    <t>2016-10-12</t>
+  </si>
+  <si>
+    <t>2016-10-24</t>
+  </si>
+  <si>
+    <t>2016-10-25</t>
+  </si>
+  <si>
+    <t>2016-11-21</t>
+  </si>
+  <si>
+    <t>2016-12-02</t>
+  </si>
+  <si>
+    <t>2016-12-05</t>
+  </si>
+  <si>
+    <t>2016-12-14</t>
+  </si>
+  <si>
+    <t>2017-01-23</t>
+  </si>
+  <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
+    <t>2017-03-27</t>
+  </si>
+  <si>
+    <t>2017-04-18</t>
+  </si>
+  <si>
+    <t>2017-04-19</t>
+  </si>
+  <si>
+    <t>2017-04-21</t>
+  </si>
+  <si>
+    <t>2017-06-07</t>
+  </si>
+  <si>
+    <t>2017-06-15</t>
+  </si>
+  <si>
+    <t>2017-07-05</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-07-07</t>
+  </si>
+  <si>
+    <t>2017-06-28</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>2017-07-20</t>
+  </si>
+  <si>
+    <t>2017-07-24</t>
+  </si>
+  <si>
+    <t>2017-07-25</t>
+  </si>
+  <si>
+    <t>2017-07-26</t>
+  </si>
+  <si>
+    <t>2017-07-27</t>
+  </si>
+  <si>
+    <t>2017-08-08</t>
+  </si>
+  <si>
+    <t>2017-08-10</t>
+  </si>
+  <si>
+    <t>2017-08-11</t>
+  </si>
+  <si>
+    <t>2017-07-31</t>
+  </si>
+  <si>
+    <t>2017-08-02</t>
+  </si>
+  <si>
+    <t>2017-08-31</t>
+  </si>
+  <si>
+    <t>2017-09-07</t>
+  </si>
+  <si>
+    <t>2017-09-13</t>
+  </si>
+  <si>
+    <t>2017-09-20</t>
+  </si>
+  <si>
+    <t>2017-10-11</t>
+  </si>
+  <si>
+    <t>2017-10-17</t>
+  </si>
+  <si>
+    <t>2017-10-13</t>
+  </si>
+  <si>
+    <t>2017-10-23</t>
+  </si>
+  <si>
+    <t>2017-10-27</t>
+  </si>
+  <si>
+    <t>2017-10-30</t>
+  </si>
+  <si>
+    <t>2017-11-01</t>
+  </si>
+  <si>
+    <t>2017-11-03</t>
+  </si>
+  <si>
+    <t>2017-11-06</t>
+  </si>
+  <si>
+    <t>2017-11-07</t>
+  </si>
+  <si>
+    <t>2017-11-08</t>
+  </si>
+  <si>
+    <t>2017-11-09</t>
+  </si>
+  <si>
+    <t>2017-11-14</t>
+  </si>
+  <si>
+    <t>2017-11-15</t>
+  </si>
+  <si>
+    <t>2017-11-16</t>
+  </si>
+  <si>
+    <t>2017-11-22</t>
+  </si>
+  <si>
+    <t>2017-11-23</t>
+  </si>
+  <si>
+    <t>2018-01-19</t>
+  </si>
+  <si>
+    <t>2018-01-09</t>
+  </si>
+  <si>
+    <t>2018-01-16</t>
+  </si>
+  <si>
+    <t>2018-01-24</t>
+  </si>
+  <si>
+    <t>2018-02-01</t>
+  </si>
+  <si>
+    <t>2018-01-15</t>
+  </si>
+  <si>
+    <t>2018-02-05</t>
+  </si>
+  <si>
+    <t>2018-02-07</t>
+  </si>
+  <si>
+    <t>2018-02-09</t>
+  </si>
+  <si>
+    <t>2018-02-22</t>
+  </si>
+  <si>
+    <t>2018-02-26</t>
+  </si>
+  <si>
+    <t>2018-02-28</t>
+  </si>
+  <si>
+    <t>2018-03-01</t>
+  </si>
+  <si>
+    <t>2018-03-08</t>
+  </si>
+  <si>
+    <t>2018-03-05</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>2018-03-12</t>
+  </si>
+  <si>
+    <t>2018-03-13</t>
+  </si>
+  <si>
+    <t>2018-03-14</t>
+  </si>
+  <si>
+    <t>2018-04-03</t>
+  </si>
+  <si>
+    <t>2018-04-11</t>
+  </si>
+  <si>
+    <t>2018-04-12</t>
+  </si>
+  <si>
+    <t>2018-04-17</t>
+  </si>
+  <si>
+    <t>2018-04-18</t>
+  </si>
+  <si>
+    <t>2018-04-20</t>
+  </si>
+  <si>
+    <t>2018-04-24</t>
+  </si>
+  <si>
+    <t>2018-09-05</t>
+  </si>
+  <si>
+    <t>2018-09-19</t>
+  </si>
+  <si>
+    <t>2018-09-21</t>
+  </si>
+  <si>
+    <t>2018-10-22</t>
+  </si>
+  <si>
+    <t>2018-09-28</t>
+  </si>
+  <si>
+    <t>2018-10-23</t>
+  </si>
+  <si>
+    <t>2018-10-24</t>
+  </si>
+  <si>
+    <t>2018-12-04</t>
+  </si>
+  <si>
+    <t>2018-12-13</t>
+  </si>
+  <si>
+    <t>2018-12-05</t>
+  </si>
+  <si>
+    <t>2018-12-14</t>
+  </si>
+  <si>
+    <t>2018-12-19</t>
+  </si>
+  <si>
+    <t>2018-12-21</t>
+  </si>
+  <si>
+    <t>2018-12-18</t>
+  </si>
+  <si>
+    <t>2018-12-27</t>
+  </si>
+  <si>
+    <t>2019-01-28</t>
+  </si>
+  <si>
+    <t>2019-03-15</t>
+  </si>
+  <si>
+    <t>2019-03-29</t>
+  </si>
+  <si>
+    <t>2019-04-01</t>
+  </si>
+  <si>
+    <t>2019-04-03</t>
+  </si>
+  <si>
+    <t>2019-04-25</t>
+  </si>
+  <si>
+    <t>2019-04-29</t>
+  </si>
+  <si>
+    <t>2019-05-14</t>
+  </si>
+  <si>
+    <t>2019-05-21</t>
+  </si>
+  <si>
+    <t>2019-05-24</t>
+  </si>
+  <si>
+    <t>2019-05-27</t>
+  </si>
+  <si>
+    <t>2019-05-28</t>
+  </si>
+  <si>
+    <t>2019-05-29</t>
+  </si>
+  <si>
+    <t>2019-07-10</t>
+  </si>
+  <si>
+    <t>2019-07-24</t>
+  </si>
+  <si>
+    <t>2019-07-25</t>
+  </si>
+  <si>
+    <t>2019-07-12</t>
+  </si>
+  <si>
+    <t>2019-08-02</t>
+  </si>
+  <si>
+    <t>2019-08-05</t>
+  </si>
+  <si>
+    <t>2019-08-08</t>
+  </si>
+  <si>
+    <t>2019-08-09</t>
+  </si>
+  <si>
+    <t>2019-08-12</t>
+  </si>
+  <si>
+    <t>2019-08-16</t>
+  </si>
+  <si>
+    <t>2019-08-19</t>
+  </si>
+  <si>
+    <t>2019-09-03</t>
+  </si>
+  <si>
+    <t>2019-09-27</t>
+  </si>
+  <si>
+    <t>2019-09-30</t>
+  </si>
+  <si>
+    <t>2019-09-25</t>
+  </si>
+  <si>
+    <t>2019-10-17</t>
+  </si>
+  <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
+    <t>2019-11-04</t>
+  </si>
+  <si>
+    <t>2019-11-05</t>
+  </si>
+  <si>
+    <t>2019-11-07</t>
+  </si>
+  <si>
+    <t>2019-11-15</t>
+  </si>
+  <si>
+    <t>2019-11-26</t>
+  </si>
+  <si>
+    <t>2019-12-05</t>
+  </si>
+  <si>
+    <t>2019-12-11</t>
+  </si>
+  <si>
+    <t>2020-01-02</t>
+  </si>
+  <si>
+    <t>2020-01-03</t>
+  </si>
+  <si>
+    <t>2020-01-06</t>
+  </si>
+  <si>
+    <t>2020-01-07</t>
+  </si>
+  <si>
+    <t>2019-12-18</t>
+  </si>
+  <si>
+    <t>2019-12-27</t>
+  </si>
+  <si>
+    <t>2020-01-16</t>
+  </si>
+  <si>
+    <t>2020-01-17</t>
+  </si>
+  <si>
+    <t>2020-02-04</t>
+  </si>
+  <si>
+    <t>2020-02-05</t>
+  </si>
+  <si>
+    <t>2020-01-23</t>
+  </si>
+  <si>
+    <t>2020-02-06</t>
+  </si>
+  <si>
+    <t>2020-02-10</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-03-19</t>
+  </si>
+  <si>
+    <t>2020-03-26</t>
+  </si>
+  <si>
+    <t>2020-03-25</t>
+  </si>
+  <si>
+    <t>2020-04-02</t>
+  </si>
+  <si>
+    <t>2020-04-16</t>
+  </si>
+  <si>
+    <t>2020-04-17</t>
+  </si>
+  <si>
+    <t>2020-04-21</t>
+  </si>
+  <si>
+    <t>2020-05-06</t>
+  </si>
+  <si>
+    <t>2020-04-14</t>
+  </si>
+  <si>
+    <t>2020-05-11</t>
+  </si>
+  <si>
+    <t>2020-05-12</t>
+  </si>
+  <si>
+    <t>2020-05-13</t>
+  </si>
+  <si>
+    <t>2020-05-14</t>
+  </si>
+  <si>
+    <t>2020-06-12</t>
+  </si>
+  <si>
+    <t>2020-06-15</t>
+  </si>
+  <si>
+    <t>2020-06-08</t>
+  </si>
+  <si>
+    <t>2020-07-03</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-24</t>
+  </si>
+  <si>
+    <t>2020-07-30</t>
+  </si>
+  <si>
+    <t>2020-08-10</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>2020-08-18</t>
+  </si>
+  <si>
+    <t>2020-08-19</t>
+  </si>
+  <si>
+    <t>2020-08-26</t>
+  </si>
+  <si>
+    <t>2020-09-01</t>
+  </si>
+  <si>
+    <t>2020-09-02</t>
+  </si>
+  <si>
+    <t>2020-09-03</t>
+  </si>
+  <si>
+    <t>2020-09-04</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>2020-09-08</t>
+  </si>
+  <si>
+    <t>2020-09-09</t>
+  </si>
+  <si>
+    <t>2020-09-14</t>
+  </si>
+  <si>
+    <t>2020-09-15</t>
+  </si>
+  <si>
+    <t>2020-09-17</t>
+  </si>
+  <si>
+    <t>2020-09-21</t>
+  </si>
+  <si>
+    <t>2020-09-22</t>
+  </si>
+  <si>
+    <t>2020-11-24</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>2021-01-22</t>
+  </si>
+  <si>
+    <t>2021-02-25</t>
+  </si>
+  <si>
+    <t>2021-03-01</t>
+  </si>
+  <si>
+    <t>2021-03-02</t>
+  </si>
+  <si>
+    <t>2021-03-17</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>2021-04-14</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>2021-04-15</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>2021-04-26</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>2021-05-21</t>
+  </si>
+  <si>
+    <t>2021-05-24</t>
+  </si>
+  <si>
+    <t>2021-05-25</t>
+  </si>
+  <si>
+    <t>2021-05-26</t>
+  </si>
+  <si>
+    <t>2021-05-31</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>2021-06-15</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>2021-06-17</t>
+  </si>
+  <si>
+    <t>2021-06-22</t>
+  </si>
+  <si>
+    <t>2021-06-25</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>2021-07-08</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
     <t>2021-07-12</t>
   </si>
   <si>
-    <t>2021-07-20</t>
-  </si>
-  <si>
-    <t>2021-07-14</t>
-  </si>
-  <si>
-    <t>2016-07-27</t>
-  </si>
-  <si>
-    <t>2016-08-10</t>
-  </si>
-  <si>
-    <t>2016-08-15</t>
-  </si>
-  <si>
-    <t>2016-08-22</t>
-  </si>
-  <si>
-    <t>2016-08-23</t>
-  </si>
-  <si>
-    <t>2016-08-24</t>
-  </si>
-  <si>
-    <t>2016-08-25</t>
-  </si>
-  <si>
-    <t>2016-08-26</t>
-  </si>
-  <si>
-    <t>2016-09-02</t>
-  </si>
-  <si>
-    <t>2016-09-05</t>
-  </si>
-  <si>
-    <t>2016-09-06</t>
-  </si>
-  <si>
-    <t>2016-09-28</t>
-  </si>
-  <si>
-    <t>2016-09-29</t>
-  </si>
-  <si>
-    <t>2016-10-12</t>
-  </si>
-  <si>
-    <t>2016-10-24</t>
-  </si>
-  <si>
-    <t>2016-10-25</t>
-  </si>
-  <si>
-    <t>2016-11-21</t>
-  </si>
-  <si>
-    <t>2016-12-02</t>
-  </si>
-  <si>
-    <t>2016-12-05</t>
-  </si>
-  <si>
-    <t>2016-12-14</t>
-  </si>
-  <si>
-    <t>2017-01-23</t>
-  </si>
-  <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
-    <t>2017-03-27</t>
-  </si>
-  <si>
-    <t>2017-04-18</t>
-  </si>
-  <si>
-    <t>2017-04-19</t>
-  </si>
-  <si>
-    <t>2017-04-21</t>
-  </si>
-  <si>
-    <t>2017-06-07</t>
-  </si>
-  <si>
-    <t>2017-06-15</t>
-  </si>
-  <si>
-    <t>2017-07-05</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-07-07</t>
-  </si>
-  <si>
-    <t>2017-06-28</t>
-  </si>
-  <si>
-    <t>2017-07-12</t>
-  </si>
-  <si>
-    <t>2017-07-20</t>
-  </si>
-  <si>
-    <t>2017-07-24</t>
-  </si>
-  <si>
-    <t>2017-07-25</t>
-  </si>
-  <si>
-    <t>2017-07-26</t>
-  </si>
-  <si>
-    <t>2017-07-27</t>
-  </si>
-  <si>
-    <t>2017-08-08</t>
-  </si>
-  <si>
-    <t>2017-08-10</t>
-  </si>
-  <si>
-    <t>2017-08-11</t>
-  </si>
-  <si>
-    <t>2017-07-31</t>
-  </si>
-  <si>
-    <t>2017-08-02</t>
-  </si>
-  <si>
-    <t>2017-08-31</t>
-  </si>
-  <si>
-    <t>2017-09-07</t>
-  </si>
-  <si>
-    <t>2017-09-13</t>
-  </si>
-  <si>
-    <t>2017-09-20</t>
-  </si>
-  <si>
-    <t>2017-10-11</t>
-  </si>
-  <si>
-    <t>2017-10-17</t>
-  </si>
-  <si>
-    <t>2017-10-13</t>
-  </si>
-  <si>
-    <t>2017-10-23</t>
-  </si>
-  <si>
-    <t>2017-10-27</t>
-  </si>
-  <si>
-    <t>2017-10-30</t>
-  </si>
-  <si>
-    <t>2017-11-01</t>
-  </si>
-  <si>
-    <t>2017-11-03</t>
-  </si>
-  <si>
-    <t>2017-11-06</t>
-  </si>
-  <si>
-    <t>2017-11-07</t>
-  </si>
-  <si>
-    <t>2017-11-08</t>
-  </si>
-  <si>
-    <t>2017-11-09</t>
-  </si>
-  <si>
-    <t>2017-11-14</t>
-  </si>
-  <si>
-    <t>2017-11-15</t>
-  </si>
-  <si>
-    <t>2017-11-16</t>
-  </si>
-  <si>
-    <t>2017-11-22</t>
-  </si>
-  <si>
-    <t>2017-11-23</t>
-  </si>
-  <si>
-    <t>2018-01-19</t>
-  </si>
-  <si>
-    <t>2018-01-09</t>
-  </si>
-  <si>
-    <t>2018-01-16</t>
-  </si>
-  <si>
-    <t>2018-01-24</t>
-  </si>
-  <si>
-    <t>2018-02-01</t>
-  </si>
-  <si>
-    <t>2018-01-15</t>
-  </si>
-  <si>
-    <t>2018-02-05</t>
-  </si>
-  <si>
-    <t>2018-02-07</t>
-  </si>
-  <si>
-    <t>2018-02-09</t>
-  </si>
-  <si>
-    <t>2018-02-22</t>
-  </si>
-  <si>
-    <t>2018-02-26</t>
-  </si>
-  <si>
-    <t>2018-02-28</t>
-  </si>
-  <si>
-    <t>2018-03-01</t>
-  </si>
-  <si>
-    <t>2018-03-08</t>
-  </si>
-  <si>
-    <t>2018-03-05</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>2018-03-12</t>
-  </si>
-  <si>
-    <t>2018-03-13</t>
-  </si>
-  <si>
-    <t>2018-03-14</t>
-  </si>
-  <si>
-    <t>2018-04-03</t>
-  </si>
-  <si>
-    <t>2018-04-11</t>
-  </si>
-  <si>
-    <t>2018-04-12</t>
-  </si>
-  <si>
-    <t>2018-04-17</t>
-  </si>
-  <si>
-    <t>2018-04-18</t>
-  </si>
-  <si>
-    <t>2018-04-20</t>
-  </si>
-  <si>
-    <t>2018-04-24</t>
-  </si>
-  <si>
-    <t>2018-09-05</t>
-  </si>
-  <si>
-    <t>2018-09-19</t>
-  </si>
-  <si>
-    <t>2018-09-21</t>
-  </si>
-  <si>
-    <t>2018-10-22</t>
-  </si>
-  <si>
-    <t>2018-09-28</t>
-  </si>
-  <si>
-    <t>2018-10-23</t>
-  </si>
-  <si>
-    <t>2018-10-24</t>
-  </si>
-  <si>
-    <t>2018-12-04</t>
-  </si>
-  <si>
-    <t>2018-12-13</t>
-  </si>
-  <si>
-    <t>2018-12-05</t>
-  </si>
-  <si>
-    <t>2018-12-14</t>
-  </si>
-  <si>
-    <t>2018-12-19</t>
-  </si>
-  <si>
-    <t>2018-12-21</t>
-  </si>
-  <si>
-    <t>2018-12-18</t>
-  </si>
-  <si>
-    <t>2018-12-27</t>
-  </si>
-  <si>
-    <t>2019-01-28</t>
-  </si>
-  <si>
-    <t>2019-03-15</t>
-  </si>
-  <si>
-    <t>2019-03-29</t>
-  </si>
-  <si>
-    <t>2019-04-01</t>
-  </si>
-  <si>
-    <t>2019-04-03</t>
-  </si>
-  <si>
-    <t>2019-04-25</t>
-  </si>
-  <si>
-    <t>2019-04-29</t>
-  </si>
-  <si>
-    <t>2019-05-14</t>
-  </si>
-  <si>
-    <t>2019-05-21</t>
-  </si>
-  <si>
-    <t>2019-05-24</t>
-  </si>
-  <si>
-    <t>2019-05-27</t>
-  </si>
-  <si>
-    <t>2019-05-28</t>
-  </si>
-  <si>
-    <t>2019-05-29</t>
-  </si>
-  <si>
-    <t>2019-07-10</t>
-  </si>
-  <si>
-    <t>2019-07-24</t>
-  </si>
-  <si>
-    <t>2019-07-25</t>
-  </si>
-  <si>
-    <t>2019-07-12</t>
-  </si>
-  <si>
-    <t>2019-08-02</t>
-  </si>
-  <si>
-    <t>2019-08-05</t>
-  </si>
-  <si>
-    <t>2019-08-08</t>
-  </si>
-  <si>
-    <t>2019-08-09</t>
-  </si>
-  <si>
-    <t>2019-08-12</t>
-  </si>
-  <si>
-    <t>2019-08-16</t>
-  </si>
-  <si>
-    <t>2019-08-19</t>
-  </si>
-  <si>
-    <t>2019-09-03</t>
-  </si>
-  <si>
-    <t>2019-09-27</t>
-  </si>
-  <si>
-    <t>2019-09-30</t>
-  </si>
-  <si>
-    <t>2019-09-25</t>
-  </si>
-  <si>
-    <t>2019-10-17</t>
-  </si>
-  <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
-    <t>2019-11-04</t>
-  </si>
-  <si>
-    <t>2019-11-05</t>
-  </si>
-  <si>
-    <t>2019-11-07</t>
-  </si>
-  <si>
-    <t>2019-11-15</t>
-  </si>
-  <si>
-    <t>2019-11-26</t>
-  </si>
-  <si>
-    <t>2019-12-05</t>
-  </si>
-  <si>
-    <t>2019-12-11</t>
-  </si>
-  <si>
-    <t>2020-01-02</t>
-  </si>
-  <si>
-    <t>2020-01-03</t>
-  </si>
-  <si>
-    <t>2020-01-06</t>
-  </si>
-  <si>
-    <t>2020-01-07</t>
-  </si>
-  <si>
-    <t>2019-12-18</t>
-  </si>
-  <si>
-    <t>2019-12-27</t>
-  </si>
-  <si>
-    <t>2020-01-16</t>
-  </si>
-  <si>
-    <t>2020-01-17</t>
-  </si>
-  <si>
-    <t>2020-02-04</t>
-  </si>
-  <si>
-    <t>2020-02-05</t>
-  </si>
-  <si>
-    <t>2020-01-23</t>
-  </si>
-  <si>
-    <t>2020-02-06</t>
-  </si>
-  <si>
-    <t>2020-02-10</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-03-19</t>
-  </si>
-  <si>
-    <t>2020-03-26</t>
-  </si>
-  <si>
-    <t>2020-03-25</t>
-  </si>
-  <si>
-    <t>2020-04-02</t>
-  </si>
-  <si>
-    <t>2020-04-16</t>
-  </si>
-  <si>
-    <t>2020-04-17</t>
-  </si>
-  <si>
-    <t>2020-04-21</t>
-  </si>
-  <si>
-    <t>2020-05-06</t>
-  </si>
-  <si>
-    <t>2020-04-14</t>
-  </si>
-  <si>
-    <t>2020-05-11</t>
-  </si>
-  <si>
-    <t>2020-05-12</t>
-  </si>
-  <si>
-    <t>2020-05-13</t>
-  </si>
-  <si>
-    <t>2020-05-14</t>
-  </si>
-  <si>
-    <t>2020-06-12</t>
-  </si>
-  <si>
-    <t>2020-06-15</t>
-  </si>
-  <si>
-    <t>2020-06-08</t>
-  </si>
-  <si>
-    <t>2020-07-03</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-24</t>
-  </si>
-  <si>
-    <t>2020-07-30</t>
-  </si>
-  <si>
-    <t>2020-08-10</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>2020-08-18</t>
-  </si>
-  <si>
-    <t>2020-08-19</t>
-  </si>
-  <si>
-    <t>2020-08-26</t>
-  </si>
-  <si>
-    <t>2020-09-01</t>
-  </si>
-  <si>
-    <t>2020-09-02</t>
-  </si>
-  <si>
-    <t>2020-09-03</t>
-  </si>
-  <si>
-    <t>2020-09-04</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>2020-09-08</t>
-  </si>
-  <si>
-    <t>2020-09-09</t>
-  </si>
-  <si>
-    <t>2020-09-14</t>
-  </si>
-  <si>
-    <t>2020-09-15</t>
-  </si>
-  <si>
-    <t>2020-09-17</t>
-  </si>
-  <si>
-    <t>2020-09-21</t>
-  </si>
-  <si>
-    <t>2020-09-22</t>
-  </si>
-  <si>
-    <t>2020-11-24</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-14</t>
-  </si>
-  <si>
-    <t>2021-01-22</t>
-  </si>
-  <si>
-    <t>2021-02-25</t>
-  </si>
-  <si>
-    <t>2021-03-01</t>
-  </si>
-  <si>
-    <t>2021-03-02</t>
-  </si>
-  <si>
-    <t>2021-03-17</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>2021-04-14</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>2021-04-15</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>2021-04-26</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>2021-05-21</t>
-  </si>
-  <si>
-    <t>2021-05-24</t>
-  </si>
-  <si>
-    <t>2021-05-25</t>
-  </si>
-  <si>
-    <t>2021-05-26</t>
-  </si>
-  <si>
-    <t>2021-05-31</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>2021-06-15</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>2021-06-17</t>
-  </si>
-  <si>
-    <t>2021-06-22</t>
-  </si>
-  <si>
-    <t>2021-06-25</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>2021-07-08</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
     <t>2021-07-13</t>
   </si>
   <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
     <t>2021-07-15</t>
   </si>
   <si>
+    <t>2021-07-28</t>
+  </si>
+  <si>
+    <t>2016-07-13</t>
+  </si>
+  <si>
+    <t>2016-07-14</t>
+  </si>
+  <si>
+    <t>2016-07-19</t>
+  </si>
+  <si>
+    <t>2016-07-21</t>
+  </si>
+  <si>
+    <t>2016-07-22</t>
+  </si>
+  <si>
+    <t>2016-07-28</t>
+  </si>
+  <si>
+    <t>2016-08-03</t>
+  </si>
+  <si>
+    <t>2016-08-04</t>
+  </si>
+  <si>
+    <t>2016-08-05</t>
+  </si>
+  <si>
+    <t>2016-08-08</t>
+  </si>
+  <si>
+    <t>2016-08-09</t>
+  </si>
+  <si>
+    <t>2016-08-29</t>
+  </si>
+  <si>
+    <t>2016-08-30</t>
+  </si>
+  <si>
+    <t>2016-08-31</t>
+  </si>
+  <si>
+    <t>2016-09-14</t>
+  </si>
+  <si>
+    <t>2016-09-19</t>
+  </si>
+  <si>
+    <t>2016-11-07</t>
+  </si>
+  <si>
+    <t>2016-11-08</t>
+  </si>
+  <si>
+    <t>2017-01-06</t>
+  </si>
+  <si>
+    <t>2017-01-09</t>
+  </si>
+  <si>
+    <t>2017-03-16</t>
+  </si>
+  <si>
+    <t>2017-03-20</t>
+  </si>
+  <si>
+    <t>2017-05-24</t>
+  </si>
+  <si>
+    <t>2017-05-26</t>
+  </si>
+  <si>
+    <t>2017-06-05</t>
+  </si>
+  <si>
+    <t>2017-06-08</t>
+  </si>
+  <si>
+    <t>2017-06-09</t>
+  </si>
+  <si>
+    <t>2017-06-12</t>
+  </si>
+  <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
+    <t>2017-06-22</t>
+  </si>
+  <si>
+    <t>2017-06-27</t>
+  </si>
+  <si>
+    <t>2017-08-16</t>
+  </si>
+  <si>
+    <t>2017-09-14</t>
+  </si>
+  <si>
+    <t>2017-09-19</t>
+  </si>
+  <si>
+    <t>2017-09-21</t>
+  </si>
+  <si>
+    <t>2017-09-25</t>
+  </si>
+  <si>
+    <t>2017-09-27</t>
+  </si>
+  <si>
+    <t>2017-09-29</t>
+  </si>
+  <si>
+    <t>2017-10-24</t>
+  </si>
+  <si>
+    <t>2017-10-25</t>
+  </si>
+  <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
+    <t>2018-01-04</t>
+  </si>
+  <si>
+    <t>2018-01-05</t>
+  </si>
+  <si>
+    <t>2018-01-10</t>
+  </si>
+  <si>
+    <t>2018-01-17</t>
+  </si>
+  <si>
+    <t>2018-01-23</t>
+  </si>
+  <si>
+    <t>2018-01-26</t>
+  </si>
+  <si>
+    <t>2018-01-29</t>
+  </si>
+  <si>
+    <t>2018-02-12</t>
+  </si>
+  <si>
+    <t>2018-02-13</t>
+  </si>
+  <si>
+    <t>2018-03-16</t>
+  </si>
+  <si>
+    <t>2018-03-20</t>
+  </si>
+  <si>
+    <t>2018-03-21</t>
+  </si>
+  <si>
+    <t>2018-08-23</t>
+  </si>
+  <si>
+    <t>2018-08-24</t>
+  </si>
+  <si>
+    <t>2018-08-28</t>
+  </si>
+  <si>
+    <t>2018-09-13</t>
+  </si>
+  <si>
+    <t>2018-11-16</t>
+  </si>
+  <si>
+    <t>2018-11-19</t>
+  </si>
+  <si>
+    <t>2018-11-22</t>
+  </si>
+  <si>
+    <t>2018-11-26</t>
+  </si>
+  <si>
+    <t>2018-12-03</t>
+  </si>
+  <si>
+    <t>2018-12-28</t>
+  </si>
+  <si>
+    <t>2019-03-01</t>
+  </si>
+  <si>
+    <t>2019-03-11</t>
+  </si>
+  <si>
+    <t>2019-03-12</t>
+  </si>
+  <si>
+    <t>2019-03-13</t>
+  </si>
+  <si>
+    <t>2019-03-21</t>
+  </si>
+  <si>
+    <t>2019-03-22</t>
+  </si>
+  <si>
+    <t>2019-03-25</t>
+  </si>
+  <si>
+    <t>2019-04-11</t>
+  </si>
+  <si>
+    <t>2019-04-12</t>
+  </si>
+  <si>
+    <t>2019-04-15</t>
+  </si>
+  <si>
+    <t>2019-04-16</t>
+  </si>
+  <si>
+    <t>2019-04-17</t>
+  </si>
+  <si>
+    <t>2019-04-18</t>
+  </si>
+  <si>
+    <t>2019-04-23</t>
+  </si>
+  <si>
+    <t>2019-06-26</t>
+  </si>
+  <si>
+    <t>2019-06-28</t>
+  </si>
+  <si>
+    <t>2019-07-02</t>
+  </si>
+  <si>
+    <t>2019-07-03</t>
+  </si>
+  <si>
+    <t>2019-07-04</t>
+  </si>
+  <si>
+    <t>2019-07-08</t>
+  </si>
+  <si>
+    <t>2019-07-15</t>
+  </si>
+  <si>
+    <t>2019-07-17</t>
+  </si>
+  <si>
+    <t>2019-07-19</t>
+  </si>
+  <si>
+    <t>2019-07-22</t>
+  </si>
+  <si>
+    <t>2019-08-29</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-09-04</t>
+  </si>
+  <si>
+    <t>2019-09-05</t>
+  </si>
+  <si>
+    <t>2019-09-06</t>
+  </si>
+  <si>
+    <t>2019-09-09</t>
+  </si>
+  <si>
+    <t>2019-09-16</t>
+  </si>
+  <si>
+    <t>2019-10-08</t>
+  </si>
+  <si>
+    <t>2019-10-10</t>
+  </si>
+  <si>
+    <t>2019-10-11</t>
+  </si>
+  <si>
+    <t>2019-10-14</t>
+  </si>
+  <si>
+    <t>2019-10-15</t>
+  </si>
+  <si>
+    <t>2019-10-18</t>
+  </si>
+  <si>
+    <t>2019-10-21</t>
+  </si>
+  <si>
+    <t>2019-10-22</t>
+  </si>
+  <si>
+    <t>2019-10-23</t>
+  </si>
+  <si>
+    <t>2019-10-28</t>
+  </si>
+  <si>
+    <t>2019-11-13</t>
+  </si>
+  <si>
+    <t>2019-11-25</t>
+  </si>
+  <si>
+    <t>2019-11-27</t>
+  </si>
+  <si>
+    <t>2019-11-28</t>
+  </si>
+  <si>
+    <t>2019-11-29</t>
+  </si>
+  <si>
+    <t>2019-12-02</t>
+  </si>
+  <si>
+    <t>2019-12-04</t>
+  </si>
+  <si>
+    <t>2019-12-10</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2019-12-13</t>
+  </si>
+  <si>
+    <t>2019-12-17</t>
+  </si>
+  <si>
+    <t>2019-12-19</t>
+  </si>
+  <si>
+    <t>2019-12-24</t>
+  </si>
+  <si>
+    <t>2020-01-09</t>
+  </si>
+  <si>
+    <t>2020-01-13</t>
+  </si>
+  <si>
+    <t>2020-01-21</t>
+  </si>
+  <si>
+    <t>2020-02-28</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-03-04</t>
+  </si>
+  <si>
+    <t>2020-03-05</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-09</t>
+  </si>
+  <si>
+    <t>2020-03-10</t>
+  </si>
+  <si>
+    <t>2020-03-11</t>
+  </si>
+  <si>
+    <t>2020-03-12</t>
+  </si>
+  <si>
+    <t>2020-03-16</t>
+  </si>
+  <si>
+    <t>2020-03-17</t>
+  </si>
+  <si>
+    <t>2020-03-18</t>
+  </si>
+  <si>
+    <t>2020-03-20</t>
+  </si>
+  <si>
+    <t>2020-03-30</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-04-03</t>
+  </si>
+  <si>
+    <t>2020-04-07</t>
+  </si>
+  <si>
+    <t>2020-04-08</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>2020-04-22</t>
+  </si>
+  <si>
+    <t>2020-04-24</t>
+  </si>
+  <si>
+    <t>2020-04-28</t>
+  </si>
+  <si>
+    <t>2020-05-15</t>
+  </si>
+  <si>
+    <t>2020-05-18</t>
+  </si>
+  <si>
+    <t>2020-05-19</t>
+  </si>
+  <si>
+    <t>2020-05-20</t>
+  </si>
+  <si>
+    <t>2020-05-21</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>2020-05-27</t>
+  </si>
+  <si>
+    <t>2020-06-01</t>
+  </si>
+  <si>
+    <t>2020-06-04</t>
+  </si>
+  <si>
+    <t>2020-06-09</t>
+  </si>
+  <si>
+    <t>2020-06-10</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>2020-06-19</t>
+  </si>
+  <si>
+    <t>2020-07-13</t>
+  </si>
+  <si>
+    <t>2020-07-16</t>
+  </si>
+  <si>
+    <t>2020-07-17</t>
+  </si>
+  <si>
+    <t>2020-07-28</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>2020-08-04</t>
+  </si>
+  <si>
+    <t>2020-08-05</t>
+  </si>
+  <si>
+    <t>2020-08-07</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>2020-08-12</t>
+  </si>
+  <si>
+    <t>2020-08-21</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>2020-11-10</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2021-01-21</t>
+  </si>
+  <si>
+    <t>2021-01-25</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>2021-03-05</t>
+  </si>
+  <si>
+    <t>2021-03-15</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>2021-04-20</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2021-04-22</t>
+  </si>
+  <si>
+    <t>2021-04-29</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>2021-05-17</t>
+  </si>
+  <si>
+    <t>2021-05-20</t>
+  </si>
+  <si>
+    <t>2021-05-28</t>
+  </si>
+  <si>
+    <t>2021-06-07</t>
+  </si>
+  <si>
     <t>2021-07-23</t>
   </si>
   <si>
-    <t>2016-07-13</t>
-  </si>
-  <si>
-    <t>2016-07-14</t>
-  </si>
-  <si>
-    <t>2016-07-19</t>
-  </si>
-  <si>
-    <t>2016-07-21</t>
-  </si>
-  <si>
-    <t>2016-07-22</t>
-  </si>
-  <si>
-    <t>2016-07-28</t>
-  </si>
-  <si>
-    <t>2016-08-03</t>
-  </si>
-  <si>
-    <t>2016-08-04</t>
-  </si>
-  <si>
-    <t>2016-08-05</t>
-  </si>
-  <si>
-    <t>2016-08-08</t>
-  </si>
-  <si>
-    <t>2016-08-09</t>
-  </si>
-  <si>
-    <t>2016-08-29</t>
-  </si>
-  <si>
-    <t>2016-08-30</t>
-  </si>
-  <si>
-    <t>2016-08-31</t>
-  </si>
-  <si>
-    <t>2016-09-14</t>
-  </si>
-  <si>
-    <t>2016-09-19</t>
-  </si>
-  <si>
-    <t>2016-11-07</t>
-  </si>
-  <si>
-    <t>2016-11-08</t>
-  </si>
-  <si>
-    <t>2017-01-06</t>
-  </si>
-  <si>
-    <t>2017-01-09</t>
-  </si>
-  <si>
-    <t>2017-03-16</t>
-  </si>
-  <si>
-    <t>2017-03-20</t>
-  </si>
-  <si>
-    <t>2017-05-24</t>
-  </si>
-  <si>
-    <t>2017-05-26</t>
-  </si>
-  <si>
-    <t>2017-06-05</t>
-  </si>
-  <si>
-    <t>2017-06-08</t>
-  </si>
-  <si>
-    <t>2017-06-09</t>
-  </si>
-  <si>
-    <t>2017-06-12</t>
-  </si>
-  <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
-    <t>2017-06-22</t>
-  </si>
-  <si>
-    <t>2017-06-27</t>
-  </si>
-  <si>
-    <t>2017-08-16</t>
-  </si>
-  <si>
-    <t>2017-09-14</t>
-  </si>
-  <si>
-    <t>2017-09-19</t>
-  </si>
-  <si>
-    <t>2017-09-21</t>
-  </si>
-  <si>
-    <t>2017-09-25</t>
-  </si>
-  <si>
-    <t>2017-09-27</t>
-  </si>
-  <si>
-    <t>2017-09-29</t>
-  </si>
-  <si>
-    <t>2017-10-24</t>
-  </si>
-  <si>
-    <t>2017-10-25</t>
-  </si>
-  <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
-    <t>2018-01-04</t>
-  </si>
-  <si>
-    <t>2018-01-05</t>
-  </si>
-  <si>
-    <t>2018-01-10</t>
-  </si>
-  <si>
-    <t>2018-01-17</t>
-  </si>
-  <si>
-    <t>2018-01-23</t>
-  </si>
-  <si>
-    <t>2018-01-26</t>
-  </si>
-  <si>
-    <t>2018-01-29</t>
-  </si>
-  <si>
-    <t>2018-02-12</t>
-  </si>
-  <si>
-    <t>2018-02-13</t>
-  </si>
-  <si>
-    <t>2018-03-16</t>
-  </si>
-  <si>
-    <t>2018-03-20</t>
-  </si>
-  <si>
-    <t>2018-03-21</t>
-  </si>
-  <si>
-    <t>2018-08-23</t>
-  </si>
-  <si>
-    <t>2018-08-24</t>
-  </si>
-  <si>
-    <t>2018-08-28</t>
-  </si>
-  <si>
-    <t>2018-09-13</t>
-  </si>
-  <si>
-    <t>2018-11-16</t>
-  </si>
-  <si>
-    <t>2018-11-19</t>
-  </si>
-  <si>
-    <t>2018-11-22</t>
-  </si>
-  <si>
-    <t>2018-11-26</t>
-  </si>
-  <si>
-    <t>2018-12-03</t>
-  </si>
-  <si>
-    <t>2018-12-28</t>
-  </si>
-  <si>
-    <t>2019-03-01</t>
-  </si>
-  <si>
-    <t>2019-03-11</t>
-  </si>
-  <si>
-    <t>2019-03-12</t>
-  </si>
-  <si>
-    <t>2019-03-13</t>
-  </si>
-  <si>
-    <t>2019-03-21</t>
-  </si>
-  <si>
-    <t>2019-03-22</t>
-  </si>
-  <si>
-    <t>2019-03-25</t>
-  </si>
-  <si>
-    <t>2019-04-11</t>
-  </si>
-  <si>
-    <t>2019-04-12</t>
-  </si>
-  <si>
-    <t>2019-04-15</t>
-  </si>
-  <si>
-    <t>2019-04-16</t>
-  </si>
-  <si>
-    <t>2019-04-17</t>
-  </si>
-  <si>
-    <t>2019-04-18</t>
-  </si>
-  <si>
-    <t>2019-04-23</t>
-  </si>
-  <si>
-    <t>2019-06-26</t>
-  </si>
-  <si>
-    <t>2019-06-28</t>
-  </si>
-  <si>
-    <t>2019-07-02</t>
-  </si>
-  <si>
-    <t>2019-07-03</t>
-  </si>
-  <si>
-    <t>2019-07-04</t>
-  </si>
-  <si>
-    <t>2019-07-08</t>
-  </si>
-  <si>
-    <t>2019-07-15</t>
-  </si>
-  <si>
-    <t>2019-07-17</t>
-  </si>
-  <si>
-    <t>2019-07-19</t>
-  </si>
-  <si>
-    <t>2019-07-22</t>
-  </si>
-  <si>
-    <t>2019-08-29</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-09-04</t>
-  </si>
-  <si>
-    <t>2019-09-05</t>
-  </si>
-  <si>
-    <t>2019-09-06</t>
-  </si>
-  <si>
-    <t>2019-09-09</t>
-  </si>
-  <si>
-    <t>2019-09-16</t>
-  </si>
-  <si>
-    <t>2019-10-08</t>
-  </si>
-  <si>
-    <t>2019-10-10</t>
-  </si>
-  <si>
-    <t>2019-10-11</t>
-  </si>
-  <si>
-    <t>2019-10-14</t>
-  </si>
-  <si>
-    <t>2019-10-15</t>
-  </si>
-  <si>
-    <t>2019-10-18</t>
-  </si>
-  <si>
-    <t>2019-10-21</t>
-  </si>
-  <si>
-    <t>2019-10-22</t>
-  </si>
-  <si>
-    <t>2019-10-23</t>
-  </si>
-  <si>
-    <t>2019-10-28</t>
-  </si>
-  <si>
-    <t>2019-11-13</t>
-  </si>
-  <si>
-    <t>2019-11-25</t>
-  </si>
-  <si>
-    <t>2019-11-27</t>
-  </si>
-  <si>
-    <t>2019-11-28</t>
-  </si>
-  <si>
-    <t>2019-11-29</t>
-  </si>
-  <si>
-    <t>2019-12-02</t>
-  </si>
-  <si>
-    <t>2019-12-04</t>
-  </si>
-  <si>
-    <t>2019-12-10</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2019-12-13</t>
-  </si>
-  <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
-    <t>2019-12-19</t>
-  </si>
-  <si>
-    <t>2019-12-24</t>
-  </si>
-  <si>
-    <t>2020-01-09</t>
-  </si>
-  <si>
-    <t>2020-01-13</t>
-  </si>
-  <si>
-    <t>2020-01-21</t>
-  </si>
-  <si>
-    <t>2020-02-28</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-03-04</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-09</t>
-  </si>
-  <si>
-    <t>2020-03-10</t>
-  </si>
-  <si>
-    <t>2020-03-11</t>
-  </si>
-  <si>
-    <t>2020-03-12</t>
-  </si>
-  <si>
-    <t>2020-03-16</t>
-  </si>
-  <si>
-    <t>2020-03-17</t>
-  </si>
-  <si>
-    <t>2020-03-18</t>
-  </si>
-  <si>
-    <t>2020-03-20</t>
-  </si>
-  <si>
-    <t>2020-03-30</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-04-03</t>
-  </si>
-  <si>
-    <t>2020-04-07</t>
-  </si>
-  <si>
-    <t>2020-04-08</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>2020-04-22</t>
-  </si>
-  <si>
-    <t>2020-04-24</t>
-  </si>
-  <si>
-    <t>2020-04-28</t>
-  </si>
-  <si>
-    <t>2020-05-15</t>
-  </si>
-  <si>
-    <t>2020-05-18</t>
-  </si>
-  <si>
-    <t>2020-05-19</t>
-  </si>
-  <si>
-    <t>2020-05-20</t>
-  </si>
-  <si>
-    <t>2020-05-21</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>2020-05-27</t>
-  </si>
-  <si>
-    <t>2020-06-01</t>
-  </si>
-  <si>
-    <t>2020-06-04</t>
-  </si>
-  <si>
-    <t>2020-06-09</t>
-  </si>
-  <si>
-    <t>2020-06-10</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>2020-06-19</t>
-  </si>
-  <si>
-    <t>2020-07-13</t>
-  </si>
-  <si>
-    <t>2020-07-16</t>
-  </si>
-  <si>
-    <t>2020-07-17</t>
-  </si>
-  <si>
-    <t>2020-07-28</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>2020-08-04</t>
-  </si>
-  <si>
-    <t>2020-08-05</t>
-  </si>
-  <si>
-    <t>2020-08-07</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>2020-08-12</t>
-  </si>
-  <si>
-    <t>2020-08-21</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>2020-11-10</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2021-01-21</t>
-  </si>
-  <si>
-    <t>2021-01-25</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>2021-03-05</t>
-  </si>
-  <si>
-    <t>2021-03-15</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>2021-04-20</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-04-22</t>
-  </si>
-  <si>
-    <t>2021-04-29</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>2021-05-17</t>
-  </si>
-  <si>
-    <t>2021-05-20</t>
-  </si>
-  <si>
-    <t>2021-05-28</t>
-  </si>
-  <si>
-    <t>2021-06-07</t>
+    <t>2021-07-26</t>
   </si>
 </sst>
 </file>
@@ -2423,7 +2435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1059"/>
+  <dimension ref="A1:P1066"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2520,7 +2532,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2570,7 +2582,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2620,7 +2632,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2670,7 +2682,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2720,7 +2732,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2770,7 +2782,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2970,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3020,7 +3032,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3070,7 +3082,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3220,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3270,7 +3282,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3620,7 +3632,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3670,7 +3682,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3820,7 +3832,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3870,7 +3882,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3920,7 +3932,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3970,7 +3982,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -4020,7 +4032,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -4070,7 +4082,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4120,7 +4132,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -4170,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4220,7 +4232,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4270,7 +4282,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4320,7 +4332,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4520,7 +4532,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4570,7 +4582,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4620,7 +4632,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4670,7 +4682,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4720,7 +4732,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4770,7 +4782,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4820,7 +4832,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4870,7 +4882,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4920,7 +4932,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4970,7 +4982,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -5020,7 +5032,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -5070,7 +5082,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -5120,7 +5132,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -5170,7 +5182,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -5320,7 +5332,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5370,7 +5382,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5420,7 +5432,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5470,7 +5482,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5520,7 +5532,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5570,7 +5582,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5620,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5770,7 +5782,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5820,7 +5832,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5970,7 +5982,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -6020,7 +6032,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -6070,7 +6082,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -6120,7 +6132,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -6170,7 +6182,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -6220,7 +6232,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6370,7 +6382,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6420,7 +6432,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6470,7 +6482,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6520,7 +6532,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6570,7 +6582,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6620,7 +6632,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6670,7 +6682,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6720,7 +6732,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6770,7 +6782,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6820,7 +6832,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6870,7 +6882,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6920,7 +6932,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6970,7 +6982,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -7220,7 +7232,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -7270,7 +7282,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -7320,7 +7332,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -7470,7 +7482,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -7520,7 +7532,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -9520,7 +9532,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9570,7 +9582,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9620,7 +9632,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -10070,7 +10082,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -10120,7 +10132,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -10170,7 +10182,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -10220,7 +10232,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -10270,7 +10282,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -10470,7 +10482,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10520,7 +10532,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10570,7 +10582,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10770,7 +10782,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10820,7 +10832,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10870,7 +10882,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10920,7 +10932,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -11220,7 +11232,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11270,7 +11282,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11320,7 +11332,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11370,7 +11382,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11420,7 +11432,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11670,7 +11682,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11720,7 +11732,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11770,7 +11782,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11820,7 +11832,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -13220,7 +13232,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -13270,7 +13282,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -13320,7 +13332,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -13370,7 +13382,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13420,7 +13432,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -13470,7 +13482,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -13920,7 +13932,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13970,7 +13982,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -14120,7 +14132,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -14170,7 +14182,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -14220,7 +14232,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -14670,7 +14682,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14720,7 +14732,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14770,7 +14782,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14820,7 +14832,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14870,7 +14882,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -15820,7 +15832,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15870,7 +15882,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15920,7 +15932,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15970,7 +15982,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -16020,7 +16032,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -16070,7 +16082,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -16870,7 +16882,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16920,7 +16932,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16970,7 +16982,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -17020,7 +17032,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -17070,7 +17082,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -17570,7 +17582,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17620,7 +17632,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17670,7 +17682,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17720,7 +17732,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17770,7 +17782,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17820,7 +17832,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17870,7 +17882,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -19370,7 +19382,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19420,7 +19432,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19470,7 +19482,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19520,7 +19532,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19570,7 +19582,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19620,7 +19632,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19670,7 +19682,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -21320,7 +21332,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21370,7 +21382,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21570,7 +21582,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21620,7 +21632,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21670,7 +21682,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21720,7 +21732,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21870,7 +21882,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21920,7 +21932,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21970,7 +21982,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -22120,7 +22132,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -22170,7 +22182,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -22220,7 +22232,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -22470,7 +22482,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22520,7 +22532,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22570,7 +22582,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22620,7 +22632,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22670,7 +22682,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22720,7 +22732,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22770,7 +22782,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22820,7 +22832,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22870,7 +22882,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22920,7 +22932,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22970,7 +22982,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -23020,7 +23032,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -23070,7 +23082,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -23170,7 +23182,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -23220,7 +23232,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23270,7 +23282,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -23320,7 +23332,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -23370,7 +23382,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23420,7 +23432,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23470,7 +23482,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -23520,7 +23532,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23970,7 +23982,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -24020,7 +24032,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -24070,7 +24082,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -24270,7 +24282,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24320,7 +24332,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24370,7 +24382,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24420,7 +24432,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24470,7 +24482,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24520,7 +24532,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24570,7 +24582,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24620,7 +24632,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24670,7 +24682,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24720,7 +24732,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24770,7 +24782,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24820,7 +24832,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24870,7 +24882,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24920,7 +24932,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24970,7 +24982,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -25020,7 +25032,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -25070,7 +25082,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -25120,7 +25132,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25170,7 +25182,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -25220,7 +25232,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -25720,7 +25732,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25770,7 +25782,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25820,7 +25832,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25870,7 +25882,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25920,7 +25932,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -26170,7 +26182,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26220,7 +26232,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26270,7 +26282,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26320,7 +26332,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26370,7 +26382,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -26420,7 +26432,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -26470,7 +26482,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -26520,7 +26532,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26570,7 +26582,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26620,7 +26632,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26670,7 +26682,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26720,7 +26732,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26770,7 +26782,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26820,7 +26832,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -27020,7 +27032,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -27070,7 +27082,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -27120,7 +27132,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -27170,7 +27182,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -27720,7 +27732,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27770,7 +27782,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27820,7 +27832,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27870,7 +27882,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27920,7 +27932,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -28170,7 +28182,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -28220,7 +28232,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -28270,7 +28282,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -28320,7 +28332,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -28520,7 +28532,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28570,7 +28582,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28620,7 +28632,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28670,7 +28682,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28720,7 +28732,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28770,7 +28782,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28820,7 +28832,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -29120,7 +29132,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -29170,7 +29182,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -29220,7 +29232,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29270,7 +29282,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29420,7 +29432,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -29470,7 +29482,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -29520,7 +29532,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29570,7 +29582,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29620,7 +29632,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29770,7 +29782,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29820,7 +29832,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29970,7 +29982,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -30020,7 +30032,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -30070,7 +30082,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -30120,7 +30132,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -30170,7 +30182,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -30220,7 +30232,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30270,7 +30282,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30320,7 +30332,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -30570,7 +30582,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -30620,7 +30632,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30670,7 +30682,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30720,7 +30732,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30770,7 +30782,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30820,7 +30832,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30870,7 +30882,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30920,7 +30932,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30970,7 +30982,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -31020,7 +31032,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -31070,7 +31082,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -31120,7 +31132,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -31170,7 +31182,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -31220,7 +31232,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31270,7 +31282,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31320,7 +31332,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31570,7 +31582,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31620,7 +31632,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31820,7 +31832,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31870,7 +31882,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31920,7 +31932,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31970,7 +31982,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -32020,7 +32032,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -32070,7 +32082,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -32120,7 +32132,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -32170,7 +32182,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -32220,7 +32232,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -32370,7 +32382,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -32420,7 +32432,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32620,7 +32632,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32670,7 +32682,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32870,7 +32882,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32920,7 +32932,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32970,7 +32982,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -33020,7 +33032,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -33070,7 +33082,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -33170,7 +33182,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -33220,7 +33232,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33270,7 +33282,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -33320,7 +33332,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -33570,7 +33582,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33620,7 +33632,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33670,7 +33682,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -34020,7 +34032,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -34070,7 +34082,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -34120,7 +34132,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -35070,7 +35082,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -35120,7 +35132,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -35170,7 +35182,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -35220,7 +35232,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35420,7 +35432,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -35470,7 +35482,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35520,7 +35532,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -36320,7 +36332,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -36370,7 +36382,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36420,7 +36432,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36470,7 +36482,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36520,7 +36532,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36570,7 +36582,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36620,7 +36632,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36670,7 +36682,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36720,7 +36732,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36770,7 +36782,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36820,7 +36832,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36870,7 +36882,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36920,7 +36932,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36970,7 +36982,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -37070,7 +37082,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -37120,7 +37132,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -37170,7 +37182,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -37220,7 +37232,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -37270,7 +37282,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -37320,7 +37332,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -37370,7 +37382,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -37570,7 +37582,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37620,7 +37632,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37670,7 +37682,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -38120,7 +38132,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -38170,7 +38182,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -38220,7 +38232,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -38270,7 +38282,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -38470,7 +38482,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38520,7 +38532,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38570,7 +38582,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38620,7 +38632,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38670,7 +38682,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38720,7 +38732,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38770,7 +38782,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38820,7 +38832,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38870,7 +38882,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38920,7 +38932,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38970,7 +38982,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -39020,7 +39032,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -40020,7 +40032,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -40070,7 +40082,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -40120,7 +40132,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -40170,7 +40182,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -40420,7 +40432,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40470,7 +40482,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40520,7 +40532,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40570,7 +40582,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -40770,7 +40782,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40820,7 +40832,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40870,7 +40882,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40970,7 +40982,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -41320,7 +41332,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -41370,7 +41382,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -41420,7 +41432,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41470,7 +41482,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41520,7 +41532,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41570,7 +41582,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41620,7 +41632,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41670,7 +41682,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41720,7 +41732,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41770,7 +41782,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -42020,7 +42032,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -42070,7 +42082,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -42120,7 +42132,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -42420,7 +42432,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -42470,7 +42482,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42520,7 +42532,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42770,7 +42782,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42820,7 +42832,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42870,7 +42882,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42920,7 +42932,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42970,7 +42982,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -43420,7 +43432,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -43470,7 +43482,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -43570,7 +43582,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -43620,7 +43632,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43670,7 +43682,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43720,7 +43732,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -44870,7 +44882,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44920,7 +44932,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44970,7 +44982,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -45020,7 +45032,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -45070,7 +45082,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -45120,7 +45132,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -45170,7 +45182,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -45220,7 +45232,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -45270,7 +45282,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -46020,7 +46032,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -46070,7 +46082,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -46120,7 +46132,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -46370,7 +46382,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -46420,7 +46432,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -46470,7 +46482,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46520,7 +46532,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46570,7 +46582,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46620,7 +46632,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46670,7 +46682,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46720,7 +46732,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46770,7 +46782,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46820,7 +46832,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46870,7 +46882,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -47070,7 +47082,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -47120,7 +47132,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -47170,7 +47182,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -47370,7 +47382,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -47420,7 +47432,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47470,7 +47482,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -47520,7 +47532,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47570,7 +47582,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47620,7 +47632,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -48520,7 +48532,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48570,7 +48582,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48670,7 +48682,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48720,7 +48732,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48770,7 +48782,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -49070,7 +49082,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -49120,7 +49132,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -49170,7 +49182,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -49220,7 +49232,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -49270,7 +49282,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -49420,7 +49432,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -49520,7 +49532,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49570,7 +49582,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49620,7 +49632,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49770,7 +49782,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49820,7 +49832,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49870,7 +49882,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -50070,7 +50082,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -50120,7 +50132,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -50170,7 +50182,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -50220,7 +50232,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -50270,7 +50282,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50620,7 +50632,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50670,7 +50682,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50720,7 +50732,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50770,7 +50782,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -50970,7 +50982,7 @@
         <v>1</v>
       </c>
       <c r="P971" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="972" spans="1:16">
@@ -51020,7 +51032,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -51520,7 +51532,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51570,7 +51582,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51620,7 +51632,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51670,7 +51682,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51720,7 +51732,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -52120,7 +52132,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -52320,7 +52332,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -52370,7 +52382,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -52420,7 +52432,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -52470,7 +52482,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -53020,7 +53032,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -53070,7 +53082,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -53120,7 +53132,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -53770,7 +53782,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53820,7 +53832,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53870,7 +53882,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -54770,7 +54782,7 @@
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
@@ -54934,7 +54946,7 @@
         <v>2.385066165658595</v>
       </c>
       <c r="D1051" t="s">
-        <v>255</v>
+        <v>491</v>
       </c>
       <c r="E1051">
         <v>2.397054367222326</v>
@@ -54984,7 +54996,7 @@
         <v>2.24487135359287</v>
       </c>
       <c r="D1052" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E1052">
         <v>2.40691738618878</v>
@@ -55031,40 +55043,40 @@
         <v>255</v>
       </c>
       <c r="C1053">
-        <v>-0.1907868162761375</v>
+        <v>0.3510294235212541</v>
       </c>
       <c r="D1053" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E1053">
-        <v>0.1420545233655446</v>
+        <v>-0.1586600711828083</v>
       </c>
       <c r="F1053">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1053">
-        <v>0.01699078681627614</v>
+        <v>0.01574897057647875</v>
       </c>
       <c r="H1053">
-        <v>0.01639794547663445</v>
+        <v>0.01505866007118281</v>
       </c>
       <c r="I1053">
-        <v>0.3328413396416821</v>
+        <v>0.5096894947040624</v>
       </c>
       <c r="J1053">
         <v>1.12888131619923</v>
       </c>
       <c r="K1053">
-        <v>7.61</v>
+        <v>6.82</v>
       </c>
       <c r="L1053">
-        <v>8.4</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M1053">
-        <v>7.2</v>
+        <v>6.74</v>
       </c>
       <c r="N1053">
-        <v>8.27</v>
+        <v>7.45</v>
       </c>
       <c r="O1053">
         <v>1</v>
@@ -55081,40 +55093,40 @@
         <v>256</v>
       </c>
       <c r="C1054">
-        <v>0.3510294235212541</v>
+        <v>0.2616036421348911</v>
       </c>
       <c r="D1054" t="s">
         <v>493</v>
       </c>
       <c r="E1054">
-        <v>0.04205452336554494</v>
+        <v>-0.1586600711828083</v>
       </c>
       <c r="F1054">
         <v>-1</v>
       </c>
       <c r="G1054">
-        <v>0.01574897057647875</v>
+        <v>0.01459839635786511</v>
       </c>
       <c r="H1054">
-        <v>0.01629794547663445</v>
+        <v>0.01505866007118281</v>
       </c>
       <c r="I1054">
-        <v>0.3089749001557092</v>
+        <v>0.4202637133176994</v>
       </c>
       <c r="J1054">
         <v>1.12888131619923</v>
       </c>
       <c r="K1054">
-        <v>6.82</v>
+        <v>6.35</v>
       </c>
       <c r="L1054">
-        <v>8.050000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="M1054">
-        <v>7.2</v>
+        <v>6.74</v>
       </c>
       <c r="N1054">
-        <v>8.17</v>
+        <v>7.45</v>
       </c>
       <c r="O1054">
         <v>1</v>
@@ -55131,40 +55143,40 @@
         <v>255</v>
       </c>
       <c r="C1055">
-        <v>-0.4293866076767205</v>
+        <v>0.1371988614513491</v>
       </c>
       <c r="D1055" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E1055">
-        <v>-0.08369035154696292</v>
+        <v>-0.3699823568647957</v>
       </c>
       <c r="F1055">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1055">
-        <v>0.01722938660767672</v>
+        <v>0.01596280113854865</v>
       </c>
       <c r="H1055">
-        <v>0.01662369035154696</v>
+        <v>0.0152699823568648</v>
       </c>
       <c r="I1055">
-        <v>0.3456962561297576</v>
+        <v>0.5071812183161448</v>
       </c>
       <c r="J1055">
         <v>1.160234771048189</v>
       </c>
       <c r="K1055">
-        <v>7.61</v>
+        <v>6.82</v>
       </c>
       <c r="L1055">
-        <v>8.4</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M1055">
-        <v>7.2</v>
+        <v>6.74</v>
       </c>
       <c r="N1055">
-        <v>8.27</v>
+        <v>7.45</v>
       </c>
       <c r="O1055">
         <v>1</v>
@@ -55181,40 +55193,40 @@
         <v>256</v>
       </c>
       <c r="C1056">
-        <v>0.1371988614513491</v>
+        <v>0.06250920384399805</v>
       </c>
       <c r="D1056" t="s">
         <v>493</v>
       </c>
       <c r="E1056">
-        <v>-0.1836903515469626</v>
+        <v>-0.3699823568647957</v>
       </c>
       <c r="F1056">
         <v>-1</v>
       </c>
       <c r="G1056">
-        <v>0.01596280113854865</v>
+        <v>0.014797490796156</v>
       </c>
       <c r="H1056">
-        <v>0.01652369035154696</v>
+        <v>0.0152699823568648</v>
       </c>
       <c r="I1056">
-        <v>0.3208892129983116</v>
+        <v>0.4324915607087938</v>
       </c>
       <c r="J1056">
         <v>1.160234771048189</v>
       </c>
       <c r="K1056">
-        <v>6.82</v>
+        <v>6.35</v>
       </c>
       <c r="L1056">
-        <v>8.050000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="M1056">
-        <v>7.2</v>
+        <v>6.74</v>
       </c>
       <c r="N1056">
-        <v>8.17</v>
+        <v>7.45</v>
       </c>
       <c r="O1056">
         <v>1</v>
@@ -55231,40 +55243,40 @@
         <v>256</v>
       </c>
       <c r="C1057">
-        <v>-0.2189357835067671</v>
+        <v>-0.2690824377225765</v>
       </c>
       <c r="D1057" t="s">
         <v>493</v>
       </c>
       <c r="E1057">
-        <v>-0.5596682758429221</v>
+        <v>-0.7219394693307359</v>
       </c>
       <c r="F1057">
         <v>-1</v>
       </c>
       <c r="G1057">
-        <v>0.01631893578350677</v>
+        <v>0.01512908243772258</v>
       </c>
       <c r="H1057">
-        <v>0.01689966827584292</v>
+        <v>0.01562193946933074</v>
       </c>
       <c r="I1057">
-        <v>0.340732492336155</v>
+        <v>0.4528570316081595</v>
       </c>
       <c r="J1057">
         <v>1.212453927200406</v>
       </c>
       <c r="K1057">
-        <v>6.82</v>
+        <v>6.35</v>
       </c>
       <c r="L1057">
-        <v>8.050000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="M1057">
-        <v>7.2</v>
+        <v>6.74</v>
       </c>
       <c r="N1057">
-        <v>8.17</v>
+        <v>7.45</v>
       </c>
       <c r="O1057">
         <v>1</v>
@@ -55278,43 +55290,43 @@
         <v>0</v>
       </c>
       <c r="B1058" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1058">
-        <v>-0.6993263373634928</v>
+        <v>-1.239456852786839</v>
       </c>
       <c r="D1058" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E1058">
-        <v>-1.066825458800169</v>
+        <v>-0.9668254588001695</v>
       </c>
       <c r="F1058">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1058">
-        <v>0.0167993263373635</v>
+        <v>0.01743945685278684</v>
       </c>
       <c r="H1058">
-        <v>0.01740682545880017</v>
+        <v>0.01750682545880017</v>
       </c>
       <c r="I1058">
-        <v>0.3674991214366763</v>
+        <v>0.2726313939866696</v>
       </c>
       <c r="J1058">
         <v>1.282892424833357</v>
       </c>
       <c r="K1058">
-        <v>6.82</v>
+        <v>7.28</v>
       </c>
       <c r="L1058">
-        <v>8.050000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="M1058">
         <v>7.2</v>
       </c>
       <c r="N1058">
-        <v>8.17</v>
+        <v>8.27</v>
       </c>
       <c r="O1058">
         <v>1</v>
@@ -55325,52 +55337,402 @@
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1059">
+        <v>-0.7163668976918167</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>493</v>
+      </c>
+      <c r="E1059">
+        <v>-1.196694943376825</v>
+      </c>
+      <c r="F1059">
+        <v>-1</v>
+      </c>
+      <c r="G1059">
+        <v>0.01557636689769182</v>
+      </c>
+      <c r="H1059">
+        <v>0.01609669494337683</v>
+      </c>
+      <c r="I1059">
+        <v>0.4803280456850088</v>
+      </c>
+      <c r="J1059">
+        <v>1.282892424833357</v>
+      </c>
+      <c r="K1059">
+        <v>6.35</v>
+      </c>
+      <c r="L1059">
+        <v>7.43</v>
+      </c>
+      <c r="M1059">
+        <v>6.74</v>
+      </c>
+      <c r="N1059">
+        <v>7.45</v>
+      </c>
+      <c r="O1059">
+        <v>1</v>
+      </c>
+      <c r="P1059" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:16">
+      <c r="A1060" s="1">
         <v>0</v>
       </c>
-      <c r="B1059" t="s">
+      <c r="B1060" t="s">
         <v>257</v>
       </c>
-      <c r="C1059">
+      <c r="C1060">
         <v>-1.416234245524462</v>
       </c>
-      <c r="D1059" t="s">
+      <c r="D1060" t="s">
+        <v>494</v>
+      </c>
+      <c r="E1060">
+        <v>-1.141660242826392</v>
+      </c>
+      <c r="F1060">
+        <v>1</v>
+      </c>
+      <c r="G1060">
+        <v>0.01761623424552446</v>
+      </c>
+      <c r="H1060">
+        <v>0.01768166024282639</v>
+      </c>
+      <c r="I1060">
+        <v>0.2745740026980705</v>
+      </c>
+      <c r="J1060">
+        <v>1.307175033725888</v>
+      </c>
+      <c r="K1060">
+        <v>7.28</v>
+      </c>
+      <c r="L1060">
+        <v>8.1</v>
+      </c>
+      <c r="M1060">
+        <v>7.2</v>
+      </c>
+      <c r="N1060">
+        <v>8.27</v>
+      </c>
+      <c r="O1060">
+        <v>1</v>
+      </c>
+      <c r="P1060" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:16">
+      <c r="A1061" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1061">
+        <v>-0.8705614641593868</v>
+      </c>
+      <c r="D1061" t="s">
+        <v>493</v>
+      </c>
+      <c r="E1061">
+        <v>-1.360359727312482</v>
+      </c>
+      <c r="F1061">
+        <v>-1</v>
+      </c>
+      <c r="G1061">
+        <v>0.01573056146415939</v>
+      </c>
+      <c r="H1061">
+        <v>0.01626035972731248</v>
+      </c>
+      <c r="I1061">
+        <v>0.4897982631530953</v>
+      </c>
+      <c r="J1061">
+        <v>1.307175033725888</v>
+      </c>
+      <c r="K1061">
+        <v>6.35</v>
+      </c>
+      <c r="L1061">
+        <v>7.43</v>
+      </c>
+      <c r="M1061">
+        <v>6.74</v>
+      </c>
+      <c r="N1061">
+        <v>7.45</v>
+      </c>
+      <c r="O1061">
+        <v>1</v>
+      </c>
+      <c r="P1061" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:16">
+      <c r="A1062" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1062" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1062">
+        <v>-0.9192034028361835</v>
+      </c>
+      <c r="D1062" t="s">
+        <v>493</v>
+      </c>
+      <c r="E1062">
+        <v>-1.411989123640295</v>
+      </c>
+      <c r="F1062">
+        <v>-1</v>
+      </c>
+      <c r="G1062">
+        <v>0.01577920340283618</v>
+      </c>
+      <c r="H1062">
+        <v>0.01631198912364029</v>
+      </c>
+      <c r="I1062">
+        <v>0.492785720804112</v>
+      </c>
+      <c r="J1062">
+        <v>1.314835181549005</v>
+      </c>
+      <c r="K1062">
+        <v>6.35</v>
+      </c>
+      <c r="L1062">
+        <v>7.43</v>
+      </c>
+      <c r="M1062">
+        <v>6.74</v>
+      </c>
+      <c r="N1062">
+        <v>7.45</v>
+      </c>
+      <c r="O1062">
+        <v>1</v>
+      </c>
+      <c r="P1062" t="s">
         <v>492</v>
       </c>
-      <c r="E1059">
-        <v>-1.141660242826392</v>
-      </c>
-      <c r="F1059">
-        <v>1</v>
-      </c>
-      <c r="G1059">
-        <v>0.01761623424552446</v>
-      </c>
-      <c r="H1059">
-        <v>0.01768166024282639</v>
-      </c>
-      <c r="I1059">
-        <v>0.2745740026980705</v>
-      </c>
-      <c r="J1059">
-        <v>1.307175033725888</v>
-      </c>
-      <c r="K1059">
-        <v>7.28</v>
-      </c>
-      <c r="L1059">
-        <v>8.1</v>
-      </c>
-      <c r="M1059">
-        <v>7.2</v>
-      </c>
-      <c r="N1059">
-        <v>8.27</v>
-      </c>
-      <c r="O1059">
-        <v>1</v>
-      </c>
-      <c r="P1059" t="s">
+    </row>
+    <row r="1063" spans="1:16">
+      <c r="A1063" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1063" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1063">
+        <v>-0.8831301526583957</v>
+      </c>
+      <c r="D1063" t="s">
+        <v>493</v>
+      </c>
+      <c r="E1063">
+        <v>-1.373700351010643</v>
+      </c>
+      <c r="F1063">
+        <v>-1</v>
+      </c>
+      <c r="G1063">
+        <v>0.01574313015265839</v>
+      </c>
+      <c r="H1063">
+        <v>0.01627370035101064</v>
+      </c>
+      <c r="I1063">
+        <v>0.4905701983522475</v>
+      </c>
+      <c r="J1063">
+        <v>1.309154354749354</v>
+      </c>
+      <c r="K1063">
+        <v>6.35</v>
+      </c>
+      <c r="L1063">
+        <v>7.43</v>
+      </c>
+      <c r="M1063">
+        <v>6.74</v>
+      </c>
+      <c r="N1063">
+        <v>7.45</v>
+      </c>
+      <c r="O1063">
+        <v>1</v>
+      </c>
+      <c r="P1063" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:16">
+      <c r="A1064" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1064" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1064">
+        <v>-0.4151176269632382</v>
+      </c>
+      <c r="D1064" t="s">
+        <v>495</v>
+      </c>
+      <c r="E1064">
+        <v>-0.6204353661828428</v>
+      </c>
+      <c r="F1064">
+        <v>-1</v>
+      </c>
+      <c r="G1064">
+        <v>0.01527511762696324</v>
+      </c>
+      <c r="H1064">
+        <v>0.01544043536618284</v>
+      </c>
+      <c r="I1064">
+        <v>0.2053177392196046</v>
+      </c>
+      <c r="J1064">
+        <v>1.23545159479736</v>
+      </c>
+      <c r="K1064">
+        <v>6.35</v>
+      </c>
+      <c r="L1064">
+        <v>7.43</v>
+      </c>
+      <c r="M1064">
+        <v>6.5</v>
+      </c>
+      <c r="N1064">
+        <v>7.41</v>
+      </c>
+      <c r="O1064">
+        <v>1</v>
+      </c>
+      <c r="P1064" t="s">
         <v>255</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:16">
+      <c r="A1065" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1065" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1065">
+        <v>-0.1604084353129611</v>
+      </c>
+      <c r="D1065" t="s">
+        <v>493</v>
+      </c>
+      <c r="E1065">
+        <v>-0.6065910006313944</v>
+      </c>
+      <c r="F1065">
+        <v>-1</v>
+      </c>
+      <c r="G1065">
+        <v>0.01502040843531296</v>
+      </c>
+      <c r="H1065">
+        <v>0.0155065910006314</v>
+      </c>
+      <c r="I1065">
+        <v>0.4461825653184333</v>
+      </c>
+      <c r="J1065">
+        <v>1.195339911072907</v>
+      </c>
+      <c r="K1065">
+        <v>6.35</v>
+      </c>
+      <c r="L1065">
+        <v>7.43</v>
+      </c>
+      <c r="M1065">
+        <v>6.74</v>
+      </c>
+      <c r="N1065">
+        <v>7.45</v>
+      </c>
+      <c r="O1065">
+        <v>1</v>
+      </c>
+      <c r="P1065" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:16">
+      <c r="A1066" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1066" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1066">
+        <v>-0.1949390005542107</v>
+      </c>
+      <c r="D1066" t="s">
+        <v>493</v>
+      </c>
+      <c r="E1066">
+        <v>-0.6432423407457284</v>
+      </c>
+      <c r="F1066">
+        <v>-1</v>
+      </c>
+      <c r="G1066">
+        <v>0.01505493900055421</v>
+      </c>
+      <c r="H1066">
+        <v>0.01554324234074573</v>
+      </c>
+      <c r="I1066">
+        <v>0.4483033401915177</v>
+      </c>
+      <c r="J1066">
+        <v>1.200777795362868</v>
+      </c>
+      <c r="K1066">
+        <v>6.35</v>
+      </c>
+      <c r="L1066">
+        <v>7.43</v>
+      </c>
+      <c r="M1066">
+        <v>6.74</v>
+      </c>
+      <c r="N1066">
+        <v>7.45</v>
+      </c>
+      <c r="O1066">
+        <v>1</v>
+      </c>
+      <c r="P1066" t="s">
+        <v>687</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3213" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3219" uniqueCount="687">
   <si>
     <t>trade_time</t>
   </si>
@@ -781,6 +781,9 @@
     <t>2021-06-18</t>
   </si>
   <si>
+    <t>2021-07-12</t>
+  </si>
+  <si>
     <t>2021-07-20</t>
   </si>
   <si>
@@ -790,721 +793,712 @@
     <t>2021-07-14</t>
   </si>
   <si>
+    <t>2016-07-27</t>
+  </si>
+  <si>
+    <t>2016-08-10</t>
+  </si>
+  <si>
+    <t>2016-08-15</t>
+  </si>
+  <si>
+    <t>2016-08-22</t>
+  </si>
+  <si>
+    <t>2016-08-23</t>
+  </si>
+  <si>
+    <t>2016-08-24</t>
+  </si>
+  <si>
+    <t>2016-08-25</t>
+  </si>
+  <si>
+    <t>2016-08-26</t>
+  </si>
+  <si>
+    <t>2016-09-02</t>
+  </si>
+  <si>
+    <t>2016-09-05</t>
+  </si>
+  <si>
+    <t>2016-09-06</t>
+  </si>
+  <si>
+    <t>2016-09-28</t>
+  </si>
+  <si>
+    <t>2016-09-29</t>
+  </si>
+  <si>
+    <t>2016-10-12</t>
+  </si>
+  <si>
+    <t>2016-10-24</t>
+  </si>
+  <si>
+    <t>2016-10-25</t>
+  </si>
+  <si>
+    <t>2016-11-21</t>
+  </si>
+  <si>
+    <t>2016-12-02</t>
+  </si>
+  <si>
+    <t>2016-12-05</t>
+  </si>
+  <si>
+    <t>2016-12-14</t>
+  </si>
+  <si>
+    <t>2017-01-23</t>
+  </si>
+  <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
+    <t>2017-03-27</t>
+  </si>
+  <si>
+    <t>2017-04-18</t>
+  </si>
+  <si>
+    <t>2017-04-19</t>
+  </si>
+  <si>
+    <t>2017-04-21</t>
+  </si>
+  <si>
+    <t>2017-06-07</t>
+  </si>
+  <si>
+    <t>2017-06-15</t>
+  </si>
+  <si>
+    <t>2017-07-05</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-07-07</t>
+  </si>
+  <si>
+    <t>2017-06-28</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>2017-07-20</t>
+  </si>
+  <si>
+    <t>2017-07-24</t>
+  </si>
+  <si>
+    <t>2017-07-25</t>
+  </si>
+  <si>
+    <t>2017-07-26</t>
+  </si>
+  <si>
+    <t>2017-07-27</t>
+  </si>
+  <si>
+    <t>2017-08-08</t>
+  </si>
+  <si>
+    <t>2017-08-10</t>
+  </si>
+  <si>
+    <t>2017-08-11</t>
+  </si>
+  <si>
+    <t>2017-07-31</t>
+  </si>
+  <si>
+    <t>2017-08-02</t>
+  </si>
+  <si>
+    <t>2017-08-31</t>
+  </si>
+  <si>
+    <t>2017-09-07</t>
+  </si>
+  <si>
+    <t>2017-09-13</t>
+  </si>
+  <si>
+    <t>2017-09-20</t>
+  </si>
+  <si>
+    <t>2017-10-11</t>
+  </si>
+  <si>
+    <t>2017-10-17</t>
+  </si>
+  <si>
+    <t>2017-10-13</t>
+  </si>
+  <si>
+    <t>2017-10-23</t>
+  </si>
+  <si>
+    <t>2017-10-27</t>
+  </si>
+  <si>
+    <t>2017-10-30</t>
+  </si>
+  <si>
+    <t>2017-11-01</t>
+  </si>
+  <si>
+    <t>2017-11-03</t>
+  </si>
+  <si>
+    <t>2017-11-06</t>
+  </si>
+  <si>
+    <t>2017-11-07</t>
+  </si>
+  <si>
+    <t>2017-11-08</t>
+  </si>
+  <si>
+    <t>2017-11-09</t>
+  </si>
+  <si>
+    <t>2017-11-14</t>
+  </si>
+  <si>
+    <t>2017-11-15</t>
+  </si>
+  <si>
+    <t>2017-11-16</t>
+  </si>
+  <si>
+    <t>2017-11-22</t>
+  </si>
+  <si>
+    <t>2017-11-23</t>
+  </si>
+  <si>
+    <t>2018-01-19</t>
+  </si>
+  <si>
+    <t>2018-01-09</t>
+  </si>
+  <si>
+    <t>2018-01-16</t>
+  </si>
+  <si>
+    <t>2018-01-24</t>
+  </si>
+  <si>
+    <t>2018-02-01</t>
+  </si>
+  <si>
+    <t>2018-01-15</t>
+  </si>
+  <si>
+    <t>2018-02-05</t>
+  </si>
+  <si>
+    <t>2018-02-07</t>
+  </si>
+  <si>
+    <t>2018-02-09</t>
+  </si>
+  <si>
+    <t>2018-02-22</t>
+  </si>
+  <si>
+    <t>2018-02-26</t>
+  </si>
+  <si>
+    <t>2018-02-28</t>
+  </si>
+  <si>
+    <t>2018-03-01</t>
+  </si>
+  <si>
+    <t>2018-03-08</t>
+  </si>
+  <si>
+    <t>2018-03-05</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>2018-03-12</t>
+  </si>
+  <si>
+    <t>2018-03-13</t>
+  </si>
+  <si>
+    <t>2018-03-14</t>
+  </si>
+  <si>
+    <t>2018-04-03</t>
+  </si>
+  <si>
+    <t>2018-04-11</t>
+  </si>
+  <si>
+    <t>2018-04-12</t>
+  </si>
+  <si>
+    <t>2018-04-17</t>
+  </si>
+  <si>
+    <t>2018-04-18</t>
+  </si>
+  <si>
+    <t>2018-04-20</t>
+  </si>
+  <si>
+    <t>2018-04-24</t>
+  </si>
+  <si>
+    <t>2018-09-05</t>
+  </si>
+  <si>
+    <t>2018-09-19</t>
+  </si>
+  <si>
+    <t>2018-09-21</t>
+  </si>
+  <si>
+    <t>2018-10-22</t>
+  </si>
+  <si>
+    <t>2018-09-28</t>
+  </si>
+  <si>
+    <t>2018-10-23</t>
+  </si>
+  <si>
+    <t>2018-10-24</t>
+  </si>
+  <si>
+    <t>2018-12-04</t>
+  </si>
+  <si>
+    <t>2018-12-13</t>
+  </si>
+  <si>
+    <t>2018-12-05</t>
+  </si>
+  <si>
+    <t>2018-12-14</t>
+  </si>
+  <si>
+    <t>2018-12-19</t>
+  </si>
+  <si>
+    <t>2018-12-21</t>
+  </si>
+  <si>
+    <t>2018-12-18</t>
+  </si>
+  <si>
+    <t>2018-12-27</t>
+  </si>
+  <si>
+    <t>2019-01-28</t>
+  </si>
+  <si>
+    <t>2019-03-15</t>
+  </si>
+  <si>
+    <t>2019-03-29</t>
+  </si>
+  <si>
+    <t>2019-04-01</t>
+  </si>
+  <si>
+    <t>2019-04-03</t>
+  </si>
+  <si>
+    <t>2019-04-25</t>
+  </si>
+  <si>
+    <t>2019-04-29</t>
+  </si>
+  <si>
+    <t>2019-05-14</t>
+  </si>
+  <si>
+    <t>2019-05-21</t>
+  </si>
+  <si>
+    <t>2019-05-24</t>
+  </si>
+  <si>
+    <t>2019-05-27</t>
+  </si>
+  <si>
+    <t>2019-05-28</t>
+  </si>
+  <si>
+    <t>2019-05-29</t>
+  </si>
+  <si>
+    <t>2019-07-10</t>
+  </si>
+  <si>
+    <t>2019-07-24</t>
+  </si>
+  <si>
+    <t>2019-07-25</t>
+  </si>
+  <si>
+    <t>2019-07-12</t>
+  </si>
+  <si>
+    <t>2019-08-02</t>
+  </si>
+  <si>
+    <t>2019-08-05</t>
+  </si>
+  <si>
+    <t>2019-08-08</t>
+  </si>
+  <si>
+    <t>2019-08-09</t>
+  </si>
+  <si>
+    <t>2019-08-12</t>
+  </si>
+  <si>
+    <t>2019-08-16</t>
+  </si>
+  <si>
+    <t>2019-08-19</t>
+  </si>
+  <si>
+    <t>2019-09-03</t>
+  </si>
+  <si>
+    <t>2019-09-27</t>
+  </si>
+  <si>
+    <t>2019-09-30</t>
+  </si>
+  <si>
+    <t>2019-09-25</t>
+  </si>
+  <si>
+    <t>2019-10-17</t>
+  </si>
+  <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
+    <t>2019-11-04</t>
+  </si>
+  <si>
+    <t>2019-11-05</t>
+  </si>
+  <si>
+    <t>2019-11-07</t>
+  </si>
+  <si>
+    <t>2019-11-15</t>
+  </si>
+  <si>
+    <t>2019-11-26</t>
+  </si>
+  <si>
+    <t>2019-12-05</t>
+  </si>
+  <si>
+    <t>2019-12-11</t>
+  </si>
+  <si>
+    <t>2020-01-02</t>
+  </si>
+  <si>
+    <t>2020-01-03</t>
+  </si>
+  <si>
+    <t>2020-01-06</t>
+  </si>
+  <si>
+    <t>2020-01-07</t>
+  </si>
+  <si>
+    <t>2019-12-18</t>
+  </si>
+  <si>
+    <t>2019-12-27</t>
+  </si>
+  <si>
+    <t>2020-01-16</t>
+  </si>
+  <si>
+    <t>2020-01-17</t>
+  </si>
+  <si>
+    <t>2020-02-04</t>
+  </si>
+  <si>
+    <t>2020-02-05</t>
+  </si>
+  <si>
+    <t>2020-01-23</t>
+  </si>
+  <si>
+    <t>2020-02-06</t>
+  </si>
+  <si>
+    <t>2020-02-10</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-03-19</t>
+  </si>
+  <si>
+    <t>2020-03-26</t>
+  </si>
+  <si>
+    <t>2020-03-25</t>
+  </si>
+  <si>
+    <t>2020-04-02</t>
+  </si>
+  <si>
+    <t>2020-04-16</t>
+  </si>
+  <si>
+    <t>2020-04-17</t>
+  </si>
+  <si>
+    <t>2020-04-21</t>
+  </si>
+  <si>
+    <t>2020-05-06</t>
+  </si>
+  <si>
+    <t>2020-04-14</t>
+  </si>
+  <si>
+    <t>2020-05-11</t>
+  </si>
+  <si>
+    <t>2020-05-12</t>
+  </si>
+  <si>
+    <t>2020-05-13</t>
+  </si>
+  <si>
+    <t>2020-05-14</t>
+  </si>
+  <si>
+    <t>2020-06-12</t>
+  </si>
+  <si>
+    <t>2020-06-15</t>
+  </si>
+  <si>
+    <t>2020-06-08</t>
+  </si>
+  <si>
+    <t>2020-07-03</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-24</t>
+  </si>
+  <si>
+    <t>2020-07-30</t>
+  </si>
+  <si>
+    <t>2020-08-10</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>2020-08-18</t>
+  </si>
+  <si>
+    <t>2020-08-19</t>
+  </si>
+  <si>
+    <t>2020-08-26</t>
+  </si>
+  <si>
+    <t>2020-09-01</t>
+  </si>
+  <si>
+    <t>2020-09-02</t>
+  </si>
+  <si>
+    <t>2020-09-03</t>
+  </si>
+  <si>
+    <t>2020-09-04</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>2020-09-08</t>
+  </si>
+  <si>
+    <t>2020-09-09</t>
+  </si>
+  <si>
+    <t>2020-09-14</t>
+  </si>
+  <si>
+    <t>2020-09-15</t>
+  </si>
+  <si>
+    <t>2020-09-17</t>
+  </si>
+  <si>
+    <t>2020-09-21</t>
+  </si>
+  <si>
+    <t>2020-09-22</t>
+  </si>
+  <si>
+    <t>2020-11-24</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>2021-01-22</t>
+  </si>
+  <si>
+    <t>2021-02-25</t>
+  </si>
+  <si>
+    <t>2021-03-01</t>
+  </si>
+  <si>
+    <t>2021-03-02</t>
+  </si>
+  <si>
+    <t>2021-03-17</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>2021-04-14</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>2021-04-15</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>2021-04-26</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>2021-05-21</t>
+  </si>
+  <si>
+    <t>2021-05-24</t>
+  </si>
+  <si>
+    <t>2021-05-25</t>
+  </si>
+  <si>
+    <t>2021-05-26</t>
+  </si>
+  <si>
+    <t>2021-05-31</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>2021-06-15</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>2021-06-17</t>
+  </si>
+  <si>
+    <t>2021-06-22</t>
+  </si>
+  <si>
+    <t>2021-06-25</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>2021-07-08</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>2021-07-15</t>
+  </si>
+  <si>
     <t>2021-07-29</t>
-  </si>
-  <si>
-    <t>2016-07-27</t>
-  </si>
-  <si>
-    <t>2016-08-10</t>
-  </si>
-  <si>
-    <t>2016-08-15</t>
-  </si>
-  <si>
-    <t>2016-08-22</t>
-  </si>
-  <si>
-    <t>2016-08-23</t>
-  </si>
-  <si>
-    <t>2016-08-24</t>
-  </si>
-  <si>
-    <t>2016-08-25</t>
-  </si>
-  <si>
-    <t>2016-08-26</t>
-  </si>
-  <si>
-    <t>2016-09-02</t>
-  </si>
-  <si>
-    <t>2016-09-05</t>
-  </si>
-  <si>
-    <t>2016-09-06</t>
-  </si>
-  <si>
-    <t>2016-09-28</t>
-  </si>
-  <si>
-    <t>2016-09-29</t>
-  </si>
-  <si>
-    <t>2016-10-12</t>
-  </si>
-  <si>
-    <t>2016-10-24</t>
-  </si>
-  <si>
-    <t>2016-10-25</t>
-  </si>
-  <si>
-    <t>2016-11-21</t>
-  </si>
-  <si>
-    <t>2016-12-02</t>
-  </si>
-  <si>
-    <t>2016-12-05</t>
-  </si>
-  <si>
-    <t>2016-12-14</t>
-  </si>
-  <si>
-    <t>2017-01-23</t>
-  </si>
-  <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
-    <t>2017-03-27</t>
-  </si>
-  <si>
-    <t>2017-04-18</t>
-  </si>
-  <si>
-    <t>2017-04-19</t>
-  </si>
-  <si>
-    <t>2017-04-21</t>
-  </si>
-  <si>
-    <t>2017-06-07</t>
-  </si>
-  <si>
-    <t>2017-06-15</t>
-  </si>
-  <si>
-    <t>2017-07-05</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-07-07</t>
-  </si>
-  <si>
-    <t>2017-06-28</t>
-  </si>
-  <si>
-    <t>2017-07-12</t>
-  </si>
-  <si>
-    <t>2017-07-20</t>
-  </si>
-  <si>
-    <t>2017-07-24</t>
-  </si>
-  <si>
-    <t>2017-07-25</t>
-  </si>
-  <si>
-    <t>2017-07-26</t>
-  </si>
-  <si>
-    <t>2017-07-27</t>
-  </si>
-  <si>
-    <t>2017-08-08</t>
-  </si>
-  <si>
-    <t>2017-08-10</t>
-  </si>
-  <si>
-    <t>2017-08-11</t>
-  </si>
-  <si>
-    <t>2017-07-31</t>
-  </si>
-  <si>
-    <t>2017-08-02</t>
-  </si>
-  <si>
-    <t>2017-08-31</t>
-  </si>
-  <si>
-    <t>2017-09-07</t>
-  </si>
-  <si>
-    <t>2017-09-13</t>
-  </si>
-  <si>
-    <t>2017-09-20</t>
-  </si>
-  <si>
-    <t>2017-10-11</t>
-  </si>
-  <si>
-    <t>2017-10-17</t>
-  </si>
-  <si>
-    <t>2017-10-13</t>
-  </si>
-  <si>
-    <t>2017-10-23</t>
-  </si>
-  <si>
-    <t>2017-10-27</t>
-  </si>
-  <si>
-    <t>2017-10-30</t>
-  </si>
-  <si>
-    <t>2017-11-01</t>
-  </si>
-  <si>
-    <t>2017-11-03</t>
-  </si>
-  <si>
-    <t>2017-11-06</t>
-  </si>
-  <si>
-    <t>2017-11-07</t>
-  </si>
-  <si>
-    <t>2017-11-08</t>
-  </si>
-  <si>
-    <t>2017-11-09</t>
-  </si>
-  <si>
-    <t>2017-11-14</t>
-  </si>
-  <si>
-    <t>2017-11-15</t>
-  </si>
-  <si>
-    <t>2017-11-16</t>
-  </si>
-  <si>
-    <t>2017-11-22</t>
-  </si>
-  <si>
-    <t>2017-11-23</t>
-  </si>
-  <si>
-    <t>2018-01-19</t>
-  </si>
-  <si>
-    <t>2018-01-09</t>
-  </si>
-  <si>
-    <t>2018-01-16</t>
-  </si>
-  <si>
-    <t>2018-01-24</t>
-  </si>
-  <si>
-    <t>2018-02-01</t>
-  </si>
-  <si>
-    <t>2018-01-15</t>
-  </si>
-  <si>
-    <t>2018-02-05</t>
-  </si>
-  <si>
-    <t>2018-02-07</t>
-  </si>
-  <si>
-    <t>2018-02-09</t>
-  </si>
-  <si>
-    <t>2018-02-22</t>
-  </si>
-  <si>
-    <t>2018-02-26</t>
-  </si>
-  <si>
-    <t>2018-02-28</t>
-  </si>
-  <si>
-    <t>2018-03-01</t>
-  </si>
-  <si>
-    <t>2018-03-08</t>
-  </si>
-  <si>
-    <t>2018-03-05</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>2018-03-12</t>
-  </si>
-  <si>
-    <t>2018-03-13</t>
-  </si>
-  <si>
-    <t>2018-03-14</t>
-  </si>
-  <si>
-    <t>2018-04-03</t>
-  </si>
-  <si>
-    <t>2018-04-11</t>
-  </si>
-  <si>
-    <t>2018-04-12</t>
-  </si>
-  <si>
-    <t>2018-04-17</t>
-  </si>
-  <si>
-    <t>2018-04-18</t>
-  </si>
-  <si>
-    <t>2018-04-20</t>
-  </si>
-  <si>
-    <t>2018-04-24</t>
-  </si>
-  <si>
-    <t>2018-09-05</t>
-  </si>
-  <si>
-    <t>2018-09-19</t>
-  </si>
-  <si>
-    <t>2018-09-21</t>
-  </si>
-  <si>
-    <t>2018-10-22</t>
-  </si>
-  <si>
-    <t>2018-09-28</t>
-  </si>
-  <si>
-    <t>2018-10-23</t>
-  </si>
-  <si>
-    <t>2018-10-24</t>
-  </si>
-  <si>
-    <t>2018-12-04</t>
-  </si>
-  <si>
-    <t>2018-12-13</t>
-  </si>
-  <si>
-    <t>2018-12-05</t>
-  </si>
-  <si>
-    <t>2018-12-14</t>
-  </si>
-  <si>
-    <t>2018-12-19</t>
-  </si>
-  <si>
-    <t>2018-12-21</t>
-  </si>
-  <si>
-    <t>2018-12-18</t>
-  </si>
-  <si>
-    <t>2018-12-27</t>
-  </si>
-  <si>
-    <t>2019-01-28</t>
-  </si>
-  <si>
-    <t>2019-03-15</t>
-  </si>
-  <si>
-    <t>2019-03-29</t>
-  </si>
-  <si>
-    <t>2019-04-01</t>
-  </si>
-  <si>
-    <t>2019-04-03</t>
-  </si>
-  <si>
-    <t>2019-04-25</t>
-  </si>
-  <si>
-    <t>2019-04-29</t>
-  </si>
-  <si>
-    <t>2019-05-14</t>
-  </si>
-  <si>
-    <t>2019-05-21</t>
-  </si>
-  <si>
-    <t>2019-05-24</t>
-  </si>
-  <si>
-    <t>2019-05-27</t>
-  </si>
-  <si>
-    <t>2019-05-28</t>
-  </si>
-  <si>
-    <t>2019-05-29</t>
-  </si>
-  <si>
-    <t>2019-07-10</t>
-  </si>
-  <si>
-    <t>2019-07-24</t>
-  </si>
-  <si>
-    <t>2019-07-25</t>
-  </si>
-  <si>
-    <t>2019-07-12</t>
-  </si>
-  <si>
-    <t>2019-08-02</t>
-  </si>
-  <si>
-    <t>2019-08-05</t>
-  </si>
-  <si>
-    <t>2019-08-08</t>
-  </si>
-  <si>
-    <t>2019-08-09</t>
-  </si>
-  <si>
-    <t>2019-08-12</t>
-  </si>
-  <si>
-    <t>2019-08-16</t>
-  </si>
-  <si>
-    <t>2019-08-19</t>
-  </si>
-  <si>
-    <t>2019-09-03</t>
-  </si>
-  <si>
-    <t>2019-09-27</t>
-  </si>
-  <si>
-    <t>2019-09-30</t>
-  </si>
-  <si>
-    <t>2019-09-25</t>
-  </si>
-  <si>
-    <t>2019-10-17</t>
-  </si>
-  <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
-    <t>2019-11-04</t>
-  </si>
-  <si>
-    <t>2019-11-05</t>
-  </si>
-  <si>
-    <t>2019-11-07</t>
-  </si>
-  <si>
-    <t>2019-11-15</t>
-  </si>
-  <si>
-    <t>2019-11-26</t>
-  </si>
-  <si>
-    <t>2019-12-05</t>
-  </si>
-  <si>
-    <t>2019-12-11</t>
-  </si>
-  <si>
-    <t>2020-01-02</t>
-  </si>
-  <si>
-    <t>2020-01-03</t>
-  </si>
-  <si>
-    <t>2020-01-06</t>
-  </si>
-  <si>
-    <t>2020-01-07</t>
-  </si>
-  <si>
-    <t>2019-12-18</t>
-  </si>
-  <si>
-    <t>2019-12-27</t>
-  </si>
-  <si>
-    <t>2020-01-16</t>
-  </si>
-  <si>
-    <t>2020-01-17</t>
-  </si>
-  <si>
-    <t>2020-02-04</t>
-  </si>
-  <si>
-    <t>2020-02-05</t>
-  </si>
-  <si>
-    <t>2020-01-23</t>
-  </si>
-  <si>
-    <t>2020-02-06</t>
-  </si>
-  <si>
-    <t>2020-02-10</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-03-19</t>
-  </si>
-  <si>
-    <t>2020-03-26</t>
-  </si>
-  <si>
-    <t>2020-03-25</t>
-  </si>
-  <si>
-    <t>2020-04-02</t>
-  </si>
-  <si>
-    <t>2020-04-16</t>
-  </si>
-  <si>
-    <t>2020-04-17</t>
-  </si>
-  <si>
-    <t>2020-04-21</t>
-  </si>
-  <si>
-    <t>2020-05-06</t>
-  </si>
-  <si>
-    <t>2020-04-14</t>
-  </si>
-  <si>
-    <t>2020-05-11</t>
-  </si>
-  <si>
-    <t>2020-05-12</t>
-  </si>
-  <si>
-    <t>2020-05-13</t>
-  </si>
-  <si>
-    <t>2020-05-14</t>
-  </si>
-  <si>
-    <t>2020-06-12</t>
-  </si>
-  <si>
-    <t>2020-06-15</t>
-  </si>
-  <si>
-    <t>2020-06-08</t>
-  </si>
-  <si>
-    <t>2020-07-03</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-24</t>
-  </si>
-  <si>
-    <t>2020-07-30</t>
-  </si>
-  <si>
-    <t>2020-08-10</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>2020-08-18</t>
-  </si>
-  <si>
-    <t>2020-08-19</t>
-  </si>
-  <si>
-    <t>2020-08-26</t>
-  </si>
-  <si>
-    <t>2020-09-01</t>
-  </si>
-  <si>
-    <t>2020-09-02</t>
-  </si>
-  <si>
-    <t>2020-09-03</t>
-  </si>
-  <si>
-    <t>2020-09-04</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>2020-09-08</t>
-  </si>
-  <si>
-    <t>2020-09-09</t>
-  </si>
-  <si>
-    <t>2020-09-14</t>
-  </si>
-  <si>
-    <t>2020-09-15</t>
-  </si>
-  <si>
-    <t>2020-09-17</t>
-  </si>
-  <si>
-    <t>2020-09-21</t>
-  </si>
-  <si>
-    <t>2020-09-22</t>
-  </si>
-  <si>
-    <t>2020-11-24</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-14</t>
-  </si>
-  <si>
-    <t>2021-01-22</t>
-  </si>
-  <si>
-    <t>2021-02-25</t>
-  </si>
-  <si>
-    <t>2021-03-01</t>
-  </si>
-  <si>
-    <t>2021-03-02</t>
-  </si>
-  <si>
-    <t>2021-03-17</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>2021-04-14</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>2021-04-15</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>2021-04-26</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>2021-05-21</t>
-  </si>
-  <si>
-    <t>2021-05-24</t>
-  </si>
-  <si>
-    <t>2021-05-25</t>
-  </si>
-  <si>
-    <t>2021-05-26</t>
-  </si>
-  <si>
-    <t>2021-05-31</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>2021-06-15</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>2021-06-17</t>
-  </si>
-  <si>
-    <t>2021-06-22</t>
-  </si>
-  <si>
-    <t>2021-06-25</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>2021-07-08</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>2021-07-12</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>2021-07-15</t>
-  </si>
-  <si>
-    <t>2021-07-28</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
   </si>
   <si>
     <t>2016-07-13</t>
@@ -2438,7 +2432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1067"/>
+  <dimension ref="A1:P1069"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2535,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2585,7 +2579,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2635,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2685,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2735,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2785,7 +2779,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2985,7 +2979,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3035,7 +3029,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3085,7 +3079,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3235,7 +3229,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3285,7 +3279,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3635,7 +3629,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3685,7 +3679,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3835,7 +3829,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3885,7 +3879,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3935,7 +3929,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3985,7 +3979,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -4035,7 +4029,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -4085,7 +4079,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4135,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -4185,7 +4179,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4235,7 +4229,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4285,7 +4279,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4335,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4535,7 +4529,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4585,7 +4579,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4635,7 +4629,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4685,7 +4679,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4735,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4785,7 +4779,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4835,7 +4829,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4885,7 +4879,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4935,7 +4929,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4985,7 +4979,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -5035,7 +5029,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -5085,7 +5079,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -5135,7 +5129,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -5185,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -5335,7 +5329,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5385,7 +5379,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5435,7 +5429,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5485,7 +5479,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5535,7 +5529,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5585,7 +5579,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5635,7 +5629,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5785,7 +5779,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5835,7 +5829,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5985,7 +5979,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -6035,7 +6029,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -6085,7 +6079,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -6135,7 +6129,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -6185,7 +6179,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -6235,7 +6229,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6385,7 +6379,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6435,7 +6429,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6485,7 +6479,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6535,7 +6529,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6585,7 +6579,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6635,7 +6629,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6685,7 +6679,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6735,7 +6729,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6785,7 +6779,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6835,7 +6829,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6885,7 +6879,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6935,7 +6929,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6985,7 +6979,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -7235,7 +7229,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -7285,7 +7279,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -7335,7 +7329,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -7485,7 +7479,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -7535,7 +7529,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -9535,7 +9529,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9585,7 +9579,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9635,7 +9629,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -10085,7 +10079,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -10135,7 +10129,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -10185,7 +10179,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -10235,7 +10229,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -10285,7 +10279,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -10485,7 +10479,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10535,7 +10529,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10585,7 +10579,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10785,7 +10779,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10835,7 +10829,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10885,7 +10879,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10935,7 +10929,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -11235,7 +11229,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11285,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11335,7 +11329,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11385,7 +11379,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11435,7 +11429,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11685,7 +11679,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11735,7 +11729,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11785,7 +11779,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11835,7 +11829,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -13235,7 +13229,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -13285,7 +13279,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -13335,7 +13329,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -13385,7 +13379,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13435,7 +13429,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -13485,7 +13479,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -13935,7 +13929,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13985,7 +13979,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -14135,7 +14129,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -14185,7 +14179,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -14235,7 +14229,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -14685,7 +14679,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14735,7 +14729,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14785,7 +14779,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14835,7 +14829,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14885,7 +14879,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -15835,7 +15829,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15885,7 +15879,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15935,7 +15929,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15985,7 +15979,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -16035,7 +16029,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -16085,7 +16079,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -16885,7 +16879,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16935,7 +16929,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16985,7 +16979,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -17035,7 +17029,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -17085,7 +17079,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -17585,7 +17579,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17635,7 +17629,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17685,7 +17679,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17735,7 +17729,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17785,7 +17779,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17835,7 +17829,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17885,7 +17879,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -19385,7 +19379,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19435,7 +19429,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19485,7 +19479,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19535,7 +19529,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19585,7 +19579,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19635,7 +19629,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19685,7 +19679,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -21335,7 +21329,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21385,7 +21379,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21585,7 +21579,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21635,7 +21629,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21685,7 +21679,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21735,7 +21729,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21885,7 +21879,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21935,7 +21929,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21985,7 +21979,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -22135,7 +22129,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -22185,7 +22179,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -22235,7 +22229,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -22485,7 +22479,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22535,7 +22529,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22585,7 +22579,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22635,7 +22629,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22685,7 +22679,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22735,7 +22729,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22785,7 +22779,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22835,7 +22829,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22885,7 +22879,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22935,7 +22929,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22985,7 +22979,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -23035,7 +23029,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -23085,7 +23079,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -23185,7 +23179,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -23235,7 +23229,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23285,7 +23279,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -23335,7 +23329,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -23385,7 +23379,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23435,7 +23429,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23485,7 +23479,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -23535,7 +23529,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23985,7 +23979,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -24035,7 +24029,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -24085,7 +24079,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -24285,7 +24279,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24335,7 +24329,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24385,7 +24379,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24435,7 +24429,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24485,7 +24479,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24535,7 +24529,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24585,7 +24579,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24635,7 +24629,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24685,7 +24679,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24735,7 +24729,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24785,7 +24779,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24835,7 +24829,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24885,7 +24879,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24935,7 +24929,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24985,7 +24979,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -25035,7 +25029,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -25085,7 +25079,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -25135,7 +25129,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25185,7 +25179,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -25235,7 +25229,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -25735,7 +25729,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25785,7 +25779,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25835,7 +25829,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25885,7 +25879,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25935,7 +25929,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -26185,7 +26179,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26235,7 +26229,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26285,7 +26279,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26335,7 +26329,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26385,7 +26379,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -26435,7 +26429,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -26485,7 +26479,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -26535,7 +26529,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26585,7 +26579,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26635,7 +26629,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26685,7 +26679,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26735,7 +26729,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26785,7 +26779,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26835,7 +26829,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -27035,7 +27029,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -27085,7 +27079,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -27135,7 +27129,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -27185,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -27735,7 +27729,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27785,7 +27779,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27835,7 +27829,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27885,7 +27879,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27935,7 +27929,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -28185,7 +28179,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -28235,7 +28229,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -28285,7 +28279,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -28335,7 +28329,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -28535,7 +28529,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28585,7 +28579,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28635,7 +28629,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28685,7 +28679,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28735,7 +28729,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28785,7 +28779,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28835,7 +28829,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -29135,7 +29129,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -29185,7 +29179,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -29235,7 +29229,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29285,7 +29279,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29435,7 +29429,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -29485,7 +29479,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -29535,7 +29529,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29585,7 +29579,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29635,7 +29629,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29785,7 +29779,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29835,7 +29829,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29985,7 +29979,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -30035,7 +30029,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -30085,7 +30079,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -30135,7 +30129,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -30185,7 +30179,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -30235,7 +30229,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30285,7 +30279,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30335,7 +30329,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -30585,7 +30579,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -30635,7 +30629,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30685,7 +30679,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30735,7 +30729,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30785,7 +30779,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30835,7 +30829,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30885,7 +30879,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30935,7 +30929,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30985,7 +30979,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -31035,7 +31029,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -31085,7 +31079,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -31135,7 +31129,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -31185,7 +31179,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -31235,7 +31229,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31285,7 +31279,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31335,7 +31329,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31585,7 +31579,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31635,7 +31629,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31835,7 +31829,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31885,7 +31879,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31935,7 +31929,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31985,7 +31979,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -32035,7 +32029,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -32085,7 +32079,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -32135,7 +32129,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -32185,7 +32179,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -32235,7 +32229,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -32385,7 +32379,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -32435,7 +32429,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32635,7 +32629,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32685,7 +32679,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32885,7 +32879,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32935,7 +32929,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32985,7 +32979,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -33035,7 +33029,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -33085,7 +33079,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -33185,7 +33179,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -33235,7 +33229,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33285,7 +33279,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -33335,7 +33329,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -33585,7 +33579,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33635,7 +33629,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33685,7 +33679,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -34035,7 +34029,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -34085,7 +34079,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -34135,7 +34129,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -35085,7 +35079,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -35135,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -35185,7 +35179,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -35235,7 +35229,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35435,7 +35429,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -35485,7 +35479,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35535,7 +35529,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -36335,7 +36329,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -36385,7 +36379,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36435,7 +36429,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36485,7 +36479,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36535,7 +36529,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36585,7 +36579,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36635,7 +36629,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36685,7 +36679,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36735,7 +36729,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36785,7 +36779,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36835,7 +36829,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36885,7 +36879,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36935,7 +36929,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36985,7 +36979,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -37085,7 +37079,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -37135,7 +37129,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -37185,7 +37179,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -37235,7 +37229,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -37285,7 +37279,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -37335,7 +37329,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -37385,7 +37379,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -37585,7 +37579,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37635,7 +37629,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37685,7 +37679,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -38135,7 +38129,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -38185,7 +38179,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -38235,7 +38229,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -38285,7 +38279,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -38485,7 +38479,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38535,7 +38529,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38585,7 +38579,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38635,7 +38629,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38685,7 +38679,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38735,7 +38729,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38785,7 +38779,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38835,7 +38829,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38885,7 +38879,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38935,7 +38929,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38985,7 +38979,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -39035,7 +39029,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -40035,7 +40029,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -40085,7 +40079,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -40135,7 +40129,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -40185,7 +40179,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -40435,7 +40429,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40485,7 +40479,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40535,7 +40529,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40585,7 +40579,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -40785,7 +40779,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40835,7 +40829,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40885,7 +40879,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40985,7 +40979,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -41335,7 +41329,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -41385,7 +41379,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -41435,7 +41429,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41485,7 +41479,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41535,7 +41529,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41585,7 +41579,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41635,7 +41629,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41685,7 +41679,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41735,7 +41729,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41785,7 +41779,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -42035,7 +42029,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -42085,7 +42079,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -42135,7 +42129,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -42435,7 +42429,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -42485,7 +42479,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42535,7 +42529,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42785,7 +42779,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42835,7 +42829,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42885,7 +42879,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42935,7 +42929,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42985,7 +42979,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -43435,7 +43429,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -43485,7 +43479,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -43585,7 +43579,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -43635,7 +43629,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43685,7 +43679,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43735,7 +43729,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -44885,7 +44879,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44935,7 +44929,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44985,7 +44979,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -45035,7 +45029,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -45085,7 +45079,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -45135,7 +45129,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -45185,7 +45179,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -45235,7 +45229,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -45285,7 +45279,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -46035,7 +46029,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -46085,7 +46079,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -46135,7 +46129,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -46385,7 +46379,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -46435,7 +46429,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -46485,7 +46479,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46535,7 +46529,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46585,7 +46579,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46635,7 +46629,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46685,7 +46679,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46735,7 +46729,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46785,7 +46779,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46835,7 +46829,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46885,7 +46879,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -47085,7 +47079,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -47135,7 +47129,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -47185,7 +47179,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -47385,7 +47379,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -47435,7 +47429,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47485,7 +47479,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -47535,7 +47529,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47585,7 +47579,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47635,7 +47629,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -48535,7 +48529,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48585,7 +48579,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48685,7 +48679,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48735,7 +48729,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48785,7 +48779,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -49085,7 +49079,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -49135,7 +49129,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -49185,7 +49179,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -49235,7 +49229,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -49285,7 +49279,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -49435,7 +49429,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -49535,7 +49529,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49585,7 +49579,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49635,7 +49629,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49785,7 +49779,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49835,7 +49829,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49885,7 +49879,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -50085,7 +50079,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -50135,7 +50129,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -50185,7 +50179,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -50235,7 +50229,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -50285,7 +50279,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50635,7 +50629,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50685,7 +50679,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50735,7 +50729,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50785,7 +50779,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -50985,7 +50979,7 @@
         <v>1</v>
       </c>
       <c r="P971" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="972" spans="1:16">
@@ -51035,7 +51029,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -51535,7 +51529,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51585,7 +51579,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51635,7 +51629,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51685,7 +51679,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51735,7 +51729,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -52135,7 +52129,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -52335,7 +52329,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -52385,7 +52379,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -52435,7 +52429,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -52485,7 +52479,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -53035,7 +53029,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -53085,7 +53079,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -53135,7 +53129,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -53785,7 +53779,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53835,7 +53829,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53885,7 +53879,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -54785,7 +54779,7 @@
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
@@ -54949,7 +54943,7 @@
         <v>2.385066165658595</v>
       </c>
       <c r="D1051" t="s">
-        <v>492</v>
+        <v>255</v>
       </c>
       <c r="E1051">
         <v>2.397054367222326</v>
@@ -54999,7 +54993,7 @@
         <v>2.24487135359287</v>
       </c>
       <c r="D1052" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E1052">
         <v>2.40691738618878</v>
@@ -55046,40 +55040,40 @@
         <v>255</v>
       </c>
       <c r="C1053">
-        <v>0.3510294235212541</v>
+        <v>-0.1907868162761375</v>
       </c>
       <c r="D1053" t="s">
-        <v>258</v>
+        <v>493</v>
       </c>
       <c r="E1053">
-        <v>-0.1586600711828083</v>
+        <v>0.1420545233655446</v>
       </c>
       <c r="F1053">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1053">
-        <v>0.01574897057647875</v>
+        <v>0.01699078681627614</v>
       </c>
       <c r="H1053">
-        <v>0.01505866007118281</v>
+        <v>0.01639794547663445</v>
       </c>
       <c r="I1053">
-        <v>0.5096894947040624</v>
+        <v>0.3328413396416821</v>
       </c>
       <c r="J1053">
         <v>1.12888131619923</v>
       </c>
       <c r="K1053">
-        <v>6.82</v>
+        <v>7.61</v>
       </c>
       <c r="L1053">
-        <v>8.050000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M1053">
-        <v>6.74</v>
+        <v>7.2</v>
       </c>
       <c r="N1053">
-        <v>7.45</v>
+        <v>8.27</v>
       </c>
       <c r="O1053">
         <v>1</v>
@@ -55096,10 +55090,10 @@
         <v>256</v>
       </c>
       <c r="C1054">
-        <v>0.2616036421348911</v>
+        <v>0.3510294235212541</v>
       </c>
       <c r="D1054" t="s">
-        <v>258</v>
+        <v>494</v>
       </c>
       <c r="E1054">
         <v>-0.1586600711828083</v>
@@ -55108,22 +55102,22 @@
         <v>-1</v>
       </c>
       <c r="G1054">
-        <v>0.01459839635786511</v>
+        <v>0.01574897057647875</v>
       </c>
       <c r="H1054">
         <v>0.01505866007118281</v>
       </c>
       <c r="I1054">
-        <v>0.4202637133176994</v>
+        <v>0.5096894947040624</v>
       </c>
       <c r="J1054">
         <v>1.12888131619923</v>
       </c>
       <c r="K1054">
-        <v>6.35</v>
+        <v>6.82</v>
       </c>
       <c r="L1054">
-        <v>7.43</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M1054">
         <v>6.74</v>
@@ -55140,40 +55134,40 @@
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1055" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C1055">
-        <v>0.1371988614513491</v>
+        <v>0.2616036421348911</v>
       </c>
       <c r="D1055" t="s">
-        <v>258</v>
+        <v>494</v>
       </c>
       <c r="E1055">
-        <v>-0.3699823568647957</v>
+        <v>-0.1586600711828083</v>
       </c>
       <c r="F1055">
         <v>-1</v>
       </c>
       <c r="G1055">
-        <v>0.01596280113854865</v>
+        <v>0.01459839635786511</v>
       </c>
       <c r="H1055">
-        <v>0.0152699823568648</v>
+        <v>0.01505866007118281</v>
       </c>
       <c r="I1055">
-        <v>0.5071812183161448</v>
+        <v>0.4202637133176994</v>
       </c>
       <c r="J1055">
-        <v>1.160234771048189</v>
+        <v>1.12888131619923</v>
       </c>
       <c r="K1055">
-        <v>6.82</v>
+        <v>6.35</v>
       </c>
       <c r="L1055">
-        <v>8.050000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="M1055">
         <v>6.74</v>
@@ -55185,51 +55179,51 @@
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>253</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1056" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1056">
-        <v>0.06250920384399805</v>
+        <v>-0.4293866076767205</v>
       </c>
       <c r="D1056" t="s">
-        <v>258</v>
+        <v>493</v>
       </c>
       <c r="E1056">
-        <v>-0.3699823568647957</v>
+        <v>-0.08369035154696292</v>
       </c>
       <c r="F1056">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1056">
-        <v>0.014797490796156</v>
+        <v>0.01722938660767672</v>
       </c>
       <c r="H1056">
-        <v>0.0152699823568648</v>
+        <v>0.01662369035154696</v>
       </c>
       <c r="I1056">
-        <v>0.4324915607087938</v>
+        <v>0.3456962561297576</v>
       </c>
       <c r="J1056">
         <v>1.160234771048189</v>
       </c>
       <c r="K1056">
-        <v>6.35</v>
+        <v>7.61</v>
       </c>
       <c r="L1056">
-        <v>7.43</v>
+        <v>8.4</v>
       </c>
       <c r="M1056">
-        <v>6.74</v>
+        <v>7.2</v>
       </c>
       <c r="N1056">
-        <v>7.45</v>
+        <v>8.27</v>
       </c>
       <c r="O1056">
         <v>1</v>
@@ -55240,40 +55234,40 @@
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1057" t="s">
         <v>256</v>
       </c>
       <c r="C1057">
-        <v>-0.2690824377225765</v>
+        <v>0.1371988614513491</v>
       </c>
       <c r="D1057" t="s">
-        <v>258</v>
+        <v>494</v>
       </c>
       <c r="E1057">
-        <v>-0.7219394693307359</v>
+        <v>-0.3699823568647957</v>
       </c>
       <c r="F1057">
         <v>-1</v>
       </c>
       <c r="G1057">
-        <v>0.01512908243772258</v>
+        <v>0.01596280113854865</v>
       </c>
       <c r="H1057">
-        <v>0.01562193946933074</v>
+        <v>0.0152699823568648</v>
       </c>
       <c r="I1057">
-        <v>0.4528570316081595</v>
+        <v>0.5071812183161448</v>
       </c>
       <c r="J1057">
-        <v>1.212453927200406</v>
+        <v>1.160234771048189</v>
       </c>
       <c r="K1057">
-        <v>6.35</v>
+        <v>6.82</v>
       </c>
       <c r="L1057">
-        <v>7.43</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M1057">
         <v>6.74</v>
@@ -55285,95 +55279,95 @@
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>490</v>
+        <v>253</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1058" t="s">
         <v>257</v>
       </c>
       <c r="C1058">
-        <v>-1.239456852786839</v>
+        <v>0.06250920384399805</v>
       </c>
       <c r="D1058" t="s">
         <v>494</v>
       </c>
       <c r="E1058">
-        <v>-0.9668254588001695</v>
+        <v>-0.3699823568647957</v>
       </c>
       <c r="F1058">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1058">
-        <v>0.01743945685278684</v>
+        <v>0.014797490796156</v>
       </c>
       <c r="H1058">
-        <v>0.01750682545880017</v>
+        <v>0.0152699823568648</v>
       </c>
       <c r="I1058">
-        <v>0.2726313939866696</v>
+        <v>0.4324915607087938</v>
       </c>
       <c r="J1058">
-        <v>1.282892424833357</v>
+        <v>1.160234771048189</v>
       </c>
       <c r="K1058">
-        <v>7.28</v>
+        <v>6.35</v>
       </c>
       <c r="L1058">
-        <v>8.1</v>
+        <v>7.43</v>
       </c>
       <c r="M1058">
-        <v>7.2</v>
+        <v>6.74</v>
       </c>
       <c r="N1058">
-        <v>8.27</v>
+        <v>7.45</v>
       </c>
       <c r="O1058">
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>491</v>
+        <v>253</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1059" t="s">
         <v>256</v>
       </c>
       <c r="C1059">
-        <v>-0.7163668976918167</v>
+        <v>-0.2189357835067671</v>
       </c>
       <c r="D1059" t="s">
-        <v>258</v>
+        <v>494</v>
       </c>
       <c r="E1059">
-        <v>-1.196694943376825</v>
+        <v>-0.7219394693307359</v>
       </c>
       <c r="F1059">
         <v>-1</v>
       </c>
       <c r="G1059">
-        <v>0.01557636689769182</v>
+        <v>0.01631893578350677</v>
       </c>
       <c r="H1059">
-        <v>0.01609669494337683</v>
+        <v>0.01562193946933074</v>
       </c>
       <c r="I1059">
-        <v>0.4803280456850088</v>
+        <v>0.5030036858239688</v>
       </c>
       <c r="J1059">
-        <v>1.282892424833357</v>
+        <v>1.212453927200406</v>
       </c>
       <c r="K1059">
-        <v>6.35</v>
+        <v>6.82</v>
       </c>
       <c r="L1059">
-        <v>7.43</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M1059">
         <v>6.74</v>
@@ -55385,95 +55379,95 @@
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1060" spans="1:16">
       <c r="A1060" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1060" t="s">
         <v>257</v>
       </c>
       <c r="C1060">
-        <v>-1.416234245524462</v>
+        <v>-0.2690824377225765</v>
       </c>
       <c r="D1060" t="s">
         <v>494</v>
       </c>
       <c r="E1060">
-        <v>-1.141660242826392</v>
+        <v>-0.7219394693307359</v>
       </c>
       <c r="F1060">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1060">
-        <v>0.01761623424552446</v>
+        <v>0.01512908243772258</v>
       </c>
       <c r="H1060">
-        <v>0.01768166024282639</v>
+        <v>0.01562193946933074</v>
       </c>
       <c r="I1060">
-        <v>0.2745740026980705</v>
+        <v>0.4528570316081595</v>
       </c>
       <c r="J1060">
-        <v>1.307175033725888</v>
+        <v>1.212453927200406</v>
       </c>
       <c r="K1060">
-        <v>7.28</v>
+        <v>6.35</v>
       </c>
       <c r="L1060">
-        <v>8.1</v>
+        <v>7.43</v>
       </c>
       <c r="M1060">
-        <v>7.2</v>
+        <v>6.74</v>
       </c>
       <c r="N1060">
-        <v>8.27</v>
+        <v>7.45</v>
       </c>
       <c r="O1060">
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
       <c r="A1061" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1061" t="s">
         <v>256</v>
       </c>
       <c r="C1061">
-        <v>-0.8705614641593868</v>
+        <v>-0.6993263373634928</v>
       </c>
       <c r="D1061" t="s">
-        <v>258</v>
+        <v>494</v>
       </c>
       <c r="E1061">
-        <v>-1.360359727312482</v>
+        <v>-1.196694943376825</v>
       </c>
       <c r="F1061">
         <v>-1</v>
       </c>
       <c r="G1061">
-        <v>0.01573056146415939</v>
+        <v>0.0167993263373635</v>
       </c>
       <c r="H1061">
-        <v>0.01626035972731248</v>
+        <v>0.01609669494337683</v>
       </c>
       <c r="I1061">
-        <v>0.4897982631530953</v>
+        <v>0.4973686060133327</v>
       </c>
       <c r="J1061">
-        <v>1.307175033725888</v>
+        <v>1.282892424833357</v>
       </c>
       <c r="K1061">
-        <v>6.35</v>
+        <v>6.82</v>
       </c>
       <c r="L1061">
-        <v>7.43</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M1061">
         <v>6.74</v>
@@ -55485,39 +55479,39 @@
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1062" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1062">
-        <v>-0.9192034028361835</v>
+        <v>-0.7163668976918167</v>
       </c>
       <c r="D1062" t="s">
-        <v>258</v>
+        <v>494</v>
       </c>
       <c r="E1062">
-        <v>-1.411989123640295</v>
+        <v>-1.196694943376825</v>
       </c>
       <c r="F1062">
         <v>-1</v>
       </c>
       <c r="G1062">
-        <v>0.01577920340283618</v>
+        <v>0.01557636689769182</v>
       </c>
       <c r="H1062">
-        <v>0.01631198912364029</v>
+        <v>0.01609669494337683</v>
       </c>
       <c r="I1062">
-        <v>0.492785720804112</v>
+        <v>0.4803280456850088</v>
       </c>
       <c r="J1062">
-        <v>1.314835181549005</v>
+        <v>1.282892424833357</v>
       </c>
       <c r="K1062">
         <v>6.35</v>
@@ -55535,7 +55529,7 @@
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
@@ -55543,31 +55537,31 @@
         <v>0</v>
       </c>
       <c r="B1063" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1063">
-        <v>-0.8831301526583957</v>
+        <v>-0.8705614641593868</v>
       </c>
       <c r="D1063" t="s">
-        <v>258</v>
+        <v>494</v>
       </c>
       <c r="E1063">
-        <v>-1.373700351010643</v>
+        <v>-1.360359727312482</v>
       </c>
       <c r="F1063">
         <v>-1</v>
       </c>
       <c r="G1063">
-        <v>0.01574313015265839</v>
+        <v>0.01573056146415939</v>
       </c>
       <c r="H1063">
-        <v>0.01627370035101064</v>
+        <v>0.01626035972731248</v>
       </c>
       <c r="I1063">
-        <v>0.4905701983522475</v>
+        <v>0.4897982631530953</v>
       </c>
       <c r="J1063">
-        <v>1.309154354749354</v>
+        <v>1.307175033725888</v>
       </c>
       <c r="K1063">
         <v>6.35</v>
@@ -55585,7 +55579,7 @@
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
@@ -55593,49 +55587,49 @@
         <v>0</v>
       </c>
       <c r="B1064" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C1064">
-        <v>-0.4151176269632382</v>
+        <v>-1.472000121676759</v>
       </c>
       <c r="D1064" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E1064">
-        <v>-0.6204353661828428</v>
+        <v>-1.196813307152839</v>
       </c>
       <c r="F1064">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1064">
-        <v>0.01527511762696324</v>
+        <v>0.01767200012167676</v>
       </c>
       <c r="H1064">
-        <v>0.01544043536618284</v>
+        <v>0.01773681330715283</v>
       </c>
       <c r="I1064">
-        <v>0.2053177392196046</v>
+        <v>0.27518681452392</v>
       </c>
       <c r="J1064">
-        <v>1.23545159479736</v>
+        <v>1.314835181549005</v>
       </c>
       <c r="K1064">
-        <v>6.35</v>
+        <v>7.28</v>
       </c>
       <c r="L1064">
-        <v>7.43</v>
+        <v>8.1</v>
       </c>
       <c r="M1064">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="N1064">
-        <v>7.41</v>
+        <v>8.27</v>
       </c>
       <c r="O1064">
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>255</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
@@ -55643,49 +55637,49 @@
         <v>1</v>
       </c>
       <c r="B1065" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C1065">
-        <v>-0.8769437489342087</v>
+        <v>-0.9192034028361835</v>
       </c>
       <c r="D1065" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E1065">
-        <v>-0.6428166532463662</v>
+        <v>-1.411989123640295</v>
       </c>
       <c r="F1065">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1065">
-        <v>0.01577694374893421</v>
+        <v>0.01577920340283618</v>
       </c>
       <c r="H1065">
-        <v>0.01586281665324637</v>
+        <v>0.01631198912364029</v>
       </c>
       <c r="I1065">
-        <v>0.2341270956878425</v>
+        <v>0.492785720804112</v>
       </c>
       <c r="J1065">
-        <v>1.23545159479736</v>
+        <v>1.314835181549005</v>
       </c>
       <c r="K1065">
+        <v>6.35</v>
+      </c>
+      <c r="L1065">
+        <v>7.43</v>
+      </c>
+      <c r="M1065">
         <v>6.74</v>
       </c>
-      <c r="L1065">
+      <c r="N1065">
         <v>7.45</v>
       </c>
-      <c r="M1065">
-        <v>6.68</v>
-      </c>
-      <c r="N1065">
-        <v>7.61</v>
-      </c>
       <c r="O1065">
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>255</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
@@ -55693,31 +55687,31 @@
         <v>0</v>
       </c>
       <c r="B1066" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1066">
-        <v>-0.1604084353129611</v>
+        <v>-0.8831301526583957</v>
       </c>
       <c r="D1066" t="s">
-        <v>258</v>
+        <v>494</v>
       </c>
       <c r="E1066">
-        <v>-0.6065910006313944</v>
+        <v>-1.373700351010643</v>
       </c>
       <c r="F1066">
         <v>-1</v>
       </c>
       <c r="G1066">
-        <v>0.01502040843531296</v>
+        <v>0.01574313015265839</v>
       </c>
       <c r="H1066">
-        <v>0.0155065910006314</v>
+        <v>0.01627370035101064</v>
       </c>
       <c r="I1066">
-        <v>0.4461825653184333</v>
+        <v>0.4905701983522475</v>
       </c>
       <c r="J1066">
-        <v>1.195339911072907</v>
+        <v>1.309154354749354</v>
       </c>
       <c r="K1066">
         <v>6.35</v>
@@ -55735,7 +55729,7 @@
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>687</v>
+        <v>258</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
@@ -55743,31 +55737,31 @@
         <v>0</v>
       </c>
       <c r="B1067" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1067">
-        <v>-0.1949390005542107</v>
+        <v>-0.4151176269632382</v>
       </c>
       <c r="D1067" t="s">
-        <v>258</v>
+        <v>494</v>
       </c>
       <c r="E1067">
-        <v>-0.6432423407457284</v>
+        <v>-0.8769437489342087</v>
       </c>
       <c r="F1067">
         <v>-1</v>
       </c>
       <c r="G1067">
-        <v>0.01505493900055421</v>
+        <v>0.01527511762696324</v>
       </c>
       <c r="H1067">
-        <v>0.01554324234074573</v>
+        <v>0.01577694374893421</v>
       </c>
       <c r="I1067">
-        <v>0.4483033401915177</v>
+        <v>0.4618261219709705</v>
       </c>
       <c r="J1067">
-        <v>1.200777795362868</v>
+        <v>1.23545159479736</v>
       </c>
       <c r="K1067">
         <v>6.35</v>
@@ -55785,7 +55779,107 @@
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>688</v>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:16">
+      <c r="A1068" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1068" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1068">
+        <v>-0.1604084353129611</v>
+      </c>
+      <c r="D1068" t="s">
+        <v>494</v>
+      </c>
+      <c r="E1068">
+        <v>-0.6065910006313944</v>
+      </c>
+      <c r="F1068">
+        <v>-1</v>
+      </c>
+      <c r="G1068">
+        <v>0.01502040843531296</v>
+      </c>
+      <c r="H1068">
+        <v>0.0155065910006314</v>
+      </c>
+      <c r="I1068">
+        <v>0.4461825653184333</v>
+      </c>
+      <c r="J1068">
+        <v>1.195339911072907</v>
+      </c>
+      <c r="K1068">
+        <v>6.35</v>
+      </c>
+      <c r="L1068">
+        <v>7.43</v>
+      </c>
+      <c r="M1068">
+        <v>6.74</v>
+      </c>
+      <c r="N1068">
+        <v>7.45</v>
+      </c>
+      <c r="O1068">
+        <v>1</v>
+      </c>
+      <c r="P1068" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:16">
+      <c r="A1069" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1069" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1069">
+        <v>-0.1949390005542107</v>
+      </c>
+      <c r="D1069" t="s">
+        <v>494</v>
+      </c>
+      <c r="E1069">
+        <v>-0.6432423407457284</v>
+      </c>
+      <c r="F1069">
+        <v>-1</v>
+      </c>
+      <c r="G1069">
+        <v>0.01505493900055421</v>
+      </c>
+      <c r="H1069">
+        <v>0.01554324234074573</v>
+      </c>
+      <c r="I1069">
+        <v>0.4483033401915177</v>
+      </c>
+      <c r="J1069">
+        <v>1.200777795362868</v>
+      </c>
+      <c r="K1069">
+        <v>6.35</v>
+      </c>
+      <c r="L1069">
+        <v>7.43</v>
+      </c>
+      <c r="M1069">
+        <v>6.74</v>
+      </c>
+      <c r="N1069">
+        <v>7.45</v>
+      </c>
+      <c r="O1069">
+        <v>1</v>
+      </c>
+      <c r="P1069" t="s">
+        <v>686</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -55437,10 +55437,10 @@
         <v>0</v>
       </c>
       <c r="B1061" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1061">
-        <v>-0.6993263373634928</v>
+        <v>-0.7163668976918167</v>
       </c>
       <c r="D1061" t="s">
         <v>494</v>
@@ -55452,22 +55452,22 @@
         <v>-1</v>
       </c>
       <c r="G1061">
-        <v>0.0167993263373635</v>
+        <v>0.01557636689769182</v>
       </c>
       <c r="H1061">
         <v>0.01609669494337683</v>
       </c>
       <c r="I1061">
-        <v>0.4973686060133327</v>
+        <v>0.4803280456850088</v>
       </c>
       <c r="J1061">
         <v>1.282892424833357</v>
       </c>
       <c r="K1061">
-        <v>6.82</v>
+        <v>6.35</v>
       </c>
       <c r="L1061">
-        <v>8.050000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="M1061">
         <v>6.74</v>
@@ -55484,57 +55484,57 @@
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1062" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1062">
-        <v>-0.7163668976918167</v>
+        <v>-1.416234245524462</v>
       </c>
       <c r="D1062" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E1062">
-        <v>-1.196694943376825</v>
+        <v>-1.141660242826392</v>
       </c>
       <c r="F1062">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1062">
-        <v>0.01557636689769182</v>
+        <v>0.01761623424552446</v>
       </c>
       <c r="H1062">
-        <v>0.01609669494337683</v>
+        <v>0.01768166024282639</v>
       </c>
       <c r="I1062">
-        <v>0.4803280456850088</v>
+        <v>0.2745740026980705</v>
       </c>
       <c r="J1062">
-        <v>1.282892424833357</v>
+        <v>1.307175033725888</v>
       </c>
       <c r="K1062">
-        <v>6.35</v>
+        <v>7.28</v>
       </c>
       <c r="L1062">
-        <v>7.43</v>
+        <v>8.1</v>
       </c>
       <c r="M1062">
-        <v>6.74</v>
+        <v>7.2</v>
       </c>
       <c r="N1062">
-        <v>7.45</v>
+        <v>8.27</v>
       </c>
       <c r="O1062">
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>491</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1063" t="s">
         <v>257</v>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3294" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3294" uniqueCount="703">
   <si>
     <t>trade_time</t>
   </si>
@@ -1532,6 +1532,9 @@
   </si>
   <si>
     <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>2021-08-25</t>
   </si>
   <si>
     <t>2021-08-18</t>
@@ -2574,7 +2577,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2624,7 +2627,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2674,7 +2677,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2724,7 +2727,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2774,7 +2777,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2824,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -3024,7 +3027,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3074,7 +3077,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3124,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3274,7 +3277,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3324,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3674,7 +3677,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3724,7 +3727,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3874,7 +3877,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3924,7 +3927,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3974,7 +3977,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -4024,7 +4027,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -4074,7 +4077,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -4124,7 +4127,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4174,7 +4177,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -4224,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4274,7 +4277,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4324,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4374,7 +4377,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4574,7 +4577,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4624,7 +4627,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4674,7 +4677,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4724,7 +4727,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4774,7 +4777,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4824,7 +4827,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4874,7 +4877,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4924,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4974,7 +4977,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -5024,7 +5027,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -5074,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -5124,7 +5127,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -5174,7 +5177,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -5224,7 +5227,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -5374,7 +5377,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5424,7 +5427,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5474,7 +5477,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5524,7 +5527,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5574,7 +5577,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5624,7 +5627,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5674,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5824,7 +5827,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5874,7 +5877,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -6024,7 +6027,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -6074,7 +6077,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -6124,7 +6127,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -6174,7 +6177,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -6224,7 +6227,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -6274,7 +6277,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6424,7 +6427,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6474,7 +6477,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6524,7 +6527,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6574,7 +6577,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6624,7 +6627,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6674,7 +6677,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6724,7 +6727,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6774,7 +6777,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6824,7 +6827,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6874,7 +6877,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6924,7 +6927,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6974,7 +6977,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -7024,7 +7027,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -7274,7 +7277,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -7324,7 +7327,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -7374,7 +7377,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -7524,7 +7527,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -7574,7 +7577,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -9574,7 +9577,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9624,7 +9627,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9674,7 +9677,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -10124,7 +10127,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -10174,7 +10177,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -10224,7 +10227,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -10274,7 +10277,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -10324,7 +10327,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -10524,7 +10527,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10574,7 +10577,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10624,7 +10627,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10824,7 +10827,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10874,7 +10877,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10924,7 +10927,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10974,7 +10977,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -11274,7 +11277,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11324,7 +11327,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11374,7 +11377,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11424,7 +11427,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11474,7 +11477,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11724,7 +11727,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11774,7 +11777,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11824,7 +11827,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11874,7 +11877,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -13274,7 +13277,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -13324,7 +13327,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -13374,7 +13377,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -13424,7 +13427,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13474,7 +13477,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -13524,7 +13527,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -13974,7 +13977,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -14024,7 +14027,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -14174,7 +14177,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -14224,7 +14227,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -14274,7 +14277,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -14724,7 +14727,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14774,7 +14777,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14824,7 +14827,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14874,7 +14877,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14924,7 +14927,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -15874,7 +15877,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15924,7 +15927,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15974,7 +15977,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -16024,7 +16027,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -16074,7 +16077,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -16124,7 +16127,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -16924,7 +16927,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16974,7 +16977,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -17024,7 +17027,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -17074,7 +17077,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -17124,7 +17127,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -17624,7 +17627,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17674,7 +17677,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17724,7 +17727,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17774,7 +17777,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17824,7 +17827,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17874,7 +17877,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17924,7 +17927,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -19424,7 +19427,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19474,7 +19477,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19524,7 +19527,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19574,7 +19577,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19624,7 +19627,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19674,7 +19677,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19724,7 +19727,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -21374,7 +21377,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21424,7 +21427,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21624,7 +21627,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21674,7 +21677,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21724,7 +21727,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21774,7 +21777,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21924,7 +21927,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21974,7 +21977,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -22024,7 +22027,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -22174,7 +22177,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -22224,7 +22227,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -22274,7 +22277,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -22524,7 +22527,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22574,7 +22577,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22624,7 +22627,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22674,7 +22677,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22724,7 +22727,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22774,7 +22777,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22824,7 +22827,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22874,7 +22877,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22924,7 +22927,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22974,7 +22977,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -23024,7 +23027,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -23074,7 +23077,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -23124,7 +23127,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -23224,7 +23227,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -23274,7 +23277,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23324,7 +23327,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -23374,7 +23377,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -23424,7 +23427,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23474,7 +23477,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23524,7 +23527,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -23574,7 +23577,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -24024,7 +24027,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -24074,7 +24077,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -24124,7 +24127,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -24324,7 +24327,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24374,7 +24377,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24424,7 +24427,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24474,7 +24477,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24524,7 +24527,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24574,7 +24577,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24624,7 +24627,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24674,7 +24677,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24724,7 +24727,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24774,7 +24777,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24824,7 +24827,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24874,7 +24877,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24924,7 +24927,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24974,7 +24977,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -25024,7 +25027,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -25074,7 +25077,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -25124,7 +25127,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -25174,7 +25177,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25224,7 +25227,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -25274,7 +25277,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -25774,7 +25777,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25824,7 +25827,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25874,7 +25877,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25924,7 +25927,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25974,7 +25977,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -26224,7 +26227,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26274,7 +26277,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26324,7 +26327,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26374,7 +26377,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26424,7 +26427,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -26474,7 +26477,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -26524,7 +26527,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -26574,7 +26577,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26624,7 +26627,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26674,7 +26677,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26724,7 +26727,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26774,7 +26777,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26824,7 +26827,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26874,7 +26877,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -27074,7 +27077,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -27124,7 +27127,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -27174,7 +27177,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -27224,7 +27227,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -27774,7 +27777,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27824,7 +27827,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27874,7 +27877,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27924,7 +27927,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27974,7 +27977,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -28224,7 +28227,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -28274,7 +28277,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -28324,7 +28327,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -28374,7 +28377,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -28574,7 +28577,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28624,7 +28627,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28674,7 +28677,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28724,7 +28727,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28774,7 +28777,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28824,7 +28827,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28874,7 +28877,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -29174,7 +29177,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -29224,7 +29227,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -29274,7 +29277,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29324,7 +29327,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29474,7 +29477,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -29524,7 +29527,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -29574,7 +29577,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29624,7 +29627,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29674,7 +29677,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29824,7 +29827,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29874,7 +29877,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -30024,7 +30027,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -30074,7 +30077,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -30124,7 +30127,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -30174,7 +30177,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -30224,7 +30227,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -30274,7 +30277,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30324,7 +30327,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30374,7 +30377,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -30624,7 +30627,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -30674,7 +30677,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30724,7 +30727,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30774,7 +30777,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30824,7 +30827,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30874,7 +30877,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30924,7 +30927,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30974,7 +30977,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -31024,7 +31027,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -31074,7 +31077,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -31124,7 +31127,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -31174,7 +31177,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -31224,7 +31227,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -31274,7 +31277,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31324,7 +31327,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31374,7 +31377,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31624,7 +31627,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31674,7 +31677,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31874,7 +31877,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31924,7 +31927,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31974,7 +31977,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -32024,7 +32027,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -32074,7 +32077,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -32124,7 +32127,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -32174,7 +32177,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -32224,7 +32227,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -32274,7 +32277,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -32424,7 +32427,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -32474,7 +32477,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32674,7 +32677,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32724,7 +32727,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32924,7 +32927,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32974,7 +32977,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -33024,7 +33027,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -33074,7 +33077,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -33124,7 +33127,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -33224,7 +33227,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -33274,7 +33277,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33324,7 +33327,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -33374,7 +33377,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -33624,7 +33627,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33674,7 +33677,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33724,7 +33727,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -34074,7 +34077,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -34124,7 +34127,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -34174,7 +34177,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -35124,7 +35127,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -35174,7 +35177,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -35224,7 +35227,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -35274,7 +35277,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35474,7 +35477,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -35524,7 +35527,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35574,7 +35577,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -36374,7 +36377,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -36424,7 +36427,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36474,7 +36477,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36524,7 +36527,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36574,7 +36577,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36624,7 +36627,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36674,7 +36677,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36724,7 +36727,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36774,7 +36777,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36824,7 +36827,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36874,7 +36877,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36924,7 +36927,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36974,7 +36977,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -37024,7 +37027,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -37124,7 +37127,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -37174,7 +37177,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -37224,7 +37227,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -37274,7 +37277,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -37324,7 +37327,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -37374,7 +37377,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -37424,7 +37427,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -37624,7 +37627,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37674,7 +37677,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37724,7 +37727,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -38174,7 +38177,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -38224,7 +38227,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -38274,7 +38277,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -38324,7 +38327,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -38524,7 +38527,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38574,7 +38577,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38624,7 +38627,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38674,7 +38677,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38724,7 +38727,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38774,7 +38777,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38824,7 +38827,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38874,7 +38877,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38924,7 +38927,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38974,7 +38977,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -39024,7 +39027,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -39074,7 +39077,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -40074,7 +40077,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -40124,7 +40127,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -40174,7 +40177,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -40224,7 +40227,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -40474,7 +40477,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40524,7 +40527,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40574,7 +40577,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40624,7 +40627,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -40824,7 +40827,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40874,7 +40877,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40924,7 +40927,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -41024,7 +41027,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -41374,7 +41377,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -41424,7 +41427,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -41474,7 +41477,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41524,7 +41527,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41574,7 +41577,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41624,7 +41627,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41674,7 +41677,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41724,7 +41727,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41774,7 +41777,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41824,7 +41827,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -42074,7 +42077,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -42124,7 +42127,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -42174,7 +42177,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -42474,7 +42477,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -42524,7 +42527,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42574,7 +42577,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42824,7 +42827,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42874,7 +42877,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42924,7 +42927,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42974,7 +42977,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -43024,7 +43027,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -43474,7 +43477,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -43524,7 +43527,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -43624,7 +43627,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -43674,7 +43677,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43724,7 +43727,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43774,7 +43777,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -44924,7 +44927,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44974,7 +44977,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -45024,7 +45027,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -45074,7 +45077,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -45124,7 +45127,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -45174,7 +45177,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -45224,7 +45227,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -45274,7 +45277,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -45324,7 +45327,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -46074,7 +46077,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -46124,7 +46127,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -46174,7 +46177,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -46424,7 +46427,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -46474,7 +46477,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -46524,7 +46527,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46574,7 +46577,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46624,7 +46627,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46674,7 +46677,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46724,7 +46727,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46774,7 +46777,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46824,7 +46827,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46874,7 +46877,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46924,7 +46927,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -47124,7 +47127,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -47174,7 +47177,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -47224,7 +47227,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -47424,7 +47427,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -47474,7 +47477,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47524,7 +47527,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -47574,7 +47577,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47624,7 +47627,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47674,7 +47677,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -48574,7 +48577,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48624,7 +48627,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48724,7 +48727,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48774,7 +48777,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48824,7 +48827,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -49124,7 +49127,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -49174,7 +49177,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -49224,7 +49227,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -49274,7 +49277,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -49324,7 +49327,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -49474,7 +49477,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -49574,7 +49577,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49624,7 +49627,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49674,7 +49677,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49824,7 +49827,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49874,7 +49877,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49924,7 +49927,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -50124,7 +50127,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -50174,7 +50177,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -50224,7 +50227,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -50274,7 +50277,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -50324,7 +50327,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50674,7 +50677,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50724,7 +50727,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50774,7 +50777,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50824,7 +50827,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -51024,7 +51027,7 @@
         <v>1</v>
       </c>
       <c r="P971" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="972" spans="1:16">
@@ -51074,7 +51077,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -51574,7 +51577,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51624,7 +51627,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51674,7 +51677,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51724,7 +51727,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51774,7 +51777,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -52174,7 +52177,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -52374,7 +52377,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -52424,7 +52427,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -52474,7 +52477,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -52524,7 +52527,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -53074,7 +53077,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -53124,7 +53127,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -53174,7 +53177,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -53824,7 +53827,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53874,7 +53877,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53924,7 +53927,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -54824,7 +54827,7 @@
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
@@ -56174,7 +56177,7 @@
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
@@ -56224,7 +56227,7 @@
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
@@ -56332,43 +56335,43 @@
         <v>2</v>
       </c>
       <c r="B1078" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C1078">
-        <v>-0.5422116573189051</v>
+        <v>-0.6153246883006815</v>
       </c>
       <c r="D1078" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E1078">
-        <v>-0.6345073136583128</v>
+        <v>-0.8597595333917987</v>
       </c>
       <c r="F1078">
         <v>-1</v>
       </c>
       <c r="G1078">
-        <v>0.0169422116573189</v>
+        <v>0.01679532468830068</v>
       </c>
       <c r="H1078">
-        <v>0.01687450731365831</v>
+        <v>0.0169197595333918</v>
       </c>
       <c r="I1078">
-        <v>0.09229565633940773</v>
+        <v>0.2444348450911171</v>
       </c>
       <c r="J1078">
         <v>1.229565633940774</v>
       </c>
       <c r="K1078">
-        <v>7.11</v>
+        <v>7.08</v>
       </c>
       <c r="L1078">
-        <v>8.199999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="M1078">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
       <c r="N1078">
-        <v>8.119999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O1078">
         <v>1</v>
@@ -56438,10 +56441,10 @@
         <v>-0.4044242740522641</v>
       </c>
       <c r="D1080" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E1080">
-        <v>-0.4965261366036735</v>
+        <v>-0.7196466246691795</v>
       </c>
       <c r="F1080">
         <v>-1</v>
@@ -56450,10 +56453,10 @@
         <v>0.01680442427405226</v>
       </c>
       <c r="H1080">
-        <v>0.01673652613660367</v>
+        <v>0.01677964662466918</v>
       </c>
       <c r="I1080">
-        <v>0.0921018625514094</v>
+        <v>0.3152223506169154</v>
       </c>
       <c r="J1080">
         <v>1.210186255140965</v>
@@ -56465,10 +56468,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M1080">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
       <c r="N1080">
-        <v>8.119999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O1080">
         <v>1</v>
@@ -56538,10 +56541,10 @@
         <v>-0.3352256931637765</v>
       </c>
       <c r="D1082" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E1082">
-        <v>-0.3528258383228948</v>
+        <v>-0.5737262375104688</v>
       </c>
       <c r="F1082">
         <v>-1</v>
@@ -56550,10 +56553,10 @@
         <v>0.01651522569316378</v>
       </c>
       <c r="H1082">
-        <v>0.0165928258383229</v>
+        <v>0.01663372623751047</v>
       </c>
       <c r="I1082">
-        <v>0.01760014515911834</v>
+        <v>0.2385005443466923</v>
       </c>
       <c r="J1082">
         <v>1.190003628977935</v>
@@ -56565,10 +56568,10 @@
         <v>8.09</v>
       </c>
       <c r="M1082">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
       <c r="N1082">
-        <v>8.119999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O1082">
         <v>1</v>
@@ -56624,7 +56627,7 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56638,10 +56641,10 @@
         <v>-0.2869595134011824</v>
       </c>
       <c r="D1084" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E1084">
-        <v>-0.3788961653187641</v>
+        <v>-0.6001993364121727</v>
       </c>
       <c r="F1084">
         <v>-1</v>
@@ -56650,10 +56653,10 @@
         <v>0.01668695951340118</v>
       </c>
       <c r="H1084">
-        <v>0.01661889616531876</v>
+        <v>0.01666019933641217</v>
       </c>
       <c r="I1084">
-        <v>0.09193665191758171</v>
+        <v>0.3132398230109903</v>
       </c>
       <c r="J1084">
         <v>1.193665191758253</v>
@@ -56665,16 +56668,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M1084">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
       <c r="N1084">
-        <v>8.119999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O1084">
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56724,7 +56727,7 @@
         <v>1</v>
       </c>
       <c r="P1085" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="1086" spans="1:16">
@@ -56738,10 +56741,10 @@
         <v>-0.1669472197411892</v>
       </c>
       <c r="D1086" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E1086">
-        <v>-0.2587150779968024</v>
+        <v>-0.4781615188085517</v>
       </c>
       <c r="F1086">
         <v>-1</v>
@@ -56750,10 +56753,10 @@
         <v>0.01656694721974119</v>
       </c>
       <c r="H1086">
-        <v>0.0164987150779968</v>
+        <v>0.01653816151880855</v>
       </c>
       <c r="I1086">
-        <v>0.09176785825561318</v>
+        <v>0.3112142990673625</v>
       </c>
       <c r="J1086">
         <v>1.176785825561349</v>
@@ -56765,16 +56768,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M1086">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
       <c r="N1086">
-        <v>8.119999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O1086">
         <v>1</v>
       </c>
       <c r="P1086" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="1087" spans="1:16">
@@ -56788,10 +56791,10 @@
         <v>-0.02918843275758931</v>
       </c>
       <c r="D1087" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E1087">
-        <v>-0.1207625374450121</v>
+        <v>-0.3380776890066617</v>
       </c>
       <c r="F1087">
         <v>-1</v>
@@ -56800,10 +56803,10 @@
         <v>0.01642918843275759</v>
       </c>
       <c r="H1087">
-        <v>0.01636076253744501</v>
+        <v>0.01639807768900666</v>
       </c>
       <c r="I1087">
-        <v>0.09157410468742277</v>
+        <v>0.3088892562490724</v>
       </c>
       <c r="J1087">
         <v>1.157410468742277</v>
@@ -56815,10 +56818,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M1087">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
       <c r="N1087">
-        <v>8.119999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O1087">
         <v>1</v>
@@ -56838,7 +56841,7 @@
         <v>-0.6487169745185035</v>
       </c>
       <c r="D1088" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E1088">
         <v>-0.1177872849157779</v>
@@ -56874,7 +56877,7 @@
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56888,10 +56891,10 @@
         <v>0.02588252599162821</v>
       </c>
       <c r="D1089" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E1089">
-        <v>0.01032254026276647</v>
+        <v>-0.2049674204916005</v>
       </c>
       <c r="F1089">
         <v>-1</v>
@@ -56900,10 +56903,10 @@
         <v>0.01615411747400837</v>
       </c>
       <c r="H1089">
-        <v>0.01622967745973723</v>
+        <v>0.0162649674204916</v>
       </c>
       <c r="I1089">
-        <v>0.01555998572886175</v>
+        <v>0.2308499464832288</v>
       </c>
       <c r="J1089">
         <v>1.138999643221521</v>
@@ -56915,16 +56918,16 @@
         <v>8.09</v>
       </c>
       <c r="M1089">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
       <c r="N1089">
-        <v>8.119999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O1089">
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -56938,7 +56941,7 @@
         <v>-0.3941793682350347</v>
       </c>
       <c r="D1090" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E1090">
         <v>0.11063620374191</v>
@@ -56974,7 +56977,7 @@
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -56988,10 +56991,10 @@
         <v>0.2383974142565988</v>
       </c>
       <c r="D1091" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E1091">
-        <v>0.2240380776139794</v>
+        <v>0.01204990184677968</v>
       </c>
       <c r="F1091">
         <v>-1</v>
@@ -57000,10 +57003,10 @@
         <v>0.0159416025857434</v>
       </c>
       <c r="H1091">
-        <v>0.01601596192238602</v>
+        <v>0.01604795009815322</v>
       </c>
       <c r="I1091">
-        <v>0.01435933664261935</v>
+        <v>0.2263475124098191</v>
       </c>
       <c r="J1091">
         <v>1.108983416065452</v>
@@ -57015,16 +57018,16 @@
         <v>8.09</v>
       </c>
       <c r="M1091">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
       <c r="N1091">
-        <v>8.119999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O1091">
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
@@ -57038,7 +57041,7 @@
         <v>-0.2536665708087877</v>
       </c>
       <c r="D1092" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E1092">
         <v>0.2367331835076811</v>
@@ -57088,10 +57091,10 @@
         <v>0.3557123441832299</v>
       </c>
       <c r="D1093" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E1093">
-        <v>0.3420158037548857</v>
+        <v>0.1318503175769417</v>
       </c>
       <c r="F1093">
         <v>-1</v>
@@ -57100,10 +57103,10 @@
         <v>0.01582428765581677</v>
       </c>
       <c r="H1093">
-        <v>0.01589798419624511</v>
+        <v>0.01592814968242306</v>
       </c>
       <c r="I1093">
-        <v>0.01369654042834423</v>
+        <v>0.2238620266062883</v>
       </c>
       <c r="J1093">
         <v>1.092413510708583</v>
@@ -57115,10 +57118,10 @@
         <v>8.09</v>
       </c>
       <c r="M1093">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
       <c r="N1093">
-        <v>8.119999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O1093">
         <v>1</v>
@@ -57138,10 +57141,10 @@
         <v>0.6509480614049288</v>
       </c>
       <c r="D1094" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E1094">
-        <v>0.6389195193789678</v>
+        <v>0.4333410288075754</v>
       </c>
       <c r="F1094">
         <v>-1</v>
@@ -57150,10 +57153,10 @@
         <v>0.01552905193859507</v>
       </c>
       <c r="H1094">
-        <v>0.01560108048062103</v>
+        <v>0.01562665897119242</v>
       </c>
       <c r="I1094">
-        <v>0.01202854202596093</v>
+        <v>0.2176070325973534</v>
       </c>
       <c r="J1094">
         <v>1.050713550649021</v>
@@ -57165,10 +57168,10 @@
         <v>8.09</v>
       </c>
       <c r="M1094">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
       <c r="N1094">
-        <v>8.119999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O1094">
         <v>1</v>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3294" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3291" uniqueCount="704">
   <si>
     <t>trade_time</t>
   </si>
@@ -1535,6 +1535,9 @@
   </si>
   <si>
     <t>2021-08-25</t>
+  </si>
+  <si>
+    <t>2021-08-26</t>
   </si>
   <si>
     <t>2021-08-18</t>
@@ -2480,7 +2483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1094"/>
+  <dimension ref="A1:P1093"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2577,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2627,7 +2630,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2677,7 +2680,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2727,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2777,7 +2780,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2827,7 +2830,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -3027,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3077,7 +3080,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3127,7 +3130,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3277,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3327,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3677,7 +3680,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3727,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3877,7 +3880,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3927,7 +3930,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3977,7 +3980,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -4027,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -4077,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -4127,7 +4130,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4177,7 +4180,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -4227,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4277,7 +4280,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4327,7 +4330,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4377,7 +4380,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4577,7 +4580,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4627,7 +4630,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4677,7 +4680,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4727,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4777,7 +4780,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4827,7 +4830,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4877,7 +4880,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4927,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4977,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -5027,7 +5030,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -5077,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -5127,7 +5130,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -5177,7 +5180,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -5227,7 +5230,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -5377,7 +5380,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5427,7 +5430,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5477,7 +5480,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5527,7 +5530,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5577,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5627,7 +5630,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5677,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5827,7 +5830,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5877,7 +5880,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -6027,7 +6030,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -6077,7 +6080,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -6127,7 +6130,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -6177,7 +6180,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -6227,7 +6230,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -6277,7 +6280,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6427,7 +6430,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6477,7 +6480,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6527,7 +6530,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6577,7 +6580,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6627,7 +6630,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6677,7 +6680,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6727,7 +6730,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6777,7 +6780,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6827,7 +6830,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6877,7 +6880,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6927,7 +6930,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6977,7 +6980,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -7027,7 +7030,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -7277,7 +7280,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -7327,7 +7330,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -7377,7 +7380,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -7527,7 +7530,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -7577,7 +7580,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -9577,7 +9580,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9627,7 +9630,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9677,7 +9680,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -10127,7 +10130,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -10177,7 +10180,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -10227,7 +10230,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -10277,7 +10280,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -10327,7 +10330,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -10527,7 +10530,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10577,7 +10580,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10627,7 +10630,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10827,7 +10830,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10877,7 +10880,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10927,7 +10930,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10977,7 +10980,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -11277,7 +11280,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11327,7 +11330,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11377,7 +11380,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11427,7 +11430,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11477,7 +11480,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11727,7 +11730,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11777,7 +11780,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11827,7 +11830,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11877,7 +11880,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -13277,7 +13280,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -13327,7 +13330,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -13377,7 +13380,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -13427,7 +13430,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13477,7 +13480,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -13527,7 +13530,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -13977,7 +13980,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -14027,7 +14030,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -14177,7 +14180,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -14227,7 +14230,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -14277,7 +14280,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -14727,7 +14730,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14777,7 +14780,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14827,7 +14830,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14877,7 +14880,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14927,7 +14930,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -15877,7 +15880,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15927,7 +15930,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15977,7 +15980,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -16027,7 +16030,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -16077,7 +16080,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -16127,7 +16130,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -16927,7 +16930,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16977,7 +16980,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -17027,7 +17030,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -17077,7 +17080,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -17127,7 +17130,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -17627,7 +17630,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17677,7 +17680,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17727,7 +17730,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17777,7 +17780,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17827,7 +17830,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17877,7 +17880,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17927,7 +17930,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -19427,7 +19430,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19477,7 +19480,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19527,7 +19530,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19577,7 +19580,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19627,7 +19630,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19677,7 +19680,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19727,7 +19730,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -21377,7 +21380,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21427,7 +21430,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21627,7 +21630,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21677,7 +21680,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21727,7 +21730,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21777,7 +21780,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21927,7 +21930,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21977,7 +21980,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -22027,7 +22030,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -22177,7 +22180,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -22227,7 +22230,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -22277,7 +22280,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -22527,7 +22530,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22577,7 +22580,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22627,7 +22630,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22677,7 +22680,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22727,7 +22730,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22777,7 +22780,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22827,7 +22830,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22877,7 +22880,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22927,7 +22930,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22977,7 +22980,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -23027,7 +23030,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -23077,7 +23080,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -23127,7 +23130,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -23227,7 +23230,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -23277,7 +23280,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23327,7 +23330,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -23377,7 +23380,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -23427,7 +23430,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23477,7 +23480,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23527,7 +23530,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -23577,7 +23580,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -24027,7 +24030,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -24077,7 +24080,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -24127,7 +24130,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -24327,7 +24330,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24377,7 +24380,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24427,7 +24430,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24477,7 +24480,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24527,7 +24530,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24577,7 +24580,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24627,7 +24630,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24677,7 +24680,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24727,7 +24730,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24777,7 +24780,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24827,7 +24830,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24877,7 +24880,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24927,7 +24930,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24977,7 +24980,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -25027,7 +25030,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -25077,7 +25080,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -25127,7 +25130,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -25177,7 +25180,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25227,7 +25230,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -25277,7 +25280,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -25777,7 +25780,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25827,7 +25830,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25877,7 +25880,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25927,7 +25930,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25977,7 +25980,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -26227,7 +26230,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26277,7 +26280,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26327,7 +26330,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26377,7 +26380,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26427,7 +26430,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -26477,7 +26480,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -26527,7 +26530,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -26577,7 +26580,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26627,7 +26630,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26677,7 +26680,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26727,7 +26730,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26777,7 +26780,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26827,7 +26830,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26877,7 +26880,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -27077,7 +27080,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -27127,7 +27130,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -27177,7 +27180,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -27227,7 +27230,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -27777,7 +27780,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27827,7 +27830,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27877,7 +27880,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27927,7 +27930,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27977,7 +27980,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -28227,7 +28230,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -28277,7 +28280,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -28327,7 +28330,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -28377,7 +28380,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -28577,7 +28580,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28627,7 +28630,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28677,7 +28680,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28727,7 +28730,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28777,7 +28780,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28827,7 +28830,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28877,7 +28880,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -29177,7 +29180,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -29227,7 +29230,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -29277,7 +29280,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29327,7 +29330,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29477,7 +29480,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -29527,7 +29530,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -29577,7 +29580,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29627,7 +29630,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29677,7 +29680,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29827,7 +29830,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29877,7 +29880,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -30027,7 +30030,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -30077,7 +30080,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -30127,7 +30130,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -30177,7 +30180,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -30227,7 +30230,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -30277,7 +30280,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30327,7 +30330,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30377,7 +30380,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -30627,7 +30630,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -30677,7 +30680,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30727,7 +30730,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30777,7 +30780,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30827,7 +30830,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30877,7 +30880,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30927,7 +30930,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30977,7 +30980,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -31027,7 +31030,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -31077,7 +31080,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -31127,7 +31130,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -31177,7 +31180,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -31227,7 +31230,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -31277,7 +31280,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31327,7 +31330,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31377,7 +31380,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31627,7 +31630,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31677,7 +31680,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31877,7 +31880,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31927,7 +31930,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31977,7 +31980,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -32027,7 +32030,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -32077,7 +32080,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -32127,7 +32130,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -32177,7 +32180,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -32227,7 +32230,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -32277,7 +32280,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -32427,7 +32430,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -32477,7 +32480,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32677,7 +32680,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32727,7 +32730,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32927,7 +32930,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32977,7 +32980,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -33027,7 +33030,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -33077,7 +33080,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -33127,7 +33130,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -33227,7 +33230,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -33277,7 +33280,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33327,7 +33330,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -33377,7 +33380,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -33627,7 +33630,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33677,7 +33680,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33727,7 +33730,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -34077,7 +34080,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -34127,7 +34130,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -34177,7 +34180,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -35127,7 +35130,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -35177,7 +35180,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -35227,7 +35230,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -35277,7 +35280,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35477,7 +35480,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -35527,7 +35530,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35577,7 +35580,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -36377,7 +36380,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -36427,7 +36430,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36477,7 +36480,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36527,7 +36530,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36577,7 +36580,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36627,7 +36630,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36677,7 +36680,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36727,7 +36730,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36777,7 +36780,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36827,7 +36830,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36877,7 +36880,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36927,7 +36930,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36977,7 +36980,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -37027,7 +37030,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -37127,7 +37130,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -37177,7 +37180,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -37227,7 +37230,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -37277,7 +37280,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -37327,7 +37330,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -37377,7 +37380,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -37427,7 +37430,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -37627,7 +37630,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37677,7 +37680,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37727,7 +37730,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -38177,7 +38180,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -38227,7 +38230,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -38277,7 +38280,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -38327,7 +38330,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -38527,7 +38530,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38577,7 +38580,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38627,7 +38630,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38677,7 +38680,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38727,7 +38730,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38777,7 +38780,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38827,7 +38830,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38877,7 +38880,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38927,7 +38930,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38977,7 +38980,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -39027,7 +39030,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -39077,7 +39080,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -40077,7 +40080,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -40127,7 +40130,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -40177,7 +40180,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -40227,7 +40230,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -40477,7 +40480,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40527,7 +40530,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40577,7 +40580,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40627,7 +40630,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -40827,7 +40830,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40877,7 +40880,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40927,7 +40930,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -41027,7 +41030,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -41377,7 +41380,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -41427,7 +41430,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -41477,7 +41480,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41527,7 +41530,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41577,7 +41580,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41627,7 +41630,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41677,7 +41680,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41727,7 +41730,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41777,7 +41780,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41827,7 +41830,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -42077,7 +42080,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -42127,7 +42130,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -42177,7 +42180,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -42477,7 +42480,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -42527,7 +42530,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42577,7 +42580,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42827,7 +42830,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42877,7 +42880,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42927,7 +42930,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42977,7 +42980,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -43027,7 +43030,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -43477,7 +43480,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -43527,7 +43530,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -43627,7 +43630,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -43677,7 +43680,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43727,7 +43730,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43777,7 +43780,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -44927,7 +44930,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44977,7 +44980,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -45027,7 +45030,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -45077,7 +45080,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -45127,7 +45130,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -45177,7 +45180,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -45227,7 +45230,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -45277,7 +45280,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -45327,7 +45330,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -46077,7 +46080,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -46127,7 +46130,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -46177,7 +46180,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -46427,7 +46430,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -46477,7 +46480,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -46527,7 +46530,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46577,7 +46580,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46627,7 +46630,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46677,7 +46680,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46727,7 +46730,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46777,7 +46780,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46827,7 +46830,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46877,7 +46880,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46927,7 +46930,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -47127,7 +47130,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -47177,7 +47180,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -47227,7 +47230,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -47427,7 +47430,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -47477,7 +47480,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47527,7 +47530,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -47577,7 +47580,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47627,7 +47630,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47677,7 +47680,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -48577,7 +48580,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48627,7 +48630,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48727,7 +48730,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48777,7 +48780,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48827,7 +48830,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -49127,7 +49130,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -49177,7 +49180,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -49227,7 +49230,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -49277,7 +49280,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -49327,7 +49330,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -49477,7 +49480,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -49577,7 +49580,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49627,7 +49630,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49677,7 +49680,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49827,7 +49830,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49877,7 +49880,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49927,7 +49930,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -50127,7 +50130,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -50177,7 +50180,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -50227,7 +50230,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -50277,7 +50280,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -50327,7 +50330,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50677,7 +50680,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50727,7 +50730,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50777,7 +50780,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50827,7 +50830,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -51027,7 +51030,7 @@
         <v>1</v>
       </c>
       <c r="P971" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="972" spans="1:16">
@@ -51077,7 +51080,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -51577,7 +51580,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51627,7 +51630,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51677,7 +51680,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51727,7 +51730,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51777,7 +51780,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -52177,7 +52180,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -52377,7 +52380,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -52427,7 +52430,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -52477,7 +52480,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -52527,7 +52530,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -53077,7 +53080,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -53127,7 +53130,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -53177,7 +53180,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -53827,7 +53830,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53877,7 +53880,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53927,7 +53930,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -54827,7 +54830,7 @@
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
@@ -56177,7 +56180,7 @@
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
@@ -56227,7 +56230,7 @@
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
@@ -56441,10 +56444,10 @@
         <v>-0.4044242740522641</v>
       </c>
       <c r="D1080" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E1080">
-        <v>-0.7196466246691795</v>
+        <v>-0.6439149612952129</v>
       </c>
       <c r="F1080">
         <v>-1</v>
@@ -56453,10 +56456,10 @@
         <v>0.01680442427405226</v>
       </c>
       <c r="H1080">
-        <v>0.01677964662466918</v>
+        <v>0.01644391496129521</v>
       </c>
       <c r="I1080">
-        <v>0.3152223506169154</v>
+        <v>0.2394906872429488</v>
       </c>
       <c r="J1080">
         <v>1.210186255140965</v>
@@ -56468,10 +56471,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M1080">
-        <v>7.23</v>
+        <v>7.06</v>
       </c>
       <c r="N1080">
-        <v>8.029999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="O1080">
         <v>1</v>
@@ -56541,10 +56544,10 @@
         <v>-0.3352256931637765</v>
       </c>
       <c r="D1082" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E1082">
-        <v>-0.5737262375104688</v>
+        <v>-0.5014256205842162</v>
       </c>
       <c r="F1082">
         <v>-1</v>
@@ -56553,10 +56556,10 @@
         <v>0.01651522569316378</v>
       </c>
       <c r="H1082">
-        <v>0.01663372623751047</v>
+        <v>0.01630142562058422</v>
       </c>
       <c r="I1082">
-        <v>0.2385005443466923</v>
+        <v>0.1661999274204398</v>
       </c>
       <c r="J1082">
         <v>1.190003628977935</v>
@@ -56568,10 +56571,10 @@
         <v>8.09</v>
       </c>
       <c r="M1082">
-        <v>7.23</v>
+        <v>7.06</v>
       </c>
       <c r="N1082">
-        <v>8.029999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="O1082">
         <v>1</v>
@@ -56627,7 +56630,7 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56641,10 +56644,10 @@
         <v>-0.2869595134011824</v>
       </c>
       <c r="D1084" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E1084">
-        <v>-0.6001993364121727</v>
+        <v>-0.5272762538132678</v>
       </c>
       <c r="F1084">
         <v>-1</v>
@@ -56653,10 +56656,10 @@
         <v>0.01668695951340118</v>
       </c>
       <c r="H1084">
-        <v>0.01666019933641217</v>
+        <v>0.01632727625381327</v>
       </c>
       <c r="I1084">
-        <v>0.3132398230109903</v>
+        <v>0.2403167404120854</v>
       </c>
       <c r="J1084">
         <v>1.193665191758253</v>
@@ -56668,16 +56671,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M1084">
-        <v>7.23</v>
+        <v>7.06</v>
       </c>
       <c r="N1084">
-        <v>8.029999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="O1084">
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56727,7 +56730,7 @@
         <v>1</v>
       </c>
       <c r="P1085" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="1086" spans="1:16">
@@ -56741,10 +56744,10 @@
         <v>-0.1669472197411892</v>
       </c>
       <c r="D1086" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E1086">
-        <v>-0.4781615188085517</v>
+        <v>-0.4081079284631208</v>
       </c>
       <c r="F1086">
         <v>-1</v>
@@ -56753,10 +56756,10 @@
         <v>0.01656694721974119</v>
       </c>
       <c r="H1086">
-        <v>0.01653816151880855</v>
+        <v>0.01620810792846312</v>
       </c>
       <c r="I1086">
-        <v>0.3112142990673625</v>
+        <v>0.2411607087219316</v>
       </c>
       <c r="J1086">
         <v>1.176785825561349</v>
@@ -56768,16 +56771,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M1086">
-        <v>7.23</v>
+        <v>7.06</v>
       </c>
       <c r="N1086">
-        <v>8.029999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="O1086">
         <v>1</v>
       </c>
       <c r="P1086" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="1087" spans="1:16">
@@ -56791,10 +56794,10 @@
         <v>-0.02918843275758931</v>
       </c>
       <c r="D1087" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E1087">
-        <v>-0.3380776890066617</v>
+        <v>-0.2713179093204729</v>
       </c>
       <c r="F1087">
         <v>-1</v>
@@ -56803,10 +56806,10 @@
         <v>0.01642918843275759</v>
       </c>
       <c r="H1087">
-        <v>0.01639807768900666</v>
+        <v>0.01607131790932047</v>
       </c>
       <c r="I1087">
-        <v>0.3088892562490724</v>
+        <v>0.2421294765628836</v>
       </c>
       <c r="J1087">
         <v>1.157410468742277</v>
@@ -56818,10 +56821,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M1087">
-        <v>7.23</v>
+        <v>7.06</v>
       </c>
       <c r="N1087">
-        <v>8.029999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="O1087">
         <v>1</v>
@@ -56835,243 +56838,243 @@
         <v>0</v>
       </c>
       <c r="B1088" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1088">
-        <v>-0.6487169745185035</v>
+        <v>0.02588252599162821</v>
       </c>
       <c r="D1088" t="s">
         <v>507</v>
       </c>
       <c r="E1088">
-        <v>-0.1177872849157779</v>
+        <v>-0.1413374811439407</v>
       </c>
       <c r="F1088">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1088">
-        <v>0.0186687169745185</v>
+        <v>0.01615411747400837</v>
       </c>
       <c r="H1088">
-        <v>0.01721778728491578</v>
+        <v>0.01594133748114394</v>
       </c>
       <c r="I1088">
-        <v>0.5309296896027256</v>
+        <v>0.1672200071355689</v>
       </c>
       <c r="J1088">
         <v>1.138999643221521</v>
       </c>
       <c r="K1088">
-        <v>8.48</v>
+        <v>7.08</v>
       </c>
       <c r="L1088">
-        <v>9.01</v>
+        <v>8.09</v>
       </c>
       <c r="M1088">
-        <v>7.61</v>
+        <v>7.06</v>
       </c>
       <c r="N1088">
-        <v>8.550000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="O1088">
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
       <c r="A1089" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1089" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1089">
-        <v>0.02588252599162821</v>
+        <v>-0.3941793682350347</v>
       </c>
       <c r="D1089" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E1089">
-        <v>-0.2049674204916005</v>
+        <v>0.11063620374191</v>
       </c>
       <c r="F1089">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1089">
-        <v>0.01615411747400837</v>
+        <v>0.01841417936823503</v>
       </c>
       <c r="H1089">
-        <v>0.0162649674204916</v>
+        <v>0.01698936379625809</v>
       </c>
       <c r="I1089">
-        <v>0.2308499464832288</v>
+        <v>0.5048155719769447</v>
       </c>
       <c r="J1089">
-        <v>1.138999643221521</v>
+        <v>1.108983416065452</v>
       </c>
       <c r="K1089">
-        <v>7.08</v>
+        <v>8.48</v>
       </c>
       <c r="L1089">
-        <v>8.09</v>
+        <v>9.01</v>
       </c>
       <c r="M1089">
-        <v>7.23</v>
+        <v>7.61</v>
       </c>
       <c r="N1089">
-        <v>8.029999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O1089">
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
       <c r="A1090" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1090" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1090">
-        <v>-0.3941793682350347</v>
+        <v>0.2383974142565988</v>
       </c>
       <c r="D1090" t="s">
         <v>507</v>
       </c>
       <c r="E1090">
-        <v>0.11063620374191</v>
+        <v>0.07057708257790907</v>
       </c>
       <c r="F1090">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1090">
-        <v>0.01841417936823503</v>
+        <v>0.0159416025857434</v>
       </c>
       <c r="H1090">
-        <v>0.01698936379625809</v>
+        <v>0.01572942291742209</v>
       </c>
       <c r="I1090">
-        <v>0.5048155719769447</v>
+        <v>0.1678203316786897</v>
       </c>
       <c r="J1090">
         <v>1.108983416065452</v>
       </c>
       <c r="K1090">
-        <v>8.48</v>
+        <v>7.08</v>
       </c>
       <c r="L1090">
-        <v>9.01</v>
+        <v>8.09</v>
       </c>
       <c r="M1090">
-        <v>7.61</v>
+        <v>7.06</v>
       </c>
       <c r="N1090">
-        <v>8.550000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="O1090">
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
       <c r="A1091" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1091" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1091">
-        <v>0.2383974142565988</v>
+        <v>-0.2536665708087877</v>
       </c>
       <c r="D1091" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E1091">
-        <v>0.01204990184677968</v>
+        <v>0.2367331835076811</v>
       </c>
       <c r="F1091">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1091">
-        <v>0.0159416025857434</v>
+        <v>0.01827366657080879</v>
       </c>
       <c r="H1091">
-        <v>0.01604795009815322</v>
+        <v>0.01686326681649232</v>
       </c>
       <c r="I1091">
-        <v>0.2263475124098191</v>
+        <v>0.4903997543164689</v>
       </c>
       <c r="J1091">
-        <v>1.108983416065452</v>
+        <v>1.092413510708583</v>
       </c>
       <c r="K1091">
-        <v>7.08</v>
+        <v>8.48</v>
       </c>
       <c r="L1091">
-        <v>8.09</v>
+        <v>9.01</v>
       </c>
       <c r="M1091">
-        <v>7.23</v>
+        <v>7.61</v>
       </c>
       <c r="N1091">
-        <v>8.029999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O1091">
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>702</v>
+        <v>259</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
       <c r="A1092" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1092" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1092">
-        <v>-0.2536665708087877</v>
+        <v>0.3557123441832299</v>
       </c>
       <c r="D1092" t="s">
         <v>507</v>
       </c>
       <c r="E1092">
-        <v>0.2367331835076811</v>
+        <v>0.1875606143974027</v>
       </c>
       <c r="F1092">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1092">
-        <v>0.01827366657080879</v>
+        <v>0.01582428765581677</v>
       </c>
       <c r="H1092">
-        <v>0.01686326681649232</v>
+        <v>0.0156124393856026</v>
       </c>
       <c r="I1092">
-        <v>0.4903997543164689</v>
+        <v>0.1681517297858273</v>
       </c>
       <c r="J1092">
         <v>1.092413510708583</v>
       </c>
       <c r="K1092">
-        <v>8.48</v>
+        <v>7.08</v>
       </c>
       <c r="L1092">
-        <v>9.01</v>
+        <v>8.09</v>
       </c>
       <c r="M1092">
-        <v>7.61</v>
+        <v>7.06</v>
       </c>
       <c r="N1092">
-        <v>8.550000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="O1092">
         <v>1</v>
@@ -57082,34 +57085,34 @@
     </row>
     <row r="1093" spans="1:16">
       <c r="A1093" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1093" t="s">
         <v>264</v>
       </c>
       <c r="C1093">
-        <v>0.3557123441832299</v>
+        <v>0.6509480614049288</v>
       </c>
       <c r="D1093" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E1093">
-        <v>0.1318503175769417</v>
+        <v>0.4819623324179103</v>
       </c>
       <c r="F1093">
         <v>-1</v>
       </c>
       <c r="G1093">
-        <v>0.01582428765581677</v>
+        <v>0.01552905193859507</v>
       </c>
       <c r="H1093">
-        <v>0.01592814968242306</v>
+        <v>0.01531803766758209</v>
       </c>
       <c r="I1093">
-        <v>0.2238620266062883</v>
+        <v>0.1689857289870185</v>
       </c>
       <c r="J1093">
-        <v>1.092413510708583</v>
+        <v>1.050713550649021</v>
       </c>
       <c r="K1093">
         <v>7.08</v>
@@ -57118,65 +57121,15 @@
         <v>8.09</v>
       </c>
       <c r="M1093">
-        <v>7.23</v>
+        <v>7.06</v>
       </c>
       <c r="N1093">
-        <v>8.029999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="O1093">
         <v>1</v>
       </c>
       <c r="P1093" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="1094" spans="1:16">
-      <c r="A1094" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>264</v>
-      </c>
-      <c r="C1094">
-        <v>0.6509480614049288</v>
-      </c>
-      <c r="D1094" t="s">
-        <v>506</v>
-      </c>
-      <c r="E1094">
-        <v>0.4333410288075754</v>
-      </c>
-      <c r="F1094">
-        <v>-1</v>
-      </c>
-      <c r="G1094">
-        <v>0.01552905193859507</v>
-      </c>
-      <c r="H1094">
-        <v>0.01562665897119242</v>
-      </c>
-      <c r="I1094">
-        <v>0.2176070325973534</v>
-      </c>
-      <c r="J1094">
-        <v>1.050713550649021</v>
-      </c>
-      <c r="K1094">
-        <v>7.08</v>
-      </c>
-      <c r="L1094">
-        <v>8.09</v>
-      </c>
-      <c r="M1094">
-        <v>7.23</v>
-      </c>
-      <c r="N1094">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="O1094">
-        <v>1</v>
-      </c>
-      <c r="P1094" t="s">
         <v>265</v>
       </c>
     </row>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3291" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3291" uniqueCount="706">
   <si>
     <t>trade_time</t>
   </si>
@@ -1538,6 +1538,12 @@
   </si>
   <si>
     <t>2021-08-26</t>
+  </si>
+  <si>
+    <t>2021-08-27</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
   </si>
   <si>
     <t>2021-08-18</t>
@@ -2580,7 +2586,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2630,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2680,7 +2686,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2730,7 +2736,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2780,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2830,7 +2836,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -3030,7 +3036,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3080,7 +3086,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3130,7 +3136,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3280,7 +3286,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3330,7 +3336,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3680,7 +3686,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3730,7 +3736,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3880,7 +3886,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3930,7 +3936,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3980,7 +3986,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -4030,7 +4036,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -4080,7 +4086,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -4130,7 +4136,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4180,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -4230,7 +4236,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4280,7 +4286,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4330,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4380,7 +4386,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4580,7 +4586,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4630,7 +4636,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4680,7 +4686,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4730,7 +4736,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4780,7 +4786,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4830,7 +4836,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4880,7 +4886,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4930,7 +4936,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4980,7 +4986,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -5030,7 +5036,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -5080,7 +5086,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -5130,7 +5136,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -5180,7 +5186,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -5230,7 +5236,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -5380,7 +5386,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5430,7 +5436,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5480,7 +5486,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5530,7 +5536,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5580,7 +5586,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5630,7 +5636,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5680,7 +5686,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5830,7 +5836,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5880,7 +5886,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -6030,7 +6036,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -6080,7 +6086,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -6130,7 +6136,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -6180,7 +6186,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -6230,7 +6236,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -6280,7 +6286,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6430,7 +6436,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6480,7 +6486,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6530,7 +6536,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6580,7 +6586,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6630,7 +6636,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6680,7 +6686,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6730,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6780,7 +6786,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6830,7 +6836,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6880,7 +6886,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6930,7 +6936,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6980,7 +6986,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -7030,7 +7036,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -7280,7 +7286,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -7330,7 +7336,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -7380,7 +7386,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -7530,7 +7536,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -7580,7 +7586,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -9580,7 +9586,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9630,7 +9636,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9680,7 +9686,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -10130,7 +10136,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -10180,7 +10186,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -10230,7 +10236,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -10280,7 +10286,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -10330,7 +10336,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -10530,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10580,7 +10586,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10630,7 +10636,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10830,7 +10836,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10880,7 +10886,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10930,7 +10936,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10980,7 +10986,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -11280,7 +11286,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11330,7 +11336,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11380,7 +11386,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11430,7 +11436,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11480,7 +11486,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11730,7 +11736,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11780,7 +11786,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11830,7 +11836,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11880,7 +11886,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -13280,7 +13286,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -13330,7 +13336,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -13380,7 +13386,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -13430,7 +13436,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13480,7 +13486,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -13530,7 +13536,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -13980,7 +13986,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -14030,7 +14036,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -14180,7 +14186,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -14230,7 +14236,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -14280,7 +14286,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -14730,7 +14736,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14780,7 +14786,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14830,7 +14836,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14880,7 +14886,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14930,7 +14936,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -15880,7 +15886,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15930,7 +15936,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15980,7 +15986,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -16030,7 +16036,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -16080,7 +16086,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -16130,7 +16136,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -16930,7 +16936,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16980,7 +16986,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -17030,7 +17036,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -17080,7 +17086,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -17130,7 +17136,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -17630,7 +17636,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17680,7 +17686,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17730,7 +17736,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17780,7 +17786,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17830,7 +17836,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17880,7 +17886,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17930,7 +17936,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -19430,7 +19436,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19480,7 +19486,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19530,7 +19536,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19580,7 +19586,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19630,7 +19636,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19680,7 +19686,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19730,7 +19736,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -21380,7 +21386,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21430,7 +21436,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21630,7 +21636,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21680,7 +21686,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21730,7 +21736,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21780,7 +21786,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21930,7 +21936,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21980,7 +21986,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -22030,7 +22036,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -22180,7 +22186,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -22230,7 +22236,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -22280,7 +22286,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -22530,7 +22536,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22580,7 +22586,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22630,7 +22636,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22680,7 +22686,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22730,7 +22736,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22780,7 +22786,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22830,7 +22836,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22880,7 +22886,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22930,7 +22936,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22980,7 +22986,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -23030,7 +23036,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -23080,7 +23086,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -23130,7 +23136,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -23230,7 +23236,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -23280,7 +23286,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23330,7 +23336,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -23380,7 +23386,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -23430,7 +23436,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23480,7 +23486,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23530,7 +23536,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -23580,7 +23586,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -24030,7 +24036,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -24080,7 +24086,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -24130,7 +24136,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -24330,7 +24336,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24380,7 +24386,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24430,7 +24436,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24480,7 +24486,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24530,7 +24536,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24580,7 +24586,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24630,7 +24636,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24680,7 +24686,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24730,7 +24736,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24780,7 +24786,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24830,7 +24836,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24880,7 +24886,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24930,7 +24936,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24980,7 +24986,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -25030,7 +25036,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -25080,7 +25086,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -25130,7 +25136,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -25180,7 +25186,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25230,7 +25236,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -25280,7 +25286,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -25780,7 +25786,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25830,7 +25836,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25880,7 +25886,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25930,7 +25936,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25980,7 +25986,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -26230,7 +26236,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26280,7 +26286,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26330,7 +26336,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26380,7 +26386,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26430,7 +26436,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -26480,7 +26486,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -26530,7 +26536,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -26580,7 +26586,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26630,7 +26636,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26680,7 +26686,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26730,7 +26736,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26780,7 +26786,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26830,7 +26836,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26880,7 +26886,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -27080,7 +27086,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -27130,7 +27136,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -27180,7 +27186,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -27230,7 +27236,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -27780,7 +27786,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27830,7 +27836,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27880,7 +27886,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27930,7 +27936,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27980,7 +27986,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -28230,7 +28236,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -28280,7 +28286,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -28330,7 +28336,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -28380,7 +28386,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -28580,7 +28586,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28630,7 +28636,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28680,7 +28686,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28730,7 +28736,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28780,7 +28786,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28830,7 +28836,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28880,7 +28886,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -29180,7 +29186,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -29230,7 +29236,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -29280,7 +29286,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29330,7 +29336,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29480,7 +29486,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -29530,7 +29536,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -29580,7 +29586,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29630,7 +29636,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29680,7 +29686,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29830,7 +29836,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29880,7 +29886,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -30030,7 +30036,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -30080,7 +30086,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -30130,7 +30136,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -30180,7 +30186,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -30230,7 +30236,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -30280,7 +30286,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30330,7 +30336,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30380,7 +30386,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -30630,7 +30636,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -30680,7 +30686,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30730,7 +30736,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30780,7 +30786,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30830,7 +30836,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30880,7 +30886,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30930,7 +30936,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30980,7 +30986,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -31030,7 +31036,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -31080,7 +31086,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -31130,7 +31136,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -31180,7 +31186,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -31230,7 +31236,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -31280,7 +31286,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31330,7 +31336,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31380,7 +31386,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31630,7 +31636,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31680,7 +31686,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31880,7 +31886,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31930,7 +31936,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31980,7 +31986,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -32030,7 +32036,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -32080,7 +32086,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -32130,7 +32136,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -32180,7 +32186,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -32230,7 +32236,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -32280,7 +32286,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -32430,7 +32436,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -32480,7 +32486,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32680,7 +32686,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32730,7 +32736,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32930,7 +32936,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32980,7 +32986,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -33030,7 +33036,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -33080,7 +33086,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -33130,7 +33136,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -33230,7 +33236,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -33280,7 +33286,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33330,7 +33336,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -33380,7 +33386,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -33630,7 +33636,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33680,7 +33686,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33730,7 +33736,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -34080,7 +34086,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -34130,7 +34136,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -34180,7 +34186,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -35130,7 +35136,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -35180,7 +35186,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -35230,7 +35236,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -35280,7 +35286,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35480,7 +35486,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -35530,7 +35536,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35580,7 +35586,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -36380,7 +36386,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -36430,7 +36436,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36480,7 +36486,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36530,7 +36536,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36580,7 +36586,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36630,7 +36636,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36680,7 +36686,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36730,7 +36736,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36780,7 +36786,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36830,7 +36836,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36880,7 +36886,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36930,7 +36936,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36980,7 +36986,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -37030,7 +37036,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -37130,7 +37136,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -37180,7 +37186,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -37230,7 +37236,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -37280,7 +37286,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -37330,7 +37336,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -37380,7 +37386,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -37430,7 +37436,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -37630,7 +37636,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37680,7 +37686,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37730,7 +37736,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -38180,7 +38186,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -38230,7 +38236,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -38280,7 +38286,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -38330,7 +38336,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -38530,7 +38536,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38580,7 +38586,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38630,7 +38636,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38680,7 +38686,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38730,7 +38736,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38780,7 +38786,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38830,7 +38836,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38880,7 +38886,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38930,7 +38936,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38980,7 +38986,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -39030,7 +39036,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -39080,7 +39086,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -40080,7 +40086,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -40130,7 +40136,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -40180,7 +40186,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -40230,7 +40236,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -40480,7 +40486,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40530,7 +40536,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40580,7 +40586,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40630,7 +40636,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -40830,7 +40836,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40880,7 +40886,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40930,7 +40936,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -41030,7 +41036,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -41380,7 +41386,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -41430,7 +41436,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -41480,7 +41486,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41530,7 +41536,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41580,7 +41586,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41630,7 +41636,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41680,7 +41686,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41730,7 +41736,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41780,7 +41786,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41830,7 +41836,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -42080,7 +42086,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -42130,7 +42136,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -42180,7 +42186,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -42480,7 +42486,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -42530,7 +42536,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42580,7 +42586,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42830,7 +42836,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42880,7 +42886,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42930,7 +42936,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42980,7 +42986,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -43030,7 +43036,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -43480,7 +43486,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -43530,7 +43536,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -43630,7 +43636,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -43680,7 +43686,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43730,7 +43736,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43780,7 +43786,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -44930,7 +44936,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44980,7 +44986,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -45030,7 +45036,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -45080,7 +45086,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -45130,7 +45136,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -45180,7 +45186,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -45230,7 +45236,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -45280,7 +45286,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -45330,7 +45336,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -46080,7 +46086,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -46130,7 +46136,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -46180,7 +46186,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -46430,7 +46436,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -46480,7 +46486,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -46530,7 +46536,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46580,7 +46586,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46630,7 +46636,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46680,7 +46686,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46730,7 +46736,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46780,7 +46786,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46830,7 +46836,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46880,7 +46886,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46930,7 +46936,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -47130,7 +47136,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -47180,7 +47186,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -47230,7 +47236,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -47430,7 +47436,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -47480,7 +47486,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47530,7 +47536,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -47580,7 +47586,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47630,7 +47636,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47680,7 +47686,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -48580,7 +48586,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48630,7 +48636,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48730,7 +48736,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48780,7 +48786,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48830,7 +48836,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -49130,7 +49136,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -49180,7 +49186,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -49230,7 +49236,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -49280,7 +49286,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -49330,7 +49336,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -49480,7 +49486,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -49580,7 +49586,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49630,7 +49636,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49680,7 +49686,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49830,7 +49836,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49880,7 +49886,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49930,7 +49936,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -50130,7 +50136,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -50180,7 +50186,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -50230,7 +50236,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -50280,7 +50286,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -50330,7 +50336,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50680,7 +50686,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50730,7 +50736,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50780,7 +50786,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50830,7 +50836,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -51030,7 +51036,7 @@
         <v>1</v>
       </c>
       <c r="P971" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="972" spans="1:16">
@@ -51080,7 +51086,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -51580,7 +51586,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51630,7 +51636,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51680,7 +51686,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51730,7 +51736,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51780,7 +51786,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -52180,7 +52186,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -52380,7 +52386,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -52430,7 +52436,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -52480,7 +52486,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -52530,7 +52536,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -53080,7 +53086,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -53130,7 +53136,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -53180,7 +53186,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -53830,7 +53836,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53880,7 +53886,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53930,7 +53936,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -54830,7 +54836,7 @@
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
@@ -56180,7 +56186,7 @@
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
@@ -56230,7 +56236,7 @@
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
@@ -56544,10 +56550,10 @@
         <v>-0.3352256931637765</v>
       </c>
       <c r="D1082" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E1082">
-        <v>-0.5014256205842162</v>
+        <v>-0.5723260197717908</v>
       </c>
       <c r="F1082">
         <v>-1</v>
@@ -56556,10 +56562,10 @@
         <v>0.01651522569316378</v>
       </c>
       <c r="H1082">
-        <v>0.01630142562058422</v>
+        <v>0.01649232601977179</v>
       </c>
       <c r="I1082">
-        <v>0.1661999274204398</v>
+        <v>0.2371003266080143</v>
       </c>
       <c r="J1082">
         <v>1.190003628977935</v>
@@ -56571,10 +56577,10 @@
         <v>8.09</v>
       </c>
       <c r="M1082">
-        <v>7.06</v>
+        <v>7.17</v>
       </c>
       <c r="N1082">
-        <v>7.9</v>
+        <v>7.96</v>
       </c>
       <c r="O1082">
         <v>1</v>
@@ -56630,7 +56636,7 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56638,49 +56644,49 @@
         <v>1</v>
       </c>
       <c r="B1084" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C1084">
-        <v>-0.2869595134011824</v>
+        <v>-0.3611495576484334</v>
       </c>
       <c r="D1084" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E1084">
-        <v>-0.5272762538132678</v>
+        <v>-0.8753396018956847</v>
       </c>
       <c r="F1084">
         <v>-1</v>
       </c>
       <c r="G1084">
-        <v>0.01668695951340118</v>
+        <v>0.01654114955764843</v>
       </c>
       <c r="H1084">
-        <v>0.01632727625381327</v>
+        <v>0.01595533960189569</v>
       </c>
       <c r="I1084">
-        <v>0.2403167404120854</v>
+        <v>0.5141900442472513</v>
       </c>
       <c r="J1084">
         <v>1.193665191758253</v>
       </c>
       <c r="K1084">
-        <v>7.11</v>
+        <v>7.08</v>
       </c>
       <c r="L1084">
-        <v>8.199999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="M1084">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
       <c r="N1084">
-        <v>7.9</v>
+        <v>7.54</v>
       </c>
       <c r="O1084">
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56730,7 +56736,7 @@
         <v>1</v>
       </c>
       <c r="P1085" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="1086" spans="1:16">
@@ -56738,49 +56744,49 @@
         <v>1</v>
       </c>
       <c r="B1086" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C1086">
-        <v>-0.1669472197411892</v>
+        <v>-0.2416436449743475</v>
       </c>
       <c r="D1086" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E1086">
-        <v>-0.4081079284631208</v>
+        <v>-0.756340070207508</v>
       </c>
       <c r="F1086">
         <v>-1</v>
       </c>
       <c r="G1086">
-        <v>0.01656694721974119</v>
+        <v>0.01642164364497434</v>
       </c>
       <c r="H1086">
-        <v>0.01620810792846312</v>
+        <v>0.01583634007020751</v>
       </c>
       <c r="I1086">
-        <v>0.2411607087219316</v>
+        <v>0.5146964252331605</v>
       </c>
       <c r="J1086">
         <v>1.176785825561349</v>
       </c>
       <c r="K1086">
-        <v>7.11</v>
+        <v>7.08</v>
       </c>
       <c r="L1086">
-        <v>8.199999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="M1086">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
       <c r="N1086">
-        <v>7.9</v>
+        <v>7.54</v>
       </c>
       <c r="O1086">
         <v>1</v>
       </c>
       <c r="P1086" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="1087" spans="1:16">
@@ -56788,43 +56794,43 @@
         <v>0</v>
       </c>
       <c r="B1087" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C1087">
-        <v>-0.02918843275758931</v>
+        <v>-0.1044661186953206</v>
       </c>
       <c r="D1087" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E1087">
-        <v>-0.2713179093204729</v>
+        <v>-0.6197438046330506</v>
       </c>
       <c r="F1087">
         <v>-1</v>
       </c>
       <c r="G1087">
-        <v>0.01642918843275759</v>
+        <v>0.01628446611869532</v>
       </c>
       <c r="H1087">
-        <v>0.01607131790932047</v>
+        <v>0.01569974380463305</v>
       </c>
       <c r="I1087">
-        <v>0.2421294765628836</v>
+        <v>0.5152776859377299</v>
       </c>
       <c r="J1087">
         <v>1.157410468742277</v>
       </c>
       <c r="K1087">
-        <v>7.11</v>
+        <v>7.08</v>
       </c>
       <c r="L1087">
-        <v>8.199999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="M1087">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
       <c r="N1087">
-        <v>7.9</v>
+        <v>7.54</v>
       </c>
       <c r="O1087">
         <v>1</v>
@@ -56844,10 +56850,10 @@
         <v>0.02588252599162821</v>
       </c>
       <c r="D1088" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E1088">
-        <v>-0.1413374811439407</v>
+        <v>-0.4899474847117267</v>
       </c>
       <c r="F1088">
         <v>-1</v>
@@ -56856,10 +56862,10 @@
         <v>0.01615411747400837</v>
       </c>
       <c r="H1088">
-        <v>0.01594133748114394</v>
+        <v>0.01556994748471173</v>
       </c>
       <c r="I1088">
-        <v>0.1672200071355689</v>
+        <v>0.5158300107033549</v>
       </c>
       <c r="J1088">
         <v>1.138999643221521</v>
@@ -56871,16 +56877,16 @@
         <v>8.09</v>
       </c>
       <c r="M1088">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
       <c r="N1088">
-        <v>7.9</v>
+        <v>7.54</v>
       </c>
       <c r="O1088">
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56894,7 +56900,7 @@
         <v>-0.3941793682350347</v>
       </c>
       <c r="D1089" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E1089">
         <v>0.11063620374191</v>
@@ -56930,7 +56936,7 @@
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -56944,10 +56950,10 @@
         <v>0.2383974142565988</v>
       </c>
       <c r="D1090" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E1090">
-        <v>0.07057708257790907</v>
+        <v>-0.2783330832614377</v>
       </c>
       <c r="F1090">
         <v>-1</v>
@@ -56956,10 +56962,10 @@
         <v>0.0159416025857434</v>
       </c>
       <c r="H1090">
-        <v>0.01572942291742209</v>
+        <v>0.01535833308326144</v>
       </c>
       <c r="I1090">
-        <v>0.1678203316786897</v>
+        <v>0.5167304975180365</v>
       </c>
       <c r="J1090">
         <v>1.108983416065452</v>
@@ -56971,16 +56977,16 @@
         <v>8.09</v>
       </c>
       <c r="M1090">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
       <c r="N1090">
-        <v>7.9</v>
+        <v>7.54</v>
       </c>
       <c r="O1090">
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -56994,7 +57000,7 @@
         <v>-0.2536665708087877</v>
       </c>
       <c r="D1091" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E1091">
         <v>0.2367331835076811</v>
@@ -57044,10 +57050,10 @@
         <v>0.3557123441832299</v>
       </c>
       <c r="D1092" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E1092">
-        <v>0.1875606143974027</v>
+        <v>-0.161515250495512</v>
       </c>
       <c r="F1092">
         <v>-1</v>
@@ -57056,10 +57062,10 @@
         <v>0.01582428765581677</v>
       </c>
       <c r="H1092">
-        <v>0.0156124393856026</v>
+        <v>0.01524151525049551</v>
       </c>
       <c r="I1092">
-        <v>0.1681517297858273</v>
+        <v>0.5172275946787419</v>
       </c>
       <c r="J1092">
         <v>1.092413510708583</v>
@@ -57071,10 +57077,10 @@
         <v>8.09</v>
       </c>
       <c r="M1092">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
       <c r="N1092">
-        <v>7.9</v>
+        <v>7.54</v>
       </c>
       <c r="O1092">
         <v>1</v>
@@ -57094,10 +57100,10 @@
         <v>0.6509480614049288</v>
       </c>
       <c r="D1093" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E1093">
-        <v>0.4819623324179103</v>
+        <v>0.1324694679244001</v>
       </c>
       <c r="F1093">
         <v>-1</v>
@@ -57106,10 +57112,10 @@
         <v>0.01552905193859507</v>
       </c>
       <c r="H1093">
-        <v>0.01531803766758209</v>
+        <v>0.0149475305320756</v>
       </c>
       <c r="I1093">
-        <v>0.1689857289870185</v>
+        <v>0.5184785934805287</v>
       </c>
       <c r="J1093">
         <v>1.050713550649021</v>
@@ -57121,10 +57127,10 @@
         <v>8.09</v>
       </c>
       <c r="M1093">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
       <c r="N1093">
-        <v>7.9</v>
+        <v>7.54</v>
       </c>
       <c r="O1093">
         <v>1</v>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3291" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3294" uniqueCount="706">
   <si>
     <t>trade_time</t>
   </si>
@@ -2489,7 +2489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1093"/>
+  <dimension ref="A1:P1094"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -56844,43 +56844,43 @@
         <v>0</v>
       </c>
       <c r="B1088" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1088">
-        <v>0.02588252599162821</v>
+        <v>-0.6487169745185035</v>
       </c>
       <c r="D1088" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E1088">
-        <v>-0.4899474847117267</v>
+        <v>-0.1177872849157779</v>
       </c>
       <c r="F1088">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1088">
-        <v>0.01615411747400837</v>
+        <v>0.0186687169745185</v>
       </c>
       <c r="H1088">
-        <v>0.01556994748471173</v>
+        <v>0.01721778728491578</v>
       </c>
       <c r="I1088">
-        <v>0.5158300107033549</v>
+        <v>0.5309296896027256</v>
       </c>
       <c r="J1088">
         <v>1.138999643221521</v>
       </c>
       <c r="K1088">
-        <v>7.08</v>
+        <v>8.48</v>
       </c>
       <c r="L1088">
-        <v>8.09</v>
+        <v>9.01</v>
       </c>
       <c r="M1088">
-        <v>7.05</v>
+        <v>7.61</v>
       </c>
       <c r="N1088">
-        <v>7.54</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O1088">
         <v>1</v>
@@ -56891,96 +56891,96 @@
     </row>
     <row r="1089" spans="1:16">
       <c r="A1089" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1089" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1089">
-        <v>-0.3941793682350347</v>
+        <v>0.02588252599162821</v>
       </c>
       <c r="D1089" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E1089">
-        <v>0.11063620374191</v>
+        <v>-0.4899474847117267</v>
       </c>
       <c r="F1089">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1089">
-        <v>0.01841417936823503</v>
+        <v>0.01615411747400837</v>
       </c>
       <c r="H1089">
-        <v>0.01698936379625809</v>
+        <v>0.01556994748471173</v>
       </c>
       <c r="I1089">
-        <v>0.5048155719769447</v>
+        <v>0.5158300107033549</v>
       </c>
       <c r="J1089">
-        <v>1.108983416065452</v>
+        <v>1.138999643221521</v>
       </c>
       <c r="K1089">
-        <v>8.48</v>
+        <v>7.08</v>
       </c>
       <c r="L1089">
-        <v>9.01</v>
+        <v>8.09</v>
       </c>
       <c r="M1089">
-        <v>7.61</v>
+        <v>7.05</v>
       </c>
       <c r="N1089">
-        <v>8.550000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="O1089">
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
       <c r="A1090" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1090" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1090">
-        <v>0.2383974142565988</v>
+        <v>-0.3941793682350347</v>
       </c>
       <c r="D1090" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E1090">
-        <v>-0.2783330832614377</v>
+        <v>0.11063620374191</v>
       </c>
       <c r="F1090">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1090">
-        <v>0.0159416025857434</v>
+        <v>0.01841417936823503</v>
       </c>
       <c r="H1090">
-        <v>0.01535833308326144</v>
+        <v>0.01698936379625809</v>
       </c>
       <c r="I1090">
-        <v>0.5167304975180365</v>
+        <v>0.5048155719769447</v>
       </c>
       <c r="J1090">
         <v>1.108983416065452</v>
       </c>
       <c r="K1090">
-        <v>7.08</v>
+        <v>8.48</v>
       </c>
       <c r="L1090">
-        <v>8.09</v>
+        <v>9.01</v>
       </c>
       <c r="M1090">
-        <v>7.05</v>
+        <v>7.61</v>
       </c>
       <c r="N1090">
-        <v>7.54</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O1090">
         <v>1</v>
@@ -56991,96 +56991,96 @@
     </row>
     <row r="1091" spans="1:16">
       <c r="A1091" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1091" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1091">
-        <v>-0.2536665708087877</v>
+        <v>0.2383974142565988</v>
       </c>
       <c r="D1091" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E1091">
-        <v>0.2367331835076811</v>
+        <v>-0.2783330832614377</v>
       </c>
       <c r="F1091">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1091">
-        <v>0.01827366657080879</v>
+        <v>0.0159416025857434</v>
       </c>
       <c r="H1091">
-        <v>0.01686326681649232</v>
+        <v>0.01535833308326144</v>
       </c>
       <c r="I1091">
-        <v>0.4903997543164689</v>
+        <v>0.5167304975180365</v>
       </c>
       <c r="J1091">
-        <v>1.092413510708583</v>
+        <v>1.108983416065452</v>
       </c>
       <c r="K1091">
-        <v>8.48</v>
+        <v>7.08</v>
       </c>
       <c r="L1091">
-        <v>9.01</v>
+        <v>8.09</v>
       </c>
       <c r="M1091">
-        <v>7.61</v>
+        <v>7.05</v>
       </c>
       <c r="N1091">
-        <v>8.550000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="O1091">
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>259</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
       <c r="A1092" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1092" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1092">
-        <v>0.3557123441832299</v>
+        <v>-0.2536665708087877</v>
       </c>
       <c r="D1092" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E1092">
-        <v>-0.161515250495512</v>
+        <v>0.2367331835076811</v>
       </c>
       <c r="F1092">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1092">
-        <v>0.01582428765581677</v>
+        <v>0.01827366657080879</v>
       </c>
       <c r="H1092">
-        <v>0.01524151525049551</v>
+        <v>0.01686326681649232</v>
       </c>
       <c r="I1092">
-        <v>0.5172275946787419</v>
+        <v>0.4903997543164689</v>
       </c>
       <c r="J1092">
         <v>1.092413510708583</v>
       </c>
       <c r="K1092">
-        <v>7.08</v>
+        <v>8.48</v>
       </c>
       <c r="L1092">
-        <v>8.09</v>
+        <v>9.01</v>
       </c>
       <c r="M1092">
-        <v>7.05</v>
+        <v>7.61</v>
       </c>
       <c r="N1092">
-        <v>7.54</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O1092">
         <v>1</v>
@@ -57091,34 +57091,34 @@
     </row>
     <row r="1093" spans="1:16">
       <c r="A1093" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1093" t="s">
         <v>264</v>
       </c>
       <c r="C1093">
-        <v>0.6509480614049288</v>
+        <v>0.3557123441832299</v>
       </c>
       <c r="D1093" t="s">
         <v>509</v>
       </c>
       <c r="E1093">
-        <v>0.1324694679244001</v>
+        <v>-0.161515250495512</v>
       </c>
       <c r="F1093">
         <v>-1</v>
       </c>
       <c r="G1093">
-        <v>0.01552905193859507</v>
+        <v>0.01582428765581677</v>
       </c>
       <c r="H1093">
-        <v>0.0149475305320756</v>
+        <v>0.01524151525049551</v>
       </c>
       <c r="I1093">
-        <v>0.5184785934805287</v>
+        <v>0.5172275946787419</v>
       </c>
       <c r="J1093">
-        <v>1.050713550649021</v>
+        <v>1.092413510708583</v>
       </c>
       <c r="K1093">
         <v>7.08</v>
@@ -57136,6 +57136,56 @@
         <v>1</v>
       </c>
       <c r="P1093" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:16">
+      <c r="A1094" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1094" t="s">
+        <v>264</v>
+      </c>
+      <c r="C1094">
+        <v>0.6509480614049288</v>
+      </c>
+      <c r="D1094" t="s">
+        <v>509</v>
+      </c>
+      <c r="E1094">
+        <v>0.1324694679244001</v>
+      </c>
+      <c r="F1094">
+        <v>-1</v>
+      </c>
+      <c r="G1094">
+        <v>0.01552905193859507</v>
+      </c>
+      <c r="H1094">
+        <v>0.0149475305320756</v>
+      </c>
+      <c r="I1094">
+        <v>0.5184785934805287</v>
+      </c>
+      <c r="J1094">
+        <v>1.050713550649021</v>
+      </c>
+      <c r="K1094">
+        <v>7.08</v>
+      </c>
+      <c r="L1094">
+        <v>8.09</v>
+      </c>
+      <c r="M1094">
+        <v>7.05</v>
+      </c>
+      <c r="N1094">
+        <v>7.54</v>
+      </c>
+      <c r="O1094">
+        <v>1</v>
+      </c>
+      <c r="P1094" t="s">
         <v>265</v>
       </c>
     </row>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3336" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3339" uniqueCount="712">
   <si>
     <t>trade_time</t>
   </si>
@@ -1562,6 +1562,9 @@
   </si>
   <si>
     <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
   </si>
   <si>
     <t>2016-07-14</t>
@@ -2504,7 +2507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1108"/>
+  <dimension ref="A1:P1109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2601,7 +2604,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2651,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2701,7 +2704,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2751,7 +2754,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2951,7 +2954,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -3001,7 +3004,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -3051,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3201,7 +3204,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -3251,7 +3254,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -3601,7 +3604,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3651,7 +3654,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3701,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3801,7 +3804,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3851,7 +3854,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3901,7 +3904,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3951,7 +3954,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -4001,7 +4004,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -4051,7 +4054,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -4101,7 +4104,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -4151,7 +4154,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4201,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -4251,7 +4254,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4301,7 +4304,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4501,7 +4504,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4551,7 +4554,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4601,7 +4604,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4651,7 +4654,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4701,7 +4704,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4751,7 +4754,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4801,7 +4804,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4851,7 +4854,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4901,7 +4904,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4951,7 +4954,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -5001,7 +5004,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -5051,7 +5054,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -5101,7 +5104,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -5151,7 +5154,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -5301,7 +5304,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -5351,7 +5354,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -5401,7 +5404,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5451,7 +5454,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5501,7 +5504,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5551,7 +5554,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5601,7 +5604,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5751,7 +5754,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5801,7 +5804,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5951,7 +5954,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -6001,7 +6004,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -6051,7 +6054,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -6101,7 +6104,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -6151,7 +6154,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -6201,7 +6204,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -6351,7 +6354,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -6401,7 +6404,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6451,7 +6454,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6501,7 +6504,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6551,7 +6554,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6601,7 +6604,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6651,7 +6654,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6701,7 +6704,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6751,7 +6754,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6801,7 +6804,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6851,7 +6854,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6901,7 +6904,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6951,7 +6954,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -7201,7 +7204,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -7251,7 +7254,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -7301,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -7451,7 +7454,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -7501,7 +7504,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -9501,7 +9504,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9551,7 +9554,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9601,7 +9604,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -10051,7 +10054,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -10101,7 +10104,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -10151,7 +10154,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -10201,7 +10204,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -10251,7 +10254,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -10451,7 +10454,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -10501,7 +10504,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -10551,7 +10554,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10751,7 +10754,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10801,7 +10804,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10851,7 +10854,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10901,7 +10904,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -11201,7 +11204,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -11251,7 +11254,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -11301,7 +11304,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11351,7 +11354,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11401,7 +11404,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11651,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11701,7 +11704,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11751,7 +11754,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11801,7 +11804,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -13201,7 +13204,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -13251,7 +13254,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -13301,7 +13304,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -13351,7 +13354,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -13401,7 +13404,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -13451,7 +13454,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13901,7 +13904,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13951,7 +13954,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -14101,7 +14104,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -14151,7 +14154,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -14201,7 +14204,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -14651,7 +14654,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14701,7 +14704,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14751,7 +14754,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14801,7 +14804,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14851,7 +14854,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -15801,7 +15804,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15851,7 +15854,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15901,7 +15904,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15951,7 +15954,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -16001,7 +16004,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -16051,7 +16054,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -16851,7 +16854,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16901,7 +16904,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16951,7 +16954,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -17001,7 +17004,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -17051,7 +17054,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -17551,7 +17554,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -17601,7 +17604,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17651,7 +17654,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17701,7 +17704,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17751,7 +17754,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17801,7 +17804,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17851,7 +17854,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -19351,7 +19354,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -19401,7 +19404,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -19451,7 +19454,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19501,7 +19504,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19551,7 +19554,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19601,7 +19604,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19651,7 +19654,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -21301,7 +21304,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -21351,7 +21354,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -21551,7 +21554,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21601,7 +21604,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21651,7 +21654,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21701,7 +21704,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21851,7 +21854,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21901,7 +21904,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21951,7 +21954,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -22101,7 +22104,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -22151,7 +22154,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -22201,7 +22204,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -22451,7 +22454,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -22501,7 +22504,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -22551,7 +22554,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22601,7 +22604,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22651,7 +22654,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22701,7 +22704,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22751,7 +22754,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22801,7 +22804,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22851,7 +22854,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22901,7 +22904,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22951,7 +22954,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -23001,7 +23004,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -23051,7 +23054,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -23151,7 +23154,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -23201,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -23251,7 +23254,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -23301,7 +23304,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23351,7 +23354,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -23401,7 +23404,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -23451,7 +23454,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23501,7 +23504,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23951,7 +23954,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -24001,7 +24004,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -24051,7 +24054,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -24251,7 +24254,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -24301,7 +24304,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24351,7 +24354,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24401,7 +24404,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24451,7 +24454,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24501,7 +24504,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24551,7 +24554,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24601,7 +24604,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24651,7 +24654,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24701,7 +24704,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24751,7 +24754,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24801,7 +24804,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24851,7 +24854,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24901,7 +24904,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24951,7 +24954,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -25001,7 +25004,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -25051,7 +25054,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -25101,7 +25104,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -25151,7 +25154,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -25201,7 +25204,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25701,7 +25704,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25751,7 +25754,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25801,7 +25804,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25851,7 +25854,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25901,7 +25904,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -26151,7 +26154,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -26201,7 +26204,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -26251,7 +26254,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26301,7 +26304,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26351,7 +26354,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26401,7 +26404,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26451,7 +26454,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -26501,7 +26504,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -26551,7 +26554,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -26601,7 +26604,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26651,7 +26654,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26701,7 +26704,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26751,7 +26754,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26801,7 +26804,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -27001,7 +27004,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -27051,7 +27054,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -27101,7 +27104,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -27151,7 +27154,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -27701,7 +27704,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27751,7 +27754,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27801,7 +27804,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27851,7 +27854,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27901,7 +27904,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -28151,7 +28154,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -28201,7 +28204,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28251,7 +28254,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -28301,7 +28304,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -28501,7 +28504,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -28551,7 +28554,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -28601,7 +28604,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28651,7 +28654,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28701,7 +28704,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28751,7 +28754,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28801,7 +28804,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -29101,7 +29104,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -29151,7 +29154,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -29201,7 +29204,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -29251,7 +29254,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -29401,7 +29404,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -29451,7 +29454,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -29501,7 +29504,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -29551,7 +29554,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -29601,7 +29604,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29751,7 +29754,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -29801,7 +29804,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29951,7 +29954,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -30001,7 +30004,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -30051,7 +30054,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -30101,7 +30104,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -30151,7 +30154,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -30201,7 +30204,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -30251,7 +30254,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -30301,7 +30304,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30551,7 +30554,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30601,7 +30604,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -30651,7 +30654,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -30701,7 +30704,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30751,7 +30754,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30801,7 +30804,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30851,7 +30854,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30901,7 +30904,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30951,7 +30954,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -31001,7 +31004,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -31051,7 +31054,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -31101,7 +31104,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -31151,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -31201,7 +31204,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -31251,7 +31254,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -31301,7 +31304,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31551,7 +31554,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -31601,7 +31604,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -31801,7 +31804,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31851,7 +31854,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31901,7 +31904,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31951,7 +31954,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -32001,7 +32004,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -32051,7 +32054,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -32101,7 +32104,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -32151,7 +32154,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -32201,7 +32204,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -32351,7 +32354,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -32401,7 +32404,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -32601,7 +32604,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -32651,7 +32654,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32851,7 +32854,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32901,7 +32904,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32951,7 +32954,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -33001,7 +33004,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -33051,7 +33054,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -33151,7 +33154,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -33201,7 +33204,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -33251,7 +33254,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -33301,7 +33304,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33551,7 +33554,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -33601,7 +33604,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -33651,7 +33654,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -34001,7 +34004,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -34051,7 +34054,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -34101,7 +34104,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -35051,7 +35054,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -35101,7 +35104,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -35151,7 +35154,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -35201,7 +35204,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -35401,7 +35404,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -35451,7 +35454,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -35501,7 +35504,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -36301,7 +36304,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -36351,7 +36354,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -36401,7 +36404,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -36451,7 +36454,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36501,7 +36504,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36551,7 +36554,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36601,7 +36604,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36651,7 +36654,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36701,7 +36704,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36751,7 +36754,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36801,7 +36804,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36851,7 +36854,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36901,7 +36904,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36951,7 +36954,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -37051,7 +37054,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -37101,7 +37104,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -37151,7 +37154,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -37201,7 +37204,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -37251,7 +37254,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -37301,7 +37304,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -37351,7 +37354,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -37551,7 +37554,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -37601,7 +37604,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37651,7 +37654,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -38101,7 +38104,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -38151,7 +38154,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -38201,7 +38204,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -38251,7 +38254,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -38451,7 +38454,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -38501,7 +38504,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -38551,7 +38554,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38601,7 +38604,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38651,7 +38654,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38701,7 +38704,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38751,7 +38754,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38801,7 +38804,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38851,7 +38854,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38901,7 +38904,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38951,7 +38954,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -39001,7 +39004,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -40001,7 +40004,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -40051,7 +40054,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -40101,7 +40104,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -40151,7 +40154,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -40401,7 +40404,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -40451,7 +40454,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -40501,7 +40504,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40551,7 +40554,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40751,7 +40754,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -40801,7 +40804,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -40851,7 +40854,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40951,7 +40954,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -41301,7 +41304,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -41351,7 +41354,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -41401,7 +41404,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -41451,7 +41454,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -41501,7 +41504,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41551,7 +41554,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41601,7 +41604,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41651,7 +41654,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41701,7 +41704,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41751,7 +41754,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -42001,7 +42004,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -42051,7 +42054,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -42101,7 +42104,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -42401,7 +42404,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -42451,7 +42454,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -42501,7 +42504,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -42751,7 +42754,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42801,7 +42804,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42851,7 +42854,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42901,7 +42904,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42951,7 +42954,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -43401,7 +43404,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -43451,7 +43454,7 @@
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="820" spans="1:16">
@@ -43551,7 +43554,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -43601,7 +43604,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -43651,7 +43654,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -43701,7 +43704,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -44851,7 +44854,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44901,7 +44904,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44951,7 +44954,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -45001,7 +45004,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -45051,7 +45054,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -45101,7 +45104,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -45151,7 +45154,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -45201,7 +45204,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -45251,7 +45254,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -46001,7 +46004,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -46051,7 +46054,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -46101,7 +46104,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -46351,7 +46354,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46401,7 +46404,7 @@
         <v>1</v>
       </c>
       <c r="P878" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="879" spans="1:16">
@@ -46451,7 +46454,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -46501,7 +46504,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -46551,7 +46554,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46601,7 +46604,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46651,7 +46654,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46701,7 +46704,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46751,7 +46754,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46801,7 +46804,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46851,7 +46854,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -47051,7 +47054,7 @@
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="892" spans="1:16">
@@ -47101,7 +47104,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -47151,7 +47154,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -47351,7 +47354,7 @@
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="898" spans="1:16">
@@ -47401,7 +47404,7 @@
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="899" spans="1:16">
@@ -47451,7 +47454,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -47501,7 +47504,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47551,7 +47554,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -47601,7 +47604,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -48501,7 +48504,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -48551,7 +48554,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -48651,7 +48654,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48701,7 +48704,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48751,7 +48754,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -49051,7 +49054,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -49101,7 +49104,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -49151,7 +49154,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -49201,7 +49204,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -49251,7 +49254,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -49401,7 +49404,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -49501,7 +49504,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -49551,7 +49554,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -49601,7 +49604,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49751,7 +49754,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49801,7 +49804,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -49851,7 +49854,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -50051,7 +50054,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -50101,7 +50104,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -50151,7 +50154,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -50201,7 +50204,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -50251,7 +50254,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -50601,7 +50604,7 @@
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="963" spans="1:16">
@@ -50651,7 +50654,7 @@
         <v>1</v>
       </c>
       <c r="P963" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="964" spans="1:16">
@@ -50701,7 +50704,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50751,7 +50754,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50951,7 +50954,7 @@
         <v>1</v>
       </c>
       <c r="P969" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="970" spans="1:16">
@@ -51001,7 +51004,7 @@
         <v>1</v>
       </c>
       <c r="P970" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="971" spans="1:16">
@@ -51501,7 +51504,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -51551,7 +51554,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -51601,7 +51604,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51651,7 +51654,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51701,7 +51704,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -52101,7 +52104,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -52301,7 +52304,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -52351,7 +52354,7 @@
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="998" spans="1:16">
@@ -52401,7 +52404,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -52451,7 +52454,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -53001,7 +53004,7 @@
         <v>1</v>
       </c>
       <c r="P1010" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="1011" spans="1:16">
@@ -53051,7 +53054,7 @@
         <v>1</v>
       </c>
       <c r="P1011" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="1012" spans="1:16">
@@ -53101,7 +53104,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -53751,7 +53754,7 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
@@ -53801,7 +53804,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53851,7 +53854,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -54751,7 +54754,7 @@
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
@@ -56101,7 +56104,7 @@
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
@@ -56151,7 +56154,7 @@
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1074" spans="1:16">
@@ -56551,7 +56554,7 @@
         <v>1</v>
       </c>
       <c r="P1081" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1082" spans="1:16">
@@ -56601,7 +56604,7 @@
         <v>1</v>
       </c>
       <c r="P1082" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1083" spans="1:16">
@@ -56651,7 +56654,7 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56701,7 +56704,7 @@
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56851,7 +56854,7 @@
         <v>1</v>
       </c>
       <c r="P1087" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1088" spans="1:16">
@@ -56901,7 +56904,7 @@
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56951,7 +56954,7 @@
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -57001,7 +57004,7 @@
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -57051,7 +57054,7 @@
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
@@ -57101,7 +57104,7 @@
         <v>1</v>
       </c>
       <c r="P1092" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1093" spans="1:16">
@@ -57465,10 +57468,10 @@
         <v>1.290045361797548</v>
       </c>
       <c r="D1100" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E1100">
-        <v>1.491724653627723</v>
+        <v>1.483704747015054</v>
       </c>
       <c r="F1100">
         <v>1</v>
@@ -57477,10 +57480,10 @@
         <v>0.01668995463820245</v>
       </c>
       <c r="H1100">
-        <v>0.01658827534637227</v>
+        <v>0.01611629525298495</v>
       </c>
       <c r="I1100">
-        <v>0.2016792918301746</v>
+        <v>0.1936593852175053</v>
       </c>
       <c r="J1100">
         <v>0.8922311284127985</v>
@@ -57492,10 +57495,10 @@
         <v>8.99</v>
       </c>
       <c r="M1100">
-        <v>8.460000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N1100">
-        <v>9.039999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O1100">
         <v>1</v>
@@ -57656,52 +57659,52 @@
     </row>
     <row r="1104" spans="1:16">
       <c r="A1104" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1104" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1104">
-        <v>2.137380482177424</v>
+        <v>1.617159803180474</v>
       </c>
       <c r="D1104" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E1104">
-        <v>1.852121306923722</v>
+        <v>1.812395357463129</v>
       </c>
       <c r="F1104">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1104">
-        <v>0.01564261951782258</v>
+        <v>0.01636284019681953</v>
       </c>
       <c r="H1104">
-        <v>0.01540787869307628</v>
+        <v>0.01626760464253687</v>
       </c>
       <c r="I1104">
-        <v>0.2852591752537013</v>
+        <v>0.1952355542826547</v>
       </c>
       <c r="J1104">
-        <v>0.8419725084566805</v>
+        <v>0.8543267898979752</v>
       </c>
       <c r="K1104">
-        <v>8.02</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L1104">
-        <v>8.890000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="M1104">
-        <v>8.050000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="N1104">
-        <v>8.630000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O1104">
         <v>1</v>
       </c>
       <c r="P1104" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1105" spans="1:16">
@@ -57712,28 +57715,28 @@
         <v>267</v>
       </c>
       <c r="C1105">
-        <v>2.278773215325976</v>
+        <v>2.137380482177424</v>
       </c>
       <c r="D1105" t="s">
-        <v>266</v>
+        <v>515</v>
       </c>
       <c r="E1105">
-        <v>1.875924295294658</v>
+        <v>1.852121306923722</v>
       </c>
       <c r="F1105">
         <v>-1</v>
       </c>
       <c r="G1105">
-        <v>0.01550122678467403</v>
+        <v>0.01564261951782258</v>
       </c>
       <c r="H1105">
-        <v>0.01610407570470534</v>
+        <v>0.01540787869307628</v>
       </c>
       <c r="I1105">
-        <v>0.4028489200313174</v>
+        <v>0.2852591752537013</v>
       </c>
       <c r="J1105">
-        <v>0.8243424918546166</v>
+        <v>0.8419725084566805</v>
       </c>
       <c r="K1105">
         <v>8.02</v>
@@ -57742,16 +57745,16 @@
         <v>8.890000000000001</v>
       </c>
       <c r="M1105">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="N1105">
         <v>8.630000000000001</v>
       </c>
-      <c r="N1105">
-        <v>8.99</v>
-      </c>
       <c r="O1105">
         <v>1</v>
       </c>
       <c r="P1105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="1106" spans="1:16">
@@ -57762,28 +57765,28 @@
         <v>267</v>
       </c>
       <c r="C1106">
-        <v>2.327682010882778</v>
+        <v>2.278773215325976</v>
       </c>
       <c r="D1106" t="s">
         <v>266</v>
       </c>
       <c r="E1106">
-        <v>1.928553086523488</v>
+        <v>1.875924295294658</v>
       </c>
       <c r="F1106">
         <v>-1</v>
       </c>
       <c r="G1106">
-        <v>0.01545231798911722</v>
+        <v>0.01550122678467403</v>
       </c>
       <c r="H1106">
-        <v>0.01605144691347651</v>
+        <v>0.01610407570470534</v>
       </c>
       <c r="I1106">
-        <v>0.3991289243592906</v>
+        <v>0.4028489200313174</v>
       </c>
       <c r="J1106">
-        <v>0.818244138293918</v>
+        <v>0.8243424918546166</v>
       </c>
       <c r="K1106">
         <v>8.02</v>
@@ -57801,7 +57804,7 @@
         <v>1</v>
       </c>
       <c r="P1106" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1107" spans="1:16">
@@ -57812,28 +57815,28 @@
         <v>267</v>
       </c>
       <c r="C1107">
-        <v>2.233426024675511</v>
+        <v>2.327682010882778</v>
       </c>
       <c r="D1107" t="s">
-        <v>515</v>
+        <v>266</v>
       </c>
       <c r="E1107">
-        <v>1.948526122024671</v>
+        <v>1.928553086523488</v>
       </c>
       <c r="F1107">
         <v>-1</v>
       </c>
       <c r="G1107">
-        <v>0.01554657397532449</v>
+        <v>0.01545231798911722</v>
       </c>
       <c r="H1107">
-        <v>0.01531147387797533</v>
+        <v>0.01605144691347651</v>
       </c>
       <c r="I1107">
-        <v>0.2848999026508396</v>
+        <v>0.3991289243592906</v>
       </c>
       <c r="J1107">
-        <v>0.8299967550279912</v>
+        <v>0.818244138293918</v>
       </c>
       <c r="K1107">
         <v>8.02</v>
@@ -57842,16 +57845,16 @@
         <v>8.890000000000001</v>
       </c>
       <c r="M1107">
-        <v>8.050000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="N1107">
-        <v>8.630000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="O1107">
         <v>1</v>
       </c>
       <c r="P1107" t="s">
-        <v>264</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1108" spans="1:16">
@@ -57859,48 +57862,98 @@
         <v>0</v>
       </c>
       <c r="B1108" t="s">
+        <v>267</v>
+      </c>
+      <c r="C1108">
+        <v>2.233426024675511</v>
+      </c>
+      <c r="D1108" t="s">
+        <v>515</v>
+      </c>
+      <c r="E1108">
+        <v>1.948526122024671</v>
+      </c>
+      <c r="F1108">
+        <v>-1</v>
+      </c>
+      <c r="G1108">
+        <v>0.01554657397532449</v>
+      </c>
+      <c r="H1108">
+        <v>0.01531147387797533</v>
+      </c>
+      <c r="I1108">
+        <v>0.2848999026508396</v>
+      </c>
+      <c r="J1108">
+        <v>0.8299967550279912</v>
+      </c>
+      <c r="K1108">
+        <v>8.02</v>
+      </c>
+      <c r="L1108">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M1108">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="N1108">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="O1108">
+        <v>1</v>
+      </c>
+      <c r="P1108" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:16">
+      <c r="A1109" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1109" t="s">
         <v>266</v>
       </c>
-      <c r="C1108">
+      <c r="C1109">
         <v>1.933692227743179</v>
       </c>
-      <c r="D1108" t="s">
+      <c r="D1109" t="s">
         <v>514</v>
       </c>
-      <c r="E1108">
+      <c r="E1109">
         <v>2.122692496721585</v>
       </c>
-      <c r="F1108">
-        <v>1</v>
-      </c>
-      <c r="G1108">
+      <c r="F1109">
+        <v>1</v>
+      </c>
+      <c r="G1109">
         <v>0.01604630777225682</v>
       </c>
-      <c r="H1108">
+      <c r="H1109">
         <v>0.01595730750327841</v>
       </c>
-      <c r="I1108">
+      <c r="I1109">
         <v>0.1890002689784067</v>
       </c>
-      <c r="J1108">
+      <c r="J1109">
         <v>0.8176486410494578</v>
       </c>
-      <c r="K1108">
+      <c r="K1109">
         <v>8.630000000000001</v>
       </c>
-      <c r="L1108">
+      <c r="L1109">
         <v>8.99</v>
       </c>
-      <c r="M1108">
+      <c r="M1109">
         <v>8.460000000000001</v>
       </c>
-      <c r="N1108">
+      <c r="N1109">
         <v>9.039999999999999</v>
       </c>
-      <c r="O1108">
-        <v>1</v>
-      </c>
-      <c r="P1108" t="s">
+      <c r="O1109">
+        <v>1</v>
+      </c>
+      <c r="P1109" t="s">
         <v>267</v>
       </c>
     </row>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3342" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3345" uniqueCount="712">
   <si>
     <t>trade_time</t>
   </si>
@@ -1561,7 +1561,7 @@
     <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-09-13</t>
+    <t>2021-09-14</t>
   </si>
   <si>
     <t>2016-07-19</t>
@@ -2507,7 +2507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1110"/>
+  <dimension ref="A1:P1111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -57271,7 +57271,7 @@
         <v>515</v>
       </c>
       <c r="E1096">
-        <v>1.844819200256151</v>
+        <v>1.732248538671191</v>
       </c>
       <c r="F1096">
         <v>-1</v>
@@ -57280,10 +57280,10 @@
         <v>0.01656453813434761</v>
       </c>
       <c r="H1096">
-        <v>0.01637518079974385</v>
+        <v>0.01570775146132881</v>
       </c>
       <c r="I1096">
-        <v>0.05064266539624107</v>
+        <v>0.1632133269812002</v>
       </c>
       <c r="J1096">
         <v>0.8669666825469986</v>
@@ -57295,10 +57295,10 @@
         <v>9.23</v>
       </c>
       <c r="M1096">
-        <v>8.380000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="N1096">
-        <v>9.109999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="O1096">
         <v>1</v>
@@ -57421,7 +57421,7 @@
         <v>515</v>
       </c>
       <c r="E1099">
-        <v>1.950741500654967</v>
+        <v>1.83412607342232</v>
       </c>
       <c r="F1099">
         <v>-1</v>
@@ -57430,10 +57430,10 @@
         <v>0.01645760464253687</v>
       </c>
       <c r="H1099">
-        <v>0.01626925849934503</v>
+        <v>0.01560587392657768</v>
       </c>
       <c r="I1099">
-        <v>0.05165385680816303</v>
+        <v>0.16826928404081</v>
       </c>
       <c r="J1099">
         <v>0.8543267898979752</v>
@@ -57445,10 +57445,10 @@
         <v>9.23</v>
       </c>
       <c r="M1099">
-        <v>8.380000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="N1099">
-        <v>9.109999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="O1099">
         <v>1</v>
@@ -57571,7 +57571,7 @@
         <v>515</v>
       </c>
       <c r="E1102">
-        <v>2.054270379133016</v>
+        <v>1.933701581839156</v>
       </c>
       <c r="F1102">
         <v>-1</v>
@@ -57580,10 +57580,10 @@
         <v>0.01635308742154352</v>
       </c>
       <c r="H1102">
-        <v>0.01616572962086698</v>
+        <v>0.01550629841816085</v>
       </c>
       <c r="I1102">
-        <v>0.0526421993234667</v>
+        <v>0.1732109966173274</v>
       </c>
       <c r="J1102">
         <v>0.8419725084566805</v>
@@ -57595,10 +57595,10 @@
         <v>9.23</v>
       </c>
       <c r="M1102">
-        <v>8.380000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="N1102">
-        <v>9.109999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="O1102">
         <v>1</v>
@@ -57662,43 +57662,43 @@
         <v>1</v>
       </c>
       <c r="B1104" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C1104">
-        <v>2.256062518909943</v>
+        <v>1.875924295294658</v>
       </c>
       <c r="D1104" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E1104">
-        <v>2.202009918258311</v>
+        <v>2.066062518909942</v>
       </c>
       <c r="F1104">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1104">
-        <v>0.01620393748109006</v>
+        <v>0.01610407570470534</v>
       </c>
       <c r="H1104">
-        <v>0.01601799008174169</v>
+        <v>0.01601393748109006</v>
       </c>
       <c r="I1104">
-        <v>0.05405260065163198</v>
+        <v>0.1901382236152838</v>
       </c>
       <c r="J1104">
         <v>0.8243424918546166</v>
       </c>
       <c r="K1104">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="L1104">
+        <v>8.99</v>
+      </c>
+      <c r="M1104">
         <v>8.460000000000001</v>
       </c>
-      <c r="L1104">
-        <v>9.23</v>
-      </c>
-      <c r="M1104">
-        <v>8.380000000000001</v>
-      </c>
       <c r="N1104">
-        <v>9.109999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O1104">
         <v>1</v>
@@ -57709,96 +57709,96 @@
     </row>
     <row r="1105" spans="1:16">
       <c r="A1105" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1105" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C1105">
-        <v>2.327682010882778</v>
+        <v>2.256062518909943</v>
       </c>
       <c r="D1105" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E1105">
-        <v>2.043134686733961</v>
+        <v>2.075799515651791</v>
       </c>
       <c r="F1105">
         <v>-1</v>
       </c>
       <c r="G1105">
-        <v>0.01545231798911722</v>
+        <v>0.01620393748109006</v>
       </c>
       <c r="H1105">
-        <v>0.01521686531326604</v>
+        <v>0.01536420048434821</v>
       </c>
       <c r="I1105">
-        <v>0.2845473241488179</v>
+        <v>0.1802630032581529</v>
       </c>
       <c r="J1105">
-        <v>0.818244138293918</v>
+        <v>0.8243424918546166</v>
       </c>
       <c r="K1105">
-        <v>8.02</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L1105">
-        <v>8.890000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="M1105">
-        <v>8.050000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="N1105">
-        <v>8.630000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="O1105">
         <v>1</v>
       </c>
       <c r="P1105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1106" spans="1:16">
       <c r="A1106" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1106" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C1106">
-        <v>2.307654590033454</v>
+        <v>2.327682010882778</v>
       </c>
       <c r="D1106" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E1106">
-        <v>2.253114121096966</v>
+        <v>2.043134686733961</v>
       </c>
       <c r="F1106">
         <v>-1</v>
       </c>
       <c r="G1106">
-        <v>0.01615234540996655</v>
+        <v>0.01545231798911722</v>
       </c>
       <c r="H1106">
-        <v>0.01596688587890303</v>
+        <v>0.01521686531326604</v>
       </c>
       <c r="I1106">
-        <v>0.05454046893648723</v>
+        <v>0.2845473241488179</v>
       </c>
       <c r="J1106">
         <v>0.818244138293918</v>
       </c>
       <c r="K1106">
-        <v>8.460000000000001</v>
+        <v>8.02</v>
       </c>
       <c r="L1106">
-        <v>9.23</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M1106">
-        <v>8.380000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N1106">
-        <v>9.109999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="O1106">
         <v>1</v>
@@ -57809,96 +57809,96 @@
     </row>
     <row r="1107" spans="1:16">
       <c r="A1107" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1107" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C1107">
-        <v>2.233426024675511</v>
+        <v>2.307654590033454</v>
       </c>
       <c r="D1107" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E1107">
-        <v>1.948526122024671</v>
+        <v>2.124952245351022</v>
       </c>
       <c r="F1107">
         <v>-1</v>
       </c>
       <c r="G1107">
-        <v>0.01554657397532449</v>
+        <v>0.01615234540996655</v>
       </c>
       <c r="H1107">
-        <v>0.01531147387797533</v>
+        <v>0.01531504775464898</v>
       </c>
       <c r="I1107">
-        <v>0.2848999026508396</v>
+        <v>0.1827023446824318</v>
       </c>
       <c r="J1107">
-        <v>0.8299967550279912</v>
+        <v>0.818244138293918</v>
       </c>
       <c r="K1107">
-        <v>8.02</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L1107">
-        <v>8.890000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="M1107">
-        <v>8.050000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="N1107">
-        <v>8.630000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="O1107">
         <v>1</v>
       </c>
       <c r="P1107" t="s">
-        <v>262</v>
+        <v>509</v>
       </c>
     </row>
     <row r="1108" spans="1:16">
       <c r="A1108" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1108" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1108">
-        <v>1.827128004108435</v>
+        <v>2.233426024675511</v>
       </c>
       <c r="D1108" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E1108">
-        <v>2.037827063066555</v>
+        <v>1.948526122024671</v>
       </c>
       <c r="F1108">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1108">
-        <v>0.01615287199589157</v>
+        <v>0.01554657397532449</v>
       </c>
       <c r="H1108">
-        <v>0.01588217293693345</v>
+        <v>0.01531147387797533</v>
       </c>
       <c r="I1108">
-        <v>0.2106990589581192</v>
+        <v>0.2848999026508396</v>
       </c>
       <c r="J1108">
         <v>0.8299967550279912</v>
       </c>
       <c r="K1108">
+        <v>8.02</v>
+      </c>
+      <c r="L1108">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M1108">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="N1108">
         <v>8.630000000000001</v>
-      </c>
-      <c r="L1108">
-        <v>8.99</v>
-      </c>
-      <c r="M1108">
-        <v>8.34</v>
-      </c>
-      <c r="N1108">
-        <v>8.960000000000001</v>
       </c>
       <c r="O1108">
         <v>1</v>
@@ -57909,46 +57909,46 @@
     </row>
     <row r="1109" spans="1:16">
       <c r="A1109" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1109" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C1109">
-        <v>2.208227452463194</v>
+        <v>1.827128004108435</v>
       </c>
       <c r="D1109" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E1109">
-        <v>2.154627192865433</v>
+        <v>2.037827063066555</v>
       </c>
       <c r="F1109">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1109">
-        <v>0.01625177254753681</v>
+        <v>0.01615287199589157</v>
       </c>
       <c r="H1109">
-        <v>0.01606537280713457</v>
+        <v>0.01588217293693345</v>
       </c>
       <c r="I1109">
-        <v>0.05360025959776138</v>
+        <v>0.2106990589581192</v>
       </c>
       <c r="J1109">
         <v>0.8299967550279912</v>
       </c>
       <c r="K1109">
-        <v>8.460000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L1109">
-        <v>9.23</v>
+        <v>8.99</v>
       </c>
       <c r="M1109">
-        <v>8.380000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="N1109">
-        <v>9.109999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O1109">
         <v>1</v>
@@ -57959,51 +57959,101 @@
     </row>
     <row r="1110" spans="1:16">
       <c r="A1110" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1110" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1110">
+        <v>2.208227452463194</v>
+      </c>
+      <c r="D1110" t="s">
+        <v>515</v>
+      </c>
+      <c r="E1110">
+        <v>2.030226154474391</v>
+      </c>
+      <c r="F1110">
+        <v>-1</v>
+      </c>
+      <c r="G1110">
+        <v>0.01625177254753681</v>
+      </c>
+      <c r="H1110">
+        <v>0.01540977384552561</v>
+      </c>
+      <c r="I1110">
+        <v>0.1780012979888026</v>
+      </c>
+      <c r="J1110">
+        <v>0.8299967550279912</v>
+      </c>
+      <c r="K1110">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="L1110">
+        <v>9.23</v>
+      </c>
+      <c r="M1110">
+        <v>8.06</v>
+      </c>
+      <c r="N1110">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="O1110">
+        <v>1</v>
+      </c>
+      <c r="P1110" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:16">
+      <c r="A1111" s="1">
         <v>0</v>
       </c>
-      <c r="B1110" t="s">
+      <c r="B1111" t="s">
         <v>264</v>
       </c>
-      <c r="C1110">
+      <c r="C1111">
         <v>1.933692227743179</v>
       </c>
-      <c r="D1110" t="s">
+      <c r="D1111" t="s">
         <v>266</v>
       </c>
-      <c r="E1110">
+      <c r="E1111">
         <v>2.312692496721587</v>
       </c>
-      <c r="F1110">
-        <v>1</v>
-      </c>
-      <c r="G1110">
+      <c r="F1111">
+        <v>1</v>
+      </c>
+      <c r="G1111">
         <v>0.01604630777225682</v>
       </c>
-      <c r="H1110">
+      <c r="H1111">
         <v>0.01614730750327841</v>
       </c>
-      <c r="I1110">
+      <c r="I1111">
         <v>0.379000268978408</v>
       </c>
-      <c r="J1110">
+      <c r="J1111">
         <v>0.8176486410494578</v>
       </c>
-      <c r="K1110">
+      <c r="K1111">
         <v>8.630000000000001</v>
       </c>
-      <c r="L1110">
+      <c r="L1111">
         <v>8.99</v>
       </c>
-      <c r="M1110">
+      <c r="M1111">
         <v>8.460000000000001</v>
       </c>
-      <c r="N1110">
+      <c r="N1111">
         <v>9.23</v>
       </c>
-      <c r="O1110">
-        <v>1</v>
-      </c>
-      <c r="P1110" t="s">
+      <c r="O1111">
+        <v>1</v>
+      </c>
+      <c r="P1111" t="s">
         <v>265</v>
       </c>
     </row>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3345" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3348" uniqueCount="712">
   <si>
     <t>trade_time</t>
   </si>
@@ -1561,7 +1561,7 @@
     <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-09-14</t>
+    <t>2021-09-15</t>
   </si>
   <si>
     <t>2016-07-19</t>
@@ -2507,7 +2507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1111"/>
+  <dimension ref="A1:P1112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -57271,7 +57271,7 @@
         <v>515</v>
       </c>
       <c r="E1096">
-        <v>1.732248538671191</v>
+        <v>1.80628454057683</v>
       </c>
       <c r="F1096">
         <v>-1</v>
@@ -57280,10 +57280,10 @@
         <v>0.01656453813434761</v>
       </c>
       <c r="H1096">
-        <v>0.01570775146132881</v>
+        <v>0.01557371545942317</v>
       </c>
       <c r="I1096">
-        <v>0.1632133269812002</v>
+        <v>0.08917732507556142</v>
       </c>
       <c r="J1096">
         <v>0.8669666825469986</v>
@@ -57295,10 +57295,10 @@
         <v>9.23</v>
       </c>
       <c r="M1096">
-        <v>8.06</v>
+        <v>7.94</v>
       </c>
       <c r="N1096">
-        <v>8.720000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="O1096">
         <v>1</v>
@@ -57368,10 +57368,10 @@
         <v>1.617159803180474</v>
       </c>
       <c r="D1098" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E1098">
-        <v>1.812395357463129</v>
+        <v>1.834914572250888</v>
       </c>
       <c r="F1098">
         <v>1</v>
@@ -57380,10 +57380,10 @@
         <v>0.01636284019681953</v>
       </c>
       <c r="H1098">
-        <v>0.01626760464253687</v>
+        <v>0.01608508542774911</v>
       </c>
       <c r="I1098">
-        <v>0.1952355542826547</v>
+        <v>0.2177547690704138</v>
       </c>
       <c r="J1098">
         <v>0.8543267898979752</v>
@@ -57395,10 +57395,10 @@
         <v>8.99</v>
       </c>
       <c r="M1098">
-        <v>8.460000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="N1098">
-        <v>9.039999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O1098">
         <v>1</v>
@@ -57421,7 +57421,7 @@
         <v>515</v>
       </c>
       <c r="E1099">
-        <v>1.83412607342232</v>
+        <v>1.906645288210076</v>
       </c>
       <c r="F1099">
         <v>-1</v>
@@ -57430,10 +57430,10 @@
         <v>0.01645760464253687</v>
       </c>
       <c r="H1099">
-        <v>0.01560587392657768</v>
+        <v>0.01547335471178992</v>
       </c>
       <c r="I1099">
-        <v>0.16826928404081</v>
+        <v>0.09575006925305374</v>
       </c>
       <c r="J1099">
         <v>0.8543267898979752</v>
@@ -57445,10 +57445,10 @@
         <v>9.23</v>
       </c>
       <c r="M1099">
-        <v>8.06</v>
+        <v>7.94</v>
       </c>
       <c r="N1099">
-        <v>8.720000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="O1099">
         <v>1</v>
@@ -57571,7 +57571,7 @@
         <v>515</v>
       </c>
       <c r="E1102">
-        <v>1.933701581839156</v>
+        <v>2.004738282853956</v>
       </c>
       <c r="F1102">
         <v>-1</v>
@@ -57580,10 +57580,10 @@
         <v>0.01635308742154352</v>
       </c>
       <c r="H1102">
-        <v>0.01550629841816085</v>
+        <v>0.01537526171714604</v>
       </c>
       <c r="I1102">
-        <v>0.1732109966173274</v>
+        <v>0.1021742956025271</v>
       </c>
       <c r="J1102">
         <v>0.8419725084566805</v>
@@ -57595,10 +57595,10 @@
         <v>9.23</v>
       </c>
       <c r="M1102">
-        <v>8.06</v>
+        <v>7.94</v>
       </c>
       <c r="N1102">
-        <v>8.720000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="O1102">
         <v>1</v>
@@ -57721,7 +57721,7 @@
         <v>515</v>
       </c>
       <c r="E1105">
-        <v>2.075799515651791</v>
+        <v>2.144720614674343</v>
       </c>
       <c r="F1105">
         <v>-1</v>
@@ -57730,10 +57730,10 @@
         <v>0.01620393748109006</v>
       </c>
       <c r="H1105">
-        <v>0.01536420048434821</v>
+        <v>0.01523527938532566</v>
       </c>
       <c r="I1105">
-        <v>0.1802630032581529</v>
+        <v>0.1113419042356005</v>
       </c>
       <c r="J1105">
         <v>0.8243424918546166</v>
@@ -57745,10 +57745,10 @@
         <v>9.23</v>
       </c>
       <c r="M1105">
-        <v>8.06</v>
+        <v>7.94</v>
       </c>
       <c r="N1105">
-        <v>8.720000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="O1105">
         <v>1</v>
@@ -57812,43 +57812,43 @@
         <v>1</v>
       </c>
       <c r="B1107" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C1107">
-        <v>2.307654590033454</v>
+        <v>1.928553086523488</v>
       </c>
       <c r="D1107" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E1107">
-        <v>2.124952245351022</v>
+        <v>2.117654590033452</v>
       </c>
       <c r="F1107">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1107">
-        <v>0.01615234540996655</v>
+        <v>0.01605144691347651</v>
       </c>
       <c r="H1107">
-        <v>0.01531504775464898</v>
+        <v>0.01596234540996655</v>
       </c>
       <c r="I1107">
-        <v>0.1827023446824318</v>
+        <v>0.1891015035099644</v>
       </c>
       <c r="J1107">
         <v>0.818244138293918</v>
       </c>
       <c r="K1107">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="L1107">
+        <v>8.99</v>
+      </c>
+      <c r="M1107">
         <v>8.460000000000001</v>
       </c>
-      <c r="L1107">
-        <v>9.23</v>
-      </c>
-      <c r="M1107">
-        <v>8.06</v>
-      </c>
       <c r="N1107">
-        <v>8.720000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O1107">
         <v>1</v>
@@ -57859,96 +57859,96 @@
     </row>
     <row r="1108" spans="1:16">
       <c r="A1108" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1108" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C1108">
-        <v>2.233426024675511</v>
+        <v>2.307654590033454</v>
       </c>
       <c r="D1108" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E1108">
-        <v>1.948526122024671</v>
+        <v>2.19314154194629</v>
       </c>
       <c r="F1108">
         <v>-1</v>
       </c>
       <c r="G1108">
-        <v>0.01554657397532449</v>
+        <v>0.01615234540996655</v>
       </c>
       <c r="H1108">
-        <v>0.01531147387797533</v>
+        <v>0.01518685845805371</v>
       </c>
       <c r="I1108">
-        <v>0.2848999026508396</v>
+        <v>0.1145130480871632</v>
       </c>
       <c r="J1108">
-        <v>0.8299967550279912</v>
+        <v>0.818244138293918</v>
       </c>
       <c r="K1108">
-        <v>8.02</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L1108">
-        <v>8.890000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="M1108">
-        <v>8.050000000000001</v>
+        <v>7.94</v>
       </c>
       <c r="N1108">
-        <v>8.630000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="O1108">
         <v>1</v>
       </c>
       <c r="P1108" t="s">
-        <v>262</v>
+        <v>509</v>
       </c>
     </row>
     <row r="1109" spans="1:16">
       <c r="A1109" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1109" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1109">
-        <v>1.827128004108435</v>
+        <v>2.233426024675511</v>
       </c>
       <c r="D1109" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E1109">
-        <v>2.037827063066555</v>
+        <v>1.948526122024671</v>
       </c>
       <c r="F1109">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1109">
-        <v>0.01615287199589157</v>
+        <v>0.01554657397532449</v>
       </c>
       <c r="H1109">
-        <v>0.01588217293693345</v>
+        <v>0.01531147387797533</v>
       </c>
       <c r="I1109">
-        <v>0.2106990589581192</v>
+        <v>0.2848999026508396</v>
       </c>
       <c r="J1109">
         <v>0.8299967550279912</v>
       </c>
       <c r="K1109">
+        <v>8.02</v>
+      </c>
+      <c r="L1109">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M1109">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="N1109">
         <v>8.630000000000001</v>
-      </c>
-      <c r="L1109">
-        <v>8.99</v>
-      </c>
-      <c r="M1109">
-        <v>8.34</v>
-      </c>
-      <c r="N1109">
-        <v>8.960000000000001</v>
       </c>
       <c r="O1109">
         <v>1</v>
@@ -57959,46 +57959,46 @@
     </row>
     <row r="1110" spans="1:16">
       <c r="A1110" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1110" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C1110">
-        <v>2.208227452463194</v>
+        <v>1.827128004108435</v>
       </c>
       <c r="D1110" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E1110">
-        <v>2.030226154474391</v>
+        <v>2.037827063066555</v>
       </c>
       <c r="F1110">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1110">
-        <v>0.01625177254753681</v>
+        <v>0.01615287199589157</v>
       </c>
       <c r="H1110">
-        <v>0.01540977384552561</v>
+        <v>0.01588217293693345</v>
       </c>
       <c r="I1110">
-        <v>0.1780012979888026</v>
+        <v>0.2106990589581192</v>
       </c>
       <c r="J1110">
         <v>0.8299967550279912</v>
       </c>
       <c r="K1110">
-        <v>8.460000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L1110">
-        <v>9.23</v>
+        <v>8.99</v>
       </c>
       <c r="M1110">
-        <v>8.06</v>
+        <v>8.34</v>
       </c>
       <c r="N1110">
-        <v>8.720000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O1110">
         <v>1</v>
@@ -58009,51 +58009,101 @@
     </row>
     <row r="1111" spans="1:16">
       <c r="A1111" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1111" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1111">
+        <v>2.208227452463194</v>
+      </c>
+      <c r="D1111" t="s">
+        <v>515</v>
+      </c>
+      <c r="E1111">
+        <v>2.099825765077749</v>
+      </c>
+      <c r="F1111">
+        <v>-1</v>
+      </c>
+      <c r="G1111">
+        <v>0.01625177254753681</v>
+      </c>
+      <c r="H1111">
+        <v>0.01528017423492225</v>
+      </c>
+      <c r="I1111">
+        <v>0.1084016873854452</v>
+      </c>
+      <c r="J1111">
+        <v>0.8299967550279912</v>
+      </c>
+      <c r="K1111">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="L1111">
+        <v>9.23</v>
+      </c>
+      <c r="M1111">
+        <v>7.94</v>
+      </c>
+      <c r="N1111">
+        <v>8.69</v>
+      </c>
+      <c r="O1111">
+        <v>1</v>
+      </c>
+      <c r="P1111" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:16">
+      <c r="A1112" s="1">
         <v>0</v>
       </c>
-      <c r="B1111" t="s">
+      <c r="B1112" t="s">
         <v>264</v>
       </c>
-      <c r="C1111">
+      <c r="C1112">
         <v>1.933692227743179</v>
       </c>
-      <c r="D1111" t="s">
+      <c r="D1112" t="s">
         <v>266</v>
       </c>
-      <c r="E1111">
+      <c r="E1112">
         <v>2.312692496721587</v>
       </c>
-      <c r="F1111">
-        <v>1</v>
-      </c>
-      <c r="G1111">
+      <c r="F1112">
+        <v>1</v>
+      </c>
+      <c r="G1112">
         <v>0.01604630777225682</v>
       </c>
-      <c r="H1111">
+      <c r="H1112">
         <v>0.01614730750327841</v>
       </c>
-      <c r="I1111">
+      <c r="I1112">
         <v>0.379000268978408</v>
       </c>
-      <c r="J1111">
+      <c r="J1112">
         <v>0.8176486410494578</v>
       </c>
-      <c r="K1111">
+      <c r="K1112">
         <v>8.630000000000001</v>
       </c>
-      <c r="L1111">
+      <c r="L1112">
         <v>8.99</v>
       </c>
-      <c r="M1111">
+      <c r="M1112">
         <v>8.460000000000001</v>
       </c>
-      <c r="N1111">
+      <c r="N1112">
         <v>9.23</v>
       </c>
-      <c r="O1111">
-        <v>1</v>
-      </c>
-      <c r="P1111" t="s">
+      <c r="O1112">
+        <v>1</v>
+      </c>
+      <c r="P1112" t="s">
         <v>265</v>
       </c>
     </row>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3354" uniqueCount="713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3342" uniqueCount="713">
   <si>
     <t>trade_time</t>
   </si>
@@ -811,15 +811,15 @@
     <t>2021-09-02</t>
   </si>
   <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
     <t>2021-09-16</t>
   </si>
   <si>
     <t>2021-09-10</t>
   </si>
   <si>
-    <t>2021-08-30</t>
-  </si>
-  <si>
     <t>2016-07-27</t>
   </si>
   <si>
@@ -1558,12 +1558,15 @@
     <t>2021-09-03</t>
   </si>
   <si>
-    <t>2021-09-17</t>
+    <t>2021-09-23</t>
   </si>
   <si>
     <t>2021-09-09</t>
   </si>
   <si>
+    <t>2021-09-14</t>
+  </si>
+  <si>
     <t>2016-07-20</t>
   </si>
   <si>
@@ -2150,9 +2153,6 @@
   </si>
   <si>
     <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-09-14</t>
   </si>
 </sst>
 </file>
@@ -2510,7 +2510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1114"/>
+  <dimension ref="A1:P1110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2607,7 +2607,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2657,7 +2657,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2707,7 +2707,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2757,7 +2757,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2807,7 +2807,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2857,7 +2857,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -3107,7 +3107,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3157,7 +3157,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3207,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -3307,7 +3307,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3357,7 +3357,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3407,7 +3407,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3457,7 +3457,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3507,7 +3507,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3557,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3607,7 +3607,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3657,7 +3657,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3707,7 +3707,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3757,7 +3757,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3807,7 +3807,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3857,7 +3857,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3907,7 +3907,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3957,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -4007,7 +4007,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -4057,7 +4057,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -4107,7 +4107,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -4157,7 +4157,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4207,7 +4207,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -4257,7 +4257,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4307,7 +4307,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4357,7 +4357,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4407,7 +4407,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4457,7 +4457,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4507,7 +4507,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4557,7 +4557,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4607,7 +4607,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4657,7 +4657,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4807,7 +4807,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4857,7 +4857,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4907,7 +4907,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4957,7 +4957,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -5007,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -5057,7 +5057,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -5107,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -5257,7 +5257,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -5307,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -5457,7 +5457,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5507,7 +5507,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5557,7 +5557,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5607,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5657,7 +5657,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5707,7 +5707,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5857,7 +5857,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5907,7 +5907,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5957,7 +5957,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -6007,7 +6007,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -6057,7 +6057,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -6107,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -6157,7 +6157,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -6207,7 +6207,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -6257,7 +6257,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -6307,7 +6307,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6357,7 +6357,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -6407,7 +6407,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6457,7 +6457,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6707,7 +6707,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6757,7 +6757,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6807,7 +6807,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6957,7 +6957,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -7007,7 +7007,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -9007,7 +9007,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -9057,7 +9057,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -9107,7 +9107,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -9557,7 +9557,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9607,7 +9607,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9657,7 +9657,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9707,7 +9707,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9757,7 +9757,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9957,7 +9957,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -10007,7 +10007,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -10057,7 +10057,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -10257,7 +10257,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -10307,7 +10307,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -10357,7 +10357,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -10407,7 +10407,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -10707,7 +10707,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10757,7 +10757,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10807,7 +10807,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10857,7 +10857,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10907,7 +10907,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -11157,7 +11157,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -11207,7 +11207,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -11257,7 +11257,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -11307,7 +11307,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -12707,7 +12707,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12757,7 +12757,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12807,7 +12807,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12857,7 +12857,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12907,7 +12907,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12957,7 +12957,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -13407,7 +13407,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -13457,7 +13457,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13607,7 +13607,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -13657,7 +13657,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -13707,7 +13707,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -14157,7 +14157,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -14207,7 +14207,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -14257,7 +14257,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -14307,7 +14307,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -14357,7 +14357,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -15307,7 +15307,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -15357,7 +15357,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -15407,7 +15407,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -15457,7 +15457,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -15507,7 +15507,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -15557,7 +15557,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -16357,7 +16357,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -16407,7 +16407,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -16457,7 +16457,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -16507,7 +16507,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -16557,7 +16557,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -17057,7 +17057,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -17107,7 +17107,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -17157,7 +17157,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -17207,7 +17207,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -17257,7 +17257,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -17307,7 +17307,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -17357,7 +17357,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -18857,7 +18857,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18907,7 +18907,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18957,7 +18957,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -19007,7 +19007,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -19057,7 +19057,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -19107,7 +19107,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -19157,7 +19157,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -20807,7 +20807,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20857,7 +20857,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -21057,7 +21057,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -21107,7 +21107,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -21157,7 +21157,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -21207,7 +21207,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -21357,7 +21357,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -21407,7 +21407,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21457,7 +21457,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21607,7 +21607,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21657,7 +21657,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21707,7 +21707,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21957,7 +21957,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -22007,7 +22007,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -22057,7 +22057,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -22107,7 +22107,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -22157,7 +22157,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -22207,7 +22207,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -22257,7 +22257,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -22307,7 +22307,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -22357,7 +22357,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -22407,7 +22407,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -22457,7 +22457,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -22507,7 +22507,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -22557,7 +22557,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22657,7 +22657,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22707,7 +22707,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22757,7 +22757,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22807,7 +22807,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22857,7 +22857,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22907,7 +22907,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22957,7 +22957,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -23007,7 +23007,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -23457,7 +23457,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23507,7 +23507,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23557,7 +23557,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -23757,7 +23757,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23807,7 +23807,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23857,7 +23857,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23907,7 +23907,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23957,7 +23957,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -24007,7 +24007,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -24057,7 +24057,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -24107,7 +24107,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -24157,7 +24157,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -24207,7 +24207,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -24257,7 +24257,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -24307,7 +24307,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24357,7 +24357,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24407,7 +24407,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24457,7 +24457,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24507,7 +24507,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24557,7 +24557,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24607,7 +24607,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24657,7 +24657,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24707,7 +24707,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -25207,7 +25207,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25257,7 +25257,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -25307,7 +25307,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -25357,7 +25357,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -25407,7 +25407,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -25657,7 +25657,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25707,7 +25707,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25757,7 +25757,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25807,7 +25807,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25857,7 +25857,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25907,7 +25907,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25957,7 +25957,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -26007,7 +26007,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -26057,7 +26057,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -26107,7 +26107,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -26157,7 +26157,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -26207,7 +26207,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -26257,7 +26257,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26307,7 +26307,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26507,7 +26507,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -26557,7 +26557,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -26607,7 +26607,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26657,7 +26657,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -27207,7 +27207,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -27257,7 +27257,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -27307,7 +27307,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -27357,7 +27357,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -27407,7 +27407,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -27657,7 +27657,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27707,7 +27707,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27757,7 +27757,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27807,7 +27807,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -28007,7 +28007,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -28057,7 +28057,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -28107,7 +28107,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -28157,7 +28157,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -28207,7 +28207,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28257,7 +28257,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -28307,7 +28307,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -28607,7 +28607,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28657,7 +28657,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28707,7 +28707,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28757,7 +28757,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28907,7 +28907,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28957,7 +28957,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -29007,7 +29007,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -29057,7 +29057,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -29107,7 +29107,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -29257,7 +29257,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -29307,7 +29307,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29457,7 +29457,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -29507,7 +29507,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -29557,7 +29557,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -29607,7 +29607,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29657,7 +29657,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29707,7 +29707,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29757,7 +29757,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -29807,7 +29807,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -30057,7 +30057,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -30107,7 +30107,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -30157,7 +30157,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -30207,7 +30207,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -30257,7 +30257,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -30307,7 +30307,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30357,7 +30357,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30407,7 +30407,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -30457,7 +30457,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -30507,7 +30507,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -30557,7 +30557,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30607,7 +30607,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -30657,7 +30657,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -30707,7 +30707,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30757,7 +30757,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30807,7 +30807,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -31057,7 +31057,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -31107,7 +31107,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -31307,7 +31307,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31357,7 +31357,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31407,7 +31407,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31457,7 +31457,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -31507,7 +31507,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -31557,7 +31557,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -31607,7 +31607,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -31657,7 +31657,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31707,7 +31707,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31857,7 +31857,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31907,7 +31907,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -32107,7 +32107,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -32157,7 +32157,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -32357,7 +32357,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -32407,7 +32407,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -32457,7 +32457,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -32507,7 +32507,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32557,7 +32557,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -32657,7 +32657,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32707,7 +32707,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32757,7 +32757,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32807,7 +32807,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -33057,7 +33057,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -33107,7 +33107,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -33157,7 +33157,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -33507,7 +33507,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -33557,7 +33557,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -33607,7 +33607,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -34557,7 +34557,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -34607,7 +34607,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -34657,7 +34657,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -34707,7 +34707,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34907,7 +34907,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34957,7 +34957,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -35007,7 +35007,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -35807,7 +35807,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35857,7 +35857,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35907,7 +35907,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35957,7 +35957,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -36007,7 +36007,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -36057,7 +36057,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -36107,7 +36107,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -36157,7 +36157,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -36207,7 +36207,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -36257,7 +36257,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -36307,7 +36307,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -36357,7 +36357,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -36407,7 +36407,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -36457,7 +36457,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36557,7 +36557,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36607,7 +36607,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36657,7 +36657,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36707,7 +36707,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36757,7 +36757,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36807,7 +36807,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36857,7 +36857,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -37057,7 +37057,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -37107,7 +37107,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -37157,7 +37157,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -37607,7 +37607,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37657,7 +37657,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37707,7 +37707,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37757,7 +37757,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37957,7 +37957,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -38007,7 +38007,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -38057,7 +38057,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -38107,7 +38107,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -38157,7 +38157,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -38207,7 +38207,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -38257,7 +38257,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -38307,7 +38307,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -38357,7 +38357,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -38407,7 +38407,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -38457,7 +38457,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -38507,7 +38507,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -39507,7 +39507,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -39557,7 +39557,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -39607,7 +39607,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39657,7 +39657,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39907,7 +39907,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39957,7 +39957,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -40007,7 +40007,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -40057,7 +40057,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -40257,7 +40257,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -40307,7 +40307,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40357,7 +40357,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -40457,7 +40457,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -40807,7 +40807,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -40857,7 +40857,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40907,7 +40907,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40957,7 +40957,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -41007,7 +41007,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -41057,7 +41057,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -41107,7 +41107,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -41157,7 +41157,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -41207,7 +41207,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -41257,7 +41257,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -41507,7 +41507,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41557,7 +41557,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41607,7 +41607,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41907,7 +41907,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41957,7 +41957,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -42007,7 +42007,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -42257,7 +42257,7 @@
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="796" spans="1:16">
@@ -42307,7 +42307,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -42357,7 +42357,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -42407,7 +42407,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -42457,7 +42457,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -42907,7 +42907,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42957,7 +42957,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -43057,7 +43057,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -43107,7 +43107,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -43157,7 +43157,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -43207,7 +43207,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -44357,7 +44357,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -44407,7 +44407,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -44457,7 +44457,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -44507,7 +44507,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -44557,7 +44557,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -44607,7 +44607,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -44657,7 +44657,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44707,7 +44707,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44757,7 +44757,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -45507,7 +45507,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -45557,7 +45557,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -45607,7 +45607,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45857,7 +45857,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45907,7 +45907,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45957,7 +45957,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -46007,7 +46007,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -46057,7 +46057,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -46107,7 +46107,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -46157,7 +46157,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -46207,7 +46207,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -46257,7 +46257,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -46307,7 +46307,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -46357,7 +46357,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46557,7 +46557,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46607,7 +46607,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46657,7 +46657,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46857,7 +46857,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46907,7 +46907,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46957,7 +46957,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -47007,7 +47007,7 @@
         <v>1</v>
       </c>
       <c r="P890" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="891" spans="1:16">
@@ -47057,7 +47057,7 @@
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="892" spans="1:16">
@@ -47107,7 +47107,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -48007,7 +48007,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -48057,7 +48057,7 @@
         <v>1</v>
       </c>
       <c r="P911" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="912" spans="1:16">
@@ -48157,7 +48157,7 @@
         <v>1</v>
       </c>
       <c r="P913" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="914" spans="1:16">
@@ -48207,7 +48207,7 @@
         <v>1</v>
       </c>
       <c r="P914" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="915" spans="1:16">
@@ -48257,7 +48257,7 @@
         <v>1</v>
       </c>
       <c r="P915" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="916" spans="1:16">
@@ -48557,7 +48557,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -48607,7 +48607,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48657,7 +48657,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48707,7 +48707,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48757,7 +48757,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48907,7 +48907,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -49007,7 +49007,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -49057,7 +49057,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -49107,7 +49107,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -49257,7 +49257,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -49307,7 +49307,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -49357,7 +49357,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -49557,7 +49557,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -49607,7 +49607,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49657,7 +49657,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49707,7 +49707,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49757,7 +49757,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -50107,7 +50107,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -50157,7 +50157,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -50207,7 +50207,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -50257,7 +50257,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -50457,7 +50457,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -50507,7 +50507,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -51007,7 +51007,7 @@
         <v>1</v>
       </c>
       <c r="P970" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="971" spans="1:16">
@@ -51057,7 +51057,7 @@
         <v>1</v>
       </c>
       <c r="P971" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="972" spans="1:16">
@@ -51107,7 +51107,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -51157,7 +51157,7 @@
         <v>1</v>
       </c>
       <c r="P973" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="974" spans="1:16">
@@ -51207,7 +51207,7 @@
         <v>1</v>
       </c>
       <c r="P974" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="975" spans="1:16">
@@ -51607,7 +51607,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51807,7 +51807,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51857,7 +51857,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51907,7 +51907,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51957,7 +51957,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -52507,7 +52507,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -52557,7 +52557,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -52607,7 +52607,7 @@
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
@@ -53257,7 +53257,7 @@
         <v>1</v>
       </c>
       <c r="P1015" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="1016" spans="1:16">
@@ -53307,7 +53307,7 @@
         <v>1</v>
       </c>
       <c r="P1016" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="1017" spans="1:16">
@@ -53357,7 +53357,7 @@
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -54257,7 +54257,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -55607,7 +55607,7 @@
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
@@ -55657,7 +55657,7 @@
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
@@ -56057,7 +56057,7 @@
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
@@ -56071,7 +56071,7 @@
         <v>-0.3611495576484334</v>
       </c>
       <c r="D1072" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E1072">
         <v>-0.8753396018956847</v>
@@ -56107,7 +56107,7 @@
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
@@ -56157,7 +56157,7 @@
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1074" spans="1:16">
@@ -56171,7 +56171,7 @@
         <v>-0.2416436449743475</v>
       </c>
       <c r="D1074" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E1074">
         <v>-0.756340070207508</v>
@@ -56207,7 +56207,7 @@
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
@@ -56221,7 +56221,7 @@
         <v>-0.1044661186953206</v>
       </c>
       <c r="D1075" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E1075">
         <v>-0.6197438046330506</v>
@@ -56357,7 +56357,7 @@
         <v>1</v>
       </c>
       <c r="P1077" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1078" spans="1:16">
@@ -56371,7 +56371,7 @@
         <v>0.02588252599162821</v>
       </c>
       <c r="D1078" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E1078">
         <v>-0.4899474847117267</v>
@@ -56407,7 +56407,7 @@
         <v>1</v>
       </c>
       <c r="P1078" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1079" spans="1:16">
@@ -56457,7 +56457,7 @@
         <v>1</v>
       </c>
       <c r="P1079" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1080" spans="1:16">
@@ -56507,7 +56507,7 @@
         <v>1</v>
       </c>
       <c r="P1080" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1081" spans="1:16">
@@ -56521,7 +56521,7 @@
         <v>0.2383974142565988</v>
       </c>
       <c r="D1081" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E1081">
         <v>-0.2783330832614377</v>
@@ -56557,7 +56557,7 @@
         <v>1</v>
       </c>
       <c r="P1081" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1082" spans="1:16">
@@ -56607,7 +56607,7 @@
         <v>1</v>
       </c>
       <c r="P1082" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1083" spans="1:16">
@@ -56671,7 +56671,7 @@
         <v>0.3557123441832299</v>
       </c>
       <c r="D1084" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E1084">
         <v>-0.161515250495512</v>
@@ -56771,7 +56771,7 @@
         <v>0.6509480614049288</v>
       </c>
       <c r="D1086" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E1086">
         <v>0.1324694679244001</v>
@@ -56971,7 +56971,7 @@
         <v>1.290045361797548</v>
       </c>
       <c r="D1090" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E1090">
         <v>1.681724653627724</v>
@@ -57015,43 +57015,43 @@
         <v>0</v>
       </c>
       <c r="B1091" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1091">
-        <v>1.936927205973072</v>
+        <v>1.42788488804366</v>
       </c>
       <c r="D1091" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E1091">
-        <v>1.650918205496661</v>
+        <v>1.777614873751361</v>
       </c>
       <c r="F1091">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1091">
-        <v>0.01584307279402693</v>
+        <v>0.01365211511195634</v>
       </c>
       <c r="H1091">
-        <v>0.01560908179450334</v>
+        <v>0.01556238512624864</v>
       </c>
       <c r="I1091">
-        <v>0.2860090004764109</v>
+        <v>0.3497299857077012</v>
       </c>
       <c r="J1091">
         <v>0.8669666825469986</v>
       </c>
       <c r="K1091">
-        <v>8.02</v>
+        <v>7.05</v>
       </c>
       <c r="L1091">
-        <v>8.890000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="M1091">
-        <v>8.050000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="N1091">
-        <v>8.630000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O1091">
         <v>1</v>
@@ -57065,43 +57065,43 @@
         <v>1</v>
       </c>
       <c r="B1092" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C1092">
-        <v>1.508077529619402</v>
+        <v>1.936927205973072</v>
       </c>
       <c r="D1092" t="s">
-        <v>266</v>
+        <v>513</v>
       </c>
       <c r="E1092">
-        <v>1.895461865652392</v>
+        <v>1.650918205496661</v>
       </c>
       <c r="F1092">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1092">
-        <v>0.0164719224703806</v>
+        <v>0.01584307279402693</v>
       </c>
       <c r="H1092">
-        <v>0.01656453813434761</v>
+        <v>0.01560908179450334</v>
       </c>
       <c r="I1092">
-        <v>0.3873843360329898</v>
+        <v>0.2860090004764109</v>
       </c>
       <c r="J1092">
         <v>0.8669666825469986</v>
       </c>
       <c r="K1092">
+        <v>8.02</v>
+      </c>
+      <c r="L1092">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M1092">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="N1092">
         <v>8.630000000000001</v>
-      </c>
-      <c r="L1092">
-        <v>8.99</v>
-      </c>
-      <c r="M1092">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="N1092">
-        <v>9.23</v>
       </c>
       <c r="O1092">
         <v>1</v>
@@ -57115,43 +57115,43 @@
         <v>2</v>
       </c>
       <c r="B1093" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C1093">
-        <v>1.881605873274951</v>
+        <v>1.508077529619402</v>
       </c>
       <c r="D1093" t="s">
-        <v>514</v>
+        <v>267</v>
       </c>
       <c r="E1093">
-        <v>1.746927205973071</v>
+        <v>1.895461865652392</v>
       </c>
       <c r="F1093">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1093">
-        <v>0.01571839412672505</v>
+        <v>0.0164719224703806</v>
       </c>
       <c r="H1093">
-        <v>0.01565307279402693</v>
+        <v>0.01656453813434761</v>
       </c>
       <c r="I1093">
-        <v>0.1346786673018805</v>
+        <v>0.3873843360329898</v>
       </c>
       <c r="J1093">
         <v>0.8669666825469986</v>
       </c>
       <c r="K1093">
-        <v>7.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L1093">
-        <v>8.800000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="M1093">
-        <v>8.02</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="N1093">
-        <v>8.699999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="O1093">
         <v>1</v>
@@ -57165,43 +57165,43 @@
         <v>0</v>
       </c>
       <c r="B1094" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1094">
-        <v>2.03829914501824</v>
+        <v>1.516996131219275</v>
       </c>
       <c r="D1094" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E1094">
-        <v>1.7526693413213</v>
+        <v>1.878102020311097</v>
       </c>
       <c r="F1094">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1094">
-        <v>0.01574170085498176</v>
+        <v>0.01356300386878073</v>
       </c>
       <c r="H1094">
-        <v>0.0155073306586787</v>
+        <v>0.0154618979796889</v>
       </c>
       <c r="I1094">
-        <v>0.2856298036969402</v>
+        <v>0.3611058890918217</v>
       </c>
       <c r="J1094">
         <v>0.8543267898979752</v>
       </c>
       <c r="K1094">
-        <v>8.02</v>
+        <v>7.05</v>
       </c>
       <c r="L1094">
-        <v>8.890000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="M1094">
-        <v>8.050000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="N1094">
-        <v>8.630000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O1094">
         <v>1</v>
@@ -57215,43 +57215,43 @@
         <v>1</v>
       </c>
       <c r="B1095" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C1095">
-        <v>1.617159803180474</v>
+        <v>2.03829914501824</v>
       </c>
       <c r="D1095" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E1095">
-        <v>1.834914572250888</v>
+        <v>1.7526693413213</v>
       </c>
       <c r="F1095">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1095">
-        <v>0.01636284019681953</v>
+        <v>0.01574170085498176</v>
       </c>
       <c r="H1095">
-        <v>0.01608508542774911</v>
+        <v>0.0155073306586787</v>
       </c>
       <c r="I1095">
-        <v>0.2177547690704138</v>
+        <v>0.2856298036969402</v>
       </c>
       <c r="J1095">
         <v>0.8543267898979752</v>
       </c>
       <c r="K1095">
+        <v>8.02</v>
+      </c>
+      <c r="L1095">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M1095">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="N1095">
         <v>8.630000000000001</v>
-      </c>
-      <c r="L1095">
-        <v>8.99</v>
-      </c>
-      <c r="M1095">
-        <v>8.34</v>
-      </c>
-      <c r="N1095">
-        <v>8.960000000000001</v>
       </c>
       <c r="O1095">
         <v>1</v>
@@ -57265,43 +57265,43 @@
         <v>2</v>
       </c>
       <c r="B1096" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C1096">
+        <v>1.617159803180474</v>
+      </c>
+      <c r="D1096" t="s">
+        <v>267</v>
+      </c>
+      <c r="E1096">
         <v>2.00239535746313</v>
       </c>
-      <c r="D1096" t="s">
-        <v>514</v>
-      </c>
-      <c r="E1096">
-        <v>1.848299145018239</v>
-      </c>
       <c r="F1096">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1096">
+        <v>0.01636284019681953</v>
+      </c>
+      <c r="H1096">
         <v>0.01645760464253687</v>
       </c>
-      <c r="H1096">
-        <v>0.01555170085498176</v>
-      </c>
       <c r="I1096">
-        <v>0.154096212444891</v>
+        <v>0.385235554282656</v>
       </c>
       <c r="J1096">
         <v>0.8543267898979752</v>
       </c>
       <c r="K1096">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="L1096">
+        <v>8.99</v>
+      </c>
+      <c r="M1096">
         <v>8.460000000000001</v>
       </c>
-      <c r="L1096">
+      <c r="N1096">
         <v>9.23</v>
-      </c>
-      <c r="M1096">
-        <v>8.02</v>
-      </c>
-      <c r="N1096">
-        <v>8.699999999999999</v>
       </c>
       <c r="O1096">
         <v>1</v>
@@ -57315,7 +57315,7 @@
         <v>3</v>
       </c>
       <c r="B1097" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C1097">
         <v>1.982472216614158</v>
@@ -57324,7 +57324,7 @@
         <v>514</v>
       </c>
       <c r="E1097">
-        <v>1.848299145018239</v>
+        <v>2.02022698568457</v>
       </c>
       <c r="F1097">
         <v>-1</v>
@@ -57333,10 +57333,10 @@
         <v>0.01561752778338584</v>
       </c>
       <c r="H1097">
-        <v>0.01555170085498176</v>
+        <v>0.01515977301431543</v>
       </c>
       <c r="I1097">
-        <v>0.1341730715959191</v>
+        <v>-0.03775476907041231</v>
       </c>
       <c r="J1097">
         <v>0.8543267898979752</v>
@@ -57348,10 +57348,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M1097">
-        <v>8.02</v>
+        <v>7.69</v>
       </c>
       <c r="N1097">
-        <v>8.699999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="O1097">
         <v>1</v>
@@ -57365,7 +57365,7 @@
         <v>0</v>
       </c>
       <c r="B1098" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C1098">
         <v>1.604093815380403</v>
@@ -57515,16 +57515,16 @@
         <v>3</v>
       </c>
       <c r="B1101" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C1101">
         <v>2.106912578456483</v>
       </c>
       <c r="D1101" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E1101">
-        <v>1.947380482177422</v>
+        <v>1.933701581839156</v>
       </c>
       <c r="F1101">
         <v>-1</v>
@@ -57533,10 +57533,10 @@
         <v>0.01635308742154352</v>
       </c>
       <c r="H1101">
-        <v>0.01545261951782258</v>
+        <v>0.01550629841816085</v>
       </c>
       <c r="I1101">
-        <v>0.1595320962790607</v>
+        <v>0.1732109966173274</v>
       </c>
       <c r="J1101">
         <v>0.8419725084566805</v>
@@ -57548,10 +57548,10 @@
         <v>9.23</v>
       </c>
       <c r="M1101">
-        <v>8.02</v>
+        <v>8.06</v>
       </c>
       <c r="N1101">
-        <v>8.699999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="O1101">
         <v>1</v>
@@ -57562,96 +57562,96 @@
     </row>
     <row r="1102" spans="1:16">
       <c r="A1102" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1102" t="s">
         <v>265</v>
       </c>
       <c r="C1102">
-        <v>2.08105938251569</v>
+        <v>1.728385432424953</v>
       </c>
       <c r="D1102" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="E1102">
-        <v>1.947380482177422</v>
+        <v>2.116477189755797</v>
       </c>
       <c r="F1102">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1102">
-        <v>0.01551894061748431</v>
+        <v>0.01335161456757505</v>
       </c>
       <c r="H1102">
-        <v>0.01545261951782258</v>
+        <v>0.0152235228102442</v>
       </c>
       <c r="I1102">
-        <v>0.1336789003382677</v>
+        <v>0.3880917573308444</v>
       </c>
       <c r="J1102">
-        <v>0.8419725084566805</v>
+        <v>0.8243424918546166</v>
       </c>
       <c r="K1102">
-        <v>7.98</v>
+        <v>7.05</v>
       </c>
       <c r="L1102">
-        <v>8.800000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="M1102">
-        <v>8.02</v>
+        <v>7.95</v>
       </c>
       <c r="N1102">
-        <v>8.699999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="O1102">
         <v>1</v>
       </c>
       <c r="P1102" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="1103" spans="1:16">
       <c r="A1103" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1103" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C1103">
-        <v>1.728385432424953</v>
+        <v>2.278773215325976</v>
       </c>
       <c r="D1103" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E1103">
-        <v>2.116477189755797</v>
+        <v>1.994042940570337</v>
       </c>
       <c r="F1103">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1103">
-        <v>0.01335161456757505</v>
+        <v>0.01550122678467403</v>
       </c>
       <c r="H1103">
-        <v>0.0152235228102442</v>
+        <v>0.01526595705942966</v>
       </c>
       <c r="I1103">
-        <v>0.3880917573308444</v>
+        <v>0.2847302747556393</v>
       </c>
       <c r="J1103">
         <v>0.8243424918546166</v>
       </c>
       <c r="K1103">
-        <v>7.05</v>
+        <v>8.02</v>
       </c>
       <c r="L1103">
-        <v>7.54</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M1103">
-        <v>7.95</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N1103">
-        <v>8.67</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="O1103">
         <v>1</v>
@@ -57662,46 +57662,46 @@
     </row>
     <row r="1104" spans="1:16">
       <c r="A1104" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1104" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C1104">
-        <v>2.278773215325976</v>
+        <v>1.875924295294658</v>
       </c>
       <c r="D1104" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E1104">
-        <v>1.994042940570337</v>
+        <v>2.084983617932498</v>
       </c>
       <c r="F1104">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1104">
-        <v>0.01550122678467403</v>
+        <v>0.01610407570470534</v>
       </c>
       <c r="H1104">
-        <v>0.01526595705942966</v>
+        <v>0.0158350163820675</v>
       </c>
       <c r="I1104">
-        <v>0.2847302747556393</v>
+        <v>0.2090593226378399</v>
       </c>
       <c r="J1104">
         <v>0.8243424918546166</v>
       </c>
       <c r="K1104">
-        <v>8.02</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L1104">
-        <v>8.890000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="M1104">
-        <v>8.050000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="N1104">
-        <v>8.630000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O1104">
         <v>1</v>
@@ -57712,46 +57712,46 @@
     </row>
     <row r="1105" spans="1:16">
       <c r="A1105" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1105" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C1105">
-        <v>1.875924295294658</v>
+        <v>2.256062518909943</v>
       </c>
       <c r="D1105" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E1105">
-        <v>2.066062518909942</v>
+        <v>2.250806237637998</v>
       </c>
       <c r="F1105">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1105">
-        <v>0.01610407570470534</v>
+        <v>0.01620393748109006</v>
       </c>
       <c r="H1105">
-        <v>0.01601393748109006</v>
+        <v>0.014929193762362</v>
       </c>
       <c r="I1105">
-        <v>0.1901382236152838</v>
+        <v>0.00525628127194544</v>
       </c>
       <c r="J1105">
         <v>0.8243424918546166</v>
       </c>
       <c r="K1105">
-        <v>8.630000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L1105">
-        <v>8.99</v>
+        <v>9.23</v>
       </c>
       <c r="M1105">
-        <v>8.460000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="N1105">
-        <v>9.039999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="O1105">
         <v>1</v>
@@ -57762,452 +57762,252 @@
     </row>
     <row r="1106" spans="1:16">
       <c r="A1106" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1106" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C1106">
-        <v>2.256062518909943</v>
+        <v>2.327682010882778</v>
       </c>
       <c r="D1106" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E1106">
-        <v>2.088773215325975</v>
+        <v>2.043134686733961</v>
       </c>
       <c r="F1106">
         <v>-1</v>
       </c>
       <c r="G1106">
-        <v>0.01620393748109006</v>
+        <v>0.01545231798911722</v>
       </c>
       <c r="H1106">
-        <v>0.01531122678467402</v>
+        <v>0.01521686531326604</v>
       </c>
       <c r="I1106">
-        <v>0.1672893035839689</v>
+        <v>0.2845473241488179</v>
       </c>
       <c r="J1106">
-        <v>0.8243424918546166</v>
+        <v>0.818244138293918</v>
       </c>
       <c r="K1106">
-        <v>8.460000000000001</v>
+        <v>8.02</v>
       </c>
       <c r="L1106">
-        <v>9.23</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M1106">
-        <v>8.02</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N1106">
-        <v>8.699999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="O1106">
         <v>1</v>
       </c>
       <c r="P1106" t="s">
-        <v>509</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1107" spans="1:16">
       <c r="A1107" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1107" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1107">
+        <v>1.928553086523488</v>
+      </c>
+      <c r="D1107" t="s">
+        <v>515</v>
+      </c>
+      <c r="E1107">
+        <v>2.135843886628725</v>
+      </c>
+      <c r="F1107">
+        <v>1</v>
+      </c>
+      <c r="G1107">
+        <v>0.01605144691347651</v>
+      </c>
+      <c r="H1107">
+        <v>0.01578415611337128</v>
+      </c>
+      <c r="I1107">
+        <v>0.2072908001052376</v>
+      </c>
+      <c r="J1107">
+        <v>0.818244138293918</v>
+      </c>
+      <c r="K1107">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="L1107">
+        <v>8.99</v>
+      </c>
+      <c r="M1107">
+        <v>8.34</v>
+      </c>
+      <c r="N1107">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="O1107">
+        <v>1</v>
+      </c>
+      <c r="P1107" t="s">
         <v>265</v>
-      </c>
-      <c r="C1107">
-        <v>2.22174691500016</v>
-      </c>
-      <c r="D1107" t="s">
-        <v>514</v>
-      </c>
-      <c r="E1107">
-        <v>2.088773215325975</v>
-      </c>
-      <c r="F1107">
-        <v>-1</v>
-      </c>
-      <c r="G1107">
-        <v>0.01537825308499984</v>
-      </c>
-      <c r="H1107">
-        <v>0.01531122678467402</v>
-      </c>
-      <c r="I1107">
-        <v>0.132973699674185</v>
-      </c>
-      <c r="J1107">
-        <v>0.8243424918546166</v>
-      </c>
-      <c r="K1107">
-        <v>7.98</v>
-      </c>
-      <c r="L1107">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="M1107">
-        <v>8.02</v>
-      </c>
-      <c r="N1107">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="O1107">
-        <v>1</v>
-      </c>
-      <c r="P1107" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="1108" spans="1:16">
       <c r="A1108" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1108" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1108">
-        <v>2.327682010882778</v>
+        <v>2.307654590033454</v>
       </c>
       <c r="D1108" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E1108">
-        <v>2.043134686733961</v>
+        <v>2.297702576519771</v>
       </c>
       <c r="F1108">
         <v>-1</v>
       </c>
       <c r="G1108">
-        <v>0.01545231798911722</v>
+        <v>0.01615234540996655</v>
       </c>
       <c r="H1108">
-        <v>0.01521686531326604</v>
+        <v>0.01488229742348023</v>
       </c>
       <c r="I1108">
-        <v>0.2845473241488179</v>
+        <v>0.0099520135136828</v>
       </c>
       <c r="J1108">
         <v>0.818244138293918</v>
       </c>
       <c r="K1108">
-        <v>8.02</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L1108">
-        <v>8.890000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="M1108">
-        <v>8.050000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="N1108">
-        <v>8.630000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="O1108">
         <v>1</v>
       </c>
       <c r="P1108" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1109" spans="1:16">
       <c r="A1109" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1109" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C1109">
-        <v>1.928553086523488</v>
+        <v>2.233426024675511</v>
       </c>
       <c r="D1109" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E1109">
-        <v>2.117654590033452</v>
+        <v>1.948526122024671</v>
       </c>
       <c r="F1109">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1109">
-        <v>0.01605144691347651</v>
+        <v>0.01554657397532449</v>
       </c>
       <c r="H1109">
-        <v>0.01596234540996655</v>
+        <v>0.01531147387797533</v>
       </c>
       <c r="I1109">
-        <v>0.1891015035099644</v>
+        <v>0.2848999026508396</v>
       </c>
       <c r="J1109">
-        <v>0.818244138293918</v>
+        <v>0.8299967550279912</v>
       </c>
       <c r="K1109">
+        <v>8.02</v>
+      </c>
+      <c r="L1109">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M1109">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="N1109">
         <v>8.630000000000001</v>
       </c>
-      <c r="L1109">
-        <v>8.99</v>
-      </c>
-      <c r="M1109">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="N1109">
-        <v>9.039999999999999</v>
-      </c>
       <c r="O1109">
         <v>1</v>
       </c>
       <c r="P1109" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="1110" spans="1:16">
       <c r="A1110" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1110" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C1110">
-        <v>2.307654590033454</v>
+        <v>1.827128004108435</v>
       </c>
       <c r="D1110" t="s">
-        <v>514</v>
+        <v>267</v>
       </c>
       <c r="E1110">
-        <v>2.137682010882777</v>
+        <v>2.208227452463194</v>
       </c>
       <c r="F1110">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1110">
-        <v>0.01615234540996655</v>
+        <v>0.01615287199589157</v>
       </c>
       <c r="H1110">
-        <v>0.01526231798911722</v>
+        <v>0.01625177254753681</v>
       </c>
       <c r="I1110">
-        <v>0.1699725791506763</v>
+        <v>0.3810994483547585</v>
       </c>
       <c r="J1110">
-        <v>0.818244138293918</v>
+        <v>0.8299967550279912</v>
       </c>
       <c r="K1110">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="L1110">
+        <v>8.99</v>
+      </c>
+      <c r="M1110">
         <v>8.460000000000001</v>
       </c>
-      <c r="L1110">
+      <c r="N1110">
         <v>9.23</v>
       </c>
-      <c r="M1110">
-        <v>8.02</v>
-      </c>
-      <c r="N1110">
-        <v>8.699999999999999</v>
-      </c>
       <c r="O1110">
         <v>1</v>
       </c>
       <c r="P1110" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="1111" spans="1:16">
-      <c r="A1111" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1111" t="s">
-        <v>264</v>
-      </c>
-      <c r="C1111">
-        <v>2.233426024675511</v>
-      </c>
-      <c r="D1111" t="s">
-        <v>513</v>
-      </c>
-      <c r="E1111">
-        <v>1.948526122024671</v>
-      </c>
-      <c r="F1111">
-        <v>-1</v>
-      </c>
-      <c r="G1111">
-        <v>0.01554657397532449</v>
-      </c>
-      <c r="H1111">
-        <v>0.01531147387797533</v>
-      </c>
-      <c r="I1111">
-        <v>0.2848999026508396</v>
-      </c>
-      <c r="J1111">
-        <v>0.8299967550279912</v>
-      </c>
-      <c r="K1111">
-        <v>8.02</v>
-      </c>
-      <c r="L1111">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="M1111">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="N1111">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="O1111">
-        <v>1</v>
-      </c>
-      <c r="P1111" t="s">
         <v>261</v>
-      </c>
-    </row>
-    <row r="1112" spans="1:16">
-      <c r="A1112" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1112" t="s">
-        <v>263</v>
-      </c>
-      <c r="C1112">
-        <v>1.827128004108435</v>
-      </c>
-      <c r="D1112" t="s">
-        <v>266</v>
-      </c>
-      <c r="E1112">
-        <v>2.208227452463194</v>
-      </c>
-      <c r="F1112">
-        <v>1</v>
-      </c>
-      <c r="G1112">
-        <v>0.01615287199589157</v>
-      </c>
-      <c r="H1112">
-        <v>0.01625177254753681</v>
-      </c>
-      <c r="I1112">
-        <v>0.3810994483547585</v>
-      </c>
-      <c r="J1112">
-        <v>0.8299967550279912</v>
-      </c>
-      <c r="K1112">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="L1112">
-        <v>8.99</v>
-      </c>
-      <c r="M1112">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="N1112">
-        <v>9.23</v>
-      </c>
-      <c r="O1112">
-        <v>1</v>
-      </c>
-      <c r="P1112" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1113" spans="1:16">
-      <c r="A1113" s="1">
-        <v>2</v>
-      </c>
-      <c r="B1113" t="s">
-        <v>265</v>
-      </c>
-      <c r="C1113">
-        <v>2.176625894876631</v>
-      </c>
-      <c r="D1113" t="s">
-        <v>514</v>
-      </c>
-      <c r="E1113">
-        <v>2.04342602467551</v>
-      </c>
-      <c r="F1113">
-        <v>-1</v>
-      </c>
-      <c r="G1113">
-        <v>0.01542337410512337</v>
-      </c>
-      <c r="H1113">
-        <v>0.01535657397532449</v>
-      </c>
-      <c r="I1113">
-        <v>0.1331998702011212</v>
-      </c>
-      <c r="J1113">
-        <v>0.8299967550279912</v>
-      </c>
-      <c r="K1113">
-        <v>7.98</v>
-      </c>
-      <c r="L1113">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="M1113">
-        <v>8.02</v>
-      </c>
-      <c r="N1113">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="O1113">
-        <v>1</v>
-      </c>
-      <c r="P1113" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1114" spans="1:16">
-      <c r="A1114" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1114" t="s">
-        <v>265</v>
-      </c>
-      <c r="C1114">
-        <v>2.441769868416329</v>
-      </c>
-      <c r="D1114" t="s">
-        <v>514</v>
-      </c>
-      <c r="E1114">
-        <v>2.309899040689092</v>
-      </c>
-      <c r="F1114">
-        <v>-1</v>
-      </c>
-      <c r="G1114">
-        <v>0.01515823013158367</v>
-      </c>
-      <c r="H1114">
-        <v>0.01509010095931091</v>
-      </c>
-      <c r="I1114">
-        <v>0.1318708277272371</v>
-      </c>
-      <c r="J1114">
-        <v>0.7967706931809112</v>
-      </c>
-      <c r="K1114">
-        <v>7.98</v>
-      </c>
-      <c r="L1114">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="M1114">
-        <v>8.02</v>
-      </c>
-      <c r="N1114">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="O1114">
-        <v>1</v>
-      </c>
-      <c r="P1114" t="s">
-        <v>712</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3339" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3333" uniqueCount="712">
   <si>
     <t>trade_time</t>
   </si>
@@ -2507,7 +2507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1109"/>
+  <dimension ref="A1:P1107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -57718,10 +57718,10 @@
         <v>1.928553086523488</v>
       </c>
       <c r="D1105" t="s">
-        <v>514</v>
+        <v>266</v>
       </c>
       <c r="E1105">
-        <v>2.135843886628725</v>
+        <v>2.307654590033454</v>
       </c>
       <c r="F1105">
         <v>1</v>
@@ -57730,10 +57730,10 @@
         <v>0.01605144691347651</v>
       </c>
       <c r="H1105">
-        <v>0.01578415611337128</v>
+        <v>0.01615234540996655</v>
       </c>
       <c r="I1105">
-        <v>0.2072908001052376</v>
+        <v>0.3791015035099656</v>
       </c>
       <c r="J1105">
         <v>0.818244138293918</v>
@@ -57745,10 +57745,10 @@
         <v>8.99</v>
       </c>
       <c r="M1105">
-        <v>8.34</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="N1105">
-        <v>8.960000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="O1105">
         <v>1</v>
@@ -57759,201 +57759,101 @@
     </row>
     <row r="1106" spans="1:16">
       <c r="A1106" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1106" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C1106">
-        <v>2.307654590033454</v>
+        <v>2.233426024675511</v>
       </c>
       <c r="D1106" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E1106">
-        <v>2.124952245351022</v>
+        <v>1.948526122024671</v>
       </c>
       <c r="F1106">
         <v>-1</v>
       </c>
       <c r="G1106">
-        <v>0.01615234540996655</v>
+        <v>0.01554657397532449</v>
       </c>
       <c r="H1106">
-        <v>0.01531504775464898</v>
+        <v>0.01531147387797533</v>
       </c>
       <c r="I1106">
-        <v>0.1827023446824318</v>
+        <v>0.2848999026508396</v>
       </c>
       <c r="J1106">
-        <v>0.818244138293918</v>
+        <v>0.8299967550279912</v>
       </c>
       <c r="K1106">
-        <v>8.460000000000001</v>
+        <v>8.02</v>
       </c>
       <c r="L1106">
-        <v>9.23</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M1106">
-        <v>8.06</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N1106">
-        <v>8.720000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="O1106">
         <v>1</v>
       </c>
       <c r="P1106" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="1107" spans="1:16">
       <c r="A1107" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1107" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C1107">
-        <v>2.297702576519771</v>
+        <v>1.827128004108435</v>
       </c>
       <c r="D1107" t="s">
-        <v>513</v>
+        <v>266</v>
       </c>
       <c r="E1107">
-        <v>2.09682464566673</v>
+        <v>2.208227452463194</v>
       </c>
       <c r="F1107">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1107">
-        <v>0.01488229742348023</v>
+        <v>0.01615287199589157</v>
       </c>
       <c r="H1107">
-        <v>0.01386317535433327</v>
+        <v>0.01625177254753681</v>
       </c>
       <c r="I1107">
-        <v>0.2008779308530411</v>
+        <v>0.3810994483547585</v>
       </c>
       <c r="J1107">
-        <v>0.818244138293918</v>
+        <v>0.8299967550279912</v>
       </c>
       <c r="K1107">
-        <v>7.69</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L1107">
-        <v>8.59</v>
+        <v>8.99</v>
       </c>
       <c r="M1107">
-        <v>7.19</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="N1107">
-        <v>7.98</v>
+        <v>9.23</v>
       </c>
       <c r="O1107">
         <v>1</v>
       </c>
       <c r="P1107" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="1108" spans="1:16">
-      <c r="A1108" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1108" t="s">
-        <v>263</v>
-      </c>
-      <c r="C1108">
-        <v>2.233426024675511</v>
-      </c>
-      <c r="D1108" t="s">
-        <v>511</v>
-      </c>
-      <c r="E1108">
-        <v>1.948526122024671</v>
-      </c>
-      <c r="F1108">
-        <v>-1</v>
-      </c>
-      <c r="G1108">
-        <v>0.01554657397532449</v>
-      </c>
-      <c r="H1108">
-        <v>0.01531147387797533</v>
-      </c>
-      <c r="I1108">
-        <v>0.2848999026508396</v>
-      </c>
-      <c r="J1108">
-        <v>0.8299967550279912</v>
-      </c>
-      <c r="K1108">
-        <v>8.02</v>
-      </c>
-      <c r="L1108">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="M1108">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="N1108">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="O1108">
-        <v>1</v>
-      </c>
-      <c r="P1108" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="1109" spans="1:16">
-      <c r="A1109" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>262</v>
-      </c>
-      <c r="C1109">
-        <v>1.827128004108435</v>
-      </c>
-      <c r="D1109" t="s">
-        <v>266</v>
-      </c>
-      <c r="E1109">
-        <v>2.208227452463194</v>
-      </c>
-      <c r="F1109">
-        <v>1</v>
-      </c>
-      <c r="G1109">
-        <v>0.01615287199589157</v>
-      </c>
-      <c r="H1109">
-        <v>0.01625177254753681</v>
-      </c>
-      <c r="I1109">
-        <v>0.3810994483547585</v>
-      </c>
-      <c r="J1109">
-        <v>0.8299967550279912</v>
-      </c>
-      <c r="K1109">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="L1109">
-        <v>8.99</v>
-      </c>
-      <c r="M1109">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="N1109">
-        <v>9.23</v>
-      </c>
-      <c r="O1109">
-        <v>1</v>
-      </c>
-      <c r="P1109" t="s">
         <v>260</v>
       </c>
     </row>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3384" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3381" uniqueCount="717">
   <si>
     <t>trade_time</t>
   </si>
@@ -1570,7 +1570,7 @@
     <t>2021-10-15</t>
   </si>
   <si>
-    <t>2021-10-19</t>
+    <t>2021-10-20</t>
   </si>
   <si>
     <t>2016-07-28</t>
@@ -2522,7 +2522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1124"/>
+  <dimension ref="A1:P1123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -58274,96 +58274,96 @@
     </row>
     <row r="1116" spans="1:16">
       <c r="A1116" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1116" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C1116">
-        <v>2.675214608767929</v>
+        <v>2.073048244401436</v>
       </c>
       <c r="D1116" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E1116">
-        <v>2.282581996794921</v>
+        <v>2.523789466408624</v>
       </c>
       <c r="F1116">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1116">
-        <v>0.01398478539123207</v>
+        <v>0.01388695175559856</v>
       </c>
       <c r="H1116">
-        <v>0.01347741800320508</v>
+        <v>0.01397621053359138</v>
       </c>
       <c r="I1116">
-        <v>0.3926326119730081</v>
+        <v>0.4507412220071885</v>
       </c>
       <c r="J1116">
-        <v>0.8195341146713147</v>
+        <v>0.8215510091235834</v>
       </c>
       <c r="K1116">
-        <v>6.9</v>
+        <v>7.19</v>
       </c>
       <c r="L1116">
-        <v>8.33</v>
+        <v>7.98</v>
       </c>
       <c r="M1116">
-        <v>6.83</v>
+        <v>6.97</v>
       </c>
       <c r="N1116">
-        <v>7.88</v>
+        <v>8.25</v>
       </c>
       <c r="O1116">
         <v>1</v>
       </c>
       <c r="P1116" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="1117" spans="1:16">
       <c r="A1117" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1117" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C1117">
-        <v>2.073048244401436</v>
+        <v>2.661298037047275</v>
       </c>
       <c r="D1117" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E1117">
-        <v>2.523789466408624</v>
+        <v>2.268806607685925</v>
       </c>
       <c r="F1117">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1117">
-        <v>0.01388695175559856</v>
+        <v>0.01399870196295273</v>
       </c>
       <c r="H1117">
-        <v>0.01397621053359138</v>
+        <v>0.01349119339231407</v>
       </c>
       <c r="I1117">
-        <v>0.4507412220071885</v>
+        <v>0.3924914293613497</v>
       </c>
       <c r="J1117">
         <v>0.8215510091235834</v>
       </c>
       <c r="K1117">
-        <v>7.19</v>
+        <v>6.9</v>
       </c>
       <c r="L1117">
-        <v>7.98</v>
+        <v>8.33</v>
       </c>
       <c r="M1117">
-        <v>6.97</v>
+        <v>6.83</v>
       </c>
       <c r="N1117">
-        <v>8.25</v>
+        <v>7.88</v>
       </c>
       <c r="O1117">
         <v>1</v>
@@ -58374,96 +58374,96 @@
     </row>
     <row r="1118" spans="1:16">
       <c r="A1118" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1118" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C1118">
-        <v>2.661298037047275</v>
+        <v>2.04151933184611</v>
       </c>
       <c r="D1118" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E1118">
-        <v>2.268806607685925</v>
+        <v>2.493225277186006</v>
       </c>
       <c r="F1118">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1118">
-        <v>0.01399870196295273</v>
+        <v>0.01391848066815389</v>
       </c>
       <c r="H1118">
-        <v>0.01349119339231407</v>
+        <v>0.01400677472281399</v>
       </c>
       <c r="I1118">
-        <v>0.3924914293613497</v>
+        <v>0.4517059453398966</v>
       </c>
       <c r="J1118">
-        <v>0.8215510091235834</v>
+        <v>0.8259361151813478</v>
       </c>
       <c r="K1118">
-        <v>6.9</v>
+        <v>7.19</v>
       </c>
       <c r="L1118">
-        <v>8.33</v>
+        <v>7.98</v>
       </c>
       <c r="M1118">
-        <v>6.83</v>
+        <v>6.97</v>
       </c>
       <c r="N1118">
-        <v>7.88</v>
+        <v>8.25</v>
       </c>
       <c r="O1118">
         <v>1</v>
       </c>
       <c r="P1118" t="s">
-        <v>264</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1119" spans="1:16">
       <c r="A1119" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1119" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C1119">
-        <v>2.04151933184611</v>
+        <v>2.6310408052487</v>
       </c>
       <c r="D1119" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E1119">
-        <v>2.493225277186006</v>
+        <v>2.238856333311395</v>
       </c>
       <c r="F1119">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1119">
-        <v>0.01391848066815389</v>
+        <v>0.0140289591947513</v>
       </c>
       <c r="H1119">
-        <v>0.01400677472281399</v>
+        <v>0.0135211436666886</v>
       </c>
       <c r="I1119">
-        <v>0.4517059453398966</v>
+        <v>0.3921844719373055</v>
       </c>
       <c r="J1119">
         <v>0.8259361151813478</v>
       </c>
       <c r="K1119">
-        <v>7.19</v>
+        <v>6.9</v>
       </c>
       <c r="L1119">
-        <v>7.98</v>
+        <v>8.33</v>
       </c>
       <c r="M1119">
-        <v>6.97</v>
+        <v>6.83</v>
       </c>
       <c r="N1119">
-        <v>8.25</v>
+        <v>7.88</v>
       </c>
       <c r="O1119">
         <v>1</v>
@@ -58474,34 +58474,34 @@
     </row>
     <row r="1120" spans="1:16">
       <c r="A1120" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1120" t="s">
         <v>270</v>
       </c>
       <c r="C1120">
-        <v>2.6310408052487</v>
+        <v>2.594233512636578</v>
       </c>
       <c r="D1120" t="s">
         <v>517</v>
       </c>
       <c r="E1120">
-        <v>2.337524834044037</v>
+        <v>2.302051138990325</v>
       </c>
       <c r="F1120">
         <v>-1</v>
       </c>
       <c r="G1120">
-        <v>0.0140289591947513</v>
+        <v>0.01406576648736342</v>
       </c>
       <c r="H1120">
-        <v>0.01332247516595596</v>
+        <v>0.01335794886100967</v>
       </c>
       <c r="I1120">
-        <v>0.2935159712046636</v>
+        <v>0.292182373646253</v>
       </c>
       <c r="J1120">
-        <v>0.8259361151813478</v>
+        <v>0.8312705054149887</v>
       </c>
       <c r="K1120">
         <v>6.9</v>
@@ -58519,7 +58519,7 @@
         <v>1</v>
       </c>
       <c r="P1120" t="s">
-        <v>514</v>
+        <v>268</v>
       </c>
     </row>
     <row r="1121" spans="1:16">
@@ -58530,28 +58530,28 @@
         <v>270</v>
       </c>
       <c r="C1121">
-        <v>2.594233512636578</v>
+        <v>2.625075768506476</v>
       </c>
       <c r="D1121" t="s">
         <v>517</v>
       </c>
       <c r="E1121">
-        <v>2.302051138990325</v>
+        <v>2.33177592182146</v>
       </c>
       <c r="F1121">
         <v>-1</v>
       </c>
       <c r="G1121">
-        <v>0.01406576648736342</v>
+        <v>0.01403492423149352</v>
       </c>
       <c r="H1121">
-        <v>0.01335794886100967</v>
+        <v>0.01332822407817854</v>
       </c>
       <c r="I1121">
-        <v>0.292182373646253</v>
+        <v>0.2932998466850165</v>
       </c>
       <c r="J1121">
-        <v>0.8312705054149887</v>
+        <v>0.8268006132599309</v>
       </c>
       <c r="K1121">
         <v>6.9</v>
@@ -58569,7 +58569,7 @@
         <v>1</v>
       </c>
       <c r="P1121" t="s">
-        <v>268</v>
+        <v>715</v>
       </c>
     </row>
     <row r="1122" spans="1:16">
@@ -58580,28 +58580,28 @@
         <v>270</v>
       </c>
       <c r="C1122">
-        <v>2.625075768506476</v>
+        <v>2.811716394539619</v>
       </c>
       <c r="D1122" t="s">
         <v>517</v>
       </c>
       <c r="E1122">
-        <v>2.33177592182146</v>
+        <v>2.511654206331662</v>
       </c>
       <c r="F1122">
         <v>-1</v>
       </c>
       <c r="G1122">
-        <v>0.01403492423149352</v>
+        <v>0.01384828360546038</v>
       </c>
       <c r="H1122">
-        <v>0.01332822407817854</v>
+        <v>0.01314834579366834</v>
       </c>
       <c r="I1122">
-        <v>0.2932998466850165</v>
+        <v>0.3000621882079573</v>
       </c>
       <c r="J1122">
-        <v>0.8268006132599309</v>
+        <v>0.799751247168171</v>
       </c>
       <c r="K1122">
         <v>6.9</v>
@@ -58619,106 +58619,56 @@
         <v>1</v>
       </c>
       <c r="P1122" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1123" spans="1:16">
       <c r="A1123" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1123" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C1123">
-        <v>2.811716394539619</v>
+        <v>2.417698981841392</v>
       </c>
       <c r="D1123" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E1123">
-        <v>2.511654206331662</v>
+        <v>2.423694006784756</v>
       </c>
       <c r="F1123">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1123">
-        <v>0.01384828360546038</v>
+        <v>0.01334230101815861</v>
       </c>
       <c r="H1123">
-        <v>0.01314834579366834</v>
+        <v>0.01331630599321524</v>
       </c>
       <c r="I1123">
-        <v>0.3000621882079573</v>
+        <v>0.005995024943364236</v>
       </c>
       <c r="J1123">
         <v>0.799751247168171</v>
       </c>
       <c r="K1123">
-        <v>6.9</v>
+        <v>6.83</v>
       </c>
       <c r="L1123">
-        <v>8.33</v>
+        <v>7.88</v>
       </c>
       <c r="M1123">
-        <v>6.65</v>
+        <v>6.81</v>
       </c>
       <c r="N1123">
-        <v>7.83</v>
+        <v>7.87</v>
       </c>
       <c r="O1123">
         <v>1</v>
       </c>
       <c r="P1123" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="1124" spans="1:16">
-      <c r="A1124" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>271</v>
-      </c>
-      <c r="C1124">
-        <v>2.417698981841392</v>
-      </c>
-      <c r="D1124" t="s">
-        <v>518</v>
-      </c>
-      <c r="E1124">
-        <v>2.517711419482983</v>
-      </c>
-      <c r="F1124">
-        <v>1</v>
-      </c>
-      <c r="G1124">
-        <v>0.01334230101815861</v>
-      </c>
-      <c r="H1124">
-        <v>0.01352228858051702</v>
-      </c>
-      <c r="I1124">
-        <v>0.100012437641591</v>
-      </c>
-      <c r="J1124">
-        <v>0.799751247168171</v>
-      </c>
-      <c r="K1124">
-        <v>6.83</v>
-      </c>
-      <c r="L1124">
-        <v>7.88</v>
-      </c>
-      <c r="M1124">
-        <v>6.88</v>
-      </c>
-      <c r="N1124">
-        <v>8.02</v>
-      </c>
-      <c r="O1124">
-        <v>1</v>
-      </c>
-      <c r="P1124" t="s">
         <v>716</v>
       </c>
     </row>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -1567,7 +1567,7 @@
     <t>2021-10-15</t>
   </si>
   <si>
-    <t>2021-10-25</t>
+    <t>2021-10-26</t>
   </si>
   <si>
     <t>2016-08-01</t>
@@ -58430,7 +58430,7 @@
         <v>517</v>
       </c>
       <c r="E1119">
-        <v>2.557674106558209</v>
+        <v>2.543669131501573</v>
       </c>
       <c r="F1119">
         <v>1</v>
@@ -58439,10 +58439,10 @@
         <v>0.01334230101815861</v>
       </c>
       <c r="H1119">
-        <v>0.01332232589344179</v>
+        <v>0.01327633086849843</v>
       </c>
       <c r="I1119">
-        <v>0.1399751247168171</v>
+        <v>0.1259701496601808</v>
       </c>
       <c r="J1119">
         <v>0.799751247168171</v>
@@ -58454,10 +58454,10 @@
         <v>7.88</v>
       </c>
       <c r="M1119">
-        <v>6.73</v>
+        <v>6.71</v>
       </c>
       <c r="N1119">
-        <v>7.94</v>
+        <v>7.91</v>
       </c>
       <c r="O1119">
         <v>1</v>
@@ -58480,7 +58480,7 @@
         <v>517</v>
       </c>
       <c r="E1120">
-        <v>2.557674106558209</v>
+        <v>2.543669131501573</v>
       </c>
       <c r="F1120">
         <v>1</v>
@@ -58489,10 +58489,10 @@
         <v>0.01332430350568693</v>
       </c>
       <c r="H1120">
-        <v>0.01332232589344179</v>
+        <v>0.01327633086849843</v>
       </c>
       <c r="I1120">
-        <v>0.1419776122451353</v>
+        <v>0.127972637188499</v>
       </c>
       <c r="J1120">
         <v>0.799751247168171</v>
@@ -58504,10 +58504,10 @@
         <v>7.87</v>
       </c>
       <c r="M1120">
-        <v>6.73</v>
+        <v>6.71</v>
       </c>
       <c r="N1120">
-        <v>7.94</v>
+        <v>7.91</v>
       </c>
       <c r="O1120">
         <v>1</v>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3363" uniqueCount="713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3366" uniqueCount="713">
   <si>
     <t>trade_time</t>
   </si>
@@ -1567,7 +1567,7 @@
     <t>2021-10-15</t>
   </si>
   <si>
-    <t>2021-10-25</t>
+    <t>2021-10-29</t>
   </si>
   <si>
     <t>2016-08-04</t>
@@ -2510,7 +2510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1117"/>
+  <dimension ref="A1:P1118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -58062,52 +58062,52 @@
     </row>
     <row r="1112" spans="1:16">
       <c r="A1112" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1112" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C1112">
-        <v>2.04151933184611</v>
+        <v>2.661298037047275</v>
       </c>
       <c r="D1112" t="s">
-        <v>265</v>
+        <v>516</v>
       </c>
       <c r="E1112">
-        <v>2.493225277186006</v>
+        <v>2.36668578932817</v>
       </c>
       <c r="F1112">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1112">
-        <v>0.01391848066815389</v>
+        <v>0.01399870196295273</v>
       </c>
       <c r="H1112">
-        <v>0.01400677472281399</v>
+        <v>0.01329331421067183</v>
       </c>
       <c r="I1112">
-        <v>0.4517059453398966</v>
+        <v>0.2946122477191047</v>
       </c>
       <c r="J1112">
-        <v>0.8259361151813478</v>
+        <v>0.8215510091235834</v>
       </c>
       <c r="K1112">
-        <v>7.19</v>
+        <v>6.9</v>
       </c>
       <c r="L1112">
-        <v>7.98</v>
+        <v>8.33</v>
       </c>
       <c r="M1112">
-        <v>6.97</v>
+        <v>6.65</v>
       </c>
       <c r="N1112">
-        <v>8.25</v>
+        <v>7.83</v>
       </c>
       <c r="O1112">
         <v>1</v>
       </c>
       <c r="P1112" t="s">
-        <v>513</v>
+        <v>263</v>
       </c>
     </row>
     <row r="1113" spans="1:16">
@@ -58118,28 +58118,28 @@
         <v>269</v>
       </c>
       <c r="C1113">
-        <v>2.594233512636578</v>
+        <v>2.6310408052487</v>
       </c>
       <c r="D1113" t="s">
         <v>516</v>
       </c>
       <c r="E1113">
-        <v>2.302051138990325</v>
+        <v>2.337524834044037</v>
       </c>
       <c r="F1113">
         <v>-1</v>
       </c>
       <c r="G1113">
-        <v>0.01406576648736342</v>
+        <v>0.0140289591947513</v>
       </c>
       <c r="H1113">
-        <v>0.01335794886100967</v>
+        <v>0.01332247516595596</v>
       </c>
       <c r="I1113">
-        <v>0.292182373646253</v>
+        <v>0.2935159712046636</v>
       </c>
       <c r="J1113">
-        <v>0.8312705054149887</v>
+        <v>0.8259361151813478</v>
       </c>
       <c r="K1113">
         <v>6.9</v>
@@ -58157,7 +58157,7 @@
         <v>1</v>
       </c>
       <c r="P1113" t="s">
-        <v>267</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1114" spans="1:16">
@@ -58168,28 +58168,28 @@
         <v>269</v>
       </c>
       <c r="C1114">
-        <v>2.625075768506476</v>
+        <v>2.594233512636578</v>
       </c>
       <c r="D1114" t="s">
         <v>516</v>
       </c>
       <c r="E1114">
-        <v>2.33177592182146</v>
+        <v>2.302051138990325</v>
       </c>
       <c r="F1114">
         <v>-1</v>
       </c>
       <c r="G1114">
-        <v>0.01403492423149352</v>
+        <v>0.01406576648736342</v>
       </c>
       <c r="H1114">
-        <v>0.01332822407817854</v>
+        <v>0.01335794886100967</v>
       </c>
       <c r="I1114">
-        <v>0.2932998466850165</v>
+        <v>0.292182373646253</v>
       </c>
       <c r="J1114">
-        <v>0.8268006132599309</v>
+        <v>0.8312705054149887</v>
       </c>
       <c r="K1114">
         <v>6.9</v>
@@ -58207,7 +58207,7 @@
         <v>1</v>
       </c>
       <c r="P1114" t="s">
-        <v>711</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1115" spans="1:16">
@@ -58218,28 +58218,28 @@
         <v>269</v>
       </c>
       <c r="C1115">
-        <v>2.811716394539619</v>
+        <v>2.625075768506476</v>
       </c>
       <c r="D1115" t="s">
         <v>516</v>
       </c>
       <c r="E1115">
-        <v>2.511654206331662</v>
+        <v>2.33177592182146</v>
       </c>
       <c r="F1115">
         <v>-1</v>
       </c>
       <c r="G1115">
-        <v>0.01384828360546038</v>
+        <v>0.01403492423149352</v>
       </c>
       <c r="H1115">
-        <v>0.01314834579366834</v>
+        <v>0.01332822407817854</v>
       </c>
       <c r="I1115">
-        <v>0.3000621882079573</v>
+        <v>0.2932998466850165</v>
       </c>
       <c r="J1115">
-        <v>0.799751247168171</v>
+        <v>0.8268006132599309</v>
       </c>
       <c r="K1115">
         <v>6.9</v>
@@ -58257,51 +58257,51 @@
         <v>1</v>
       </c>
       <c r="P1115" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1116" spans="1:16">
       <c r="A1116" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1116" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C1116">
-        <v>2.417698981841392</v>
+        <v>2.811716394539619</v>
       </c>
       <c r="D1116" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E1116">
-        <v>2.557674106558209</v>
+        <v>2.511654206331662</v>
       </c>
       <c r="F1116">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1116">
-        <v>0.01334230101815861</v>
+        <v>0.01384828360546038</v>
       </c>
       <c r="H1116">
-        <v>0.01332232589344179</v>
+        <v>0.01314834579366834</v>
       </c>
       <c r="I1116">
-        <v>0.1399751247168171</v>
+        <v>0.3000621882079573</v>
       </c>
       <c r="J1116">
         <v>0.799751247168171</v>
       </c>
       <c r="K1116">
-        <v>6.83</v>
+        <v>6.9</v>
       </c>
       <c r="L1116">
-        <v>7.88</v>
+        <v>8.33</v>
       </c>
       <c r="M1116">
-        <v>6.73</v>
+        <v>6.65</v>
       </c>
       <c r="N1116">
-        <v>7.94</v>
+        <v>7.83</v>
       </c>
       <c r="O1116">
         <v>1</v>
@@ -58312,51 +58312,101 @@
     </row>
     <row r="1117" spans="1:16">
       <c r="A1117" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1117" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1117">
-        <v>2.423694006784756</v>
+        <v>2.417698981841392</v>
       </c>
       <c r="D1117" t="s">
         <v>517</v>
       </c>
       <c r="E1117">
-        <v>2.557674106558209</v>
+        <v>2.795397990914879</v>
       </c>
       <c r="F1117">
         <v>1</v>
       </c>
       <c r="G1117">
-        <v>0.01331630599321524</v>
+        <v>0.01334230101815861</v>
       </c>
       <c r="H1117">
-        <v>0.01332232589344179</v>
+        <v>0.01178460200908512</v>
       </c>
       <c r="I1117">
-        <v>0.1339800997734528</v>
+        <v>0.3776990090734866</v>
       </c>
       <c r="J1117">
         <v>0.799751247168171</v>
       </c>
       <c r="K1117">
+        <v>6.83</v>
+      </c>
+      <c r="L1117">
+        <v>7.88</v>
+      </c>
+      <c r="M1117">
+        <v>5.62</v>
+      </c>
+      <c r="N1117">
+        <v>7.29</v>
+      </c>
+      <c r="O1117">
+        <v>1</v>
+      </c>
+      <c r="P1117" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:16">
+      <c r="A1118" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1118" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1118">
+        <v>2.423694006784756</v>
+      </c>
+      <c r="D1118" t="s">
+        <v>517</v>
+      </c>
+      <c r="E1118">
+        <v>2.795397990914879</v>
+      </c>
+      <c r="F1118">
+        <v>1</v>
+      </c>
+      <c r="G1118">
+        <v>0.01331630599321524</v>
+      </c>
+      <c r="H1118">
+        <v>0.01178460200908512</v>
+      </c>
+      <c r="I1118">
+        <v>0.3717039841301224</v>
+      </c>
+      <c r="J1118">
+        <v>0.799751247168171</v>
+      </c>
+      <c r="K1118">
         <v>6.81</v>
       </c>
-      <c r="L1117">
+      <c r="L1118">
         <v>7.87</v>
       </c>
-      <c r="M1117">
-        <v>6.73</v>
-      </c>
-      <c r="N1117">
-        <v>7.94</v>
-      </c>
-      <c r="O1117">
-        <v>1</v>
-      </c>
-      <c r="P1117" t="s">
+      <c r="M1118">
+        <v>5.62</v>
+      </c>
+      <c r="N1118">
+        <v>7.29</v>
+      </c>
+      <c r="O1118">
+        <v>1</v>
+      </c>
+      <c r="P1118" t="s">
         <v>712</v>
       </c>
     </row>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -1549,7 +1549,7 @@
     <t>2021-10-29</t>
   </si>
   <si>
-    <t>2021-11-15</t>
+    <t>2021-11-16</t>
   </si>
   <si>
     <t>2016-08-29</t>
@@ -57847,7 +57847,7 @@
         <v>511</v>
       </c>
       <c r="E1108">
-        <v>3.545227360108585</v>
+        <v>3.467022386826795</v>
       </c>
       <c r="F1108">
         <v>1</v>
@@ -57856,10 +57856,10 @@
         <v>0.01037391757754893</v>
       </c>
       <c r="H1108">
-        <v>0.01029477263989141</v>
+        <v>0.0102929776131732</v>
       </c>
       <c r="I1108">
-        <v>0.09914493765750931</v>
+        <v>0.02093996437571954</v>
       </c>
       <c r="J1108">
         <v>0.6367495546964934</v>
@@ -57871,10 +57871,10 @@
         <v>6.91</v>
       </c>
       <c r="M1108">
-        <v>5.3</v>
+        <v>5.36</v>
       </c>
       <c r="N1108">
-        <v>6.92</v>
+        <v>6.88</v>
       </c>
       <c r="O1108">
         <v>1</v>
@@ -57897,7 +57897,7 @@
         <v>511</v>
       </c>
       <c r="E1109">
-        <v>3.587194203031346</v>
+        <v>3.50946432608453</v>
       </c>
       <c r="F1109">
         <v>1</v>
@@ -57906,10 +57906,10 @@
         <v>0.01033084217651122</v>
       </c>
       <c r="H1109">
-        <v>0.01025280579696865</v>
+        <v>0.01025053567391547</v>
       </c>
       <c r="I1109">
-        <v>0.09803637954256805</v>
+        <v>0.02030650259575273</v>
       </c>
       <c r="J1109">
         <v>0.6288312824469159</v>
@@ -57921,10 +57921,10 @@
         <v>6.91</v>
       </c>
       <c r="M1109">
-        <v>5.3</v>
+        <v>5.36</v>
       </c>
       <c r="N1109">
-        <v>6.92</v>
+        <v>6.88</v>
       </c>
       <c r="O1109">
         <v>1</v>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3387" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3396" uniqueCount="713">
   <si>
     <t>trade_time</t>
   </si>
@@ -832,7 +832,7 @@
     <t>2021-11-23</t>
   </si>
   <si>
-    <t>2021-11-19</t>
+    <t>2021-11-24</t>
   </si>
   <si>
     <t>2016-09-28</t>
@@ -1561,7 +1561,7 @@
     <t>2021-11-22</t>
   </si>
   <si>
-    <t>2021-11-24</t>
+    <t>2021-11-25</t>
   </si>
   <si>
     <t>2016-08-29</t>
@@ -2150,6 +2150,9 @@
   </si>
   <si>
     <t>2021-11-17</t>
+  </si>
+  <si>
+    <t>2021-11-18</t>
   </si>
 </sst>
 </file>
@@ -2507,7 +2510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1125"/>
+  <dimension ref="A1:P1128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -57971,7 +57974,7 @@
         <v>515</v>
       </c>
       <c r="E1110">
-        <v>3.744329846749479</v>
+        <v>3.677022386826795</v>
       </c>
       <c r="F1110">
         <v>-1</v>
@@ -57980,10 +57983,10 @@
         <v>0.01063755008200196</v>
       </c>
       <c r="H1110">
-        <v>0.01045567015325052</v>
+        <v>0.01050297761317321</v>
       </c>
       <c r="I1110">
-        <v>-0.02187992875143863</v>
+        <v>0.04542753117124576</v>
       </c>
       <c r="J1110">
         <v>0.6367495546964934</v>
@@ -57995,10 +57998,10 @@
         <v>7.18</v>
       </c>
       <c r="M1110">
-        <v>5.27</v>
+        <v>5.36</v>
       </c>
       <c r="N1110">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="O1110">
         <v>1</v>
@@ -58121,7 +58124,7 @@
         <v>515</v>
       </c>
       <c r="E1113">
-        <v>3.786059141504753</v>
+        <v>3.71946432608453</v>
       </c>
       <c r="F1113">
         <v>-1</v>
@@ -58130,10 +58133,10 @@
         <v>0.01059455386368675</v>
       </c>
       <c r="H1113">
-        <v>0.01041394085849525</v>
+        <v>0.01046053567391547</v>
       </c>
       <c r="I1113">
-        <v>-0.02061300519150633</v>
+        <v>0.04598181022871639</v>
       </c>
       <c r="J1113">
         <v>0.6288312824469159</v>
@@ -58145,10 +58148,10 @@
         <v>7.18</v>
       </c>
       <c r="M1113">
-        <v>5.27</v>
+        <v>5.36</v>
       </c>
       <c r="N1113">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="O1113">
         <v>1</v>
@@ -58259,63 +58262,63 @@
     </row>
     <row r="1116" spans="1:16">
       <c r="A1116" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1116" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C1116">
-        <v>3.47813903198738</v>
+        <v>3.775848714512787</v>
       </c>
       <c r="D1116" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E1116">
-        <v>3.699544662929113</v>
+        <v>3.729732801066029</v>
       </c>
       <c r="F1116">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1116">
-        <v>0.01034186096801262</v>
+        <v>0.01058415128548721</v>
       </c>
       <c r="H1116">
-        <v>0.01026045533707089</v>
+        <v>0.01045026719893397</v>
       </c>
       <c r="I1116">
-        <v>0.2214056309417338</v>
+        <v>0.04611591344675814</v>
       </c>
       <c r="J1116">
-        <v>0.6308567955905552</v>
+        <v>0.6269155221891737</v>
       </c>
       <c r="K1116">
-        <v>5.44</v>
+        <v>5.43</v>
       </c>
       <c r="L1116">
-        <v>6.91</v>
+        <v>7.18</v>
       </c>
       <c r="M1116">
-        <v>5.2</v>
+        <v>5.36</v>
       </c>
       <c r="N1116">
-        <v>6.98</v>
+        <v>7.09</v>
       </c>
       <c r="O1116">
         <v>1</v>
       </c>
       <c r="P1116" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1117" spans="1:16">
       <c r="A1117" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1117" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C1117">
-        <v>3.498607575634624</v>
+        <v>3.47813903198738</v>
       </c>
       <c r="D1117" t="s">
         <v>514</v>
@@ -58327,22 +58330,22 @@
         <v>1</v>
       </c>
       <c r="G1117">
-        <v>0.01026139242436538</v>
+        <v>0.01034186096801262</v>
       </c>
       <c r="H1117">
         <v>0.01026045533707089</v>
       </c>
       <c r="I1117">
-        <v>0.2009370872944896</v>
+        <v>0.2214056309417338</v>
       </c>
       <c r="J1117">
         <v>0.6308567955905552</v>
       </c>
       <c r="K1117">
-        <v>5.36</v>
+        <v>5.44</v>
       </c>
       <c r="L1117">
-        <v>6.88</v>
+        <v>6.91</v>
       </c>
       <c r="M1117">
         <v>5.2</v>
@@ -58359,46 +58362,46 @@
     </row>
     <row r="1118" spans="1:16">
       <c r="A1118" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1118" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1118">
-        <v>3.754447599943285</v>
+        <v>3.498607575634624</v>
       </c>
       <c r="D1118" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E1118">
-        <v>3.775384687237774</v>
+        <v>3.699544662929113</v>
       </c>
       <c r="F1118">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1118">
-        <v>0.01060555240005671</v>
+        <v>0.01026139242436538</v>
       </c>
       <c r="H1118">
-        <v>0.01042461531276222</v>
+        <v>0.01026045533707089</v>
       </c>
       <c r="I1118">
-        <v>-0.02093708729448895</v>
+        <v>0.2009370872944896</v>
       </c>
       <c r="J1118">
         <v>0.6308567955905552</v>
       </c>
       <c r="K1118">
-        <v>5.43</v>
+        <v>5.36</v>
       </c>
       <c r="L1118">
-        <v>7.18</v>
+        <v>6.88</v>
       </c>
       <c r="M1118">
-        <v>5.27</v>
+        <v>5.2</v>
       </c>
       <c r="N1118">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O1118">
         <v>1</v>
@@ -58409,96 +58412,96 @@
     </row>
     <row r="1119" spans="1:16">
       <c r="A1119" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1119" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C1119">
-        <v>3.501629292170211</v>
+        <v>3.754447599943285</v>
       </c>
       <c r="D1119" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E1119">
-        <v>3.702476178971101</v>
+        <v>3.708607575634624</v>
       </c>
       <c r="F1119">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1119">
-        <v>0.01025837070782979</v>
+        <v>0.01060555240005671</v>
       </c>
       <c r="H1119">
-        <v>0.0102575238210289</v>
+        <v>0.01047139242436538</v>
       </c>
       <c r="I1119">
-        <v>0.2008468868008899</v>
+        <v>0.04584002430866141</v>
       </c>
       <c r="J1119">
-        <v>0.6302930425055575</v>
+        <v>0.6308567955905552</v>
       </c>
       <c r="K1119">
+        <v>5.43</v>
+      </c>
+      <c r="L1119">
+        <v>7.18</v>
+      </c>
+      <c r="M1119">
         <v>5.36</v>
       </c>
-      <c r="L1119">
-        <v>6.88</v>
-      </c>
-      <c r="M1119">
-        <v>5.2</v>
-      </c>
       <c r="N1119">
-        <v>6.98</v>
+        <v>7.09</v>
       </c>
       <c r="O1119">
         <v>1</v>
       </c>
       <c r="P1119" t="s">
-        <v>269</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1120" spans="1:16">
       <c r="A1120" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1120" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1120">
-        <v>3.757508779194823</v>
+        <v>3.501629292170211</v>
       </c>
       <c r="D1120" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E1120">
-        <v>3.778355665995712</v>
+        <v>3.702476178971101</v>
       </c>
       <c r="F1120">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1120">
-        <v>0.01060249122080518</v>
+        <v>0.01025837070782979</v>
       </c>
       <c r="H1120">
-        <v>0.01042164433400429</v>
+        <v>0.0102575238210289</v>
       </c>
       <c r="I1120">
-        <v>-0.02084688680088931</v>
+        <v>0.2008468868008899</v>
       </c>
       <c r="J1120">
         <v>0.6302930425055575</v>
       </c>
       <c r="K1120">
-        <v>5.43</v>
+        <v>5.36</v>
       </c>
       <c r="L1120">
-        <v>7.18</v>
+        <v>6.88</v>
       </c>
       <c r="M1120">
-        <v>5.27</v>
+        <v>5.2</v>
       </c>
       <c r="N1120">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O1120">
         <v>1</v>
@@ -58509,96 +58512,96 @@
     </row>
     <row r="1121" spans="1:16">
       <c r="A1121" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1121" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C1121">
-        <v>3.450415009789521</v>
+        <v>3.757508779194823</v>
       </c>
       <c r="D1121" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E1121">
-        <v>3.652790681139088</v>
+        <v>3.711629292170211</v>
       </c>
       <c r="F1121">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1121">
-        <v>0.01030958499021048</v>
+        <v>0.01060249122080518</v>
       </c>
       <c r="H1121">
-        <v>0.01030720931886091</v>
+        <v>0.01046837070782979</v>
       </c>
       <c r="I1121">
-        <v>0.202375671349567</v>
+        <v>0.04587948702461109</v>
       </c>
       <c r="J1121">
-        <v>0.6398479459347908</v>
+        <v>0.6302930425055575</v>
       </c>
       <c r="K1121">
+        <v>5.43</v>
+      </c>
+      <c r="L1121">
+        <v>7.18</v>
+      </c>
+      <c r="M1121">
         <v>5.36</v>
       </c>
-      <c r="L1121">
-        <v>6.88</v>
-      </c>
-      <c r="M1121">
-        <v>5.2</v>
-      </c>
       <c r="N1121">
-        <v>6.98</v>
+        <v>7.09</v>
       </c>
       <c r="O1121">
         <v>1</v>
       </c>
       <c r="P1121" t="s">
-        <v>710</v>
+        <v>269</v>
       </c>
     </row>
     <row r="1122" spans="1:16">
       <c r="A1122" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1122" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1122">
-        <v>3.705625653574086</v>
+        <v>3.450415009789521</v>
       </c>
       <c r="D1122" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E1122">
-        <v>3.728001324923652</v>
+        <v>3.652790681139088</v>
       </c>
       <c r="F1122">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1122">
-        <v>0.01065437434642592</v>
+        <v>0.01030958499021048</v>
       </c>
       <c r="H1122">
-        <v>0.01047199867507635</v>
+        <v>0.01030720931886091</v>
       </c>
       <c r="I1122">
-        <v>-0.02237567134956642</v>
+        <v>0.202375671349567</v>
       </c>
       <c r="J1122">
         <v>0.6398479459347908</v>
       </c>
       <c r="K1122">
-        <v>5.43</v>
+        <v>5.36</v>
       </c>
       <c r="L1122">
-        <v>7.18</v>
+        <v>6.88</v>
       </c>
       <c r="M1122">
-        <v>5.27</v>
+        <v>5.2</v>
       </c>
       <c r="N1122">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O1122">
         <v>1</v>
@@ -58609,34 +58612,34 @@
     </row>
     <row r="1123" spans="1:16">
       <c r="A1123" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1123" t="s">
         <v>271</v>
       </c>
       <c r="C1123">
-        <v>3.655166259867152</v>
+        <v>3.705625653574086</v>
       </c>
       <c r="D1123" t="s">
         <v>515</v>
       </c>
       <c r="E1123">
-        <v>3.679028764180458</v>
+        <v>3.660415009789521</v>
       </c>
       <c r="F1123">
         <v>-1</v>
       </c>
       <c r="G1123">
-        <v>0.01070483374013285</v>
+        <v>0.01065437434642592</v>
       </c>
       <c r="H1123">
-        <v>0.01052097123581954</v>
+        <v>0.01051958499021048</v>
       </c>
       <c r="I1123">
-        <v>-0.0238625043133065</v>
+        <v>0.04521064378456474</v>
       </c>
       <c r="J1123">
-        <v>0.6491406519581673</v>
+        <v>0.6398479459347908</v>
       </c>
       <c r="K1123">
         <v>5.43</v>
@@ -58645,16 +58648,16 @@
         <v>7.18</v>
       </c>
       <c r="M1123">
-        <v>5.27</v>
+        <v>5.36</v>
       </c>
       <c r="N1123">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="O1123">
         <v>1</v>
       </c>
       <c r="P1123" t="s">
-        <v>270</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1124" spans="1:16">
@@ -58662,54 +58665,54 @@
         <v>0</v>
       </c>
       <c r="B1124" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C1124">
-        <v>3.422696366106458</v>
+        <v>3.655166259867152</v>
       </c>
       <c r="D1124" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E1124">
-        <v>3.578117189387469</v>
+        <v>3.610606105504223</v>
       </c>
       <c r="F1124">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1124">
-        <v>0.01035730363389354</v>
+        <v>0.01070483374013285</v>
       </c>
       <c r="H1124">
-        <v>0.01038188281061253</v>
+        <v>0.01056939389449578</v>
       </c>
       <c r="I1124">
-        <v>0.1554208232810108</v>
+        <v>0.04456015436292882</v>
       </c>
       <c r="J1124">
-        <v>0.6542082328101022</v>
+        <v>0.6491406519581673</v>
       </c>
       <c r="K1124">
-        <v>5.3</v>
+        <v>5.43</v>
       </c>
       <c r="L1124">
-        <v>6.89</v>
+        <v>7.18</v>
       </c>
       <c r="M1124">
-        <v>5.2</v>
+        <v>5.36</v>
       </c>
       <c r="N1124">
-        <v>6.98</v>
+        <v>7.09</v>
       </c>
       <c r="O1124">
         <v>1</v>
       </c>
       <c r="P1124" t="s">
-        <v>711</v>
+        <v>270</v>
       </c>
     </row>
     <row r="1125" spans="1:16">
       <c r="A1125" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1125" t="s">
         <v>271</v>
@@ -58721,7 +58724,7 @@
         <v>515</v>
       </c>
       <c r="E1125">
-        <v>3.652322613090761</v>
+        <v>3.583443872137852</v>
       </c>
       <c r="F1125">
         <v>-1</v>
@@ -58730,10 +58733,10 @@
         <v>0.01073235070415885</v>
       </c>
       <c r="H1125">
-        <v>0.01054767738690924</v>
+        <v>0.01059655612786215</v>
       </c>
       <c r="I1125">
-        <v>-0.0246733172496163</v>
+        <v>0.04420542370329317</v>
       </c>
       <c r="J1125">
         <v>0.6542082328101022</v>
@@ -58745,16 +58748,166 @@
         <v>7.18</v>
       </c>
       <c r="M1125">
-        <v>5.27</v>
+        <v>5.36</v>
       </c>
       <c r="N1125">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="O1125">
         <v>1</v>
       </c>
       <c r="P1125" t="s">
         <v>711</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:16">
+      <c r="A1126" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1126" t="s">
+        <v>272</v>
+      </c>
+      <c r="C1126">
+        <v>3.621276282748954</v>
+      </c>
+      <c r="D1126" t="s">
+        <v>515</v>
+      </c>
+      <c r="E1126">
+        <v>3.55186733881108</v>
+      </c>
+      <c r="F1126">
+        <v>-1</v>
+      </c>
+      <c r="G1126">
+        <v>0.01057872371725104</v>
+      </c>
+      <c r="H1126">
+        <v>0.01062813266118892</v>
+      </c>
+      <c r="I1126">
+        <v>0.06940894393787378</v>
+      </c>
+      <c r="J1126">
+        <v>0.660099377087485</v>
+      </c>
+      <c r="K1126">
+        <v>5.27</v>
+      </c>
+      <c r="L1126">
+        <v>7.1</v>
+      </c>
+      <c r="M1126">
+        <v>5.36</v>
+      </c>
+      <c r="N1126">
+        <v>7.09</v>
+      </c>
+      <c r="O1126">
+        <v>1</v>
+      </c>
+      <c r="P1126" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:16">
+      <c r="A1127" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1127" t="s">
+        <v>272</v>
+      </c>
+      <c r="C1127">
+        <v>3.634548533744118</v>
+      </c>
+      <c r="D1127" t="s">
+        <v>515</v>
+      </c>
+      <c r="E1127">
+        <v>3.565366250639179</v>
+      </c>
+      <c r="F1127">
+        <v>-1</v>
+      </c>
+      <c r="G1127">
+        <v>0.01056545146625588</v>
+      </c>
+      <c r="H1127">
+        <v>0.01061463374936082</v>
+      </c>
+      <c r="I1127">
+        <v>0.06918228310493957</v>
+      </c>
+      <c r="J1127">
+        <v>0.6575809233882128</v>
+      </c>
+      <c r="K1127">
+        <v>5.27</v>
+      </c>
+      <c r="L1127">
+        <v>7.1</v>
+      </c>
+      <c r="M1127">
+        <v>5.36</v>
+      </c>
+      <c r="N1127">
+        <v>7.09</v>
+      </c>
+      <c r="O1127">
+        <v>1</v>
+      </c>
+      <c r="P1127" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:16">
+      <c r="A1128" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1128" t="s">
+        <v>272</v>
+      </c>
+      <c r="C1128">
+        <v>3.679346784171853</v>
+      </c>
+      <c r="D1128" t="s">
+        <v>515</v>
+      </c>
+      <c r="E1128">
+        <v>3.610929556577065</v>
+      </c>
+      <c r="F1128">
+        <v>-1</v>
+      </c>
+      <c r="G1128">
+        <v>0.01052065321582815</v>
+      </c>
+      <c r="H1128">
+        <v>0.01056907044342293</v>
+      </c>
+      <c r="I1128">
+        <v>0.06841722759478852</v>
+      </c>
+      <c r="J1128">
+        <v>0.6490803066087565</v>
+      </c>
+      <c r="K1128">
+        <v>5.27</v>
+      </c>
+      <c r="L1128">
+        <v>7.1</v>
+      </c>
+      <c r="M1128">
+        <v>5.36</v>
+      </c>
+      <c r="N1128">
+        <v>7.09</v>
+      </c>
+      <c r="O1128">
+        <v>1</v>
+      </c>
+      <c r="P1128" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3426" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3420" uniqueCount="717">
   <si>
     <t>trade_time</t>
   </si>
@@ -1565,6 +1565,9 @@
   </si>
   <si>
     <t>2021-11-22</t>
+  </si>
+  <si>
+    <t>2021-11-30</t>
   </si>
   <si>
     <t>2021-11-29</t>
@@ -2519,7 +2522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1138"/>
+  <dimension ref="A1:P1136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2616,7 +2619,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2666,7 +2669,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2716,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2766,7 +2769,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2816,7 +2819,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2866,7 +2869,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2916,7 +2919,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2966,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -3016,7 +3019,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -3066,7 +3069,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3116,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3166,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3216,7 +3219,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -3266,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -3416,7 +3419,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3466,7 +3469,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3516,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3566,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3616,7 +3619,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3666,7 +3669,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3716,7 +3719,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3866,7 +3869,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3916,7 +3919,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -4066,7 +4069,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -4116,7 +4119,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -4166,7 +4169,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4216,7 +4219,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -4266,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4316,7 +4319,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4466,7 +4469,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4516,7 +4519,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4566,7 +4569,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4616,7 +4619,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4666,7 +4669,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4716,7 +4719,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4766,7 +4769,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4816,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4866,7 +4869,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4916,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4966,7 +4969,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -5016,7 +5019,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -5066,7 +5069,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -5316,7 +5319,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -5366,7 +5369,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -5416,7 +5419,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5566,7 +5569,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5616,7 +5619,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -7616,7 +7619,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7666,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7716,7 +7719,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -8166,7 +8169,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -8216,7 +8219,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -8266,7 +8269,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -8316,7 +8319,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -8366,7 +8369,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -8566,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8616,7 +8619,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -8666,7 +8669,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8866,7 +8869,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8916,7 +8919,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8966,7 +8969,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -9016,7 +9019,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -9316,7 +9319,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -9366,7 +9369,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -9416,7 +9419,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -9466,7 +9469,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9516,7 +9519,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9766,7 +9769,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9816,7 +9819,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9866,7 +9869,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9916,7 +9919,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -11316,7 +11319,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11366,7 +11369,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11416,7 +11419,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11466,7 +11469,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11516,7 +11519,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11566,7 +11569,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -12016,7 +12019,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -12066,7 +12069,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -12216,7 +12219,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -12266,7 +12269,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -12316,7 +12319,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -12766,7 +12769,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12816,7 +12819,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12866,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12916,7 +12919,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12966,7 +12969,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -13916,7 +13919,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13966,7 +13969,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -14016,7 +14019,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -14066,7 +14069,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -14116,7 +14119,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -14166,7 +14169,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -14966,7 +14969,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -15016,7 +15019,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -15066,7 +15069,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -15116,7 +15119,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -15166,7 +15169,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -15666,7 +15669,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15716,7 +15719,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15766,7 +15769,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15816,7 +15819,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15866,7 +15869,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15916,7 +15919,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15966,7 +15969,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -17466,7 +17469,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -17516,7 +17519,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -17566,7 +17569,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -17616,7 +17619,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17666,7 +17669,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17716,7 +17719,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17766,7 +17769,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -19416,7 +19419,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -19466,7 +19469,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19666,7 +19669,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19716,7 +19719,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19766,7 +19769,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19816,7 +19819,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19966,7 +19969,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -20016,7 +20019,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -20066,7 +20069,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -20216,7 +20219,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -20266,7 +20269,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -20316,7 +20319,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -20566,7 +20569,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -20616,7 +20619,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20666,7 +20669,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20716,7 +20719,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20766,7 +20769,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20816,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20866,7 +20869,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20916,7 +20919,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20966,7 +20969,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -21016,7 +21019,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -21066,7 +21069,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -21116,7 +21119,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -21166,7 +21169,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -21266,7 +21269,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -21316,7 +21319,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -21366,7 +21369,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -21416,7 +21419,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21466,7 +21469,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21516,7 +21519,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -21566,7 +21569,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21616,7 +21619,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -22066,7 +22069,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -22116,7 +22119,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -22166,7 +22169,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -22366,7 +22369,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -22416,7 +22419,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -22466,7 +22469,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -22516,7 +22519,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -22566,7 +22569,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22616,7 +22619,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22666,7 +22669,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22716,7 +22719,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22766,7 +22769,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22816,7 +22819,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22866,7 +22869,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22916,7 +22919,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22966,7 +22969,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -23016,7 +23019,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -23066,7 +23069,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -23116,7 +23119,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -23166,7 +23169,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -23216,7 +23219,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -23266,7 +23269,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -23316,7 +23319,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23816,7 +23819,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23866,7 +23869,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23916,7 +23919,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23966,7 +23969,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -24016,7 +24019,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -24266,7 +24269,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -24316,7 +24319,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24366,7 +24369,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24416,7 +24419,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24466,7 +24469,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24516,7 +24519,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24566,7 +24569,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24616,7 +24619,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24666,7 +24669,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24716,7 +24719,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24766,7 +24769,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24816,7 +24819,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24866,7 +24869,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24916,7 +24919,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -25116,7 +25119,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -25166,7 +25169,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -25216,7 +25219,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25266,7 +25269,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -25816,7 +25819,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25866,7 +25869,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25916,7 +25919,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25966,7 +25969,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -26016,7 +26019,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -26266,7 +26269,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26316,7 +26319,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26366,7 +26369,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26416,7 +26419,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26616,7 +26619,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26666,7 +26669,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26716,7 +26719,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26766,7 +26769,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26816,7 +26819,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26866,7 +26869,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26916,7 +26919,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -27216,7 +27219,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -27266,7 +27269,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -27316,7 +27319,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -27366,7 +27369,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -27516,7 +27519,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -27566,7 +27569,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -27616,7 +27619,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27666,7 +27669,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27716,7 +27719,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27866,7 +27869,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27916,7 +27919,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -28066,7 +28069,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -28116,7 +28119,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -28166,7 +28169,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -28216,7 +28219,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28266,7 +28269,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -28316,7 +28319,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -28366,7 +28369,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -28416,7 +28419,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -28666,7 +28669,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28716,7 +28719,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28766,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28816,7 +28819,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28866,7 +28869,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28916,7 +28919,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28966,7 +28969,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -29016,7 +29019,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -29066,7 +29069,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -29116,7 +29119,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -29166,7 +29169,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -29216,7 +29219,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -29266,7 +29269,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -29316,7 +29319,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29366,7 +29369,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29416,7 +29419,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -29666,7 +29669,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29716,7 +29719,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29916,7 +29919,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29966,7 +29969,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -30016,7 +30019,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -30066,7 +30069,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -30116,7 +30119,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -30166,7 +30169,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -30216,7 +30219,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -30266,7 +30269,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -30316,7 +30319,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30466,7 +30469,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -30516,7 +30519,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -30716,7 +30719,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30766,7 +30769,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30966,7 +30969,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -31016,7 +31019,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -31066,7 +31069,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -31116,7 +31119,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -31166,7 +31169,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -31266,7 +31269,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -31316,7 +31319,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31366,7 +31369,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31416,7 +31419,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31666,7 +31669,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31716,7 +31719,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31766,7 +31769,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -32116,7 +32119,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -32166,7 +32169,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -32216,7 +32219,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -33166,7 +33169,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -33216,7 +33219,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -33266,7 +33269,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -33316,7 +33319,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33516,7 +33519,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -33566,7 +33569,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -33616,7 +33619,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -34416,7 +34419,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -34466,7 +34469,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -34516,7 +34519,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -34566,7 +34569,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -34616,7 +34619,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -34666,7 +34669,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -34716,7 +34719,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34766,7 +34769,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34816,7 +34819,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34866,7 +34869,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34916,7 +34919,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34966,7 +34969,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -35016,7 +35019,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -35066,7 +35069,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -35166,7 +35169,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -35216,7 +35219,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -35266,7 +35269,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -35316,7 +35319,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35366,7 +35369,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -35416,7 +35419,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -35466,7 +35469,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -35666,7 +35669,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35716,7 +35719,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -35766,7 +35769,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -36216,7 +36219,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -36266,7 +36269,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -36316,7 +36319,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -36366,7 +36369,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -36566,7 +36569,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36616,7 +36619,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36666,7 +36669,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36716,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36766,7 +36769,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36816,7 +36819,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36866,7 +36869,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36916,7 +36919,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36966,7 +36969,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -37016,7 +37019,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -37066,7 +37069,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -37116,7 +37119,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -38116,7 +38119,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -38166,7 +38169,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -38216,7 +38219,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -38266,7 +38269,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -38516,7 +38519,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -38566,7 +38569,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38616,7 +38619,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38666,7 +38669,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38866,7 +38869,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38916,7 +38919,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38966,7 +38969,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -39066,7 +39069,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -39416,7 +39419,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -39466,7 +39469,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -39516,7 +39519,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -39566,7 +39569,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -39616,7 +39619,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39666,7 +39669,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39716,7 +39719,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39766,7 +39769,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39816,7 +39819,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39866,7 +39869,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -40116,7 +40119,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -40166,7 +40169,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -40216,7 +40219,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -40516,7 +40519,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40566,7 +40569,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40616,7 +40619,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40866,7 +40869,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40916,7 +40919,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40966,7 +40969,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -41016,7 +41019,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -41066,7 +41069,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -41516,7 +41519,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41566,7 +41569,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41666,7 +41669,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41716,7 +41719,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41766,7 +41769,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41816,7 +41819,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -42966,7 +42969,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -43016,7 +43019,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -43066,7 +43069,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -43116,7 +43119,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -43166,7 +43169,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -43216,7 +43219,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -43266,7 +43269,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -43316,7 +43319,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43366,7 +43369,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -44116,7 +44119,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -44166,7 +44169,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -44216,7 +44219,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -44466,7 +44469,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -44516,7 +44519,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -44566,7 +44569,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -44616,7 +44619,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -44666,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44716,7 +44719,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44766,7 +44769,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44816,7 +44819,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44866,7 +44869,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44916,7 +44919,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44966,7 +44969,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -45166,7 +45169,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -45216,7 +45219,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -45266,7 +45269,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -45466,7 +45469,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -45516,7 +45519,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -45566,7 +45569,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -45616,7 +45619,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45666,7 +45669,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45716,7 +45719,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -46616,7 +46619,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46666,7 +46669,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46766,7 +46769,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46816,7 +46819,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46866,7 +46869,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -47166,7 +47169,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -47216,7 +47219,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -47266,7 +47269,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -47316,7 +47319,7 @@
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="897" spans="1:16">
@@ -47366,7 +47369,7 @@
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="898" spans="1:16">
@@ -47516,7 +47519,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47616,7 +47619,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47666,7 +47669,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47716,7 +47719,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47866,7 +47869,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47916,7 +47919,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47966,7 +47969,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -48166,7 +48169,7 @@
         <v>1</v>
       </c>
       <c r="P913" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="914" spans="1:16">
@@ -48216,7 +48219,7 @@
         <v>1</v>
       </c>
       <c r="P914" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="915" spans="1:16">
@@ -48266,7 +48269,7 @@
         <v>1</v>
       </c>
       <c r="P915" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="916" spans="1:16">
@@ -48316,7 +48319,7 @@
         <v>1</v>
       </c>
       <c r="P916" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="917" spans="1:16">
@@ -48366,7 +48369,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -48716,7 +48719,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48766,7 +48769,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48816,7 +48819,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48866,7 +48869,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -49066,7 +49069,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -49116,7 +49119,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -49616,7 +49619,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49666,7 +49669,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49716,7 +49719,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49766,7 +49769,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49816,7 +49819,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -50216,7 +50219,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -50416,7 +50419,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -50466,7 +50469,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -50516,7 +50519,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -50566,7 +50569,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -51116,7 +51119,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -51166,7 +51169,7 @@
         <v>1</v>
       </c>
       <c r="P973" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="974" spans="1:16">
@@ -51216,7 +51219,7 @@
         <v>1</v>
       </c>
       <c r="P974" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="975" spans="1:16">
@@ -51866,7 +51869,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51916,7 +51919,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51966,7 +51969,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -52866,7 +52869,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -54216,7 +54219,7 @@
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -54266,7 +54269,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -54666,7 +54669,7 @@
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
@@ -54716,7 +54719,7 @@
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
@@ -54766,7 +54769,7 @@
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
@@ -54816,7 +54819,7 @@
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
@@ -54966,7 +54969,7 @@
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
@@ -55016,7 +55019,7 @@
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
@@ -55066,7 +55069,7 @@
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
@@ -55116,7 +55119,7 @@
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
@@ -55166,7 +55169,7 @@
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
@@ -55216,7 +55219,7 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
@@ -56666,7 +56669,7 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56716,7 +56719,7 @@
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56916,7 +56919,7 @@
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56966,7 +56969,7 @@
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -57016,7 +57019,7 @@
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -57166,7 +57169,7 @@
         <v>1</v>
       </c>
       <c r="P1093" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="1094" spans="1:16">
@@ -57216,7 +57219,7 @@
         <v>1</v>
       </c>
       <c r="P1094" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="1095" spans="1:16">
@@ -57266,7 +57269,7 @@
         <v>1</v>
       </c>
       <c r="P1095" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1096" spans="1:16">
@@ -57316,7 +57319,7 @@
         <v>1</v>
       </c>
       <c r="P1096" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1097" spans="1:16">
@@ -57616,7 +57619,7 @@
         <v>1</v>
       </c>
       <c r="P1102" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1103" spans="1:16">
@@ -57666,7 +57669,7 @@
         <v>1</v>
       </c>
       <c r="P1103" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1104" spans="1:16">
@@ -57716,7 +57719,7 @@
         <v>1</v>
       </c>
       <c r="P1104" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1105" spans="1:16">
@@ -57766,7 +57769,7 @@
         <v>1</v>
       </c>
       <c r="P1105" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1106" spans="1:16">
@@ -57816,7 +57819,7 @@
         <v>1</v>
       </c>
       <c r="P1106" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1107" spans="1:16">
@@ -57866,7 +57869,7 @@
         <v>1</v>
       </c>
       <c r="P1107" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1108" spans="1:16">
@@ -57916,7 +57919,7 @@
         <v>1</v>
       </c>
       <c r="P1108" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1109" spans="1:16">
@@ -57966,7 +57969,7 @@
         <v>1</v>
       </c>
       <c r="P1109" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1110" spans="1:16">
@@ -58016,7 +58019,7 @@
         <v>1</v>
       </c>
       <c r="P1110" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1111" spans="1:16">
@@ -58033,7 +58036,7 @@
         <v>517</v>
       </c>
       <c r="E1111">
-        <v>3.644372297766094</v>
+        <v>3.719842279953954</v>
       </c>
       <c r="F1111">
         <v>-1</v>
@@ -58042,10 +58045,10 @@
         <v>0.01045567015325052</v>
       </c>
       <c r="H1111">
-        <v>0.01021562770223391</v>
+        <v>0.01024015772004605</v>
       </c>
       <c r="I1111">
-        <v>0.09995754898338571</v>
+        <v>0.02448756679552533</v>
       </c>
       <c r="J1111">
         <v>0.6367495546964934</v>
@@ -58057,16 +58060,16 @@
         <v>7.1</v>
       </c>
       <c r="M1111">
-        <v>5.16</v>
+        <v>5.12</v>
       </c>
       <c r="N1111">
-        <v>6.93</v>
+        <v>6.98</v>
       </c>
       <c r="O1111">
         <v>1</v>
       </c>
       <c r="P1111" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1112" spans="1:16">
@@ -58116,7 +58119,7 @@
         <v>1</v>
       </c>
       <c r="P1112" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1113" spans="1:16">
@@ -58166,7 +58169,7 @@
         <v>1</v>
       </c>
       <c r="P1113" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1114" spans="1:16">
@@ -58174,49 +58177,49 @@
         <v>2</v>
       </c>
       <c r="B1114" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C1114">
-        <v>3.765446136313247</v>
+        <v>3.557194203031345</v>
       </c>
       <c r="D1114" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E1114">
-        <v>3.685230582573914</v>
+        <v>3.710077331276038</v>
       </c>
       <c r="F1114">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1114">
-        <v>0.01059455386368675</v>
+        <v>0.01022280579696865</v>
       </c>
       <c r="H1114">
-        <v>0.01017476941742609</v>
+        <v>0.01024992266872396</v>
       </c>
       <c r="I1114">
-        <v>0.08021555373933298</v>
+        <v>0.1528831282446923</v>
       </c>
       <c r="J1114">
         <v>0.6288312824469159</v>
       </c>
       <c r="K1114">
-        <v>5.43</v>
+        <v>5.3</v>
       </c>
       <c r="L1114">
-        <v>7.18</v>
+        <v>6.89</v>
       </c>
       <c r="M1114">
-        <v>5.16</v>
+        <v>5.2</v>
       </c>
       <c r="N1114">
-        <v>6.93</v>
+        <v>6.98</v>
       </c>
       <c r="O1114">
         <v>1</v>
       </c>
       <c r="P1114" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1115" spans="1:16">
@@ -58224,90 +58227,90 @@
         <v>3</v>
       </c>
       <c r="B1115" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C1115">
-        <v>3.760077331276038</v>
+        <v>3.765446136313247</v>
       </c>
       <c r="D1115" t="s">
         <v>517</v>
       </c>
       <c r="E1115">
-        <v>3.685230582573914</v>
+        <v>3.760383833871791</v>
       </c>
       <c r="F1115">
         <v>-1</v>
       </c>
       <c r="G1115">
-        <v>0.01029992266872396</v>
+        <v>0.01059455386368675</v>
       </c>
       <c r="H1115">
-        <v>0.01017476941742609</v>
+        <v>0.01019961616612821</v>
       </c>
       <c r="I1115">
-        <v>0.07484674870212382</v>
+        <v>0.005062302441455557</v>
       </c>
       <c r="J1115">
         <v>0.6288312824469159</v>
       </c>
       <c r="K1115">
-        <v>5.2</v>
+        <v>5.43</v>
       </c>
       <c r="L1115">
-        <v>7.03</v>
+        <v>7.18</v>
       </c>
       <c r="M1115">
-        <v>5.16</v>
+        <v>5.12</v>
       </c>
       <c r="N1115">
-        <v>6.93</v>
+        <v>6.98</v>
       </c>
       <c r="O1115">
         <v>1</v>
       </c>
       <c r="P1115" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1116" spans="1:16">
       <c r="A1116" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1116" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C1116">
-        <v>3.499579559290895</v>
+        <v>3.760077331276038</v>
       </c>
       <c r="D1116" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E1116">
-        <v>3.720039284616297</v>
+        <v>3.760383833871791</v>
       </c>
       <c r="F1116">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1116">
-        <v>0.0103204204407091</v>
+        <v>0.01029992266872396</v>
       </c>
       <c r="H1116">
-        <v>0.0102399607153837</v>
+        <v>0.01019961616612821</v>
       </c>
       <c r="I1116">
-        <v>0.2204597253254019</v>
+        <v>-0.0003065025957535994</v>
       </c>
       <c r="J1116">
-        <v>0.6269155221891737</v>
+        <v>0.6288312824469159</v>
       </c>
       <c r="K1116">
-        <v>5.44</v>
+        <v>5.2</v>
       </c>
       <c r="L1116">
-        <v>6.91</v>
+        <v>7.03</v>
       </c>
       <c r="M1116">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="N1116">
         <v>6.98</v>
@@ -58321,13 +58324,13 @@
     </row>
     <row r="1117" spans="1:16">
       <c r="A1117" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1117" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C1117">
-        <v>3.519732801066029</v>
+        <v>3.499579559290895</v>
       </c>
       <c r="D1117" t="s">
         <v>516</v>
@@ -58339,22 +58342,22 @@
         <v>1</v>
       </c>
       <c r="G1117">
-        <v>0.01024026719893397</v>
+        <v>0.0103204204407091</v>
       </c>
       <c r="H1117">
         <v>0.0102399607153837</v>
       </c>
       <c r="I1117">
-        <v>0.2003064835502681</v>
+        <v>0.2204597253254019</v>
       </c>
       <c r="J1117">
         <v>0.6269155221891737</v>
       </c>
       <c r="K1117">
-        <v>5.36</v>
+        <v>5.44</v>
       </c>
       <c r="L1117">
-        <v>6.88</v>
+        <v>6.91</v>
       </c>
       <c r="M1117">
         <v>5.2</v>
@@ -58366,148 +58369,148 @@
         <v>1</v>
       </c>
       <c r="P1117" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1118" spans="1:16">
       <c r="A1118" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1118" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C1118">
-        <v>3.775848714512787</v>
+        <v>3.519732801066029</v>
       </c>
       <c r="D1118" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E1118">
-        <v>3.695115905503863</v>
+        <v>3.720039284616297</v>
       </c>
       <c r="F1118">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1118">
-        <v>0.01058415128548721</v>
+        <v>0.01024026719893397</v>
       </c>
       <c r="H1118">
-        <v>0.01016488409449614</v>
+        <v>0.0102399607153837</v>
       </c>
       <c r="I1118">
-        <v>0.08073280900892366</v>
+        <v>0.2003064835502681</v>
       </c>
       <c r="J1118">
         <v>0.6269155221891737</v>
       </c>
       <c r="K1118">
-        <v>5.43</v>
+        <v>5.36</v>
       </c>
       <c r="L1118">
-        <v>7.18</v>
+        <v>6.88</v>
       </c>
       <c r="M1118">
-        <v>5.16</v>
+        <v>5.2</v>
       </c>
       <c r="N1118">
-        <v>6.93</v>
+        <v>6.98</v>
       </c>
       <c r="O1118">
         <v>1</v>
       </c>
       <c r="P1118" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1119" spans="1:16">
       <c r="A1119" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1119" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C1119">
-        <v>3.770039284616297</v>
+        <v>3.775848714512787</v>
       </c>
       <c r="D1119" t="s">
         <v>517</v>
       </c>
       <c r="E1119">
-        <v>3.695115905503863</v>
+        <v>3.770192526391431</v>
       </c>
       <c r="F1119">
         <v>-1</v>
       </c>
       <c r="G1119">
-        <v>0.0102899607153837</v>
+        <v>0.01058415128548721</v>
       </c>
       <c r="H1119">
-        <v>0.01016488409449614</v>
+        <v>0.01018980747360857</v>
       </c>
       <c r="I1119">
-        <v>0.07492337911243352</v>
+        <v>0.005656188121355932</v>
       </c>
       <c r="J1119">
         <v>0.6269155221891737</v>
       </c>
       <c r="K1119">
-        <v>5.2</v>
+        <v>5.43</v>
       </c>
       <c r="L1119">
-        <v>7.03</v>
+        <v>7.18</v>
       </c>
       <c r="M1119">
-        <v>5.16</v>
+        <v>5.12</v>
       </c>
       <c r="N1119">
-        <v>6.93</v>
+        <v>6.98</v>
       </c>
       <c r="O1119">
         <v>1</v>
       </c>
       <c r="P1119" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1120" spans="1:16">
       <c r="A1120" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1120" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C1120">
-        <v>3.47813903198738</v>
+        <v>3.770039284616297</v>
       </c>
       <c r="D1120" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E1120">
-        <v>3.699544662929113</v>
+        <v>3.770192526391431</v>
       </c>
       <c r="F1120">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1120">
-        <v>0.01034186096801262</v>
+        <v>0.0102899607153837</v>
       </c>
       <c r="H1120">
-        <v>0.01026045533707089</v>
+        <v>0.01018980747360857</v>
       </c>
       <c r="I1120">
-        <v>0.2214056309417338</v>
+        <v>-0.0001532417751342052</v>
       </c>
       <c r="J1120">
-        <v>0.6308567955905552</v>
+        <v>0.6269155221891737</v>
       </c>
       <c r="K1120">
-        <v>5.44</v>
+        <v>5.2</v>
       </c>
       <c r="L1120">
-        <v>6.91</v>
+        <v>7.03</v>
       </c>
       <c r="M1120">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="N1120">
         <v>6.98</v>
@@ -58521,13 +58524,13 @@
     </row>
     <row r="1121" spans="1:16">
       <c r="A1121" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1121" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C1121">
-        <v>3.498607575634624</v>
+        <v>3.47813903198738</v>
       </c>
       <c r="D1121" t="s">
         <v>516</v>
@@ -58539,22 +58542,22 @@
         <v>1</v>
       </c>
       <c r="G1121">
-        <v>0.01026139242436538</v>
+        <v>0.01034186096801262</v>
       </c>
       <c r="H1121">
         <v>0.01026045533707089</v>
       </c>
       <c r="I1121">
-        <v>0.2009370872944896</v>
+        <v>0.2214056309417338</v>
       </c>
       <c r="J1121">
         <v>0.6308567955905552</v>
       </c>
       <c r="K1121">
-        <v>5.36</v>
+        <v>5.44</v>
       </c>
       <c r="L1121">
-        <v>6.88</v>
+        <v>6.91</v>
       </c>
       <c r="M1121">
         <v>5.2</v>
@@ -58566,148 +58569,148 @@
         <v>1</v>
       </c>
       <c r="P1121" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1122" spans="1:16">
       <c r="A1122" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1122" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C1122">
-        <v>3.754447599943285</v>
+        <v>3.498607575634624</v>
       </c>
       <c r="D1122" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E1122">
-        <v>3.674778934752735</v>
+        <v>3.699544662929113</v>
       </c>
       <c r="F1122">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1122">
-        <v>0.01060555240005671</v>
+        <v>0.01026139242436538</v>
       </c>
       <c r="H1122">
-        <v>0.01018522106524727</v>
+        <v>0.01026045533707089</v>
       </c>
       <c r="I1122">
-        <v>0.07966866519055049</v>
+        <v>0.2009370872944896</v>
       </c>
       <c r="J1122">
         <v>0.6308567955905552</v>
       </c>
       <c r="K1122">
-        <v>5.43</v>
+        <v>5.36</v>
       </c>
       <c r="L1122">
-        <v>7.18</v>
+        <v>6.88</v>
       </c>
       <c r="M1122">
-        <v>5.16</v>
+        <v>5.2</v>
       </c>
       <c r="N1122">
-        <v>6.93</v>
+        <v>6.98</v>
       </c>
       <c r="O1122">
         <v>1</v>
       </c>
       <c r="P1122" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1123" spans="1:16">
       <c r="A1123" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1123" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C1123">
-        <v>3.749544662929113</v>
+        <v>3.754447599943285</v>
       </c>
       <c r="D1123" t="s">
         <v>517</v>
       </c>
       <c r="E1123">
-        <v>3.674778934752735</v>
+        <v>3.750013206576358</v>
       </c>
       <c r="F1123">
         <v>-1</v>
       </c>
       <c r="G1123">
-        <v>0.01031045533707089</v>
+        <v>0.01060555240005671</v>
       </c>
       <c r="H1123">
-        <v>0.01018522106524727</v>
+        <v>0.01020998679342364</v>
       </c>
       <c r="I1123">
-        <v>0.0747657281763785</v>
+        <v>0.004434393366927303</v>
       </c>
       <c r="J1123">
         <v>0.6308567955905552</v>
       </c>
       <c r="K1123">
-        <v>5.2</v>
+        <v>5.43</v>
       </c>
       <c r="L1123">
-        <v>7.03</v>
+        <v>7.18</v>
       </c>
       <c r="M1123">
-        <v>5.16</v>
+        <v>5.12</v>
       </c>
       <c r="N1123">
-        <v>6.93</v>
+        <v>6.98</v>
       </c>
       <c r="O1123">
         <v>1</v>
       </c>
       <c r="P1123" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1124" spans="1:16">
       <c r="A1124" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1124" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C1124">
-        <v>3.501629292170211</v>
+        <v>3.749544662929113</v>
       </c>
       <c r="D1124" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E1124">
-        <v>3.702476178971101</v>
+        <v>3.750013206576358</v>
       </c>
       <c r="F1124">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1124">
-        <v>0.01025837070782979</v>
+        <v>0.01031045533707089</v>
       </c>
       <c r="H1124">
-        <v>0.0102575238210289</v>
+        <v>0.01020998679342364</v>
       </c>
       <c r="I1124">
-        <v>0.2008468868008899</v>
+        <v>-0.0004685436472446902</v>
       </c>
       <c r="J1124">
-        <v>0.6302930425055575</v>
+        <v>0.6308567955905552</v>
       </c>
       <c r="K1124">
-        <v>5.36</v>
+        <v>5.2</v>
       </c>
       <c r="L1124">
-        <v>6.88</v>
+        <v>7.03</v>
       </c>
       <c r="M1124">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="N1124">
         <v>6.98</v>
@@ -58716,51 +58719,51 @@
         <v>1</v>
       </c>
       <c r="P1124" t="s">
-        <v>269</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1125" spans="1:16">
       <c r="A1125" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1125" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C1125">
-        <v>3.757508779194823</v>
+        <v>3.501629292170211</v>
       </c>
       <c r="D1125" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E1125">
-        <v>3.677687900671323</v>
+        <v>3.702476178971101</v>
       </c>
       <c r="F1125">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1125">
-        <v>0.01060249122080518</v>
+        <v>0.01025837070782979</v>
       </c>
       <c r="H1125">
-        <v>0.01018231209932868</v>
+        <v>0.0102575238210289</v>
       </c>
       <c r="I1125">
-        <v>0.07982087852349951</v>
+        <v>0.2008468868008899</v>
       </c>
       <c r="J1125">
         <v>0.6302930425055575</v>
       </c>
       <c r="K1125">
-        <v>5.43</v>
+        <v>5.36</v>
       </c>
       <c r="L1125">
-        <v>7.18</v>
+        <v>6.88</v>
       </c>
       <c r="M1125">
-        <v>5.16</v>
+        <v>5.2</v>
       </c>
       <c r="N1125">
-        <v>6.93</v>
+        <v>6.98</v>
       </c>
       <c r="O1125">
         <v>1</v>
@@ -58771,46 +58774,46 @@
     </row>
     <row r="1126" spans="1:16">
       <c r="A1126" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1126" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C1126">
-        <v>3.752476178971101</v>
+        <v>3.757508779194823</v>
       </c>
       <c r="D1126" t="s">
         <v>517</v>
       </c>
       <c r="E1126">
-        <v>3.677687900671323</v>
+        <v>3.752899622371546</v>
       </c>
       <c r="F1126">
         <v>-1</v>
       </c>
       <c r="G1126">
-        <v>0.0103075238210289</v>
+        <v>0.01060249122080518</v>
       </c>
       <c r="H1126">
-        <v>0.01018231209932868</v>
+        <v>0.01020710037762845</v>
       </c>
       <c r="I1126">
-        <v>0.07478827829977819</v>
+        <v>0.00460915682327645</v>
       </c>
       <c r="J1126">
         <v>0.6302930425055575</v>
       </c>
       <c r="K1126">
-        <v>5.2</v>
+        <v>5.43</v>
       </c>
       <c r="L1126">
-        <v>7.03</v>
+        <v>7.18</v>
       </c>
       <c r="M1126">
-        <v>5.16</v>
+        <v>5.12</v>
       </c>
       <c r="N1126">
-        <v>6.93</v>
+        <v>6.98</v>
       </c>
       <c r="O1126">
         <v>1</v>
@@ -58821,43 +58824,43 @@
     </row>
     <row r="1127" spans="1:16">
       <c r="A1127" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1127" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C1127">
-        <v>3.450415009789521</v>
+        <v>3.752476178971101</v>
       </c>
       <c r="D1127" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E1127">
-        <v>3.652790681139088</v>
+        <v>3.752899622371546</v>
       </c>
       <c r="F1127">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1127">
-        <v>0.01030958499021048</v>
+        <v>0.0103075238210289</v>
       </c>
       <c r="H1127">
-        <v>0.01030720931886091</v>
+        <v>0.01020710037762845</v>
       </c>
       <c r="I1127">
-        <v>0.202375671349567</v>
+        <v>-0.0004234434004448673</v>
       </c>
       <c r="J1127">
-        <v>0.6398479459347908</v>
+        <v>0.6302930425055575</v>
       </c>
       <c r="K1127">
-        <v>5.36</v>
+        <v>5.2</v>
       </c>
       <c r="L1127">
-        <v>6.88</v>
+        <v>7.03</v>
       </c>
       <c r="M1127">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="N1127">
         <v>6.98</v>
@@ -58866,18 +58869,18 @@
         <v>1</v>
       </c>
       <c r="P1127" t="s">
-        <v>713</v>
+        <v>269</v>
       </c>
     </row>
     <row r="1128" spans="1:16">
       <c r="A1128" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1128" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1128">
-        <v>3.498805886545609</v>
+        <v>3.450415009789521</v>
       </c>
       <c r="D1128" t="s">
         <v>516</v>
@@ -58889,22 +58892,22 @@
         <v>1</v>
       </c>
       <c r="G1128">
-        <v>0.01028119411345439</v>
+        <v>0.01030958499021048</v>
       </c>
       <c r="H1128">
         <v>0.01030720931886091</v>
       </c>
       <c r="I1128">
-        <v>0.1539847945934794</v>
+        <v>0.202375671349567</v>
       </c>
       <c r="J1128">
         <v>0.6398479459347908</v>
       </c>
       <c r="K1128">
-        <v>5.3</v>
+        <v>5.36</v>
       </c>
       <c r="L1128">
-        <v>6.89</v>
+        <v>6.88</v>
       </c>
       <c r="M1128">
         <v>5.2</v>
@@ -58916,148 +58919,148 @@
         <v>1</v>
       </c>
       <c r="P1128" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="1129" spans="1:16">
       <c r="A1129" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1129" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C1129">
-        <v>3.705625653574086</v>
+        <v>3.498805886545609</v>
       </c>
       <c r="D1129" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E1129">
-        <v>3.628384598976479</v>
+        <v>3.652790681139088</v>
       </c>
       <c r="F1129">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1129">
-        <v>0.01065437434642592</v>
+        <v>0.01028119411345439</v>
       </c>
       <c r="H1129">
-        <v>0.01023161540102352</v>
+        <v>0.01030720931886091</v>
       </c>
       <c r="I1129">
-        <v>0.07724105459760677</v>
+        <v>0.1539847945934794</v>
       </c>
       <c r="J1129">
         <v>0.6398479459347908</v>
       </c>
       <c r="K1129">
-        <v>5.43</v>
+        <v>5.3</v>
       </c>
       <c r="L1129">
-        <v>7.18</v>
+        <v>6.89</v>
       </c>
       <c r="M1129">
-        <v>5.16</v>
+        <v>5.2</v>
       </c>
       <c r="N1129">
-        <v>6.93</v>
+        <v>6.98</v>
       </c>
       <c r="O1129">
         <v>1</v>
       </c>
       <c r="P1129" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="1130" spans="1:16">
       <c r="A1130" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1130" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C1130">
-        <v>3.702790681139088</v>
+        <v>3.705625653574086</v>
       </c>
       <c r="D1130" t="s">
         <v>517</v>
       </c>
       <c r="E1130">
-        <v>3.628384598976479</v>
+        <v>3.703978516813871</v>
       </c>
       <c r="F1130">
         <v>-1</v>
       </c>
       <c r="G1130">
-        <v>0.01035720931886091</v>
+        <v>0.01065437434642592</v>
       </c>
       <c r="H1130">
-        <v>0.01023161540102352</v>
+        <v>0.01025602148318613</v>
       </c>
       <c r="I1130">
-        <v>0.07440608216260891</v>
+        <v>0.00164713676021444</v>
       </c>
       <c r="J1130">
         <v>0.6398479459347908</v>
       </c>
       <c r="K1130">
-        <v>5.2</v>
+        <v>5.43</v>
       </c>
       <c r="L1130">
-        <v>7.03</v>
+        <v>7.18</v>
       </c>
       <c r="M1130">
-        <v>5.16</v>
+        <v>5.12</v>
       </c>
       <c r="N1130">
-        <v>6.93</v>
+        <v>6.98</v>
       </c>
       <c r="O1130">
         <v>1</v>
       </c>
       <c r="P1130" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="1131" spans="1:16">
       <c r="A1131" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1131" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C1131">
-        <v>3.449554544621713</v>
+        <v>3.702790681139088</v>
       </c>
       <c r="D1131" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E1131">
-        <v>3.60446860981753</v>
+        <v>3.703978516813871</v>
       </c>
       <c r="F1131">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1131">
-        <v>0.01033044545537829</v>
+        <v>0.01035720931886091</v>
       </c>
       <c r="H1131">
-        <v>0.01035553139018247</v>
+        <v>0.01025602148318613</v>
       </c>
       <c r="I1131">
-        <v>0.1549140651958174</v>
+        <v>-0.001187835674783422</v>
       </c>
       <c r="J1131">
-        <v>0.6491406519581673</v>
+        <v>0.6398479459347908</v>
       </c>
       <c r="K1131">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L1131">
-        <v>6.89</v>
+        <v>7.03</v>
       </c>
       <c r="M1131">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="N1131">
         <v>6.98</v>
@@ -59066,51 +59069,51 @@
         <v>1</v>
       </c>
       <c r="P1131" t="s">
-        <v>270</v>
+        <v>714</v>
       </c>
     </row>
     <row r="1132" spans="1:16">
       <c r="A1132" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1132" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C1132">
-        <v>3.655166259867152</v>
+        <v>3.679028764180458</v>
       </c>
       <c r="D1132" t="s">
         <v>517</v>
       </c>
       <c r="E1132">
-        <v>3.580434235895857</v>
+        <v>3.656399861974184</v>
       </c>
       <c r="F1132">
         <v>-1</v>
       </c>
       <c r="G1132">
-        <v>0.01070483374013285</v>
+        <v>0.01052097123581954</v>
       </c>
       <c r="H1132">
-        <v>0.01027956576410414</v>
+        <v>0.01030360013802582</v>
       </c>
       <c r="I1132">
-        <v>0.07473202397129519</v>
+        <v>0.02262890220627423</v>
       </c>
       <c r="J1132">
         <v>0.6491406519581673</v>
       </c>
       <c r="K1132">
-        <v>5.43</v>
+        <v>5.27</v>
       </c>
       <c r="L1132">
-        <v>7.18</v>
+        <v>7.1</v>
       </c>
       <c r="M1132">
-        <v>5.16</v>
+        <v>5.12</v>
       </c>
       <c r="N1132">
-        <v>6.93</v>
+        <v>6.98</v>
       </c>
       <c r="O1132">
         <v>1</v>
@@ -59121,40 +59124,40 @@
     </row>
     <row r="1133" spans="1:16">
       <c r="A1133" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1133" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C1133">
-        <v>3.65446860981753</v>
+        <v>3.652322613090761</v>
       </c>
       <c r="D1133" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E1133">
-        <v>3.580434235895857</v>
+        <v>3.554285518699872</v>
       </c>
       <c r="F1133">
         <v>-1</v>
       </c>
       <c r="G1133">
-        <v>0.01040553139018247</v>
+        <v>0.01054767738690924</v>
       </c>
       <c r="H1133">
-        <v>0.01027956576410414</v>
+        <v>0.01030571448130013</v>
       </c>
       <c r="I1133">
-        <v>0.07403437392167378</v>
+        <v>0.09803709439088903</v>
       </c>
       <c r="J1133">
-        <v>0.6491406519581673</v>
+        <v>0.6542082328101022</v>
       </c>
       <c r="K1133">
-        <v>5.2</v>
+        <v>5.27</v>
       </c>
       <c r="L1133">
-        <v>7.03</v>
+        <v>7.1</v>
       </c>
       <c r="M1133">
         <v>5.16</v>
@@ -59166,7 +59169,7 @@
         <v>1</v>
       </c>
       <c r="P1133" t="s">
-        <v>270</v>
+        <v>715</v>
       </c>
     </row>
     <row r="1134" spans="1:16">
@@ -59177,28 +59180,28 @@
         <v>272</v>
       </c>
       <c r="C1134">
-        <v>3.652322613090761</v>
+        <v>3.621276282748954</v>
       </c>
       <c r="D1134" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E1134">
-        <v>3.554285518699872</v>
+        <v>3.523887214228577</v>
       </c>
       <c r="F1134">
         <v>-1</v>
       </c>
       <c r="G1134">
-        <v>0.01054767738690924</v>
+        <v>0.01057872371725104</v>
       </c>
       <c r="H1134">
-        <v>0.01030571448130013</v>
+        <v>0.01033611278577142</v>
       </c>
       <c r="I1134">
-        <v>0.09803709439088903</v>
+        <v>0.0973890685203771</v>
       </c>
       <c r="J1134">
-        <v>0.6542082328101022</v>
+        <v>0.660099377087485</v>
       </c>
       <c r="K1134">
         <v>5.27</v>
@@ -59216,7 +59219,7 @@
         <v>1</v>
       </c>
       <c r="P1134" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1135" spans="1:16">
@@ -59227,28 +59230,28 @@
         <v>272</v>
       </c>
       <c r="C1135">
-        <v>3.621276282748954</v>
+        <v>3.634548533744118</v>
       </c>
       <c r="D1135" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E1135">
-        <v>3.523887214228577</v>
+        <v>3.565366250639179</v>
       </c>
       <c r="F1135">
         <v>-1</v>
       </c>
       <c r="G1135">
-        <v>0.01057872371725104</v>
+        <v>0.01056545146625588</v>
       </c>
       <c r="H1135">
-        <v>0.01033611278577142</v>
+        <v>0.01061463374936082</v>
       </c>
       <c r="I1135">
-        <v>0.0973890685203771</v>
+        <v>0.06918228310493957</v>
       </c>
       <c r="J1135">
-        <v>0.660099377087485</v>
+        <v>0.6575809233882128</v>
       </c>
       <c r="K1135">
         <v>5.27</v>
@@ -59257,16 +59260,16 @@
         <v>7.1</v>
       </c>
       <c r="M1135">
-        <v>5.16</v>
+        <v>5.36</v>
       </c>
       <c r="N1135">
-        <v>6.93</v>
+        <v>7.09</v>
       </c>
       <c r="O1135">
         <v>1</v>
       </c>
       <c r="P1135" t="s">
-        <v>715</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1136" spans="1:16">
@@ -59277,28 +59280,28 @@
         <v>272</v>
       </c>
       <c r="C1136">
-        <v>3.603049572151039</v>
+        <v>3.679346784171853</v>
       </c>
       <c r="D1136" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E1136">
-        <v>3.506040947305381</v>
+        <v>3.610929556577065</v>
       </c>
       <c r="F1136">
         <v>-1</v>
       </c>
       <c r="G1136">
-        <v>0.01059695042784896</v>
+        <v>0.01052065321582815</v>
       </c>
       <c r="H1136">
-        <v>0.01035395905269462</v>
+        <v>0.01056907044342293</v>
       </c>
       <c r="I1136">
-        <v>0.09700862484565764</v>
+        <v>0.06841722759478852</v>
       </c>
       <c r="J1136">
-        <v>0.6635579559485695</v>
+        <v>0.6490803066087565</v>
       </c>
       <c r="K1136">
         <v>5.27</v>
@@ -59307,115 +59310,15 @@
         <v>7.1</v>
       </c>
       <c r="M1136">
-        <v>5.16</v>
+        <v>5.36</v>
       </c>
       <c r="N1136">
-        <v>6.93</v>
+        <v>7.09</v>
       </c>
       <c r="O1136">
         <v>1</v>
       </c>
       <c r="P1136" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="1137" spans="1:16">
-      <c r="A1137" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>272</v>
-      </c>
-      <c r="C1137">
-        <v>3.634548533744118</v>
-      </c>
-      <c r="D1137" t="s">
-        <v>518</v>
-      </c>
-      <c r="E1137">
-        <v>3.565366250639179</v>
-      </c>
-      <c r="F1137">
-        <v>-1</v>
-      </c>
-      <c r="G1137">
-        <v>0.01056545146625588</v>
-      </c>
-      <c r="H1137">
-        <v>0.01061463374936082</v>
-      </c>
-      <c r="I1137">
-        <v>0.06918228310493957</v>
-      </c>
-      <c r="J1137">
-        <v>0.6575809233882128</v>
-      </c>
-      <c r="K1137">
-        <v>5.27</v>
-      </c>
-      <c r="L1137">
-        <v>7.1</v>
-      </c>
-      <c r="M1137">
-        <v>5.36</v>
-      </c>
-      <c r="N1137">
-        <v>7.09</v>
-      </c>
-      <c r="O1137">
-        <v>1</v>
-      </c>
-      <c r="P1137" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="1138" spans="1:16">
-      <c r="A1138" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>272</v>
-      </c>
-      <c r="C1138">
-        <v>3.679346784171853</v>
-      </c>
-      <c r="D1138" t="s">
-        <v>518</v>
-      </c>
-      <c r="E1138">
-        <v>3.610929556577065</v>
-      </c>
-      <c r="F1138">
-        <v>-1</v>
-      </c>
-      <c r="G1138">
-        <v>0.01052065321582815</v>
-      </c>
-      <c r="H1138">
-        <v>0.01056907044342293</v>
-      </c>
-      <c r="I1138">
-        <v>0.06841722759478852</v>
-      </c>
-      <c r="J1138">
-        <v>0.6490803066087565</v>
-      </c>
-      <c r="K1138">
-        <v>5.27</v>
-      </c>
-      <c r="L1138">
-        <v>7.1</v>
-      </c>
-      <c r="M1138">
-        <v>5.36</v>
-      </c>
-      <c r="N1138">
-        <v>7.09</v>
-      </c>
-      <c r="O1138">
-        <v>1</v>
-      </c>
-      <c r="P1138" t="s">
         <v>273</v>
       </c>
     </row>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3423" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3429" uniqueCount="721">
   <si>
     <t>trade_time</t>
   </si>
@@ -835,1342 +835,1348 @@
     <t>2021-12-02</t>
   </si>
   <si>
+    <t>2021-11-29</t>
+  </si>
+  <si>
+    <t>2021-12-07</t>
+  </si>
+  <si>
+    <t>2021-11-25</t>
+  </si>
+  <si>
+    <t>2016-09-28</t>
+  </si>
+  <si>
+    <t>2016-09-29</t>
+  </si>
+  <si>
+    <t>2016-10-12</t>
+  </si>
+  <si>
+    <t>2016-10-24</t>
+  </si>
+  <si>
+    <t>2016-10-25</t>
+  </si>
+  <si>
+    <t>2016-11-21</t>
+  </si>
+  <si>
+    <t>2016-12-02</t>
+  </si>
+  <si>
+    <t>2016-12-05</t>
+  </si>
+  <si>
+    <t>2016-12-14</t>
+  </si>
+  <si>
+    <t>2017-01-23</t>
+  </si>
+  <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
+    <t>2017-03-27</t>
+  </si>
+  <si>
+    <t>2017-04-18</t>
+  </si>
+  <si>
+    <t>2017-04-19</t>
+  </si>
+  <si>
+    <t>2017-04-21</t>
+  </si>
+  <si>
+    <t>2017-06-07</t>
+  </si>
+  <si>
+    <t>2017-06-15</t>
+  </si>
+  <si>
+    <t>2017-07-05</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-07-07</t>
+  </si>
+  <si>
+    <t>2017-06-28</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>2017-07-20</t>
+  </si>
+  <si>
+    <t>2017-07-24</t>
+  </si>
+  <si>
+    <t>2017-07-25</t>
+  </si>
+  <si>
+    <t>2017-07-26</t>
+  </si>
+  <si>
+    <t>2017-07-27</t>
+  </si>
+  <si>
+    <t>2017-08-08</t>
+  </si>
+  <si>
+    <t>2017-08-10</t>
+  </si>
+  <si>
+    <t>2017-08-11</t>
+  </si>
+  <si>
+    <t>2017-07-31</t>
+  </si>
+  <si>
+    <t>2017-08-02</t>
+  </si>
+  <si>
+    <t>2017-08-31</t>
+  </si>
+  <si>
+    <t>2017-09-07</t>
+  </si>
+  <si>
+    <t>2017-09-13</t>
+  </si>
+  <si>
+    <t>2017-09-20</t>
+  </si>
+  <si>
+    <t>2017-10-11</t>
+  </si>
+  <si>
+    <t>2017-10-17</t>
+  </si>
+  <si>
+    <t>2017-10-13</t>
+  </si>
+  <si>
+    <t>2017-10-23</t>
+  </si>
+  <si>
+    <t>2017-10-27</t>
+  </si>
+  <si>
+    <t>2017-10-30</t>
+  </si>
+  <si>
+    <t>2017-11-01</t>
+  </si>
+  <si>
+    <t>2017-11-03</t>
+  </si>
+  <si>
+    <t>2017-11-06</t>
+  </si>
+  <si>
+    <t>2017-11-07</t>
+  </si>
+  <si>
+    <t>2017-11-08</t>
+  </si>
+  <si>
+    <t>2017-11-09</t>
+  </si>
+  <si>
+    <t>2017-11-14</t>
+  </si>
+  <si>
+    <t>2017-11-15</t>
+  </si>
+  <si>
+    <t>2017-11-16</t>
+  </si>
+  <si>
+    <t>2017-11-22</t>
+  </si>
+  <si>
+    <t>2017-11-23</t>
+  </si>
+  <si>
+    <t>2018-01-19</t>
+  </si>
+  <si>
+    <t>2018-01-09</t>
+  </si>
+  <si>
+    <t>2018-01-16</t>
+  </si>
+  <si>
+    <t>2018-01-24</t>
+  </si>
+  <si>
+    <t>2018-02-01</t>
+  </si>
+  <si>
+    <t>2018-01-15</t>
+  </si>
+  <si>
+    <t>2018-02-05</t>
+  </si>
+  <si>
+    <t>2018-02-07</t>
+  </si>
+  <si>
+    <t>2018-02-09</t>
+  </si>
+  <si>
+    <t>2018-02-22</t>
+  </si>
+  <si>
+    <t>2018-02-26</t>
+  </si>
+  <si>
+    <t>2018-02-28</t>
+  </si>
+  <si>
+    <t>2018-03-01</t>
+  </si>
+  <si>
+    <t>2018-03-08</t>
+  </si>
+  <si>
+    <t>2018-03-05</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>2018-03-12</t>
+  </si>
+  <si>
+    <t>2018-03-13</t>
+  </si>
+  <si>
+    <t>2018-03-14</t>
+  </si>
+  <si>
+    <t>2018-04-03</t>
+  </si>
+  <si>
+    <t>2018-04-11</t>
+  </si>
+  <si>
+    <t>2018-04-12</t>
+  </si>
+  <si>
+    <t>2018-04-17</t>
+  </si>
+  <si>
+    <t>2018-04-18</t>
+  </si>
+  <si>
+    <t>2018-04-20</t>
+  </si>
+  <si>
+    <t>2018-04-24</t>
+  </si>
+  <si>
+    <t>2018-09-05</t>
+  </si>
+  <si>
+    <t>2018-09-19</t>
+  </si>
+  <si>
+    <t>2018-09-21</t>
+  </si>
+  <si>
+    <t>2018-10-22</t>
+  </si>
+  <si>
+    <t>2018-09-28</t>
+  </si>
+  <si>
+    <t>2018-10-23</t>
+  </si>
+  <si>
+    <t>2018-10-24</t>
+  </si>
+  <si>
+    <t>2018-12-04</t>
+  </si>
+  <si>
+    <t>2018-12-13</t>
+  </si>
+  <si>
+    <t>2018-12-05</t>
+  </si>
+  <si>
+    <t>2018-12-14</t>
+  </si>
+  <si>
+    <t>2018-12-19</t>
+  </si>
+  <si>
+    <t>2018-12-21</t>
+  </si>
+  <si>
+    <t>2018-12-18</t>
+  </si>
+  <si>
+    <t>2018-12-27</t>
+  </si>
+  <si>
+    <t>2019-01-28</t>
+  </si>
+  <si>
+    <t>2019-03-15</t>
+  </si>
+  <si>
+    <t>2019-03-29</t>
+  </si>
+  <si>
+    <t>2019-04-01</t>
+  </si>
+  <si>
+    <t>2019-04-03</t>
+  </si>
+  <si>
+    <t>2019-04-25</t>
+  </si>
+  <si>
+    <t>2019-04-29</t>
+  </si>
+  <si>
+    <t>2019-05-14</t>
+  </si>
+  <si>
+    <t>2019-05-21</t>
+  </si>
+  <si>
+    <t>2019-05-24</t>
+  </si>
+  <si>
+    <t>2019-05-27</t>
+  </si>
+  <si>
+    <t>2019-05-28</t>
+  </si>
+  <si>
+    <t>2019-05-29</t>
+  </si>
+  <si>
+    <t>2019-07-10</t>
+  </si>
+  <si>
+    <t>2019-07-24</t>
+  </si>
+  <si>
+    <t>2019-07-25</t>
+  </si>
+  <si>
+    <t>2019-07-12</t>
+  </si>
+  <si>
+    <t>2019-08-02</t>
+  </si>
+  <si>
+    <t>2019-08-05</t>
+  </si>
+  <si>
+    <t>2019-08-08</t>
+  </si>
+  <si>
+    <t>2019-08-09</t>
+  </si>
+  <si>
+    <t>2019-08-12</t>
+  </si>
+  <si>
+    <t>2019-08-16</t>
+  </si>
+  <si>
+    <t>2019-08-19</t>
+  </si>
+  <si>
+    <t>2019-09-03</t>
+  </si>
+  <si>
+    <t>2019-09-27</t>
+  </si>
+  <si>
+    <t>2019-09-30</t>
+  </si>
+  <si>
+    <t>2019-09-25</t>
+  </si>
+  <si>
+    <t>2019-10-17</t>
+  </si>
+  <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
+    <t>2019-11-04</t>
+  </si>
+  <si>
+    <t>2019-11-05</t>
+  </si>
+  <si>
+    <t>2019-11-07</t>
+  </si>
+  <si>
+    <t>2019-11-15</t>
+  </si>
+  <si>
+    <t>2019-11-26</t>
+  </si>
+  <si>
+    <t>2019-12-05</t>
+  </si>
+  <si>
+    <t>2019-12-11</t>
+  </si>
+  <si>
+    <t>2020-01-02</t>
+  </si>
+  <si>
+    <t>2020-01-03</t>
+  </si>
+  <si>
+    <t>2020-01-06</t>
+  </si>
+  <si>
+    <t>2020-01-07</t>
+  </si>
+  <si>
+    <t>2019-12-18</t>
+  </si>
+  <si>
+    <t>2019-12-27</t>
+  </si>
+  <si>
+    <t>2020-01-16</t>
+  </si>
+  <si>
+    <t>2020-01-17</t>
+  </si>
+  <si>
+    <t>2020-02-04</t>
+  </si>
+  <si>
+    <t>2020-02-05</t>
+  </si>
+  <si>
+    <t>2020-01-23</t>
+  </si>
+  <si>
+    <t>2020-02-06</t>
+  </si>
+  <si>
+    <t>2020-02-10</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-03-19</t>
+  </si>
+  <si>
+    <t>2020-03-26</t>
+  </si>
+  <si>
+    <t>2020-03-25</t>
+  </si>
+  <si>
+    <t>2020-04-02</t>
+  </si>
+  <si>
+    <t>2020-04-16</t>
+  </si>
+  <si>
+    <t>2020-04-17</t>
+  </si>
+  <si>
+    <t>2020-04-21</t>
+  </si>
+  <si>
+    <t>2020-05-06</t>
+  </si>
+  <si>
+    <t>2020-04-14</t>
+  </si>
+  <si>
+    <t>2020-05-11</t>
+  </si>
+  <si>
+    <t>2020-05-12</t>
+  </si>
+  <si>
+    <t>2020-05-13</t>
+  </si>
+  <si>
+    <t>2020-05-14</t>
+  </si>
+  <si>
+    <t>2020-06-12</t>
+  </si>
+  <si>
+    <t>2020-06-15</t>
+  </si>
+  <si>
+    <t>2020-06-08</t>
+  </si>
+  <si>
+    <t>2020-07-03</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-24</t>
+  </si>
+  <si>
+    <t>2020-07-30</t>
+  </si>
+  <si>
+    <t>2020-08-10</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>2020-08-18</t>
+  </si>
+  <si>
+    <t>2020-08-19</t>
+  </si>
+  <si>
+    <t>2020-08-26</t>
+  </si>
+  <si>
+    <t>2020-09-01</t>
+  </si>
+  <si>
+    <t>2020-09-02</t>
+  </si>
+  <si>
+    <t>2020-09-03</t>
+  </si>
+  <si>
+    <t>2020-09-04</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>2020-09-08</t>
+  </si>
+  <si>
+    <t>2020-09-09</t>
+  </si>
+  <si>
+    <t>2020-09-14</t>
+  </si>
+  <si>
+    <t>2020-09-15</t>
+  </si>
+  <si>
+    <t>2020-09-17</t>
+  </si>
+  <si>
+    <t>2020-09-21</t>
+  </si>
+  <si>
+    <t>2020-09-22</t>
+  </si>
+  <si>
+    <t>2020-11-24</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>2021-01-22</t>
+  </si>
+  <si>
+    <t>2021-02-25</t>
+  </si>
+  <si>
+    <t>2021-03-01</t>
+  </si>
+  <si>
+    <t>2021-03-02</t>
+  </si>
+  <si>
+    <t>2021-03-17</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>2021-04-14</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>2021-04-15</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>2021-04-26</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>2021-05-21</t>
+  </si>
+  <si>
+    <t>2021-05-24</t>
+  </si>
+  <si>
+    <t>2021-05-25</t>
+  </si>
+  <si>
+    <t>2021-05-26</t>
+  </si>
+  <si>
+    <t>2021-05-31</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>2021-06-15</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>2021-06-17</t>
+  </si>
+  <si>
+    <t>2021-06-22</t>
+  </si>
+  <si>
+    <t>2021-06-25</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>2021-07-08</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>2021-07-15</t>
+  </si>
+  <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
+    <t>2021-08-16</t>
+  </si>
+  <si>
+    <t>2021-08-24</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>2021-08-25</t>
+  </si>
+  <si>
+    <t>2021-08-26</t>
+  </si>
+  <si>
+    <t>2021-08-27</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-08-18</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>2021-09-24</t>
+  </si>
+  <si>
+    <t>2021-09-09</t>
+  </si>
+  <si>
+    <t>2021-10-11</t>
+  </si>
+  <si>
+    <t>2021-10-15</t>
+  </si>
+  <si>
+    <t>2021-10-29</t>
+  </si>
+  <si>
+    <t>2021-11-23</t>
+  </si>
+  <si>
+    <t>2021-12-03</t>
+  </si>
+  <si>
+    <t>2021-11-24</t>
+  </si>
+  <si>
+    <t>2021-12-08</t>
+  </si>
+  <si>
+    <t>2016-08-29</t>
+  </si>
+  <si>
+    <t>2016-08-30</t>
+  </si>
+  <si>
+    <t>2016-08-31</t>
+  </si>
+  <si>
+    <t>2016-09-14</t>
+  </si>
+  <si>
+    <t>2016-09-19</t>
+  </si>
+  <si>
+    <t>2016-11-07</t>
+  </si>
+  <si>
+    <t>2016-11-08</t>
+  </si>
+  <si>
+    <t>2017-01-06</t>
+  </si>
+  <si>
+    <t>2017-01-09</t>
+  </si>
+  <si>
+    <t>2017-03-16</t>
+  </si>
+  <si>
+    <t>2017-03-20</t>
+  </si>
+  <si>
+    <t>2017-05-24</t>
+  </si>
+  <si>
+    <t>2017-05-26</t>
+  </si>
+  <si>
+    <t>2017-06-05</t>
+  </si>
+  <si>
+    <t>2017-06-08</t>
+  </si>
+  <si>
+    <t>2017-06-09</t>
+  </si>
+  <si>
+    <t>2017-06-12</t>
+  </si>
+  <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
+    <t>2017-06-22</t>
+  </si>
+  <si>
+    <t>2017-06-27</t>
+  </si>
+  <si>
+    <t>2017-08-16</t>
+  </si>
+  <si>
+    <t>2017-09-14</t>
+  </si>
+  <si>
+    <t>2017-09-19</t>
+  </si>
+  <si>
+    <t>2017-09-21</t>
+  </si>
+  <si>
+    <t>2017-09-25</t>
+  </si>
+  <si>
+    <t>2017-09-27</t>
+  </si>
+  <si>
+    <t>2017-09-29</t>
+  </si>
+  <si>
+    <t>2017-10-24</t>
+  </si>
+  <si>
+    <t>2017-10-25</t>
+  </si>
+  <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
+    <t>2018-01-04</t>
+  </si>
+  <si>
+    <t>2018-01-05</t>
+  </si>
+  <si>
+    <t>2018-01-10</t>
+  </si>
+  <si>
+    <t>2018-01-17</t>
+  </si>
+  <si>
+    <t>2018-01-23</t>
+  </si>
+  <si>
+    <t>2018-01-26</t>
+  </si>
+  <si>
+    <t>2018-01-29</t>
+  </si>
+  <si>
+    <t>2018-02-12</t>
+  </si>
+  <si>
+    <t>2018-02-13</t>
+  </si>
+  <si>
+    <t>2018-03-16</t>
+  </si>
+  <si>
+    <t>2018-03-20</t>
+  </si>
+  <si>
+    <t>2018-03-21</t>
+  </si>
+  <si>
+    <t>2018-08-23</t>
+  </si>
+  <si>
+    <t>2018-08-24</t>
+  </si>
+  <si>
+    <t>2018-08-28</t>
+  </si>
+  <si>
+    <t>2018-09-13</t>
+  </si>
+  <si>
+    <t>2018-11-16</t>
+  </si>
+  <si>
+    <t>2018-11-19</t>
+  </si>
+  <si>
+    <t>2018-11-22</t>
+  </si>
+  <si>
+    <t>2018-11-26</t>
+  </si>
+  <si>
+    <t>2018-12-03</t>
+  </si>
+  <si>
+    <t>2018-12-28</t>
+  </si>
+  <si>
+    <t>2019-03-01</t>
+  </si>
+  <si>
+    <t>2019-03-11</t>
+  </si>
+  <si>
+    <t>2019-03-12</t>
+  </si>
+  <si>
+    <t>2019-03-13</t>
+  </si>
+  <si>
+    <t>2019-03-21</t>
+  </si>
+  <si>
+    <t>2019-03-22</t>
+  </si>
+  <si>
+    <t>2019-03-25</t>
+  </si>
+  <si>
+    <t>2019-04-11</t>
+  </si>
+  <si>
+    <t>2019-04-12</t>
+  </si>
+  <si>
+    <t>2019-04-15</t>
+  </si>
+  <si>
+    <t>2019-04-16</t>
+  </si>
+  <si>
+    <t>2019-04-17</t>
+  </si>
+  <si>
+    <t>2019-04-18</t>
+  </si>
+  <si>
+    <t>2019-04-23</t>
+  </si>
+  <si>
+    <t>2019-06-26</t>
+  </si>
+  <si>
+    <t>2019-06-28</t>
+  </si>
+  <si>
+    <t>2019-07-02</t>
+  </si>
+  <si>
+    <t>2019-07-03</t>
+  </si>
+  <si>
+    <t>2019-07-04</t>
+  </si>
+  <si>
+    <t>2019-07-08</t>
+  </si>
+  <si>
+    <t>2019-07-15</t>
+  </si>
+  <si>
+    <t>2019-07-17</t>
+  </si>
+  <si>
+    <t>2019-07-19</t>
+  </si>
+  <si>
+    <t>2019-07-22</t>
+  </si>
+  <si>
+    <t>2019-08-29</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-09-04</t>
+  </si>
+  <si>
+    <t>2019-09-05</t>
+  </si>
+  <si>
+    <t>2019-09-06</t>
+  </si>
+  <si>
+    <t>2019-09-09</t>
+  </si>
+  <si>
+    <t>2019-09-16</t>
+  </si>
+  <si>
+    <t>2019-10-08</t>
+  </si>
+  <si>
+    <t>2019-10-10</t>
+  </si>
+  <si>
+    <t>2019-10-11</t>
+  </si>
+  <si>
+    <t>2019-10-14</t>
+  </si>
+  <si>
+    <t>2019-10-15</t>
+  </si>
+  <si>
+    <t>2019-10-18</t>
+  </si>
+  <si>
+    <t>2019-10-21</t>
+  </si>
+  <si>
+    <t>2019-10-22</t>
+  </si>
+  <si>
+    <t>2019-10-23</t>
+  </si>
+  <si>
+    <t>2019-10-28</t>
+  </si>
+  <si>
+    <t>2019-11-13</t>
+  </si>
+  <si>
+    <t>2019-11-25</t>
+  </si>
+  <si>
+    <t>2019-11-27</t>
+  </si>
+  <si>
+    <t>2019-11-28</t>
+  </si>
+  <si>
+    <t>2019-11-29</t>
+  </si>
+  <si>
+    <t>2019-12-02</t>
+  </si>
+  <si>
+    <t>2019-12-04</t>
+  </si>
+  <si>
+    <t>2019-12-10</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2019-12-13</t>
+  </si>
+  <si>
+    <t>2019-12-17</t>
+  </si>
+  <si>
+    <t>2019-12-19</t>
+  </si>
+  <si>
+    <t>2019-12-24</t>
+  </si>
+  <si>
+    <t>2020-01-09</t>
+  </si>
+  <si>
+    <t>2020-01-13</t>
+  </si>
+  <si>
+    <t>2020-01-21</t>
+  </si>
+  <si>
+    <t>2020-02-28</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-03-04</t>
+  </si>
+  <si>
+    <t>2020-03-05</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-09</t>
+  </si>
+  <si>
+    <t>2020-03-10</t>
+  </si>
+  <si>
+    <t>2020-03-11</t>
+  </si>
+  <si>
+    <t>2020-03-12</t>
+  </si>
+  <si>
+    <t>2020-03-16</t>
+  </si>
+  <si>
+    <t>2020-03-17</t>
+  </si>
+  <si>
+    <t>2020-03-18</t>
+  </si>
+  <si>
+    <t>2020-03-20</t>
+  </si>
+  <si>
+    <t>2020-03-30</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-04-03</t>
+  </si>
+  <si>
+    <t>2020-04-07</t>
+  </si>
+  <si>
+    <t>2020-04-08</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>2020-04-22</t>
+  </si>
+  <si>
+    <t>2020-04-24</t>
+  </si>
+  <si>
+    <t>2020-04-28</t>
+  </si>
+  <si>
+    <t>2020-05-15</t>
+  </si>
+  <si>
+    <t>2020-05-18</t>
+  </si>
+  <si>
+    <t>2020-05-19</t>
+  </si>
+  <si>
+    <t>2020-05-20</t>
+  </si>
+  <si>
+    <t>2020-05-21</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>2020-05-27</t>
+  </si>
+  <si>
+    <t>2020-06-01</t>
+  </si>
+  <si>
+    <t>2020-06-04</t>
+  </si>
+  <si>
+    <t>2020-06-09</t>
+  </si>
+  <si>
+    <t>2020-06-10</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>2020-06-19</t>
+  </si>
+  <si>
+    <t>2020-07-13</t>
+  </si>
+  <si>
+    <t>2020-07-16</t>
+  </si>
+  <si>
+    <t>2020-07-17</t>
+  </si>
+  <si>
+    <t>2020-07-28</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>2020-08-04</t>
+  </si>
+  <si>
+    <t>2020-08-05</t>
+  </si>
+  <si>
+    <t>2020-08-07</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>2020-08-12</t>
+  </si>
+  <si>
+    <t>2020-08-21</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>2020-11-10</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2021-01-21</t>
+  </si>
+  <si>
+    <t>2021-01-25</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>2021-03-05</t>
+  </si>
+  <si>
+    <t>2021-03-15</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>2021-04-20</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2021-04-22</t>
+  </si>
+  <si>
+    <t>2021-04-29</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>2021-05-17</t>
+  </si>
+  <si>
+    <t>2021-05-20</t>
+  </si>
+  <si>
+    <t>2021-05-28</t>
+  </si>
+  <si>
+    <t>2021-06-07</t>
+  </si>
+  <si>
+    <t>2021-07-28</t>
+  </si>
+  <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>2021-08-06</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>2021-09-13</t>
+  </si>
+  <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
+    <t>2021-09-16</t>
+  </si>
+  <si>
+    <t>2021-09-28</t>
+  </si>
+  <si>
+    <t>2021-09-29</t>
+  </si>
+  <si>
+    <t>2021-11-05</t>
+  </si>
+  <si>
+    <t>2021-11-08</t>
+  </si>
+  <si>
+    <t>2021-11-10</t>
+  </si>
+  <si>
+    <t>2021-11-11</t>
+  </si>
+  <si>
+    <t>2021-11-15</t>
+  </si>
+  <si>
+    <t>2021-11-17</t>
+  </si>
+  <si>
+    <t>2021-11-18</t>
+  </si>
+  <si>
     <t>2021-11-19</t>
   </si>
   <si>
-    <t>2021-11-29</t>
-  </si>
-  <si>
-    <t>2021-11-25</t>
-  </si>
-  <si>
-    <t>2016-09-28</t>
-  </si>
-  <si>
-    <t>2016-09-29</t>
-  </si>
-  <si>
-    <t>2016-10-12</t>
-  </si>
-  <si>
-    <t>2016-10-24</t>
-  </si>
-  <si>
-    <t>2016-10-25</t>
-  </si>
-  <si>
-    <t>2016-11-21</t>
-  </si>
-  <si>
-    <t>2016-12-02</t>
-  </si>
-  <si>
-    <t>2016-12-05</t>
-  </si>
-  <si>
-    <t>2016-12-14</t>
-  </si>
-  <si>
-    <t>2017-01-23</t>
-  </si>
-  <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
-    <t>2017-03-27</t>
-  </si>
-  <si>
-    <t>2017-04-18</t>
-  </si>
-  <si>
-    <t>2017-04-19</t>
-  </si>
-  <si>
-    <t>2017-04-21</t>
-  </si>
-  <si>
-    <t>2017-06-07</t>
-  </si>
-  <si>
-    <t>2017-06-15</t>
-  </si>
-  <si>
-    <t>2017-07-05</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-07-07</t>
-  </si>
-  <si>
-    <t>2017-06-28</t>
-  </si>
-  <si>
-    <t>2017-07-12</t>
-  </si>
-  <si>
-    <t>2017-07-20</t>
-  </si>
-  <si>
-    <t>2017-07-24</t>
-  </si>
-  <si>
-    <t>2017-07-25</t>
-  </si>
-  <si>
-    <t>2017-07-26</t>
-  </si>
-  <si>
-    <t>2017-07-27</t>
-  </si>
-  <si>
-    <t>2017-08-08</t>
-  </si>
-  <si>
-    <t>2017-08-10</t>
-  </si>
-  <si>
-    <t>2017-08-11</t>
-  </si>
-  <si>
-    <t>2017-07-31</t>
-  </si>
-  <si>
-    <t>2017-08-02</t>
-  </si>
-  <si>
-    <t>2017-08-31</t>
-  </si>
-  <si>
-    <t>2017-09-07</t>
-  </si>
-  <si>
-    <t>2017-09-13</t>
-  </si>
-  <si>
-    <t>2017-09-20</t>
-  </si>
-  <si>
-    <t>2017-10-11</t>
-  </si>
-  <si>
-    <t>2017-10-17</t>
-  </si>
-  <si>
-    <t>2017-10-13</t>
-  </si>
-  <si>
-    <t>2017-10-23</t>
-  </si>
-  <si>
-    <t>2017-10-27</t>
-  </si>
-  <si>
-    <t>2017-10-30</t>
-  </si>
-  <si>
-    <t>2017-11-01</t>
-  </si>
-  <si>
-    <t>2017-11-03</t>
-  </si>
-  <si>
-    <t>2017-11-06</t>
-  </si>
-  <si>
-    <t>2017-11-07</t>
-  </si>
-  <si>
-    <t>2017-11-08</t>
-  </si>
-  <si>
-    <t>2017-11-09</t>
-  </si>
-  <si>
-    <t>2017-11-14</t>
-  </si>
-  <si>
-    <t>2017-11-15</t>
-  </si>
-  <si>
-    <t>2017-11-16</t>
-  </si>
-  <si>
-    <t>2017-11-22</t>
-  </si>
-  <si>
-    <t>2017-11-23</t>
-  </si>
-  <si>
-    <t>2018-01-19</t>
-  </si>
-  <si>
-    <t>2018-01-09</t>
-  </si>
-  <si>
-    <t>2018-01-16</t>
-  </si>
-  <si>
-    <t>2018-01-24</t>
-  </si>
-  <si>
-    <t>2018-02-01</t>
-  </si>
-  <si>
-    <t>2018-01-15</t>
-  </si>
-  <si>
-    <t>2018-02-05</t>
-  </si>
-  <si>
-    <t>2018-02-07</t>
-  </si>
-  <si>
-    <t>2018-02-09</t>
-  </si>
-  <si>
-    <t>2018-02-22</t>
-  </si>
-  <si>
-    <t>2018-02-26</t>
-  </si>
-  <si>
-    <t>2018-02-28</t>
-  </si>
-  <si>
-    <t>2018-03-01</t>
-  </si>
-  <si>
-    <t>2018-03-08</t>
-  </si>
-  <si>
-    <t>2018-03-05</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>2018-03-12</t>
-  </si>
-  <si>
-    <t>2018-03-13</t>
-  </si>
-  <si>
-    <t>2018-03-14</t>
-  </si>
-  <si>
-    <t>2018-04-03</t>
-  </si>
-  <si>
-    <t>2018-04-11</t>
-  </si>
-  <si>
-    <t>2018-04-12</t>
-  </si>
-  <si>
-    <t>2018-04-17</t>
-  </si>
-  <si>
-    <t>2018-04-18</t>
-  </si>
-  <si>
-    <t>2018-04-20</t>
-  </si>
-  <si>
-    <t>2018-04-24</t>
-  </si>
-  <si>
-    <t>2018-09-05</t>
-  </si>
-  <si>
-    <t>2018-09-19</t>
-  </si>
-  <si>
-    <t>2018-09-21</t>
-  </si>
-  <si>
-    <t>2018-10-22</t>
-  </si>
-  <si>
-    <t>2018-09-28</t>
-  </si>
-  <si>
-    <t>2018-10-23</t>
-  </si>
-  <si>
-    <t>2018-10-24</t>
-  </si>
-  <si>
-    <t>2018-12-04</t>
-  </si>
-  <si>
-    <t>2018-12-13</t>
-  </si>
-  <si>
-    <t>2018-12-05</t>
-  </si>
-  <si>
-    <t>2018-12-14</t>
-  </si>
-  <si>
-    <t>2018-12-19</t>
-  </si>
-  <si>
-    <t>2018-12-21</t>
-  </si>
-  <si>
-    <t>2018-12-18</t>
-  </si>
-  <si>
-    <t>2018-12-27</t>
-  </si>
-  <si>
-    <t>2019-01-28</t>
-  </si>
-  <si>
-    <t>2019-03-15</t>
-  </si>
-  <si>
-    <t>2019-03-29</t>
-  </si>
-  <si>
-    <t>2019-04-01</t>
-  </si>
-  <si>
-    <t>2019-04-03</t>
-  </si>
-  <si>
-    <t>2019-04-25</t>
-  </si>
-  <si>
-    <t>2019-04-29</t>
-  </si>
-  <si>
-    <t>2019-05-14</t>
-  </si>
-  <si>
-    <t>2019-05-21</t>
-  </si>
-  <si>
-    <t>2019-05-24</t>
-  </si>
-  <si>
-    <t>2019-05-27</t>
-  </si>
-  <si>
-    <t>2019-05-28</t>
-  </si>
-  <si>
-    <t>2019-05-29</t>
-  </si>
-  <si>
-    <t>2019-07-10</t>
-  </si>
-  <si>
-    <t>2019-07-24</t>
-  </si>
-  <si>
-    <t>2019-07-25</t>
-  </si>
-  <si>
-    <t>2019-07-12</t>
-  </si>
-  <si>
-    <t>2019-08-02</t>
-  </si>
-  <si>
-    <t>2019-08-05</t>
-  </si>
-  <si>
-    <t>2019-08-08</t>
-  </si>
-  <si>
-    <t>2019-08-09</t>
-  </si>
-  <si>
-    <t>2019-08-12</t>
-  </si>
-  <si>
-    <t>2019-08-16</t>
-  </si>
-  <si>
-    <t>2019-08-19</t>
-  </si>
-  <si>
-    <t>2019-09-03</t>
-  </si>
-  <si>
-    <t>2019-09-27</t>
-  </si>
-  <si>
-    <t>2019-09-30</t>
-  </si>
-  <si>
-    <t>2019-09-25</t>
-  </si>
-  <si>
-    <t>2019-10-17</t>
-  </si>
-  <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
-    <t>2019-11-04</t>
-  </si>
-  <si>
-    <t>2019-11-05</t>
-  </si>
-  <si>
-    <t>2019-11-07</t>
-  </si>
-  <si>
-    <t>2019-11-15</t>
-  </si>
-  <si>
-    <t>2019-11-26</t>
-  </si>
-  <si>
-    <t>2019-12-05</t>
-  </si>
-  <si>
-    <t>2019-12-11</t>
-  </si>
-  <si>
-    <t>2020-01-02</t>
-  </si>
-  <si>
-    <t>2020-01-03</t>
-  </si>
-  <si>
-    <t>2020-01-06</t>
-  </si>
-  <si>
-    <t>2020-01-07</t>
-  </si>
-  <si>
-    <t>2019-12-18</t>
-  </si>
-  <si>
-    <t>2019-12-27</t>
-  </si>
-  <si>
-    <t>2020-01-16</t>
-  </si>
-  <si>
-    <t>2020-01-17</t>
-  </si>
-  <si>
-    <t>2020-02-04</t>
-  </si>
-  <si>
-    <t>2020-02-05</t>
-  </si>
-  <si>
-    <t>2020-01-23</t>
-  </si>
-  <si>
-    <t>2020-02-06</t>
-  </si>
-  <si>
-    <t>2020-02-10</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-03-19</t>
-  </si>
-  <si>
-    <t>2020-03-26</t>
-  </si>
-  <si>
-    <t>2020-03-25</t>
-  </si>
-  <si>
-    <t>2020-04-02</t>
-  </si>
-  <si>
-    <t>2020-04-16</t>
-  </si>
-  <si>
-    <t>2020-04-17</t>
-  </si>
-  <si>
-    <t>2020-04-21</t>
-  </si>
-  <si>
-    <t>2020-05-06</t>
-  </si>
-  <si>
-    <t>2020-04-14</t>
-  </si>
-  <si>
-    <t>2020-05-11</t>
-  </si>
-  <si>
-    <t>2020-05-12</t>
-  </si>
-  <si>
-    <t>2020-05-13</t>
-  </si>
-  <si>
-    <t>2020-05-14</t>
-  </si>
-  <si>
-    <t>2020-06-12</t>
-  </si>
-  <si>
-    <t>2020-06-15</t>
-  </si>
-  <si>
-    <t>2020-06-08</t>
-  </si>
-  <si>
-    <t>2020-07-03</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-24</t>
-  </si>
-  <si>
-    <t>2020-07-30</t>
-  </si>
-  <si>
-    <t>2020-08-10</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>2020-08-18</t>
-  </si>
-  <si>
-    <t>2020-08-19</t>
-  </si>
-  <si>
-    <t>2020-08-26</t>
-  </si>
-  <si>
-    <t>2020-09-01</t>
-  </si>
-  <si>
-    <t>2020-09-02</t>
-  </si>
-  <si>
-    <t>2020-09-03</t>
-  </si>
-  <si>
-    <t>2020-09-04</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>2020-09-08</t>
-  </si>
-  <si>
-    <t>2020-09-09</t>
-  </si>
-  <si>
-    <t>2020-09-14</t>
-  </si>
-  <si>
-    <t>2020-09-15</t>
-  </si>
-  <si>
-    <t>2020-09-17</t>
-  </si>
-  <si>
-    <t>2020-09-21</t>
-  </si>
-  <si>
-    <t>2020-09-22</t>
-  </si>
-  <si>
-    <t>2020-11-24</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-14</t>
-  </si>
-  <si>
-    <t>2021-01-22</t>
-  </si>
-  <si>
-    <t>2021-02-25</t>
-  </si>
-  <si>
-    <t>2021-03-01</t>
-  </si>
-  <si>
-    <t>2021-03-02</t>
-  </si>
-  <si>
-    <t>2021-03-17</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>2021-04-14</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>2021-04-15</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>2021-04-26</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>2021-05-21</t>
-  </si>
-  <si>
-    <t>2021-05-24</t>
-  </si>
-  <si>
-    <t>2021-05-25</t>
-  </si>
-  <si>
-    <t>2021-05-26</t>
-  </si>
-  <si>
-    <t>2021-05-31</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>2021-06-15</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>2021-06-17</t>
-  </si>
-  <si>
-    <t>2021-06-22</t>
-  </si>
-  <si>
-    <t>2021-06-25</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>2021-07-08</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>2021-07-15</t>
-  </si>
-  <si>
-    <t>2021-07-29</t>
-  </si>
-  <si>
-    <t>2021-07-23</t>
-  </si>
-  <si>
-    <t>2021-08-16</t>
-  </si>
-  <si>
-    <t>2021-08-24</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>2021-08-25</t>
-  </si>
-  <si>
-    <t>2021-08-26</t>
-  </si>
-  <si>
-    <t>2021-08-27</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
-    <t>2021-08-18</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>2021-09-24</t>
-  </si>
-  <si>
-    <t>2021-09-09</t>
-  </si>
-  <si>
-    <t>2021-10-11</t>
-  </si>
-  <si>
-    <t>2021-10-15</t>
-  </si>
-  <si>
-    <t>2021-10-29</t>
-  </si>
-  <si>
-    <t>2021-11-23</t>
-  </si>
-  <si>
-    <t>2021-12-03</t>
-  </si>
-  <si>
-    <t>2021-11-24</t>
-  </si>
-  <si>
-    <t>2021-12-07</t>
-  </si>
-  <si>
-    <t>2016-08-29</t>
-  </si>
-  <si>
-    <t>2016-08-30</t>
-  </si>
-  <si>
-    <t>2016-08-31</t>
-  </si>
-  <si>
-    <t>2016-09-14</t>
-  </si>
-  <si>
-    <t>2016-09-19</t>
-  </si>
-  <si>
-    <t>2016-11-07</t>
-  </si>
-  <si>
-    <t>2016-11-08</t>
-  </si>
-  <si>
-    <t>2017-01-06</t>
-  </si>
-  <si>
-    <t>2017-01-09</t>
-  </si>
-  <si>
-    <t>2017-03-16</t>
-  </si>
-  <si>
-    <t>2017-03-20</t>
-  </si>
-  <si>
-    <t>2017-05-24</t>
-  </si>
-  <si>
-    <t>2017-05-26</t>
-  </si>
-  <si>
-    <t>2017-06-05</t>
-  </si>
-  <si>
-    <t>2017-06-08</t>
-  </si>
-  <si>
-    <t>2017-06-09</t>
-  </si>
-  <si>
-    <t>2017-06-12</t>
-  </si>
-  <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
-    <t>2017-06-22</t>
-  </si>
-  <si>
-    <t>2017-06-27</t>
-  </si>
-  <si>
-    <t>2017-08-16</t>
-  </si>
-  <si>
-    <t>2017-09-14</t>
-  </si>
-  <si>
-    <t>2017-09-19</t>
-  </si>
-  <si>
-    <t>2017-09-21</t>
-  </si>
-  <si>
-    <t>2017-09-25</t>
-  </si>
-  <si>
-    <t>2017-09-27</t>
-  </si>
-  <si>
-    <t>2017-09-29</t>
-  </si>
-  <si>
-    <t>2017-10-24</t>
-  </si>
-  <si>
-    <t>2017-10-25</t>
-  </si>
-  <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
-    <t>2018-01-04</t>
-  </si>
-  <si>
-    <t>2018-01-05</t>
-  </si>
-  <si>
-    <t>2018-01-10</t>
-  </si>
-  <si>
-    <t>2018-01-17</t>
-  </si>
-  <si>
-    <t>2018-01-23</t>
-  </si>
-  <si>
-    <t>2018-01-26</t>
-  </si>
-  <si>
-    <t>2018-01-29</t>
-  </si>
-  <si>
-    <t>2018-02-12</t>
-  </si>
-  <si>
-    <t>2018-02-13</t>
-  </si>
-  <si>
-    <t>2018-03-16</t>
-  </si>
-  <si>
-    <t>2018-03-20</t>
-  </si>
-  <si>
-    <t>2018-03-21</t>
-  </si>
-  <si>
-    <t>2018-08-23</t>
-  </si>
-  <si>
-    <t>2018-08-24</t>
-  </si>
-  <si>
-    <t>2018-08-28</t>
-  </si>
-  <si>
-    <t>2018-09-13</t>
-  </si>
-  <si>
-    <t>2018-11-16</t>
-  </si>
-  <si>
-    <t>2018-11-19</t>
-  </si>
-  <si>
-    <t>2018-11-22</t>
-  </si>
-  <si>
-    <t>2018-11-26</t>
-  </si>
-  <si>
-    <t>2018-12-03</t>
-  </si>
-  <si>
-    <t>2018-12-28</t>
-  </si>
-  <si>
-    <t>2019-03-01</t>
-  </si>
-  <si>
-    <t>2019-03-11</t>
-  </si>
-  <si>
-    <t>2019-03-12</t>
-  </si>
-  <si>
-    <t>2019-03-13</t>
-  </si>
-  <si>
-    <t>2019-03-21</t>
-  </si>
-  <si>
-    <t>2019-03-22</t>
-  </si>
-  <si>
-    <t>2019-03-25</t>
-  </si>
-  <si>
-    <t>2019-04-11</t>
-  </si>
-  <si>
-    <t>2019-04-12</t>
-  </si>
-  <si>
-    <t>2019-04-15</t>
-  </si>
-  <si>
-    <t>2019-04-16</t>
-  </si>
-  <si>
-    <t>2019-04-17</t>
-  </si>
-  <si>
-    <t>2019-04-18</t>
-  </si>
-  <si>
-    <t>2019-04-23</t>
-  </si>
-  <si>
-    <t>2019-06-26</t>
-  </si>
-  <si>
-    <t>2019-06-28</t>
-  </si>
-  <si>
-    <t>2019-07-02</t>
-  </si>
-  <si>
-    <t>2019-07-03</t>
-  </si>
-  <si>
-    <t>2019-07-04</t>
-  </si>
-  <si>
-    <t>2019-07-08</t>
-  </si>
-  <si>
-    <t>2019-07-15</t>
-  </si>
-  <si>
-    <t>2019-07-17</t>
-  </si>
-  <si>
-    <t>2019-07-19</t>
-  </si>
-  <si>
-    <t>2019-07-22</t>
-  </si>
-  <si>
-    <t>2019-08-29</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-09-04</t>
-  </si>
-  <si>
-    <t>2019-09-05</t>
-  </si>
-  <si>
-    <t>2019-09-06</t>
-  </si>
-  <si>
-    <t>2019-09-09</t>
-  </si>
-  <si>
-    <t>2019-09-16</t>
-  </si>
-  <si>
-    <t>2019-10-08</t>
-  </si>
-  <si>
-    <t>2019-10-10</t>
-  </si>
-  <si>
-    <t>2019-10-11</t>
-  </si>
-  <si>
-    <t>2019-10-14</t>
-  </si>
-  <si>
-    <t>2019-10-15</t>
-  </si>
-  <si>
-    <t>2019-10-18</t>
-  </si>
-  <si>
-    <t>2019-10-21</t>
-  </si>
-  <si>
-    <t>2019-10-22</t>
-  </si>
-  <si>
-    <t>2019-10-23</t>
-  </si>
-  <si>
-    <t>2019-10-28</t>
-  </si>
-  <si>
-    <t>2019-11-13</t>
-  </si>
-  <si>
-    <t>2019-11-25</t>
-  </si>
-  <si>
-    <t>2019-11-27</t>
-  </si>
-  <si>
-    <t>2019-11-28</t>
-  </si>
-  <si>
-    <t>2019-11-29</t>
-  </si>
-  <si>
-    <t>2019-12-02</t>
-  </si>
-  <si>
-    <t>2019-12-04</t>
-  </si>
-  <si>
-    <t>2019-12-10</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2019-12-13</t>
-  </si>
-  <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
-    <t>2019-12-19</t>
-  </si>
-  <si>
-    <t>2019-12-24</t>
-  </si>
-  <si>
-    <t>2020-01-09</t>
-  </si>
-  <si>
-    <t>2020-01-13</t>
-  </si>
-  <si>
-    <t>2020-01-21</t>
-  </si>
-  <si>
-    <t>2020-02-28</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-03-04</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-09</t>
-  </si>
-  <si>
-    <t>2020-03-10</t>
-  </si>
-  <si>
-    <t>2020-03-11</t>
-  </si>
-  <si>
-    <t>2020-03-12</t>
-  </si>
-  <si>
-    <t>2020-03-16</t>
-  </si>
-  <si>
-    <t>2020-03-17</t>
-  </si>
-  <si>
-    <t>2020-03-18</t>
-  </si>
-  <si>
-    <t>2020-03-20</t>
-  </si>
-  <si>
-    <t>2020-03-30</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-04-03</t>
-  </si>
-  <si>
-    <t>2020-04-07</t>
-  </si>
-  <si>
-    <t>2020-04-08</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>2020-04-22</t>
-  </si>
-  <si>
-    <t>2020-04-24</t>
-  </si>
-  <si>
-    <t>2020-04-28</t>
-  </si>
-  <si>
-    <t>2020-05-15</t>
-  </si>
-  <si>
-    <t>2020-05-18</t>
-  </si>
-  <si>
-    <t>2020-05-19</t>
-  </si>
-  <si>
-    <t>2020-05-20</t>
-  </si>
-  <si>
-    <t>2020-05-21</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>2020-05-27</t>
-  </si>
-  <si>
-    <t>2020-06-01</t>
-  </si>
-  <si>
-    <t>2020-06-04</t>
-  </si>
-  <si>
-    <t>2020-06-09</t>
-  </si>
-  <si>
-    <t>2020-06-10</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>2020-06-19</t>
-  </si>
-  <si>
-    <t>2020-07-13</t>
-  </si>
-  <si>
-    <t>2020-07-16</t>
-  </si>
-  <si>
-    <t>2020-07-17</t>
-  </si>
-  <si>
-    <t>2020-07-28</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>2020-08-04</t>
-  </si>
-  <si>
-    <t>2020-08-05</t>
-  </si>
-  <si>
-    <t>2020-08-07</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>2020-08-12</t>
-  </si>
-  <si>
-    <t>2020-08-21</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>2020-11-10</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2021-01-21</t>
-  </si>
-  <si>
-    <t>2021-01-25</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>2021-03-05</t>
-  </si>
-  <si>
-    <t>2021-03-15</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>2021-04-20</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-04-22</t>
-  </si>
-  <si>
-    <t>2021-04-29</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>2021-05-17</t>
-  </si>
-  <si>
-    <t>2021-05-20</t>
-  </si>
-  <si>
-    <t>2021-05-28</t>
-  </si>
-  <si>
-    <t>2021-06-07</t>
-  </si>
-  <si>
-    <t>2021-07-28</t>
-  </si>
-  <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>2021-08-06</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>2021-09-13</t>
-  </si>
-  <si>
-    <t>2021-09-15</t>
-  </si>
-  <si>
-    <t>2021-09-16</t>
-  </si>
-  <si>
-    <t>2021-09-28</t>
-  </si>
-  <si>
-    <t>2021-09-29</t>
-  </si>
-  <si>
-    <t>2021-11-05</t>
-  </si>
-  <si>
-    <t>2021-11-08</t>
-  </si>
-  <si>
-    <t>2021-11-10</t>
-  </si>
-  <si>
-    <t>2021-11-11</t>
-  </si>
-  <si>
-    <t>2021-11-15</t>
-  </si>
-  <si>
-    <t>2021-11-17</t>
-  </si>
-  <si>
-    <t>2021-11-18</t>
-  </si>
-  <si>
     <t>2021-11-22</t>
+  </si>
+  <si>
+    <t>2021-11-26</t>
   </si>
 </sst>
 </file>
@@ -2528,7 +2534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1137"/>
+  <dimension ref="A1:P1139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -58289,7 +58295,7 @@
         <v>4.248999992057106</v>
       </c>
       <c r="D1116" t="s">
-        <v>520</v>
+        <v>274</v>
       </c>
       <c r="E1116">
         <v>4.272271111509813</v>
@@ -58339,10 +58345,10 @@
         <v>3.47813903198738</v>
       </c>
       <c r="D1117" t="s">
-        <v>519</v>
+        <v>271</v>
       </c>
       <c r="E1117">
-        <v>3.775384687237774</v>
+        <v>3.967258861826751</v>
       </c>
       <c r="F1117">
         <v>1</v>
@@ -58351,10 +58357,10 @@
         <v>0.01034186096801262</v>
       </c>
       <c r="H1117">
-        <v>0.01042461531276222</v>
+        <v>0.01021274113817325</v>
       </c>
       <c r="I1117">
-        <v>0.2972456552503946</v>
+        <v>0.489119829839372</v>
       </c>
       <c r="J1117">
         <v>0.6308567955905552</v>
@@ -58366,10 +58372,10 @@
         <v>6.91</v>
       </c>
       <c r="M1117">
-        <v>5.27</v>
+        <v>4.95</v>
       </c>
       <c r="N1117">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="O1117">
         <v>1</v>
@@ -58389,10 +58395,10 @@
         <v>3.498607575634624</v>
       </c>
       <c r="D1118" t="s">
-        <v>519</v>
+        <v>271</v>
       </c>
       <c r="E1118">
-        <v>3.775384687237774</v>
+        <v>3.967258861826751</v>
       </c>
       <c r="F1118">
         <v>1</v>
@@ -58401,10 +58407,10 @@
         <v>0.01026139242436538</v>
       </c>
       <c r="H1118">
-        <v>0.01042461531276222</v>
+        <v>0.01021274113817325</v>
       </c>
       <c r="I1118">
-        <v>0.2767771116031503</v>
+        <v>0.4686512861921277</v>
       </c>
       <c r="J1118">
         <v>0.6308567955905552</v>
@@ -58416,10 +58422,10 @@
         <v>6.88</v>
       </c>
       <c r="M1118">
-        <v>5.27</v>
+        <v>4.95</v>
       </c>
       <c r="N1118">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="O1118">
         <v>1</v>
@@ -58442,7 +58448,7 @@
         <v>520</v>
       </c>
       <c r="E1119">
-        <v>4.251224711546436</v>
+        <v>4.236458983370058</v>
       </c>
       <c r="F1119">
         <v>-1</v>
@@ -58451,10 +58457,10 @@
         <v>0.01065106108955593</v>
       </c>
       <c r="H1119">
-        <v>0.01098877528845356</v>
+        <v>0.01092354101662994</v>
       </c>
       <c r="I1119">
-        <v>-0.02228580110236056</v>
+        <v>-0.007520072925983001</v>
       </c>
       <c r="J1119">
         <v>0.6308567955905552</v>
@@ -58466,10 +58472,10 @@
         <v>7.44</v>
       </c>
       <c r="M1119">
-        <v>5.34</v>
+        <v>5.3</v>
       </c>
       <c r="N1119">
-        <v>7.62</v>
+        <v>7.58</v>
       </c>
       <c r="O1119">
         <v>1</v>
@@ -58542,7 +58548,7 @@
         <v>520</v>
       </c>
       <c r="E1121">
-        <v>4.254235153020323</v>
+        <v>4.239446874720546</v>
       </c>
       <c r="F1121">
         <v>-1</v>
@@ -58551,10 +58557,10 @@
         <v>0.01064819158635329</v>
       </c>
       <c r="H1121">
-        <v>0.01098576484697968</v>
+        <v>0.01092055312527945</v>
       </c>
       <c r="I1121">
-        <v>-0.02242673937361062</v>
+        <v>-0.007638461073833369</v>
       </c>
       <c r="J1121">
         <v>0.6302930425055575</v>
@@ -58566,10 +58572,10 @@
         <v>7.44</v>
       </c>
       <c r="M1121">
-        <v>5.34</v>
+        <v>5.3</v>
       </c>
       <c r="N1121">
-        <v>7.62</v>
+        <v>7.58</v>
       </c>
       <c r="O1121">
         <v>1</v>
@@ -58633,43 +58639,43 @@
         <v>1</v>
       </c>
       <c r="B1123" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C1123">
-        <v>3.498805886545609</v>
+        <v>4.183173955191915</v>
       </c>
       <c r="D1123" t="s">
-        <v>271</v>
+        <v>520</v>
       </c>
       <c r="E1123">
-        <v>3.922752667622786</v>
+        <v>4.188805886545609</v>
       </c>
       <c r="F1123">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1123">
-        <v>0.01028119411345439</v>
+        <v>0.01069682604480809</v>
       </c>
       <c r="H1123">
-        <v>0.01025724733237721</v>
+        <v>0.01097119411345439</v>
       </c>
       <c r="I1123">
-        <v>0.4239467810771766</v>
+        <v>-0.005631931353693886</v>
       </c>
       <c r="J1123">
         <v>0.6398479459347908</v>
       </c>
       <c r="K1123">
+        <v>5.09</v>
+      </c>
+      <c r="L1123">
+        <v>7.44</v>
+      </c>
+      <c r="M1123">
         <v>5.3</v>
       </c>
-      <c r="L1123">
-        <v>6.89</v>
-      </c>
-      <c r="M1123">
-        <v>4.95</v>
-      </c>
       <c r="N1123">
-        <v>7.09</v>
+        <v>7.58</v>
       </c>
       <c r="O1123">
         <v>1</v>
@@ -58680,34 +58686,34 @@
     </row>
     <row r="1124" spans="1:16">
       <c r="A1124" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1124" t="s">
         <v>272</v>
       </c>
       <c r="C1124">
-        <v>4.183173955191915</v>
+        <v>4.135874081532929</v>
       </c>
       <c r="D1124" t="s">
         <v>520</v>
       </c>
       <c r="E1124">
-        <v>4.203211968708217</v>
+        <v>4.139554544621713</v>
       </c>
       <c r="F1124">
         <v>-1</v>
       </c>
       <c r="G1124">
-        <v>0.01069682604480809</v>
+        <v>0.01074412591846707</v>
       </c>
       <c r="H1124">
-        <v>0.01103678803129178</v>
+        <v>0.01102044545537829</v>
       </c>
       <c r="I1124">
-        <v>-0.0200380135163023</v>
+        <v>-0.003680463088784336</v>
       </c>
       <c r="J1124">
-        <v>0.6398479459347908</v>
+        <v>0.6491406519581673</v>
       </c>
       <c r="K1124">
         <v>5.09</v>
@@ -58716,16 +58722,16 @@
         <v>7.44</v>
       </c>
       <c r="M1124">
-        <v>5.34</v>
+        <v>5.3</v>
       </c>
       <c r="N1124">
-        <v>7.62</v>
+        <v>7.58</v>
       </c>
       <c r="O1124">
         <v>1</v>
       </c>
       <c r="P1124" t="s">
-        <v>715</v>
+        <v>270</v>
       </c>
     </row>
     <row r="1125" spans="1:16">
@@ -58736,28 +58742,28 @@
         <v>272</v>
       </c>
       <c r="C1125">
-        <v>4.135874081532929</v>
+        <v>4.11008009499658</v>
       </c>
       <c r="D1125" t="s">
         <v>520</v>
       </c>
       <c r="E1125">
-        <v>4.153588918543386</v>
+        <v>4.112696366106459</v>
       </c>
       <c r="F1125">
         <v>-1</v>
       </c>
       <c r="G1125">
-        <v>0.01074412591846707</v>
+        <v>0.01076991990500342</v>
       </c>
       <c r="H1125">
-        <v>0.01108641108145661</v>
+        <v>0.01104730363389354</v>
       </c>
       <c r="I1125">
-        <v>-0.01771483701045717</v>
+        <v>-0.002616271109878276</v>
       </c>
       <c r="J1125">
-        <v>0.6491406519581673</v>
+        <v>0.6542082328101022</v>
       </c>
       <c r="K1125">
         <v>5.09</v>
@@ -58766,16 +58772,16 @@
         <v>7.44</v>
       </c>
       <c r="M1125">
-        <v>5.34</v>
+        <v>5.3</v>
       </c>
       <c r="N1125">
-        <v>7.62</v>
+        <v>7.58</v>
       </c>
       <c r="O1125">
         <v>1</v>
       </c>
       <c r="P1125" t="s">
-        <v>270</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1126" spans="1:16">
@@ -58786,28 +58792,28 @@
         <v>272</v>
       </c>
       <c r="C1126">
-        <v>4.11008009499658</v>
+        <v>4.080094170624702</v>
       </c>
       <c r="D1126" t="s">
         <v>520</v>
       </c>
       <c r="E1126">
-        <v>4.126528036794054</v>
+        <v>4.081473301436329</v>
       </c>
       <c r="F1126">
         <v>-1</v>
       </c>
       <c r="G1126">
-        <v>0.01076991990500342</v>
+        <v>0.0107999058293753</v>
       </c>
       <c r="H1126">
-        <v>0.01111347196320595</v>
+        <v>0.01107852669856367</v>
       </c>
       <c r="I1126">
-        <v>-0.01644794179747411</v>
+        <v>-0.001379130811627327</v>
       </c>
       <c r="J1126">
-        <v>0.6542082328101022</v>
+        <v>0.660099377087485</v>
       </c>
       <c r="K1126">
         <v>5.09</v>
@@ -58816,16 +58822,16 @@
         <v>7.44</v>
       </c>
       <c r="M1126">
-        <v>5.34</v>
+        <v>5.3</v>
       </c>
       <c r="N1126">
-        <v>7.62</v>
+        <v>7.58</v>
       </c>
       <c r="O1126">
         <v>1</v>
       </c>
       <c r="P1126" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1127" spans="1:16">
@@ -58836,28 +58842,28 @@
         <v>272</v>
       </c>
       <c r="C1127">
-        <v>4.080094170624702</v>
+        <v>4.062490004221782</v>
       </c>
       <c r="D1127" t="s">
         <v>520</v>
       </c>
       <c r="E1127">
-        <v>4.09506932635283</v>
+        <v>4.063142833472583</v>
       </c>
       <c r="F1127">
         <v>-1</v>
       </c>
       <c r="G1127">
-        <v>0.0107999058293753</v>
+        <v>0.01081750999577822</v>
       </c>
       <c r="H1127">
-        <v>0.01114493067364717</v>
+        <v>0.01109685716652742</v>
       </c>
       <c r="I1127">
-        <v>-0.01497515572812791</v>
+        <v>-0.0006528292508001243</v>
       </c>
       <c r="J1127">
-        <v>0.660099377087485</v>
+        <v>0.6635579559485695</v>
       </c>
       <c r="K1127">
         <v>5.09</v>
@@ -58866,16 +58872,16 @@
         <v>7.44</v>
       </c>
       <c r="M1127">
-        <v>5.34</v>
+        <v>5.3</v>
       </c>
       <c r="N1127">
-        <v>7.62</v>
+        <v>7.58</v>
       </c>
       <c r="O1127">
         <v>1</v>
       </c>
       <c r="P1127" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1128" spans="1:16">
@@ -58883,149 +58889,149 @@
         <v>0</v>
       </c>
       <c r="B1128" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C1128">
-        <v>4.062490004221782</v>
+        <v>3.536882435316822</v>
       </c>
       <c r="D1128" t="s">
-        <v>520</v>
+        <v>271</v>
       </c>
       <c r="E1128">
-        <v>4.07660051523464</v>
+        <v>3.834974429228346</v>
       </c>
       <c r="F1128">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1128">
-        <v>0.01081750999577822</v>
+        <v>0.01032311756468318</v>
       </c>
       <c r="H1128">
-        <v>0.01116339948476536</v>
+        <v>0.01034502557077165</v>
       </c>
       <c r="I1128">
-        <v>-0.01411051101285743</v>
+        <v>0.2980919939115245</v>
       </c>
       <c r="J1128">
-        <v>0.6635579559485695</v>
+        <v>0.6575809233882128</v>
       </c>
       <c r="K1128">
-        <v>5.09</v>
+        <v>5.16</v>
       </c>
       <c r="L1128">
-        <v>7.44</v>
+        <v>6.93</v>
       </c>
       <c r="M1128">
-        <v>5.34</v>
+        <v>4.95</v>
       </c>
       <c r="N1128">
-        <v>7.62</v>
+        <v>7.09</v>
       </c>
       <c r="O1128">
         <v>1</v>
       </c>
       <c r="P1128" t="s">
-        <v>273</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1129" spans="1:16">
       <c r="A1129" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1129" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C1129">
-        <v>3.536882435316822</v>
+        <v>4.092913099953997</v>
       </c>
       <c r="D1129" t="s">
-        <v>271</v>
+        <v>520</v>
       </c>
       <c r="E1129">
-        <v>3.834974429228346</v>
+        <v>4.094821106042472</v>
       </c>
       <c r="F1129">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1129">
-        <v>0.01032311756468318</v>
+        <v>0.010787086900046</v>
       </c>
       <c r="H1129">
-        <v>0.01034502557077165</v>
+        <v>0.01106517889395753</v>
       </c>
       <c r="I1129">
-        <v>0.2980919939115245</v>
+        <v>-0.001908006088474856</v>
       </c>
       <c r="J1129">
         <v>0.6575809233882128</v>
       </c>
       <c r="K1129">
-        <v>5.16</v>
+        <v>5.09</v>
       </c>
       <c r="L1129">
-        <v>6.93</v>
+        <v>7.44</v>
       </c>
       <c r="M1129">
-        <v>4.95</v>
+        <v>5.3</v>
       </c>
       <c r="N1129">
-        <v>7.09</v>
+        <v>7.58</v>
       </c>
       <c r="O1129">
         <v>1</v>
       </c>
       <c r="P1129" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1130" spans="1:16">
       <c r="A1130" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1130" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C1130">
-        <v>4.092913099953997</v>
+        <v>4.108517869106944</v>
       </c>
       <c r="D1130" t="s">
         <v>520</v>
       </c>
       <c r="E1130">
-        <v>4.108517869106944</v>
+        <v>4.094821106042472</v>
       </c>
       <c r="F1130">
         <v>-1</v>
       </c>
       <c r="G1130">
-        <v>0.010787086900046</v>
+        <v>0.01113148213089306</v>
       </c>
       <c r="H1130">
-        <v>0.01113148213089306</v>
+        <v>0.01106517889395753</v>
       </c>
       <c r="I1130">
-        <v>-0.0156047691529464</v>
+        <v>0.01369676306447154</v>
       </c>
       <c r="J1130">
         <v>0.6575809233882128</v>
       </c>
       <c r="K1130">
-        <v>5.09</v>
+        <v>5.34</v>
       </c>
       <c r="L1130">
-        <v>7.44</v>
+        <v>7.62</v>
       </c>
       <c r="M1130">
-        <v>5.34</v>
+        <v>5.3</v>
       </c>
       <c r="N1130">
-        <v>7.62</v>
+        <v>7.58</v>
       </c>
       <c r="O1130">
         <v>1</v>
       </c>
       <c r="P1130" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1131" spans="1:16">
@@ -59033,10 +59039,10 @@
         <v>0</v>
       </c>
       <c r="B1131" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C1131">
-        <v>3.580745617898816</v>
+        <v>3.610929556577065</v>
       </c>
       <c r="D1131" t="s">
         <v>271</v>
@@ -59048,22 +59054,22 @@
         <v>1</v>
       </c>
       <c r="G1131">
-        <v>0.01027925438210118</v>
+        <v>0.01056907044342293</v>
       </c>
       <c r="H1131">
         <v>0.01030294751771335</v>
       </c>
       <c r="I1131">
-        <v>0.296306864387839</v>
+        <v>0.2661229257095901</v>
       </c>
       <c r="J1131">
         <v>0.6490803066087565</v>
       </c>
       <c r="K1131">
-        <v>5.16</v>
+        <v>5.36</v>
       </c>
       <c r="L1131">
-        <v>6.93</v>
+        <v>7.09</v>
       </c>
       <c r="M1131">
         <v>4.95</v>
@@ -59083,43 +59089,43 @@
         <v>1</v>
       </c>
       <c r="B1132" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C1132">
-        <v>4.13618123936143</v>
+        <v>3.580745617898816</v>
       </c>
       <c r="D1132" t="s">
-        <v>520</v>
+        <v>271</v>
       </c>
       <c r="E1132">
-        <v>4.153911162709241</v>
+        <v>3.877052482286655</v>
       </c>
       <c r="F1132">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1132">
-        <v>0.01074381876063857</v>
+        <v>0.01027925438210118</v>
       </c>
       <c r="H1132">
-        <v>0.01108608883729076</v>
+        <v>0.01030294751771335</v>
       </c>
       <c r="I1132">
-        <v>-0.01772992334781076</v>
+        <v>0.296306864387839</v>
       </c>
       <c r="J1132">
         <v>0.6490803066087565</v>
       </c>
       <c r="K1132">
-        <v>5.09</v>
+        <v>5.16</v>
       </c>
       <c r="L1132">
-        <v>7.44</v>
+        <v>6.93</v>
       </c>
       <c r="M1132">
-        <v>5.34</v>
+        <v>4.95</v>
       </c>
       <c r="N1132">
-        <v>7.62</v>
+        <v>7.09</v>
       </c>
       <c r="O1132">
         <v>1</v>
@@ -59130,146 +59136,146 @@
     </row>
     <row r="1133" spans="1:16">
       <c r="A1133" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1133" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C1133">
-        <v>3.610221685972557</v>
+        <v>4.13618123936143</v>
       </c>
       <c r="D1133" t="s">
-        <v>271</v>
+        <v>520</v>
       </c>
       <c r="E1133">
-        <v>3.876398758500776</v>
+        <v>4.139874374973591</v>
       </c>
       <c r="F1133">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1133">
-        <v>0.01056977831402744</v>
+        <v>0.01074381876063857</v>
       </c>
       <c r="H1133">
-        <v>0.01030360124149922</v>
+        <v>0.01102012562502641</v>
       </c>
       <c r="I1133">
-        <v>0.2661770725282189</v>
+        <v>-0.003693135612160781</v>
       </c>
       <c r="J1133">
-        <v>0.6492123720200452</v>
+        <v>0.6490803066087565</v>
       </c>
       <c r="K1133">
-        <v>5.36</v>
+        <v>5.09</v>
       </c>
       <c r="L1133">
-        <v>7.09</v>
+        <v>7.44</v>
       </c>
       <c r="M1133">
-        <v>4.95</v>
+        <v>5.3</v>
       </c>
       <c r="N1133">
-        <v>7.09</v>
+        <v>7.58</v>
       </c>
       <c r="O1133">
         <v>1</v>
       </c>
       <c r="P1133" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1134" spans="1:16">
       <c r="A1134" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1134" t="s">
         <v>274</v>
       </c>
       <c r="C1134">
-        <v>3.580064160376566</v>
+        <v>4.153911162709241</v>
       </c>
       <c r="D1134" t="s">
-        <v>271</v>
+        <v>520</v>
       </c>
       <c r="E1134">
-        <v>3.876398758500776</v>
+        <v>4.139874374973591</v>
       </c>
       <c r="F1134">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1134">
-        <v>0.01027993583962343</v>
+        <v>0.01108608883729076</v>
       </c>
       <c r="H1134">
-        <v>0.01030360124149922</v>
+        <v>0.01102012562502641</v>
       </c>
       <c r="I1134">
-        <v>0.2963345981242096</v>
+        <v>0.01403678773564998</v>
       </c>
       <c r="J1134">
-        <v>0.6492123720200452</v>
+        <v>0.6490803066087565</v>
       </c>
       <c r="K1134">
-        <v>5.16</v>
+        <v>5.34</v>
       </c>
       <c r="L1134">
-        <v>6.93</v>
+        <v>7.62</v>
       </c>
       <c r="M1134">
-        <v>4.95</v>
+        <v>5.3</v>
       </c>
       <c r="N1134">
-        <v>7.09</v>
+        <v>7.58</v>
       </c>
       <c r="O1134">
         <v>1</v>
       </c>
       <c r="P1134" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1135" spans="1:16">
       <c r="A1135" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1135" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1135">
+        <v>3.610221685972557</v>
+      </c>
+      <c r="D1135" t="s">
         <v>272</v>
       </c>
-      <c r="C1135">
+      <c r="E1135">
         <v>4.135509026417971</v>
       </c>
-      <c r="D1135" t="s">
-        <v>520</v>
-      </c>
-      <c r="E1135">
-        <v>4.153205933412959</v>
-      </c>
       <c r="F1135">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1135">
+        <v>0.01056977831402744</v>
+      </c>
+      <c r="H1135">
         <v>0.01074449097358203</v>
       </c>
-      <c r="H1135">
-        <v>0.01108679406658704</v>
-      </c>
       <c r="I1135">
-        <v>-0.01769690699498838</v>
+        <v>0.5252873404454137</v>
       </c>
       <c r="J1135">
         <v>0.6492123720200452</v>
       </c>
       <c r="K1135">
+        <v>5.36</v>
+      </c>
+      <c r="L1135">
+        <v>7.09</v>
+      </c>
+      <c r="M1135">
         <v>5.09</v>
       </c>
-      <c r="L1135">
+      <c r="N1135">
         <v>7.44</v>
-      </c>
-      <c r="M1135">
-        <v>5.34</v>
-      </c>
-      <c r="N1135">
-        <v>7.62</v>
       </c>
       <c r="O1135">
         <v>1</v>
@@ -59280,34 +59286,34 @@
     </row>
     <row r="1136" spans="1:16">
       <c r="A1136" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1136" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C1136">
-        <v>3.597069472111373</v>
+        <v>3.580064160376566</v>
       </c>
       <c r="D1136" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E1136">
-        <v>3.892711993595213</v>
+        <v>4.135509026417971</v>
       </c>
       <c r="F1136">
         <v>1</v>
       </c>
       <c r="G1136">
-        <v>0.01026293052788863</v>
+        <v>0.01027993583962343</v>
       </c>
       <c r="H1136">
-        <v>0.01028728800640479</v>
+        <v>0.01074449097358203</v>
       </c>
       <c r="I1136">
-        <v>0.2956425214838396</v>
+        <v>0.5554448660414044</v>
       </c>
       <c r="J1136">
-        <v>0.6459167689706641</v>
+        <v>0.6492123720200452</v>
       </c>
       <c r="K1136">
         <v>5.16</v>
@@ -59316,66 +59322,166 @@
         <v>6.93</v>
       </c>
       <c r="M1136">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
       <c r="N1136">
-        <v>7.09</v>
+        <v>7.44</v>
       </c>
       <c r="O1136">
         <v>1</v>
       </c>
       <c r="P1136" t="s">
-        <v>275</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1137" spans="1:16">
       <c r="A1137" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1137" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C1137">
-        <v>4.15228364593932</v>
+        <v>4.153205933412959</v>
       </c>
       <c r="D1137" t="s">
         <v>520</v>
       </c>
       <c r="E1137">
-        <v>4.170804453696654</v>
+        <v>4.13917442829376</v>
       </c>
       <c r="F1137">
         <v>-1</v>
       </c>
       <c r="G1137">
-        <v>0.01072771635406068</v>
+        <v>0.01108679406658704</v>
       </c>
       <c r="H1137">
+        <v>0.01102082557170624</v>
+      </c>
+      <c r="I1137">
+        <v>0.01403150511919904</v>
+      </c>
+      <c r="J1137">
+        <v>0.6492123720200452</v>
+      </c>
+      <c r="K1137">
+        <v>5.34</v>
+      </c>
+      <c r="L1137">
+        <v>7.62</v>
+      </c>
+      <c r="M1137">
+        <v>5.3</v>
+      </c>
+      <c r="N1137">
+        <v>7.58</v>
+      </c>
+      <c r="O1137">
+        <v>1</v>
+      </c>
+      <c r="P1137" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:16">
+      <c r="A1138" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1138" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1138">
+        <v>4.170804453696654</v>
+      </c>
+      <c r="D1138" t="s">
+        <v>520</v>
+      </c>
+      <c r="E1138">
+        <v>4.156641124455481</v>
+      </c>
+      <c r="F1138">
+        <v>-1</v>
+      </c>
+      <c r="G1138">
         <v>0.01106919554630335</v>
       </c>
-      <c r="I1137">
-        <v>-0.01852080775733356</v>
-      </c>
-      <c r="J1137">
+      <c r="H1138">
+        <v>0.01100335887554452</v>
+      </c>
+      <c r="I1138">
+        <v>0.01416332924117292</v>
+      </c>
+      <c r="J1138">
         <v>0.6459167689706641</v>
       </c>
-      <c r="K1137">
-        <v>5.09</v>
-      </c>
-      <c r="L1137">
-        <v>7.44</v>
-      </c>
-      <c r="M1137">
+      <c r="K1138">
         <v>5.34</v>
       </c>
-      <c r="N1137">
+      <c r="L1138">
         <v>7.62</v>
       </c>
-      <c r="O1137">
-        <v>1</v>
-      </c>
-      <c r="P1137" t="s">
+      <c r="M1138">
+        <v>5.3</v>
+      </c>
+      <c r="N1138">
+        <v>7.58</v>
+      </c>
+      <c r="O1138">
+        <v>1</v>
+      </c>
+      <c r="P1138" t="s">
         <v>275</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:16">
+      <c r="A1139" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1139" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1139">
+        <v>4.204775956214513</v>
+      </c>
+      <c r="D1139" t="s">
+        <v>520</v>
+      </c>
+      <c r="E1139">
+        <v>4.190358158789685</v>
+      </c>
+      <c r="F1139">
+        <v>-1</v>
+      </c>
+      <c r="G1139">
+        <v>0.01103522404378549</v>
+      </c>
+      <c r="H1139">
+        <v>0.01096964184121032</v>
+      </c>
+      <c r="I1139">
+        <v>0.01441779742482741</v>
+      </c>
+      <c r="J1139">
+        <v>0.6395550643793048</v>
+      </c>
+      <c r="K1139">
+        <v>5.34</v>
+      </c>
+      <c r="L1139">
+        <v>7.62</v>
+      </c>
+      <c r="M1139">
+        <v>5.3</v>
+      </c>
+      <c r="N1139">
+        <v>7.58</v>
+      </c>
+      <c r="O1139">
+        <v>1</v>
+      </c>
+      <c r="P1139" t="s">
+        <v>720</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3429" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3432" uniqueCount="723">
   <si>
     <t>trade_time</t>
   </si>
@@ -838,15 +838,15 @@
     <t>2021-11-19</t>
   </si>
   <si>
+    <t>2021-12-07</t>
+  </si>
+  <si>
+    <t>2021-11-25</t>
+  </si>
+  <si>
     <t>2021-11-29</t>
   </si>
   <si>
-    <t>2021-12-07</t>
-  </si>
-  <si>
-    <t>2021-11-25</t>
-  </si>
-  <si>
     <t>2016-09-28</t>
   </si>
   <si>
@@ -1583,6 +1583,12 @@
   </si>
   <si>
     <t>2021-12-09</t>
+  </si>
+  <si>
+    <t>2021-12-10</t>
+  </si>
+  <si>
+    <t>2021-12-13</t>
   </si>
   <si>
     <t>2016-08-29</t>
@@ -2534,7 +2540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1139"/>
+  <dimension ref="A1:P1140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2631,7 +2637,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2681,7 +2687,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2731,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2781,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2831,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2881,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2931,7 +2937,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2981,7 +2987,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -3031,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -3081,7 +3087,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3131,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3181,7 +3187,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3231,7 +3237,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -3281,7 +3287,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -3431,7 +3437,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3481,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3531,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3581,7 +3587,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3631,7 +3637,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3681,7 +3687,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3731,7 +3737,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3881,7 +3887,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3931,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -4081,7 +4087,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -4131,7 +4137,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -4181,7 +4187,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4231,7 +4237,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -4281,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4331,7 +4337,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4481,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4531,7 +4537,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4581,7 +4587,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4631,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4681,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4731,7 +4737,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4781,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4831,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4881,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4931,7 +4937,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4981,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -5031,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -5081,7 +5087,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -5331,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -5381,7 +5387,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -5431,7 +5437,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5581,7 +5587,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5631,7 +5637,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -7631,7 +7637,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7681,7 +7687,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7731,7 +7737,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -8181,7 +8187,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -8231,7 +8237,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -8281,7 +8287,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -8331,7 +8337,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -8381,7 +8387,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -8581,7 +8587,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8631,7 +8637,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -8681,7 +8687,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8881,7 +8887,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8931,7 +8937,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8981,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -9031,7 +9037,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -9331,7 +9337,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -9381,7 +9387,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -9431,7 +9437,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -9481,7 +9487,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9531,7 +9537,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9781,7 +9787,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9831,7 +9837,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9881,7 +9887,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9931,7 +9937,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -11331,7 +11337,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11381,7 +11387,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11431,7 +11437,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11481,7 +11487,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11531,7 +11537,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11581,7 +11587,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -12031,7 +12037,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -12081,7 +12087,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -12231,7 +12237,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -12281,7 +12287,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -12331,7 +12337,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -12781,7 +12787,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12831,7 +12837,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12881,7 +12887,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12931,7 +12937,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12981,7 +12987,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -13931,7 +13937,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13981,7 +13987,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -14031,7 +14037,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -14081,7 +14087,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -14131,7 +14137,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -14181,7 +14187,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -14981,7 +14987,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -15031,7 +15037,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -15081,7 +15087,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -15131,7 +15137,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -15181,7 +15187,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -15681,7 +15687,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15731,7 +15737,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15781,7 +15787,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15831,7 +15837,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15881,7 +15887,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15931,7 +15937,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15981,7 +15987,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -17481,7 +17487,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -17531,7 +17537,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -17581,7 +17587,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -17631,7 +17637,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17681,7 +17687,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17731,7 +17737,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17781,7 +17787,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -19431,7 +19437,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -19481,7 +19487,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19681,7 +19687,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19731,7 +19737,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19781,7 +19787,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19831,7 +19837,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19981,7 +19987,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -20031,7 +20037,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -20081,7 +20087,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -20231,7 +20237,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -20281,7 +20287,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -20331,7 +20337,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -20581,7 +20587,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -20631,7 +20637,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20681,7 +20687,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20731,7 +20737,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20781,7 +20787,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20831,7 +20837,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20881,7 +20887,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20931,7 +20937,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20981,7 +20987,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -21031,7 +21037,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -21081,7 +21087,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -21131,7 +21137,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -21181,7 +21187,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -21281,7 +21287,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -21331,7 +21337,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -21381,7 +21387,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -21431,7 +21437,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21481,7 +21487,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21531,7 +21537,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -21581,7 +21587,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21631,7 +21637,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -22081,7 +22087,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -22131,7 +22137,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -22181,7 +22187,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -22381,7 +22387,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -22431,7 +22437,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -22481,7 +22487,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -22531,7 +22537,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -22581,7 +22587,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22631,7 +22637,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22681,7 +22687,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22731,7 +22737,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22781,7 +22787,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22831,7 +22837,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22881,7 +22887,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22931,7 +22937,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22981,7 +22987,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -23031,7 +23037,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -23081,7 +23087,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -23131,7 +23137,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -23181,7 +23187,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -23231,7 +23237,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -23281,7 +23287,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -23331,7 +23337,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23831,7 +23837,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23881,7 +23887,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23931,7 +23937,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23981,7 +23987,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -24031,7 +24037,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -24281,7 +24287,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -24331,7 +24337,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24381,7 +24387,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24431,7 +24437,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24481,7 +24487,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24531,7 +24537,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24581,7 +24587,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24631,7 +24637,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24681,7 +24687,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24731,7 +24737,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24781,7 +24787,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24831,7 +24837,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24881,7 +24887,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24931,7 +24937,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -25131,7 +25137,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -25181,7 +25187,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -25231,7 +25237,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25281,7 +25287,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -25831,7 +25837,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25881,7 +25887,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25931,7 +25937,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25981,7 +25987,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -26031,7 +26037,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -26281,7 +26287,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26331,7 +26337,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26381,7 +26387,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26431,7 +26437,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26631,7 +26637,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26681,7 +26687,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26731,7 +26737,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26781,7 +26787,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26831,7 +26837,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26881,7 +26887,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26931,7 +26937,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -27231,7 +27237,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -27281,7 +27287,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -27331,7 +27337,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -27381,7 +27387,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -27531,7 +27537,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -27581,7 +27587,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -27631,7 +27637,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27681,7 +27687,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27731,7 +27737,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27881,7 +27887,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27931,7 +27937,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -28081,7 +28087,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -28131,7 +28137,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -28181,7 +28187,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -28231,7 +28237,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28281,7 +28287,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -28331,7 +28337,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -28381,7 +28387,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -28431,7 +28437,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -28681,7 +28687,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28731,7 +28737,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28781,7 +28787,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28831,7 +28837,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28881,7 +28887,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28931,7 +28937,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28981,7 +28987,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -29031,7 +29037,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -29081,7 +29087,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -29131,7 +29137,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -29181,7 +29187,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -29231,7 +29237,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -29281,7 +29287,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -29331,7 +29337,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29381,7 +29387,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29431,7 +29437,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -29681,7 +29687,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29731,7 +29737,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29931,7 +29937,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29981,7 +29987,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -30031,7 +30037,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -30081,7 +30087,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -30131,7 +30137,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -30181,7 +30187,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -30231,7 +30237,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -30281,7 +30287,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -30331,7 +30337,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30481,7 +30487,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -30531,7 +30537,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -30731,7 +30737,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30781,7 +30787,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30981,7 +30987,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -31031,7 +31037,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -31081,7 +31087,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -31131,7 +31137,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -31181,7 +31187,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -31281,7 +31287,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -31331,7 +31337,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31381,7 +31387,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31431,7 +31437,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31681,7 +31687,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31731,7 +31737,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31781,7 +31787,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -32131,7 +32137,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -32181,7 +32187,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -32231,7 +32237,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -33181,7 +33187,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -33231,7 +33237,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -33281,7 +33287,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -33331,7 +33337,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33531,7 +33537,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -33581,7 +33587,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -33631,7 +33637,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -34431,7 +34437,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -34481,7 +34487,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -34531,7 +34537,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -34581,7 +34587,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -34631,7 +34637,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -34681,7 +34687,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -34731,7 +34737,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34781,7 +34787,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34831,7 +34837,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34881,7 +34887,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34931,7 +34937,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34981,7 +34987,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -35031,7 +35037,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -35081,7 +35087,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -35181,7 +35187,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -35231,7 +35237,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -35281,7 +35287,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -35331,7 +35337,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35381,7 +35387,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -35431,7 +35437,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -35481,7 +35487,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -35681,7 +35687,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35731,7 +35737,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -35781,7 +35787,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -36231,7 +36237,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -36281,7 +36287,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -36331,7 +36337,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -36381,7 +36387,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -36581,7 +36587,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36631,7 +36637,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36681,7 +36687,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36731,7 +36737,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36781,7 +36787,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36831,7 +36837,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36881,7 +36887,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36931,7 +36937,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36981,7 +36987,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -37031,7 +37037,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -37081,7 +37087,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -37131,7 +37137,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -38131,7 +38137,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -38181,7 +38187,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -38231,7 +38237,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -38281,7 +38287,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -38531,7 +38537,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -38581,7 +38587,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38631,7 +38637,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38681,7 +38687,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38881,7 +38887,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38931,7 +38937,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38981,7 +38987,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -39081,7 +39087,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -39431,7 +39437,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -39481,7 +39487,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -39531,7 +39537,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -39581,7 +39587,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -39631,7 +39637,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39681,7 +39687,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39731,7 +39737,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39781,7 +39787,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39831,7 +39837,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39881,7 +39887,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -40131,7 +40137,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -40181,7 +40187,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -40231,7 +40237,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -40531,7 +40537,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40581,7 +40587,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40631,7 +40637,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40881,7 +40887,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40931,7 +40937,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40981,7 +40987,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -41031,7 +41037,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -41081,7 +41087,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -41531,7 +41537,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41581,7 +41587,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41681,7 +41687,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41731,7 +41737,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41781,7 +41787,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41831,7 +41837,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -42981,7 +42987,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -43031,7 +43037,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -43081,7 +43087,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -43131,7 +43137,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -43181,7 +43187,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -43231,7 +43237,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -43281,7 +43287,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -43331,7 +43337,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43381,7 +43387,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -44131,7 +44137,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -44181,7 +44187,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -44231,7 +44237,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -44481,7 +44487,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -44531,7 +44537,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -44581,7 +44587,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -44631,7 +44637,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -44681,7 +44687,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44731,7 +44737,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44781,7 +44787,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44831,7 +44837,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44881,7 +44887,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44931,7 +44937,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44981,7 +44987,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -45181,7 +45187,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -45231,7 +45237,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -45281,7 +45287,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -45481,7 +45487,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -45531,7 +45537,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -45581,7 +45587,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -45631,7 +45637,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45681,7 +45687,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45731,7 +45737,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -46631,7 +46637,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46681,7 +46687,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46781,7 +46787,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46831,7 +46837,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46881,7 +46887,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -47181,7 +47187,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -47231,7 +47237,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -47281,7 +47287,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -47331,7 +47337,7 @@
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="897" spans="1:16">
@@ -47381,7 +47387,7 @@
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="898" spans="1:16">
@@ -47531,7 +47537,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47631,7 +47637,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47681,7 +47687,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47731,7 +47737,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47881,7 +47887,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47931,7 +47937,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47981,7 +47987,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -48181,7 +48187,7 @@
         <v>1</v>
       </c>
       <c r="P913" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="914" spans="1:16">
@@ -48231,7 +48237,7 @@
         <v>1</v>
       </c>
       <c r="P914" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="915" spans="1:16">
@@ -48281,7 +48287,7 @@
         <v>1</v>
       </c>
       <c r="P915" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="916" spans="1:16">
@@ -48331,7 +48337,7 @@
         <v>1</v>
       </c>
       <c r="P916" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="917" spans="1:16">
@@ -48381,7 +48387,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -48731,7 +48737,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48781,7 +48787,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48831,7 +48837,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48881,7 +48887,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -49081,7 +49087,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -49131,7 +49137,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -49631,7 +49637,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49681,7 +49687,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49731,7 +49737,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49781,7 +49787,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49831,7 +49837,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -50231,7 +50237,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -50431,7 +50437,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -50481,7 +50487,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -50531,7 +50537,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -50581,7 +50587,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -51131,7 +51137,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -51181,7 +51187,7 @@
         <v>1</v>
       </c>
       <c r="P973" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="974" spans="1:16">
@@ -51231,7 +51237,7 @@
         <v>1</v>
       </c>
       <c r="P974" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="975" spans="1:16">
@@ -51881,7 +51887,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51931,7 +51937,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51981,7 +51987,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -52881,7 +52887,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -54231,7 +54237,7 @@
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -54281,7 +54287,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -54681,7 +54687,7 @@
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
@@ -54731,7 +54737,7 @@
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
@@ -54781,7 +54787,7 @@
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
@@ -54831,7 +54837,7 @@
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
@@ -54981,7 +54987,7 @@
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
@@ -55031,7 +55037,7 @@
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
@@ -55081,7 +55087,7 @@
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
@@ -55131,7 +55137,7 @@
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
@@ -55181,7 +55187,7 @@
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
@@ -55231,7 +55237,7 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
@@ -56681,7 +56687,7 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56731,7 +56737,7 @@
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56931,7 +56937,7 @@
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56981,7 +56987,7 @@
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -57031,7 +57037,7 @@
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -57181,7 +57187,7 @@
         <v>1</v>
       </c>
       <c r="P1093" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1094" spans="1:16">
@@ -57231,7 +57237,7 @@
         <v>1</v>
       </c>
       <c r="P1094" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1095" spans="1:16">
@@ -57281,7 +57287,7 @@
         <v>1</v>
       </c>
       <c r="P1095" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1096" spans="1:16">
@@ -57331,7 +57337,7 @@
         <v>1</v>
       </c>
       <c r="P1096" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1097" spans="1:16">
@@ -57631,7 +57637,7 @@
         <v>1</v>
       </c>
       <c r="P1102" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1103" spans="1:16">
@@ -57681,7 +57687,7 @@
         <v>1</v>
       </c>
       <c r="P1103" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1104" spans="1:16">
@@ -57731,7 +57737,7 @@
         <v>1</v>
       </c>
       <c r="P1104" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1105" spans="1:16">
@@ -57781,7 +57787,7 @@
         <v>1</v>
       </c>
       <c r="P1105" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="1106" spans="1:16">
@@ -57831,7 +57837,7 @@
         <v>1</v>
       </c>
       <c r="P1106" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="1107" spans="1:16">
@@ -57881,7 +57887,7 @@
         <v>1</v>
       </c>
       <c r="P1107" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="1108" spans="1:16">
@@ -57931,7 +57937,7 @@
         <v>1</v>
       </c>
       <c r="P1108" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="1109" spans="1:16">
@@ -57981,7 +57987,7 @@
         <v>1</v>
       </c>
       <c r="P1109" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="1110" spans="1:16">
@@ -58031,7 +58037,7 @@
         <v>1</v>
       </c>
       <c r="P1110" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="1111" spans="1:16">
@@ -58081,7 +58087,7 @@
         <v>1</v>
       </c>
       <c r="P1111" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1112" spans="1:16">
@@ -58131,7 +58137,7 @@
         <v>1</v>
       </c>
       <c r="P1112" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1113" spans="1:16">
@@ -58181,7 +58187,7 @@
         <v>1</v>
       </c>
       <c r="P1113" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1114" spans="1:16">
@@ -58231,7 +58237,7 @@
         <v>1</v>
       </c>
       <c r="P1114" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1115" spans="1:16">
@@ -58281,7 +58287,7 @@
         <v>1</v>
       </c>
       <c r="P1115" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1116" spans="1:16">
@@ -58295,7 +58301,7 @@
         <v>4.248999992057106</v>
       </c>
       <c r="D1116" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E1116">
         <v>4.272271111509813</v>
@@ -58331,7 +58337,7 @@
         <v>1</v>
       </c>
       <c r="P1116" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1117" spans="1:16">
@@ -58381,7 +58387,7 @@
         <v>1</v>
       </c>
       <c r="P1117" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1118" spans="1:16">
@@ -58431,7 +58437,7 @@
         <v>1</v>
       </c>
       <c r="P1118" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1119" spans="1:16">
@@ -58481,7 +58487,7 @@
         <v>1</v>
       </c>
       <c r="P1119" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1120" spans="1:16">
@@ -58645,10 +58651,10 @@
         <v>4.183173955191915</v>
       </c>
       <c r="D1123" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E1123">
-        <v>4.146008927626912</v>
+        <v>4.05639220167974</v>
       </c>
       <c r="F1123">
         <v>-1</v>
@@ -58657,10 +58663,10 @@
         <v>0.01069682604480809</v>
       </c>
       <c r="H1123">
-        <v>0.01095399107237309</v>
+        <v>0.01072360779832026</v>
       </c>
       <c r="I1123">
-        <v>0.03716502756500262</v>
+        <v>0.1267817535121747</v>
       </c>
       <c r="J1123">
         <v>0.6398479459347908</v>
@@ -58672,16 +58678,16 @@
         <v>7.44</v>
       </c>
       <c r="M1123">
-        <v>5.32</v>
+        <v>5.21</v>
       </c>
       <c r="N1123">
-        <v>7.55</v>
+        <v>7.39</v>
       </c>
       <c r="O1123">
         <v>1</v>
       </c>
       <c r="P1123" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1124" spans="1:16">
@@ -58695,10 +58701,10 @@
         <v>4.135874081532929</v>
       </c>
       <c r="D1124" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E1124">
-        <v>4.09657173158255</v>
+        <v>3.982709227269243</v>
       </c>
       <c r="F1124">
         <v>-1</v>
@@ -58707,10 +58713,10 @@
         <v>0.01074412591846707</v>
       </c>
       <c r="H1124">
-        <v>0.01100342826841745</v>
+        <v>0.01109729077273076</v>
       </c>
       <c r="I1124">
-        <v>0.03930234995037907</v>
+        <v>0.1531648542636859</v>
       </c>
       <c r="J1124">
         <v>0.6491406519581673</v>
@@ -58722,10 +58728,10 @@
         <v>7.44</v>
       </c>
       <c r="M1124">
-        <v>5.32</v>
+        <v>5.48</v>
       </c>
       <c r="N1124">
-        <v>7.55</v>
+        <v>7.54</v>
       </c>
       <c r="O1124">
         <v>1</v>
@@ -58745,10 +58751,10 @@
         <v>4.11008009499658</v>
       </c>
       <c r="D1125" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E1125">
-        <v>4.069612201450256</v>
+        <v>3.95493888420064</v>
       </c>
       <c r="F1125">
         <v>-1</v>
@@ -58757,10 +58763,10 @@
         <v>0.01076991990500342</v>
       </c>
       <c r="H1125">
-        <v>0.01103038779854974</v>
+        <v>0.01112506111579936</v>
       </c>
       <c r="I1125">
-        <v>0.04046789354632452</v>
+        <v>0.1551412107959407</v>
       </c>
       <c r="J1125">
         <v>0.6542082328101022</v>
@@ -58772,16 +58778,16 @@
         <v>7.44</v>
       </c>
       <c r="M1125">
-        <v>5.32</v>
+        <v>5.48</v>
       </c>
       <c r="N1125">
-        <v>7.55</v>
+        <v>7.54</v>
       </c>
       <c r="O1125">
         <v>1</v>
       </c>
       <c r="P1125" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="1126" spans="1:16">
@@ -58795,10 +58801,10 @@
         <v>4.080094170624702</v>
       </c>
       <c r="D1126" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E1126">
-        <v>4.03827131389458</v>
+        <v>3.922655413560582</v>
       </c>
       <c r="F1126">
         <v>-1</v>
@@ -58807,10 +58813,10 @@
         <v>0.0107999058293753</v>
       </c>
       <c r="H1126">
-        <v>0.01106172868610542</v>
+        <v>0.01115734458643942</v>
       </c>
       <c r="I1126">
-        <v>0.0418228567301222</v>
+        <v>0.1574387570641198</v>
       </c>
       <c r="J1126">
         <v>0.660099377087485</v>
@@ -58822,110 +58828,110 @@
         <v>7.44</v>
       </c>
       <c r="M1126">
-        <v>5.32</v>
+        <v>5.48</v>
       </c>
       <c r="N1126">
-        <v>7.55</v>
+        <v>7.54</v>
       </c>
       <c r="O1126">
         <v>1</v>
       </c>
       <c r="P1126" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="1127" spans="1:16">
       <c r="A1127" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1127" t="s">
         <v>274</v>
       </c>
       <c r="C1127">
-        <v>3.506040947305381</v>
+        <v>4.09506932635283</v>
       </c>
       <c r="D1127" t="s">
-        <v>271</v>
+        <v>524</v>
       </c>
       <c r="E1127">
-        <v>3.805388118054581</v>
+        <v>3.922655413560582</v>
       </c>
       <c r="F1127">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1127">
-        <v>0.01035395905269462</v>
+        <v>0.01114493067364717</v>
       </c>
       <c r="H1127">
-        <v>0.01037461188194542</v>
+        <v>0.01115734458643942</v>
       </c>
       <c r="I1127">
-        <v>0.2993471707491997</v>
+        <v>0.1724139127922477</v>
       </c>
       <c r="J1127">
-        <v>0.6635579559485695</v>
+        <v>0.660099377087485</v>
       </c>
       <c r="K1127">
-        <v>5.16</v>
+        <v>5.34</v>
       </c>
       <c r="L1127">
-        <v>6.93</v>
+        <v>7.62</v>
       </c>
       <c r="M1127">
-        <v>4.95</v>
+        <v>5.48</v>
       </c>
       <c r="N1127">
-        <v>7.09</v>
+        <v>7.54</v>
       </c>
       <c r="O1127">
         <v>1</v>
       </c>
       <c r="P1127" t="s">
-        <v>273</v>
+        <v>721</v>
       </c>
     </row>
     <row r="1128" spans="1:16">
       <c r="A1128" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1128" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C1128">
-        <v>4.062490004221782</v>
+        <v>3.533329356115667</v>
       </c>
       <c r="D1128" t="s">
-        <v>522</v>
+        <v>271</v>
       </c>
       <c r="E1128">
-        <v>4.01987167435361</v>
+        <v>3.805388118054581</v>
       </c>
       <c r="F1128">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1128">
-        <v>0.01081750999577822</v>
+        <v>0.01064667064388433</v>
       </c>
       <c r="H1128">
-        <v>0.01108012832564639</v>
+        <v>0.01037461188194542</v>
       </c>
       <c r="I1128">
-        <v>0.04261832986817282</v>
+        <v>0.2720587619389137</v>
       </c>
       <c r="J1128">
         <v>0.6635579559485695</v>
       </c>
       <c r="K1128">
-        <v>5.09</v>
+        <v>5.36</v>
       </c>
       <c r="L1128">
-        <v>7.44</v>
+        <v>7.09</v>
       </c>
       <c r="M1128">
-        <v>5.32</v>
+        <v>4.95</v>
       </c>
       <c r="N1128">
-        <v>7.55</v>
+        <v>7.09</v>
       </c>
       <c r="O1128">
         <v>1</v>
@@ -58936,46 +58942,46 @@
     </row>
     <row r="1129" spans="1:16">
       <c r="A1129" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1129" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C1129">
-        <v>4.07660051523464</v>
+        <v>3.506040947305381</v>
       </c>
       <c r="D1129" t="s">
-        <v>522</v>
+        <v>271</v>
       </c>
       <c r="E1129">
-        <v>4.01987167435361</v>
+        <v>3.805388118054581</v>
       </c>
       <c r="F1129">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1129">
-        <v>0.01116339948476536</v>
+        <v>0.01035395905269462</v>
       </c>
       <c r="H1129">
-        <v>0.01108012832564639</v>
+        <v>0.01037461188194542</v>
       </c>
       <c r="I1129">
-        <v>0.05672884088103025</v>
+        <v>0.2993471707491997</v>
       </c>
       <c r="J1129">
         <v>0.6635579559485695</v>
       </c>
       <c r="K1129">
-        <v>5.34</v>
+        <v>5.16</v>
       </c>
       <c r="L1129">
-        <v>7.62</v>
+        <v>6.93</v>
       </c>
       <c r="M1129">
-        <v>5.32</v>
+        <v>4.95</v>
       </c>
       <c r="N1129">
-        <v>7.55</v>
+        <v>7.09</v>
       </c>
       <c r="O1129">
         <v>1</v>
@@ -58986,346 +58992,346 @@
     </row>
     <row r="1130" spans="1:16">
       <c r="A1130" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1130" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C1130">
-        <v>3.565366250639179</v>
+        <v>4.062490004221782</v>
       </c>
       <c r="D1130" t="s">
-        <v>271</v>
+        <v>524</v>
       </c>
       <c r="E1130">
-        <v>3.834974429228346</v>
+        <v>3.903702401401839</v>
       </c>
       <c r="F1130">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1130">
-        <v>0.01061463374936082</v>
+        <v>0.01081750999577822</v>
       </c>
       <c r="H1130">
-        <v>0.01034502557077165</v>
+        <v>0.01117629759859816</v>
       </c>
       <c r="I1130">
-        <v>0.2696081785891673</v>
+        <v>0.1587876028199435</v>
       </c>
       <c r="J1130">
-        <v>0.6575809233882128</v>
+        <v>0.6635579559485695</v>
       </c>
       <c r="K1130">
-        <v>5.36</v>
+        <v>5.09</v>
       </c>
       <c r="L1130">
-        <v>7.09</v>
+        <v>7.44</v>
       </c>
       <c r="M1130">
-        <v>4.95</v>
+        <v>5.48</v>
       </c>
       <c r="N1130">
-        <v>7.09</v>
+        <v>7.54</v>
       </c>
       <c r="O1130">
         <v>1</v>
       </c>
       <c r="P1130" t="s">
-        <v>720</v>
+        <v>273</v>
       </c>
     </row>
     <row r="1131" spans="1:16">
       <c r="A1131" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1131" t="s">
         <v>274</v>
       </c>
       <c r="C1131">
-        <v>3.536882435316822</v>
+        <v>4.07660051523464</v>
       </c>
       <c r="D1131" t="s">
-        <v>271</v>
+        <v>524</v>
       </c>
       <c r="E1131">
-        <v>3.834974429228346</v>
+        <v>3.903702401401839</v>
       </c>
       <c r="F1131">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1131">
-        <v>0.01032311756468318</v>
+        <v>0.01116339948476536</v>
       </c>
       <c r="H1131">
-        <v>0.01034502557077165</v>
+        <v>0.01117629759859816</v>
       </c>
       <c r="I1131">
-        <v>0.2980919939115245</v>
+        <v>0.172898113832801</v>
       </c>
       <c r="J1131">
-        <v>0.6575809233882128</v>
+        <v>0.6635579559485695</v>
       </c>
       <c r="K1131">
-        <v>5.16</v>
+        <v>5.34</v>
       </c>
       <c r="L1131">
-        <v>6.93</v>
+        <v>7.62</v>
       </c>
       <c r="M1131">
-        <v>4.95</v>
+        <v>5.48</v>
       </c>
       <c r="N1131">
-        <v>7.09</v>
+        <v>7.54</v>
       </c>
       <c r="O1131">
         <v>1</v>
       </c>
       <c r="P1131" t="s">
-        <v>720</v>
+        <v>273</v>
       </c>
     </row>
     <row r="1132" spans="1:16">
       <c r="A1132" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1132" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C1132">
-        <v>4.092913099953997</v>
+        <v>3.565366250639179</v>
       </c>
       <c r="D1132" t="s">
-        <v>522</v>
+        <v>271</v>
       </c>
       <c r="E1132">
-        <v>4.051669487574707</v>
+        <v>3.834974429228346</v>
       </c>
       <c r="F1132">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1132">
-        <v>0.010787086900046</v>
+        <v>0.01061463374936082</v>
       </c>
       <c r="H1132">
-        <v>0.01104833051242529</v>
+        <v>0.01034502557077165</v>
       </c>
       <c r="I1132">
-        <v>0.04124361237929008</v>
+        <v>0.2696081785891673</v>
       </c>
       <c r="J1132">
         <v>0.6575809233882128</v>
       </c>
       <c r="K1132">
-        <v>5.09</v>
+        <v>5.36</v>
       </c>
       <c r="L1132">
-        <v>7.44</v>
+        <v>7.09</v>
       </c>
       <c r="M1132">
-        <v>5.32</v>
+        <v>4.95</v>
       </c>
       <c r="N1132">
-        <v>7.55</v>
+        <v>7.09</v>
       </c>
       <c r="O1132">
         <v>1</v>
       </c>
       <c r="P1132" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="1133" spans="1:16">
       <c r="A1133" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1133" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C1133">
-        <v>4.108517869106944</v>
+        <v>3.536882435316822</v>
       </c>
       <c r="D1133" t="s">
-        <v>522</v>
+        <v>271</v>
       </c>
       <c r="E1133">
-        <v>4.051669487574707</v>
+        <v>3.834974429228346</v>
       </c>
       <c r="F1133">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1133">
-        <v>0.01113148213089306</v>
+        <v>0.01032311756468318</v>
       </c>
       <c r="H1133">
-        <v>0.01104833051242529</v>
+        <v>0.01034502557077165</v>
       </c>
       <c r="I1133">
-        <v>0.05684838153223648</v>
+        <v>0.2980919939115245</v>
       </c>
       <c r="J1133">
         <v>0.6575809233882128</v>
       </c>
       <c r="K1133">
-        <v>5.34</v>
+        <v>5.16</v>
       </c>
       <c r="L1133">
-        <v>7.62</v>
+        <v>6.93</v>
       </c>
       <c r="M1133">
-        <v>5.32</v>
+        <v>4.95</v>
       </c>
       <c r="N1133">
-        <v>7.55</v>
+        <v>7.09</v>
       </c>
       <c r="O1133">
         <v>1</v>
       </c>
       <c r="P1133" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="1134" spans="1:16">
       <c r="A1134" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1134" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C1134">
-        <v>3.610929556577065</v>
+        <v>4.092913099953997</v>
       </c>
       <c r="D1134" t="s">
-        <v>272</v>
+        <v>524</v>
       </c>
       <c r="E1134">
-        <v>4.13618123936143</v>
+        <v>3.936456539832593</v>
       </c>
       <c r="F1134">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1134">
-        <v>0.01056907044342293</v>
+        <v>0.010787086900046</v>
       </c>
       <c r="H1134">
-        <v>0.01074381876063857</v>
+        <v>0.01114354346016741</v>
       </c>
       <c r="I1134">
-        <v>0.525251682784365</v>
+        <v>0.1564565601214039</v>
       </c>
       <c r="J1134">
-        <v>0.6490803066087565</v>
+        <v>0.6575809233882128</v>
       </c>
       <c r="K1134">
-        <v>5.36</v>
+        <v>5.09</v>
       </c>
       <c r="L1134">
-        <v>7.09</v>
+        <v>7.44</v>
       </c>
       <c r="M1134">
-        <v>5.09</v>
+        <v>5.48</v>
       </c>
       <c r="N1134">
-        <v>7.44</v>
+        <v>7.54</v>
       </c>
       <c r="O1134">
         <v>1</v>
       </c>
       <c r="P1134" t="s">
-        <v>518</v>
+        <v>722</v>
       </c>
     </row>
     <row r="1135" spans="1:16">
       <c r="A1135" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1135" t="s">
         <v>274</v>
       </c>
       <c r="C1135">
-        <v>3.580745617898816</v>
+        <v>4.108517869106944</v>
       </c>
       <c r="D1135" t="s">
-        <v>272</v>
+        <v>524</v>
       </c>
       <c r="E1135">
-        <v>4.13618123936143</v>
+        <v>3.936456539832593</v>
       </c>
       <c r="F1135">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1135">
-        <v>0.01027925438210118</v>
+        <v>0.01113148213089306</v>
       </c>
       <c r="H1135">
-        <v>0.01074381876063857</v>
+        <v>0.01114354346016741</v>
       </c>
       <c r="I1135">
-        <v>0.5554356214626139</v>
+        <v>0.1720613292743502</v>
       </c>
       <c r="J1135">
-        <v>0.6490803066087565</v>
+        <v>0.6575809233882128</v>
       </c>
       <c r="K1135">
-        <v>5.16</v>
+        <v>5.34</v>
       </c>
       <c r="L1135">
-        <v>6.93</v>
+        <v>7.62</v>
       </c>
       <c r="M1135">
-        <v>5.09</v>
+        <v>5.48</v>
       </c>
       <c r="N1135">
-        <v>7.44</v>
+        <v>7.54</v>
       </c>
       <c r="O1135">
         <v>1</v>
       </c>
       <c r="P1135" t="s">
-        <v>518</v>
+        <v>722</v>
       </c>
     </row>
     <row r="1136" spans="1:16">
       <c r="A1136" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1136" t="s">
         <v>275</v>
       </c>
       <c r="C1136">
-        <v>4.153911162709241</v>
+        <v>3.610929556577065</v>
       </c>
       <c r="D1136" t="s">
-        <v>522</v>
+        <v>272</v>
       </c>
       <c r="E1136">
-        <v>4.096892768841415</v>
+        <v>4.13618123936143</v>
       </c>
       <c r="F1136">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1136">
-        <v>0.01108608883729076</v>
+        <v>0.01056907044342293</v>
       </c>
       <c r="H1136">
-        <v>0.01100310723115858</v>
+        <v>0.01074381876063857</v>
       </c>
       <c r="I1136">
-        <v>0.0570183938678257</v>
+        <v>0.525251682784365</v>
       </c>
       <c r="J1136">
         <v>0.6490803066087565</v>
       </c>
       <c r="K1136">
-        <v>5.34</v>
+        <v>5.36</v>
       </c>
       <c r="L1136">
-        <v>7.62</v>
+        <v>7.09</v>
       </c>
       <c r="M1136">
-        <v>5.32</v>
+        <v>5.09</v>
       </c>
       <c r="N1136">
-        <v>7.55</v>
+        <v>7.44</v>
       </c>
       <c r="O1136">
         <v>1</v>
@@ -59336,69 +59342,69 @@
     </row>
     <row r="1137" spans="1:16">
       <c r="A1137" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1137" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C1137">
-        <v>3.610221685972557</v>
+        <v>4.153911162709241</v>
       </c>
       <c r="D1137" t="s">
-        <v>272</v>
+        <v>524</v>
       </c>
       <c r="E1137">
-        <v>4.135509026417971</v>
+        <v>3.983039919784014</v>
       </c>
       <c r="F1137">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1137">
-        <v>0.01056977831402744</v>
+        <v>0.01108608883729076</v>
       </c>
       <c r="H1137">
-        <v>0.01074449097358203</v>
+        <v>0.01109696008021599</v>
       </c>
       <c r="I1137">
-        <v>0.5252873404454137</v>
+        <v>0.1708712429252266</v>
       </c>
       <c r="J1137">
-        <v>0.6492123720200452</v>
+        <v>0.6490803066087565</v>
       </c>
       <c r="K1137">
-        <v>5.36</v>
+        <v>5.34</v>
       </c>
       <c r="L1137">
-        <v>7.09</v>
+        <v>7.62</v>
       </c>
       <c r="M1137">
-        <v>5.09</v>
+        <v>5.48</v>
       </c>
       <c r="N1137">
-        <v>7.44</v>
+        <v>7.54</v>
       </c>
       <c r="O1137">
         <v>1</v>
       </c>
       <c r="P1137" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1138" spans="1:16">
       <c r="A1138" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1138" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C1138">
         <v>4.153205933412959</v>
       </c>
       <c r="D1138" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E1138">
-        <v>4.096190180853359</v>
+        <v>3.982316201330152</v>
       </c>
       <c r="F1138">
         <v>-1</v>
@@ -59407,10 +59413,10 @@
         <v>0.01108679406658704</v>
       </c>
       <c r="H1138">
-        <v>0.01100380981914664</v>
+        <v>0.01109768379866985</v>
       </c>
       <c r="I1138">
-        <v>0.05701575255960023</v>
+        <v>0.1708897320828071</v>
       </c>
       <c r="J1138">
         <v>0.6492123720200452</v>
@@ -59422,10 +59428,10 @@
         <v>7.62</v>
       </c>
       <c r="M1138">
-        <v>5.32</v>
+        <v>5.48</v>
       </c>
       <c r="N1138">
-        <v>7.55</v>
+        <v>7.54</v>
       </c>
       <c r="O1138">
         <v>1</v>
@@ -59439,16 +59445,16 @@
         <v>0</v>
       </c>
       <c r="B1139" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C1139">
         <v>4.170804453696654</v>
       </c>
       <c r="D1139" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E1139">
-        <v>4.113722789076067</v>
+        <v>4.000376106040761</v>
       </c>
       <c r="F1139">
         <v>-1</v>
@@ -59457,10 +59463,10 @@
         <v>0.01106919554630335</v>
       </c>
       <c r="H1139">
-        <v>0.01098627721092393</v>
+        <v>0.01107962389395924</v>
       </c>
       <c r="I1139">
-        <v>0.05708166462058717</v>
+        <v>0.1704283476558928</v>
       </c>
       <c r="J1139">
         <v>0.6459167689706641</v>
@@ -59472,16 +59478,66 @@
         <v>7.62</v>
       </c>
       <c r="M1139">
-        <v>5.32</v>
+        <v>5.48</v>
       </c>
       <c r="N1139">
-        <v>7.55</v>
+        <v>7.54</v>
       </c>
       <c r="O1139">
         <v>1</v>
       </c>
       <c r="P1139" t="s">
-        <v>276</v>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:16">
+      <c r="A1140" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1140" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1140">
+        <v>4.234279683025449</v>
+      </c>
+      <c r="D1140" t="s">
+        <v>523</v>
+      </c>
+      <c r="E1140">
+        <v>4.086703585873142</v>
+      </c>
+      <c r="F1140">
+        <v>-1</v>
+      </c>
+      <c r="G1140">
+        <v>0.01100572031697455</v>
+      </c>
+      <c r="H1140">
+        <v>0.01069329641412686</v>
+      </c>
+      <c r="I1140">
+        <v>0.1475760971523066</v>
+      </c>
+      <c r="J1140">
+        <v>0.6340300219053469</v>
+      </c>
+      <c r="K1140">
+        <v>5.34</v>
+      </c>
+      <c r="L1140">
+        <v>7.62</v>
+      </c>
+      <c r="M1140">
+        <v>5.21</v>
+      </c>
+      <c r="N1140">
+        <v>7.39</v>
+      </c>
+      <c r="O1140">
+        <v>1</v>
+      </c>
+      <c r="P1140" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3432" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3429" uniqueCount="724">
   <si>
     <t>trade_time</t>
   </si>
@@ -841,12 +841,12 @@
     <t>2021-12-07</t>
   </si>
   <si>
+    <t>2021-11-29</t>
+  </si>
+  <si>
     <t>2021-11-25</t>
   </si>
   <si>
-    <t>2021-11-29</t>
-  </si>
-  <si>
     <t>2016-09-28</t>
   </si>
   <si>
@@ -1589,6 +1589,9 @@
   </si>
   <si>
     <t>2021-12-13</t>
+  </si>
+  <si>
+    <t>2021-12-14</t>
   </si>
   <si>
     <t>2016-08-29</t>
@@ -2540,7 +2543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1140"/>
+  <dimension ref="A1:P1139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2637,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2687,7 +2690,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2737,7 +2740,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2787,7 +2790,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2837,7 +2840,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2887,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2937,7 +2940,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2987,7 +2990,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -3037,7 +3040,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -3087,7 +3090,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3137,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3187,7 +3190,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3237,7 +3240,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -3287,7 +3290,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -3437,7 +3440,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3487,7 +3490,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3537,7 +3540,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3587,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3637,7 +3640,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3687,7 +3690,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3737,7 +3740,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3887,7 +3890,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3937,7 +3940,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -4087,7 +4090,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -4137,7 +4140,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -4187,7 +4190,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4237,7 +4240,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -4287,7 +4290,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4337,7 +4340,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4487,7 +4490,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4537,7 +4540,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4587,7 +4590,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4637,7 +4640,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4687,7 +4690,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4737,7 +4740,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4787,7 +4790,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4837,7 +4840,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4887,7 +4890,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4937,7 +4940,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4987,7 +4990,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -5037,7 +5040,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -5087,7 +5090,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -5337,7 +5340,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -5387,7 +5390,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -5437,7 +5440,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5587,7 +5590,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5637,7 +5640,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -7637,7 +7640,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7687,7 +7690,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7737,7 +7740,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -8187,7 +8190,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -8237,7 +8240,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -8287,7 +8290,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -8337,7 +8340,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -8387,7 +8390,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -8587,7 +8590,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8637,7 +8640,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -8687,7 +8690,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8887,7 +8890,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8937,7 +8940,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8987,7 +8990,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -9037,7 +9040,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -9337,7 +9340,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -9387,7 +9390,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -9437,7 +9440,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -9487,7 +9490,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9537,7 +9540,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9787,7 +9790,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9837,7 +9840,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9887,7 +9890,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9937,7 +9940,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -11337,7 +11340,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11387,7 +11390,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11437,7 +11440,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11487,7 +11490,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11537,7 +11540,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11587,7 +11590,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -12037,7 +12040,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -12087,7 +12090,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -12237,7 +12240,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -12287,7 +12290,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -12337,7 +12340,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -12787,7 +12790,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12837,7 +12840,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12887,7 +12890,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12937,7 +12940,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12987,7 +12990,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -13937,7 +13940,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13987,7 +13990,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -14037,7 +14040,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -14087,7 +14090,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -14137,7 +14140,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -14187,7 +14190,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -14987,7 +14990,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -15037,7 +15040,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -15087,7 +15090,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -15137,7 +15140,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -15187,7 +15190,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -15687,7 +15690,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15737,7 +15740,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15787,7 +15790,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15837,7 +15840,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15887,7 +15890,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15937,7 +15940,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15987,7 +15990,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -17487,7 +17490,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -17537,7 +17540,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -17587,7 +17590,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -17637,7 +17640,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17687,7 +17690,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17737,7 +17740,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17787,7 +17790,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -19437,7 +19440,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -19487,7 +19490,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19687,7 +19690,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19737,7 +19740,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19787,7 +19790,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19837,7 +19840,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19987,7 +19990,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -20037,7 +20040,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -20087,7 +20090,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -20237,7 +20240,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -20287,7 +20290,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -20337,7 +20340,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -20587,7 +20590,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -20637,7 +20640,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20687,7 +20690,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20737,7 +20740,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20787,7 +20790,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20837,7 +20840,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20887,7 +20890,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20937,7 +20940,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20987,7 +20990,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -21037,7 +21040,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -21087,7 +21090,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -21137,7 +21140,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -21187,7 +21190,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -21287,7 +21290,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -21337,7 +21340,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -21387,7 +21390,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -21437,7 +21440,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21487,7 +21490,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21537,7 +21540,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -21587,7 +21590,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21637,7 +21640,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -22087,7 +22090,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -22137,7 +22140,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -22187,7 +22190,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -22387,7 +22390,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -22437,7 +22440,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -22487,7 +22490,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -22537,7 +22540,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -22587,7 +22590,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22637,7 +22640,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22687,7 +22690,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22737,7 +22740,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22787,7 +22790,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22837,7 +22840,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22887,7 +22890,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22937,7 +22940,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22987,7 +22990,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -23037,7 +23040,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -23087,7 +23090,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -23137,7 +23140,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -23187,7 +23190,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -23237,7 +23240,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -23287,7 +23290,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -23337,7 +23340,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23837,7 +23840,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23887,7 +23890,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23937,7 +23940,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23987,7 +23990,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -24037,7 +24040,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -24287,7 +24290,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -24337,7 +24340,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24387,7 +24390,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24437,7 +24440,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24487,7 +24490,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24537,7 +24540,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24587,7 +24590,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24637,7 +24640,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24687,7 +24690,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24737,7 +24740,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24787,7 +24790,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24837,7 +24840,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24887,7 +24890,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24937,7 +24940,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -25137,7 +25140,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -25187,7 +25190,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -25237,7 +25240,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25287,7 +25290,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -25837,7 +25840,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25887,7 +25890,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25937,7 +25940,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25987,7 +25990,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -26037,7 +26040,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -26287,7 +26290,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26337,7 +26340,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26387,7 +26390,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26437,7 +26440,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26637,7 +26640,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26687,7 +26690,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26737,7 +26740,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26787,7 +26790,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26837,7 +26840,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26887,7 +26890,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26937,7 +26940,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -27237,7 +27240,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -27287,7 +27290,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -27337,7 +27340,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -27387,7 +27390,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -27537,7 +27540,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -27587,7 +27590,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -27637,7 +27640,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27687,7 +27690,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27737,7 +27740,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27887,7 +27890,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27937,7 +27940,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -28087,7 +28090,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -28137,7 +28140,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -28187,7 +28190,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -28237,7 +28240,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28287,7 +28290,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -28337,7 +28340,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -28387,7 +28390,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -28437,7 +28440,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -28687,7 +28690,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28737,7 +28740,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28787,7 +28790,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28837,7 +28840,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28887,7 +28890,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28937,7 +28940,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28987,7 +28990,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -29037,7 +29040,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -29087,7 +29090,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -29137,7 +29140,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -29187,7 +29190,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -29237,7 +29240,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -29287,7 +29290,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -29337,7 +29340,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29387,7 +29390,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29437,7 +29440,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -29687,7 +29690,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29737,7 +29740,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29937,7 +29940,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29987,7 +29990,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -30037,7 +30040,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -30087,7 +30090,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -30137,7 +30140,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -30187,7 +30190,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -30237,7 +30240,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -30287,7 +30290,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -30337,7 +30340,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30487,7 +30490,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -30537,7 +30540,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -30737,7 +30740,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30787,7 +30790,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30987,7 +30990,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -31037,7 +31040,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -31087,7 +31090,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -31137,7 +31140,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -31187,7 +31190,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -31287,7 +31290,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -31337,7 +31340,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31387,7 +31390,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31437,7 +31440,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31687,7 +31690,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31737,7 +31740,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31787,7 +31790,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -32137,7 +32140,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -32187,7 +32190,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -32237,7 +32240,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -33187,7 +33190,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -33237,7 +33240,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -33287,7 +33290,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -33337,7 +33340,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33537,7 +33540,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -33587,7 +33590,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -33637,7 +33640,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -34437,7 +34440,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -34487,7 +34490,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -34537,7 +34540,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -34587,7 +34590,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -34637,7 +34640,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -34687,7 +34690,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -34737,7 +34740,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34787,7 +34790,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34837,7 +34840,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34887,7 +34890,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34937,7 +34940,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34987,7 +34990,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -35037,7 +35040,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -35087,7 +35090,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -35187,7 +35190,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -35237,7 +35240,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -35287,7 +35290,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -35337,7 +35340,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35387,7 +35390,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -35437,7 +35440,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -35487,7 +35490,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -35687,7 +35690,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35737,7 +35740,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -35787,7 +35790,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -36237,7 +36240,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -36287,7 +36290,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -36337,7 +36340,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -36387,7 +36390,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -36587,7 +36590,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36637,7 +36640,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36687,7 +36690,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36737,7 +36740,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36787,7 +36790,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36837,7 +36840,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36887,7 +36890,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36937,7 +36940,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36987,7 +36990,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -37037,7 +37040,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -37087,7 +37090,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -37137,7 +37140,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -38137,7 +38140,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -38187,7 +38190,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -38237,7 +38240,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -38287,7 +38290,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -38537,7 +38540,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -38587,7 +38590,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38637,7 +38640,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38687,7 +38690,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38887,7 +38890,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38937,7 +38940,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38987,7 +38990,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -39087,7 +39090,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -39437,7 +39440,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -39487,7 +39490,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -39537,7 +39540,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -39587,7 +39590,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -39637,7 +39640,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39687,7 +39690,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39737,7 +39740,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39787,7 +39790,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39837,7 +39840,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39887,7 +39890,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -40137,7 +40140,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -40187,7 +40190,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -40237,7 +40240,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -40537,7 +40540,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40587,7 +40590,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40637,7 +40640,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40887,7 +40890,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40937,7 +40940,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40987,7 +40990,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -41037,7 +41040,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -41087,7 +41090,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -41537,7 +41540,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41587,7 +41590,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41687,7 +41690,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41737,7 +41740,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41787,7 +41790,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41837,7 +41840,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -42987,7 +42990,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -43037,7 +43040,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -43087,7 +43090,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -43137,7 +43140,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -43187,7 +43190,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -43237,7 +43240,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -43287,7 +43290,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -43337,7 +43340,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43387,7 +43390,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -44137,7 +44140,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -44187,7 +44190,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -44237,7 +44240,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -44487,7 +44490,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -44537,7 +44540,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -44587,7 +44590,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -44637,7 +44640,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -44687,7 +44690,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44737,7 +44740,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44787,7 +44790,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44837,7 +44840,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44887,7 +44890,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44937,7 +44940,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44987,7 +44990,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -45187,7 +45190,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -45237,7 +45240,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -45287,7 +45290,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -45487,7 +45490,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -45537,7 +45540,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -45587,7 +45590,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -45637,7 +45640,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45687,7 +45690,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45737,7 +45740,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -46637,7 +46640,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46687,7 +46690,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46787,7 +46790,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46837,7 +46840,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46887,7 +46890,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -47187,7 +47190,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -47237,7 +47240,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -47287,7 +47290,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -47337,7 +47340,7 @@
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="897" spans="1:16">
@@ -47387,7 +47390,7 @@
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="898" spans="1:16">
@@ -47537,7 +47540,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47637,7 +47640,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47687,7 +47690,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47737,7 +47740,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47887,7 +47890,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47937,7 +47940,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47987,7 +47990,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -48187,7 +48190,7 @@
         <v>1</v>
       </c>
       <c r="P913" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="914" spans="1:16">
@@ -48237,7 +48240,7 @@
         <v>1</v>
       </c>
       <c r="P914" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="915" spans="1:16">
@@ -48287,7 +48290,7 @@
         <v>1</v>
       </c>
       <c r="P915" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="916" spans="1:16">
@@ -48337,7 +48340,7 @@
         <v>1</v>
       </c>
       <c r="P916" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="917" spans="1:16">
@@ -48387,7 +48390,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -48737,7 +48740,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48787,7 +48790,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48837,7 +48840,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48887,7 +48890,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -49087,7 +49090,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -49137,7 +49140,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -49637,7 +49640,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49687,7 +49690,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49737,7 +49740,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49787,7 +49790,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49837,7 +49840,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -50237,7 +50240,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -50437,7 +50440,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -50487,7 +50490,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -50537,7 +50540,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -50587,7 +50590,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -51137,7 +51140,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -51187,7 +51190,7 @@
         <v>1</v>
       </c>
       <c r="P973" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="974" spans="1:16">
@@ -51237,7 +51240,7 @@
         <v>1</v>
       </c>
       <c r="P974" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="975" spans="1:16">
@@ -51887,7 +51890,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51937,7 +51940,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51987,7 +51990,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -52887,7 +52890,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -54237,7 +54240,7 @@
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -54287,7 +54290,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -54687,7 +54690,7 @@
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
@@ -54737,7 +54740,7 @@
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
@@ -54787,7 +54790,7 @@
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
@@ -54837,7 +54840,7 @@
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
@@ -54987,7 +54990,7 @@
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
@@ -55037,7 +55040,7 @@
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
@@ -55087,7 +55090,7 @@
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
@@ -55137,7 +55140,7 @@
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
@@ -55187,7 +55190,7 @@
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
@@ -55237,7 +55240,7 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
@@ -56687,7 +56690,7 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56737,7 +56740,7 @@
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56937,7 +56940,7 @@
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56987,7 +56990,7 @@
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -57037,7 +57040,7 @@
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -57187,7 +57190,7 @@
         <v>1</v>
       </c>
       <c r="P1093" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1094" spans="1:16">
@@ -57237,7 +57240,7 @@
         <v>1</v>
       </c>
       <c r="P1094" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1095" spans="1:16">
@@ -57287,7 +57290,7 @@
         <v>1</v>
       </c>
       <c r="P1095" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1096" spans="1:16">
@@ -57337,7 +57340,7 @@
         <v>1</v>
       </c>
       <c r="P1096" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1097" spans="1:16">
@@ -57637,7 +57640,7 @@
         <v>1</v>
       </c>
       <c r="P1102" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="1103" spans="1:16">
@@ -57687,7 +57690,7 @@
         <v>1</v>
       </c>
       <c r="P1103" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="1104" spans="1:16">
@@ -57737,7 +57740,7 @@
         <v>1</v>
       </c>
       <c r="P1104" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="1105" spans="1:16">
@@ -57787,7 +57790,7 @@
         <v>1</v>
       </c>
       <c r="P1105" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="1106" spans="1:16">
@@ -57837,7 +57840,7 @@
         <v>1</v>
       </c>
       <c r="P1106" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="1107" spans="1:16">
@@ -57887,7 +57890,7 @@
         <v>1</v>
       </c>
       <c r="P1107" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="1108" spans="1:16">
@@ -57937,7 +57940,7 @@
         <v>1</v>
       </c>
       <c r="P1108" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1109" spans="1:16">
@@ -57987,7 +57990,7 @@
         <v>1</v>
       </c>
       <c r="P1109" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1110" spans="1:16">
@@ -58037,7 +58040,7 @@
         <v>1</v>
       </c>
       <c r="P1110" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1111" spans="1:16">
@@ -58087,7 +58090,7 @@
         <v>1</v>
       </c>
       <c r="P1111" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1112" spans="1:16">
@@ -58137,7 +58140,7 @@
         <v>1</v>
       </c>
       <c r="P1112" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1113" spans="1:16">
@@ -58187,7 +58190,7 @@
         <v>1</v>
       </c>
       <c r="P1113" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1114" spans="1:16">
@@ -58237,7 +58240,7 @@
         <v>1</v>
       </c>
       <c r="P1114" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1115" spans="1:16">
@@ -58287,7 +58290,7 @@
         <v>1</v>
       </c>
       <c r="P1115" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1116" spans="1:16">
@@ -58337,7 +58340,7 @@
         <v>1</v>
       </c>
       <c r="P1116" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1117" spans="1:16">
@@ -58387,7 +58390,7 @@
         <v>1</v>
       </c>
       <c r="P1117" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1118" spans="1:16">
@@ -58437,7 +58440,7 @@
         <v>1</v>
       </c>
       <c r="P1118" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1119" spans="1:16">
@@ -58487,7 +58490,7 @@
         <v>1</v>
       </c>
       <c r="P1119" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1120" spans="1:16">
@@ -58687,7 +58690,7 @@
         <v>1</v>
       </c>
       <c r="P1123" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="1124" spans="1:16">
@@ -58751,10 +58754,10 @@
         <v>4.11008009499658</v>
       </c>
       <c r="D1125" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E1125">
-        <v>3.95493888420064</v>
+        <v>4.063538012668479</v>
       </c>
       <c r="F1125">
         <v>-1</v>
@@ -58763,10 +58766,10 @@
         <v>0.01076991990500342</v>
       </c>
       <c r="H1125">
-        <v>0.01112506111579936</v>
+        <v>0.01073646198733152</v>
       </c>
       <c r="I1125">
-        <v>0.1551412107959407</v>
+        <v>0.04654208232810131</v>
       </c>
       <c r="J1125">
         <v>0.6542082328101022</v>
@@ -58778,60 +58781,60 @@
         <v>7.44</v>
       </c>
       <c r="M1125">
-        <v>5.48</v>
+        <v>5.1</v>
       </c>
       <c r="N1125">
-        <v>7.54</v>
+        <v>7.4</v>
       </c>
       <c r="O1125">
         <v>1</v>
       </c>
       <c r="P1125" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="1126" spans="1:16">
       <c r="A1126" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1126" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C1126">
-        <v>4.080094170624702</v>
+        <v>4.126528036794054</v>
       </c>
       <c r="D1126" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E1126">
-        <v>3.922655413560582</v>
+        <v>4.063538012668479</v>
       </c>
       <c r="F1126">
         <v>-1</v>
       </c>
       <c r="G1126">
-        <v>0.0107999058293753</v>
+        <v>0.01111347196320595</v>
       </c>
       <c r="H1126">
-        <v>0.01115734458643942</v>
+        <v>0.01073646198733152</v>
       </c>
       <c r="I1126">
-        <v>0.1574387570641198</v>
+        <v>0.06299002412557542</v>
       </c>
       <c r="J1126">
-        <v>0.660099377087485</v>
+        <v>0.6542082328101022</v>
       </c>
       <c r="K1126">
-        <v>5.09</v>
+        <v>5.34</v>
       </c>
       <c r="L1126">
-        <v>7.44</v>
+        <v>7.62</v>
       </c>
       <c r="M1126">
-        <v>5.48</v>
+        <v>5.1</v>
       </c>
       <c r="N1126">
-        <v>7.54</v>
+        <v>7.4</v>
       </c>
       <c r="O1126">
         <v>1</v>
@@ -58842,196 +58845,196 @@
     </row>
     <row r="1127" spans="1:16">
       <c r="A1127" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1127" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C1127">
-        <v>4.09506932635283</v>
+        <v>3.523887214228577</v>
       </c>
       <c r="D1127" t="s">
-        <v>524</v>
+        <v>271</v>
       </c>
       <c r="E1127">
-        <v>3.922655413560582</v>
+        <v>3.822508083416949</v>
       </c>
       <c r="F1127">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1127">
-        <v>0.01114493067364717</v>
+        <v>0.01033611278577142</v>
       </c>
       <c r="H1127">
-        <v>0.01115734458643942</v>
+        <v>0.01035749191658305</v>
       </c>
       <c r="I1127">
-        <v>0.1724139127922477</v>
+        <v>0.2986208691883721</v>
       </c>
       <c r="J1127">
         <v>0.660099377087485</v>
       </c>
       <c r="K1127">
-        <v>5.34</v>
+        <v>5.16</v>
       </c>
       <c r="L1127">
-        <v>7.62</v>
+        <v>6.93</v>
       </c>
       <c r="M1127">
-        <v>5.48</v>
+        <v>4.95</v>
       </c>
       <c r="N1127">
-        <v>7.54</v>
+        <v>7.09</v>
       </c>
       <c r="O1127">
         <v>1</v>
       </c>
       <c r="P1127" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="1128" spans="1:16">
       <c r="A1128" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1128" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C1128">
-        <v>3.533329356115667</v>
+        <v>4.080094170624702</v>
       </c>
       <c r="D1128" t="s">
-        <v>271</v>
+        <v>525</v>
       </c>
       <c r="E1128">
-        <v>3.805388118054581</v>
+        <v>4.033493176853828</v>
       </c>
       <c r="F1128">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1128">
-        <v>0.01064667064388433</v>
+        <v>0.0107999058293753</v>
       </c>
       <c r="H1128">
-        <v>0.01037461188194542</v>
+        <v>0.01076650682314617</v>
       </c>
       <c r="I1128">
-        <v>0.2720587619389137</v>
+        <v>0.04660099377087423</v>
       </c>
       <c r="J1128">
-        <v>0.6635579559485695</v>
+        <v>0.660099377087485</v>
       </c>
       <c r="K1128">
-        <v>5.36</v>
+        <v>5.09</v>
       </c>
       <c r="L1128">
-        <v>7.09</v>
+        <v>7.44</v>
       </c>
       <c r="M1128">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="N1128">
-        <v>7.09</v>
+        <v>7.4</v>
       </c>
       <c r="O1128">
         <v>1</v>
       </c>
       <c r="P1128" t="s">
-        <v>273</v>
+        <v>722</v>
       </c>
     </row>
     <row r="1129" spans="1:16">
       <c r="A1129" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1129" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C1129">
-        <v>3.506040947305381</v>
+        <v>4.09506932635283</v>
       </c>
       <c r="D1129" t="s">
-        <v>271</v>
+        <v>525</v>
       </c>
       <c r="E1129">
-        <v>3.805388118054581</v>
+        <v>4.033493176853828</v>
       </c>
       <c r="F1129">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1129">
-        <v>0.01035395905269462</v>
+        <v>0.01114493067364717</v>
       </c>
       <c r="H1129">
-        <v>0.01037461188194542</v>
+        <v>0.01076650682314617</v>
       </c>
       <c r="I1129">
-        <v>0.2993471707491997</v>
+        <v>0.06157614949900214</v>
       </c>
       <c r="J1129">
-        <v>0.6635579559485695</v>
+        <v>0.660099377087485</v>
       </c>
       <c r="K1129">
-        <v>5.16</v>
+        <v>5.34</v>
       </c>
       <c r="L1129">
-        <v>6.93</v>
+        <v>7.62</v>
       </c>
       <c r="M1129">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="N1129">
-        <v>7.09</v>
+        <v>7.4</v>
       </c>
       <c r="O1129">
         <v>1</v>
       </c>
       <c r="P1129" t="s">
-        <v>273</v>
+        <v>722</v>
       </c>
     </row>
     <row r="1130" spans="1:16">
       <c r="A1130" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1130" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C1130">
-        <v>4.062490004221782</v>
+        <v>3.533329356115667</v>
       </c>
       <c r="D1130" t="s">
-        <v>524</v>
+        <v>271</v>
       </c>
       <c r="E1130">
-        <v>3.903702401401839</v>
+        <v>3.805388118054581</v>
       </c>
       <c r="F1130">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1130">
-        <v>0.01081750999577822</v>
+        <v>0.01064667064388433</v>
       </c>
       <c r="H1130">
-        <v>0.01117629759859816</v>
+        <v>0.01037461188194542</v>
       </c>
       <c r="I1130">
-        <v>0.1587876028199435</v>
+        <v>0.2720587619389137</v>
       </c>
       <c r="J1130">
         <v>0.6635579559485695</v>
       </c>
       <c r="K1130">
-        <v>5.09</v>
+        <v>5.36</v>
       </c>
       <c r="L1130">
-        <v>7.44</v>
+        <v>7.09</v>
       </c>
       <c r="M1130">
-        <v>5.48</v>
+        <v>4.95</v>
       </c>
       <c r="N1130">
-        <v>7.54</v>
+        <v>7.09</v>
       </c>
       <c r="O1130">
         <v>1</v>
@@ -59042,46 +59045,46 @@
     </row>
     <row r="1131" spans="1:16">
       <c r="A1131" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1131" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C1131">
-        <v>4.07660051523464</v>
+        <v>3.506040947305381</v>
       </c>
       <c r="D1131" t="s">
-        <v>524</v>
+        <v>271</v>
       </c>
       <c r="E1131">
-        <v>3.903702401401839</v>
+        <v>3.805388118054581</v>
       </c>
       <c r="F1131">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1131">
-        <v>0.01116339948476536</v>
+        <v>0.01035395905269462</v>
       </c>
       <c r="H1131">
-        <v>0.01117629759859816</v>
+        <v>0.01037461188194542</v>
       </c>
       <c r="I1131">
-        <v>0.172898113832801</v>
+        <v>0.2993471707491997</v>
       </c>
       <c r="J1131">
         <v>0.6635579559485695</v>
       </c>
       <c r="K1131">
-        <v>5.34</v>
+        <v>5.16</v>
       </c>
       <c r="L1131">
-        <v>7.62</v>
+        <v>6.93</v>
       </c>
       <c r="M1131">
-        <v>5.48</v>
+        <v>4.95</v>
       </c>
       <c r="N1131">
-        <v>7.54</v>
+        <v>7.09</v>
       </c>
       <c r="O1131">
         <v>1</v>
@@ -59092,157 +59095,157 @@
     </row>
     <row r="1132" spans="1:16">
       <c r="A1132" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1132" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C1132">
-        <v>3.565366250639179</v>
+        <v>4.062490004221782</v>
       </c>
       <c r="D1132" t="s">
-        <v>271</v>
+        <v>525</v>
       </c>
       <c r="E1132">
-        <v>3.834974429228346</v>
+        <v>4.015854424662296</v>
       </c>
       <c r="F1132">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1132">
-        <v>0.01061463374936082</v>
+        <v>0.01081750999577822</v>
       </c>
       <c r="H1132">
-        <v>0.01034502557077165</v>
+        <v>0.0107841455753377</v>
       </c>
       <c r="I1132">
-        <v>0.2696081785891673</v>
+        <v>0.04663557955948594</v>
       </c>
       <c r="J1132">
-        <v>0.6575809233882128</v>
+        <v>0.6635579559485695</v>
       </c>
       <c r="K1132">
-        <v>5.36</v>
+        <v>5.09</v>
       </c>
       <c r="L1132">
-        <v>7.09</v>
+        <v>7.44</v>
       </c>
       <c r="M1132">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="N1132">
-        <v>7.09</v>
+        <v>7.4</v>
       </c>
       <c r="O1132">
         <v>1</v>
       </c>
       <c r="P1132" t="s">
-        <v>722</v>
+        <v>273</v>
       </c>
     </row>
     <row r="1133" spans="1:16">
       <c r="A1133" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1133" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C1133">
-        <v>3.536882435316822</v>
+        <v>4.07660051523464</v>
       </c>
       <c r="D1133" t="s">
-        <v>271</v>
+        <v>525</v>
       </c>
       <c r="E1133">
-        <v>3.834974429228346</v>
+        <v>4.015854424662296</v>
       </c>
       <c r="F1133">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1133">
-        <v>0.01032311756468318</v>
+        <v>0.01116339948476536</v>
       </c>
       <c r="H1133">
-        <v>0.01034502557077165</v>
+        <v>0.0107841455753377</v>
       </c>
       <c r="I1133">
-        <v>0.2980919939115245</v>
+        <v>0.06074609057234337</v>
       </c>
       <c r="J1133">
-        <v>0.6575809233882128</v>
+        <v>0.6635579559485695</v>
       </c>
       <c r="K1133">
-        <v>5.16</v>
+        <v>5.34</v>
       </c>
       <c r="L1133">
-        <v>6.93</v>
+        <v>7.62</v>
       </c>
       <c r="M1133">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="N1133">
-        <v>7.09</v>
+        <v>7.4</v>
       </c>
       <c r="O1133">
         <v>1</v>
       </c>
       <c r="P1133" t="s">
-        <v>722</v>
+        <v>273</v>
       </c>
     </row>
     <row r="1134" spans="1:16">
       <c r="A1134" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1134" t="s">
+        <v>276</v>
+      </c>
+      <c r="C1134">
+        <v>3.565366250639179</v>
+      </c>
+      <c r="D1134" t="s">
         <v>272</v>
       </c>
-      <c r="C1134">
+      <c r="E1134">
         <v>4.092913099953997</v>
       </c>
-      <c r="D1134" t="s">
-        <v>524</v>
-      </c>
-      <c r="E1134">
-        <v>3.936456539832593</v>
-      </c>
       <c r="F1134">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1134">
+        <v>0.01061463374936082</v>
+      </c>
+      <c r="H1134">
         <v>0.010787086900046</v>
       </c>
-      <c r="H1134">
-        <v>0.01114354346016741</v>
-      </c>
       <c r="I1134">
-        <v>0.1564565601214039</v>
+        <v>0.5275468493148185</v>
       </c>
       <c r="J1134">
         <v>0.6575809233882128</v>
       </c>
       <c r="K1134">
+        <v>5.36</v>
+      </c>
+      <c r="L1134">
+        <v>7.09</v>
+      </c>
+      <c r="M1134">
         <v>5.09</v>
       </c>
-      <c r="L1134">
+      <c r="N1134">
         <v>7.44</v>
       </c>
-      <c r="M1134">
-        <v>5.48</v>
-      </c>
-      <c r="N1134">
-        <v>7.54</v>
-      </c>
       <c r="O1134">
         <v>1</v>
       </c>
       <c r="P1134" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="1135" spans="1:16">
       <c r="A1135" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1135" t="s">
         <v>274</v>
@@ -59251,10 +59254,10 @@
         <v>4.108517869106944</v>
       </c>
       <c r="D1135" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E1135">
-        <v>3.936456539832593</v>
+        <v>4.046337290720115</v>
       </c>
       <c r="F1135">
         <v>-1</v>
@@ -59263,10 +59266,10 @@
         <v>0.01113148213089306</v>
       </c>
       <c r="H1135">
-        <v>0.01114354346016741</v>
+        <v>0.01075366270927989</v>
       </c>
       <c r="I1135">
-        <v>0.1720613292743502</v>
+        <v>0.06218057838682878</v>
       </c>
       <c r="J1135">
         <v>0.6575809233882128</v>
@@ -59278,16 +59281,16 @@
         <v>7.62</v>
       </c>
       <c r="M1135">
-        <v>5.48</v>
+        <v>5.1</v>
       </c>
       <c r="N1135">
-        <v>7.54</v>
+        <v>7.4</v>
       </c>
       <c r="O1135">
         <v>1</v>
       </c>
       <c r="P1135" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="1136" spans="1:16">
@@ -59295,43 +59298,43 @@
         <v>0</v>
       </c>
       <c r="B1136" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C1136">
-        <v>3.610929556577065</v>
+        <v>4.153911162709241</v>
       </c>
       <c r="D1136" t="s">
-        <v>272</v>
+        <v>525</v>
       </c>
       <c r="E1136">
-        <v>4.13618123936143</v>
+        <v>4.089690436295342</v>
       </c>
       <c r="F1136">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1136">
-        <v>0.01056907044342293</v>
+        <v>0.01108608883729076</v>
       </c>
       <c r="H1136">
-        <v>0.01074381876063857</v>
+        <v>0.01071030956370466</v>
       </c>
       <c r="I1136">
-        <v>0.525251682784365</v>
+        <v>0.06422072641389853</v>
       </c>
       <c r="J1136">
         <v>0.6490803066087565</v>
       </c>
       <c r="K1136">
-        <v>5.36</v>
+        <v>5.34</v>
       </c>
       <c r="L1136">
-        <v>7.09</v>
+        <v>7.62</v>
       </c>
       <c r="M1136">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="N1136">
-        <v>7.44</v>
+        <v>7.4</v>
       </c>
       <c r="O1136">
         <v>1</v>
@@ -59342,34 +59345,34 @@
     </row>
     <row r="1137" spans="1:16">
       <c r="A1137" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1137" t="s">
         <v>274</v>
       </c>
       <c r="C1137">
-        <v>4.153911162709241</v>
+        <v>4.153205933412959</v>
       </c>
       <c r="D1137" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E1137">
-        <v>3.983039919784014</v>
+        <v>4.08901690269777</v>
       </c>
       <c r="F1137">
         <v>-1</v>
       </c>
       <c r="G1137">
-        <v>0.01108608883729076</v>
+        <v>0.01108679406658704</v>
       </c>
       <c r="H1137">
-        <v>0.01109696008021599</v>
+        <v>0.01071098309730223</v>
       </c>
       <c r="I1137">
-        <v>0.1708712429252266</v>
+        <v>0.06418903071518933</v>
       </c>
       <c r="J1137">
-        <v>0.6490803066087565</v>
+        <v>0.6492123720200452</v>
       </c>
       <c r="K1137">
         <v>5.34</v>
@@ -59378,16 +59381,16 @@
         <v>7.62</v>
       </c>
       <c r="M1137">
-        <v>5.48</v>
+        <v>5.1</v>
       </c>
       <c r="N1137">
-        <v>7.54</v>
+        <v>7.4</v>
       </c>
       <c r="O1137">
         <v>1</v>
       </c>
       <c r="P1137" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="1138" spans="1:16">
@@ -59398,28 +59401,28 @@
         <v>274</v>
       </c>
       <c r="C1138">
-        <v>4.153205933412959</v>
+        <v>4.170804453696654</v>
       </c>
       <c r="D1138" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E1138">
-        <v>3.982316201330152</v>
+        <v>4.105824478249614</v>
       </c>
       <c r="F1138">
         <v>-1</v>
       </c>
       <c r="G1138">
-        <v>0.01108679406658704</v>
+        <v>0.01106919554630335</v>
       </c>
       <c r="H1138">
-        <v>0.01109768379866985</v>
+        <v>0.01069417552175039</v>
       </c>
       <c r="I1138">
-        <v>0.1708897320828071</v>
+        <v>0.06497997544703971</v>
       </c>
       <c r="J1138">
-        <v>0.6492123720200452</v>
+        <v>0.6459167689706641</v>
       </c>
       <c r="K1138">
         <v>5.34</v>
@@ -59428,16 +59431,16 @@
         <v>7.62</v>
       </c>
       <c r="M1138">
-        <v>5.48</v>
+        <v>5.1</v>
       </c>
       <c r="N1138">
-        <v>7.54</v>
+        <v>7.4</v>
       </c>
       <c r="O1138">
         <v>1</v>
       </c>
       <c r="P1138" t="s">
-        <v>520</v>
+        <v>276</v>
       </c>
     </row>
     <row r="1139" spans="1:16">
@@ -59448,28 +59451,28 @@
         <v>274</v>
       </c>
       <c r="C1139">
-        <v>4.170804453696654</v>
+        <v>4.234279683025449</v>
       </c>
       <c r="D1139" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E1139">
-        <v>4.000376106040761</v>
+        <v>4.086703585873142</v>
       </c>
       <c r="F1139">
         <v>-1</v>
       </c>
       <c r="G1139">
-        <v>0.01106919554630335</v>
+        <v>0.01100572031697455</v>
       </c>
       <c r="H1139">
-        <v>0.01107962389395924</v>
+        <v>0.01069329641412686</v>
       </c>
       <c r="I1139">
-        <v>0.1704283476558928</v>
+        <v>0.1475760971523066</v>
       </c>
       <c r="J1139">
-        <v>0.6459167689706641</v>
+        <v>0.6340300219053469</v>
       </c>
       <c r="K1139">
         <v>5.34</v>
@@ -59478,65 +59481,15 @@
         <v>7.62</v>
       </c>
       <c r="M1139">
-        <v>5.48</v>
+        <v>5.21</v>
       </c>
       <c r="N1139">
-        <v>7.54</v>
+        <v>7.39</v>
       </c>
       <c r="O1139">
         <v>1</v>
       </c>
       <c r="P1139" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="1140" spans="1:16">
-      <c r="A1140" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1140" t="s">
-        <v>274</v>
-      </c>
-      <c r="C1140">
-        <v>4.234279683025449</v>
-      </c>
-      <c r="D1140" t="s">
-        <v>523</v>
-      </c>
-      <c r="E1140">
-        <v>4.086703585873142</v>
-      </c>
-      <c r="F1140">
-        <v>-1</v>
-      </c>
-      <c r="G1140">
-        <v>0.01100572031697455</v>
-      </c>
-      <c r="H1140">
-        <v>0.01069329641412686</v>
-      </c>
-      <c r="I1140">
-        <v>0.1475760971523066</v>
-      </c>
-      <c r="J1140">
-        <v>0.6340300219053469</v>
-      </c>
-      <c r="K1140">
-        <v>5.34</v>
-      </c>
-      <c r="L1140">
-        <v>7.62</v>
-      </c>
-      <c r="M1140">
-        <v>5.21</v>
-      </c>
-      <c r="N1140">
-        <v>7.39</v>
-      </c>
-      <c r="O1140">
-        <v>1</v>
-      </c>
-      <c r="P1140" t="s">
         <v>271</v>
       </c>
     </row>

--- a/s60_signal/position-01157-000157.xlsx
+++ b/s60_signal/position-01157-000157.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3426" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3420" uniqueCount="726">
   <si>
     <t>trade_time</t>
   </si>
@@ -1595,6 +1595,9 @@
   </si>
   <si>
     <t>2021-12-15</t>
+  </si>
+  <si>
+    <t>2021-12-16</t>
   </si>
   <si>
     <t>2016-08-29</t>
@@ -2546,7 +2549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1138"/>
+  <dimension ref="A1:P1136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2643,7 +2646,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2693,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2743,7 +2746,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2793,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2843,7 +2846,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2893,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2943,7 +2946,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2993,7 +2996,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -3043,7 +3046,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -3093,7 +3096,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3143,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3193,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3243,7 +3246,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -3293,7 +3296,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -3443,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3493,7 +3496,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3543,7 +3546,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3593,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3643,7 +3646,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3693,7 +3696,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3743,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3893,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3943,7 +3946,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -4093,7 +4096,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -4143,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -4193,7 +4196,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4243,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -4293,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4343,7 +4346,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4493,7 +4496,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4543,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4593,7 +4596,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4643,7 +4646,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4693,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4743,7 +4746,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4793,7 +4796,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4843,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4893,7 +4896,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4943,7 +4946,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4993,7 +4996,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -5043,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -5093,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -5343,7 +5346,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -5393,7 +5396,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -5443,7 +5446,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5593,7 +5596,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5643,7 +5646,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -7643,7 +7646,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7693,7 +7696,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7743,7 +7746,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -8193,7 +8196,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -8243,7 +8246,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -8293,7 +8296,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -8343,7 +8346,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -8393,7 +8396,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -8593,7 +8596,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8643,7 +8646,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -8693,7 +8696,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8893,7 +8896,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8943,7 +8946,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8993,7 +8996,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -9043,7 +9046,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -9343,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -9393,7 +9396,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -9443,7 +9446,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -9493,7 +9496,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9543,7 +9546,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9793,7 +9796,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9843,7 +9846,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9893,7 +9896,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9943,7 +9946,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -11343,7 +11346,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11393,7 +11396,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11443,7 +11446,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11493,7 +11496,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11543,7 +11546,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11593,7 +11596,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -12043,7 +12046,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -12093,7 +12096,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -12243,7 +12246,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -12293,7 +12296,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -12343,7 +12346,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -12793,7 +12796,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12843,7 +12846,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12893,7 +12896,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12943,7 +12946,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12993,7 +12996,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -13943,7 +13946,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13993,7 +13996,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -14043,7 +14046,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -14093,7 +14096,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -14143,7 +14146,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -14193,7 +14196,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -14993,7 +14996,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -15043,7 +15046,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -15093,7 +15096,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -15143,7 +15146,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -15193,7 +15196,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -15693,7 +15696,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15743,7 +15746,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15793,7 +15796,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15843,7 +15846,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15893,7 +15896,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15943,7 +15946,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15993,7 +15996,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -17493,7 +17496,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -17543,7 +17546,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -17593,7 +17596,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -17643,7 +17646,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17693,7 +17696,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17743,7 +17746,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17793,7 +17796,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -19443,7 +19446,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -19493,7 +19496,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19693,7 +19696,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19743,7 +19746,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19793,7 +19796,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19843,7 +19846,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19993,7 +19996,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -20043,7 +20046,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -20093,7 +20096,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -20243,7 +20246,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -20293,7 +20296,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -20343,7 +20346,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -20593,7 +20596,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -20643,7 +20646,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20693,7 +20696,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20743,7 +20746,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20793,7 +20796,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20843,7 +20846,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20893,7 +20896,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20943,7 +20946,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20993,7 +20996,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -21043,7 +21046,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -21093,7 +21096,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -21143,7 +21146,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -21193,7 +21196,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -21293,7 +21296,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -21343,7 +21346,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -21393,7 +21396,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -21443,7 +21446,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21493,7 +21496,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21543,7 +21546,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -21593,7 +21596,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21643,7 +21646,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -22093,7 +22096,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -22143,7 +22146,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -22193,7 +22196,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -22393,7 +22396,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -22443,7 +22446,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -22493,7 +22496,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -22543,7 +22546,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -22593,7 +22596,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22643,7 +22646,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22693,7 +22696,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22743,7 +22746,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22793,7 +22796,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22843,7 +22846,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22893,7 +22896,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22943,7 +22946,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22993,7 +22996,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -23043,7 +23046,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -23093,7 +23096,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -23143,7 +23146,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -23193,7 +23196,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -23243,7 +23246,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -23293,7 +23296,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -23343,7 +23346,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23843,7 +23846,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23893,7 +23896,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23943,7 +23946,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23993,7 +23996,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -24043,7 +24046,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -24293,7 +24296,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -24343,7 +24346,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24393,7 +24396,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24443,7 +24446,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24493,7 +24496,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24543,7 +24546,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24593,7 +24596,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24643,7 +24646,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24693,7 +24696,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24743,7 +24746,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24793,7 +24796,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24843,7 +24846,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24893,7 +24896,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24943,7 +24946,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -25143,7 +25146,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -25193,7 +25196,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -25243,7 +25246,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25293,7 +25296,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -25843,7 +25846,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25893,7 +25896,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25943,7 +25946,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25993,7 +25996,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -26043,7 +26046,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -26293,7 +26296,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26343,7 +26346,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26393,7 +26396,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26443,7 +26446,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26643,7 +26646,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26693,7 +26696,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26743,7 +26746,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26793,7 +26796,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26843,7 +26846,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26893,7 +26896,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26943,7 +26946,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -27243,7 +27246,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -27293,7 +27296,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -27343,7 +27346,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -27393,7 +27396,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -27543,7 +27546,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -27593,7 +27596,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -27643,7 +27646,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27693,7 +27696,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27743,7 +27746,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27893,7 +27896,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27943,7 +27946,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -28093,7 +28096,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -28143,7 +28146,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -28193,7 +28196,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -28243,7 +28246,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28293,7 +28296,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -28343,7 +28346,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -28393,7 +28396,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -28443,7 +28446,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -28693,7 +28696,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28743,7 +28746,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28793,7 +28796,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28843,7 +28846,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28893,7 +28896,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28943,7 +28946,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28993,7 +28996,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -29043,7 +29046,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -29093,7 +29096,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -29143,7 +29146,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -29193,7 +29196,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -29243,7 +29246,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -29293,7 +29296,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -29343,7 +29346,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29393,7 +29396,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29443,7 +29446,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -29693,7 +29696,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29743,7 +29746,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29943,7 +29946,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29993,7 +29996,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -30043,7 +30046,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -30093,7 +30096,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -30143,7 +30146,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -30193,7 +30196,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -30243,7 +30246,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -30293,7 +30296,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -30343,7 +30346,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30493,7 +30496,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -30543,7 +30546,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -30743,7 +30746,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30793,7 +30796,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30993,7 +30996,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -31043,7 +31046,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -31093,7 +31096,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -31143,7 +31146,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -31193,7 +31196,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -31293,7 +31296,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -31343,7 +31346,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31393,7 +31396,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31443,7 +31446,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31693,7 +31696,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31743,7 +31746,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31793,7 +31796,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -32143,7 +32146,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -32193,7 +32196,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -32243,7 +32246,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -33193,7 +33196,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -33243,7 +33246,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -33293,7 +33296,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -33343,7 +33346,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33543,7 +33546,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -33593,7 +33596,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -33643,7 +33646,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -34443,7 +34446,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -34493,7 +34496,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -34543,7 +34546,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -34593,7 +34596,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -34643,7 +34646,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -34693,7 +34696,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -34743,7 +34746,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34793,7 +34796,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34843,7 +34846,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34893,7 +34896,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34943,7 +34946,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34993,7 +34996,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -35043,7 +35046,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -35093,7 +35096,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -35193,7 +35196,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -35243,7 +35246,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -35293,7 +35296,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -35343,7 +35346,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35393,7 +35396,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -35443,7 +35446,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -35493,7 +35496,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -35693,7 +35696,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35743,7 +35746,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -35793,7 +35796,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -36243,7 +36246,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -36293,7 +36296,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -36343,7 +36346,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -36393,7 +36396,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -36593,7 +36596,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36643,7 +36646,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36693,7 +36696,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36743,7 +36746,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36793,7 +36796,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36843,7 +36846,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36893,7 +36896,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36943,7 +36946,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36993,7 +36996,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -37043,7 +37046,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -37093,7 +37096,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -37143,7 +37146,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -38143,7 +38146,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -38193,7 +38196,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -38243,7 +38246,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -38293,7 +38296,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -38543,7 +38546,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -38593,7 +38596,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38643,7 +38646,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38693,7 +38696,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38893,7 +38896,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38943,7 +38946,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38993,7 +38996,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -39093,7 +39096,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -39443,7 +39446,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -39493,7 +39496,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -39543,7 +39546,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -39593,7 +39596,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -39643,7 +39646,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39693,7 +39696,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39743,7 +39746,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39793,7 +39796,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39843,7 +39846,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39893,7 +39896,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -40143,7 +40146,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -40193,7 +40196,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -40243,7 +40246,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -40543,7 +40546,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40593,7 +40596,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40643,7 +40646,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40893,7 +40896,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40943,7 +40946,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40993,7 +40996,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -41043,7 +41046,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -41093,7 +41096,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -41543,7 +41546,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41593,7 +41596,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41693,7 +41696,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41743,7 +41746,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41793,7 +41796,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41843,7 +41846,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -42993,7 +42996,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -43043,7 +43046,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -43093,7 +43096,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -43143,7 +43146,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -43193,7 +43196,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -43243,7 +43246,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -43293,7 +43296,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -43343,7 +43346,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43393,7 +43396,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -44143,7 +44146,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -44193,7 +44196,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -44243,7 +44246,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -44493,7 +44496,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -44543,7 +44546,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -44593,7 +44596,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -44643,7 +44646,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -44693,7 +44696,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44743,7 +44746,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44793,7 +44796,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44843,7 +44846,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44893,7 +44896,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44943,7 +44946,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44993,7 +44996,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -45193,7 +45196,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -45243,7 +45246,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -45293,7 +45296,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -45493,7 +45496,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -45543,7 +45546,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -45593,7 +45596,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -45643,7 +45646,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45693,7 +45696,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45743,7 +45746,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -46643,7 +46646,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46693,7 +46696,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46793,7 +46796,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46843,7 +46846,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46893,7 +46896,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -47193,7 +47196,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -47243,7 +47246,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -47293,7 +47296,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -47343,7 +47346,7 @@
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="897" spans="1:16">
@@ -47393,7 +47396,7 @@
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="898" spans="1:16">
@@ -47543,7 +47546,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47643,7 +47646,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47693,7 +47696,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47743,7 +47746,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47893,7 +47896,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47943,7 +47946,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47993,7 +47996,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -48193,7 +48196,7 @@
         <v>1</v>
       </c>
       <c r="P913" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="914" spans="1:16">
@@ -48243,7 +48246,7 @@
         <v>1</v>
       </c>
       <c r="P914" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="915" spans="1:16">
@@ -48293,7 +48296,7 @@
         <v>1</v>
       </c>
       <c r="P915" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="916" spans="1:16">
@@ -48343,7 +48346,7 @@
         <v>1</v>
       </c>
       <c r="P916" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="917" spans="1:16">
@@ -48393,7 +48396,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -48743,7 +48746,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48793,7 +48796,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48843,7 +48846,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48893,7 +48896,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -49093,7 +49096,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -49143,7 +49146,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -49643,7 +49646,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49693,7 +49696,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49743,7 +49746,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49793,7 +49796,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49843,7 +49846,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -50243,7 +50246,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -50443,7 +50446,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -50493,7 +50496,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -50543,7 +50546,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -50593,7 +50596,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -51143,7 +51146,7 @@
         <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="973" spans="1:16">
@@ -51193,7 +51196,7 @@
         <v>1</v>
       </c>
       <c r="P973" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="974" spans="1:16">
@@ -51243,7 +51246,7 @@
         <v>1</v>
       </c>
       <c r="P974" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="975" spans="1:16">
@@ -51893,7 +51896,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51943,7 +51946,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51993,7 +51996,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -52893,7 +52896,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -54243,7 +54246,7 @@
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -54293,7 +54296,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -54693,7 +54696,7 @@
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
@@ -54743,7 +54746,7 @@
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
@@ -54793,7 +54796,7 @@
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
@@ -54843,7 +54846,7 @@
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
@@ -54993,7 +54996,7 @@
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
@@ -55043,7 +55046,7 @@
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
@@ -55093,7 +55096,7 @@
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
@@ -55143,7 +55146,7 @@
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
@@ -55193,7 +55196,7 @@
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
@@ -55243,7 +55246,7 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
@@ -56693,7 +56696,7 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56743,7 +56746,7 @@
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56943,7 +56946,7 @@
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56993,7 +56996,7 @@
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -57043,7 +57046,7 @@
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -57193,7 +57196,7 @@
         <v>1</v>
       </c>
       <c r="P1093" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="1094" spans="1:16">
@@ -57243,7 +57246,7 @@
         <v>1</v>
       </c>
       <c r="P1094" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="1095" spans="1:16">
@@ -57293,7 +57296,7 @@
         <v>1</v>
       </c>
       <c r="P1095" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="1096" spans="1:16">
@@ -57343,7 +57346,7 @@
         <v>1</v>
       </c>
       <c r="P1096" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="1097" spans="1:16">
@@ -57643,7 +57646,7 @@
         <v>1</v>
       </c>
       <c r="P1102" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1103" spans="1:16">
@@ -57693,7 +57696,7 @@
         <v>1</v>
       </c>
       <c r="P1103" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1104" spans="1:16">
@@ -57743,7 +57746,7 @@
         <v>1</v>
       </c>
       <c r="P1104" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1105" spans="1:16">
@@ -57793,7 +57796,7 @@
         <v>1</v>
       </c>
       <c r="P1105" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1106" spans="1:16">
@@ -57843,7 +57846,7 @@
         <v>1</v>
       </c>
       <c r="P1106" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1107" spans="1:16">
@@ -57893,7 +57896,7 @@
         <v>1</v>
       </c>
       <c r="P1107" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1108" spans="1:16">
@@ -57943,7 +57946,7 @@
         <v>1</v>
       </c>
       <c r="P1108" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1109" spans="1:16">
@@ -57993,7 +57996,7 @@
         <v>1</v>
       </c>
       <c r="P1109" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1110" spans="1:16">
@@ -58043,7 +58046,7 @@
         <v>1</v>
       </c>
       <c r="P1110" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1111" spans="1:16">
@@ -58093,7 +58096,7 @@
         <v>1</v>
       </c>
       <c r="P1111" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1112" spans="1:16">
@@ -58143,7 +58146,7 @@
         <v>1</v>
       </c>
       <c r="P1112" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1113" spans="1:16">
@@ -58193,7 +58196,7 @@
         <v>1</v>
       </c>
       <c r="P1113" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1114" spans="1:16">
@@ -58243,7 +58246,7 @@
         <v>1</v>
       </c>
       <c r="P1114" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="1115" spans="1:16">
@@ -58293,7 +58296,7 @@
         <v>1</v>
       </c>
       <c r="P1115" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="1116" spans="1:16">
@@ -58343,7 +58346,7 @@
         <v>1</v>
       </c>
       <c r="P1116" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="1117" spans="1:16">
@@ -58393,7 +58396,7 @@
         <v>1</v>
       </c>
       <c r="P1117" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="1118" spans="1:16">
@@ -58443,7 +58446,7 @@
         <v>1</v>
       </c>
       <c r="P1118" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="1119" spans="1:16">
@@ -58493,7 +58496,7 @@
         <v>1</v>
       </c>
       <c r="P1119" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="1120" spans="1:16">
@@ -58693,7 +58696,7 @@
         <v>1</v>
       </c>
       <c r="P1123" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="1124" spans="1:16">
@@ -58793,7 +58796,7 @@
         <v>1</v>
       </c>
       <c r="P1125" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="1126" spans="1:16">
@@ -58843,7 +58846,7 @@
         <v>1</v>
       </c>
       <c r="P1126" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="1127" spans="1:16">
@@ -58893,7 +58896,7 @@
         <v>1</v>
       </c>
       <c r="P1127" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="1128" spans="1:16">
@@ -58943,7 +58946,7 @@
         <v>1</v>
       </c>
       <c r="P1128" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="1129" spans="1:16">
@@ -58993,7 +58996,7 @@
         <v>1</v>
       </c>
       <c r="P1129" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="1130" spans="1:16">
@@ -59007,10 +59010,10 @@
         <v>3.533329356115667</v>
       </c>
       <c r="D1130" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E1130">
-        <v>3.805388118054581</v>
+        <v>4.062490004221782</v>
       </c>
       <c r="F1130">
         <v>1</v>
@@ -59019,10 +59022,10 @@
         <v>0.01064667064388433</v>
       </c>
       <c r="H1130">
-        <v>0.01037461188194542</v>
+        <v>0.01081750999577822</v>
       </c>
       <c r="I1130">
-        <v>0.2720587619389137</v>
+        <v>0.5291606481061151</v>
       </c>
       <c r="J1130">
         <v>0.6635579559485695</v>
@@ -59034,10 +59037,10 @@
         <v>7.09</v>
       </c>
       <c r="M1130">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
       <c r="N1130">
-        <v>7.09</v>
+        <v>7.44</v>
       </c>
       <c r="O1130">
         <v>1</v>
@@ -59057,10 +59060,10 @@
         <v>3.506040947305381</v>
       </c>
       <c r="D1131" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E1131">
-        <v>3.805388118054581</v>
+        <v>4.062490004221782</v>
       </c>
       <c r="F1131">
         <v>1</v>
@@ -59069,10 +59072,10 @@
         <v>0.01035395905269462</v>
       </c>
       <c r="H1131">
-        <v>0.01037461188194542</v>
+        <v>0.01081750999577822</v>
       </c>
       <c r="I1131">
-        <v>0.2993471707491997</v>
+        <v>0.5564490569164011</v>
       </c>
       <c r="J1131">
         <v>0.6635579559485695</v>
@@ -59084,10 +59087,10 @@
         <v>6.93</v>
       </c>
       <c r="M1131">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
       <c r="N1131">
-        <v>7.09</v>
+        <v>7.44</v>
       </c>
       <c r="O1131">
         <v>1</v>
@@ -59101,43 +59104,43 @@
         <v>2</v>
       </c>
       <c r="B1132" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C1132">
-        <v>4.062490004221782</v>
+        <v>4.07660051523464</v>
       </c>
       <c r="D1132" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E1132">
-        <v>4.022396742900239</v>
+        <v>3.969498629067438</v>
       </c>
       <c r="F1132">
         <v>-1</v>
       </c>
       <c r="G1132">
-        <v>0.01081750999577822</v>
+        <v>0.01116339948476536</v>
       </c>
       <c r="H1132">
-        <v>0.01073760325709976</v>
+        <v>0.01087050137093256</v>
       </c>
       <c r="I1132">
-        <v>0.04009326132154367</v>
+        <v>0.1071018861672015</v>
       </c>
       <c r="J1132">
         <v>0.6635579559485695</v>
       </c>
       <c r="K1132">
-        <v>5.09</v>
+        <v>5.34</v>
       </c>
       <c r="L1132">
-        <v>7.44</v>
+        <v>7.62</v>
       </c>
       <c r="M1132">
-        <v>5.06</v>
+        <v>5.2</v>
       </c>
       <c r="N1132">
-        <v>7.38</v>
+        <v>7.42</v>
       </c>
       <c r="O1132">
         <v>1</v>
@@ -59148,34 +59151,34 @@
     </row>
     <row r="1133" spans="1:16">
       <c r="A1133" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1133" t="s">
         <v>274</v>
       </c>
       <c r="C1133">
-        <v>4.07660051523464</v>
+        <v>4.108517869106944</v>
       </c>
       <c r="D1133" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E1133">
-        <v>4.022396742900239</v>
+        <v>4.000579198381294</v>
       </c>
       <c r="F1133">
         <v>-1</v>
       </c>
       <c r="G1133">
-        <v>0.01116339948476536</v>
+        <v>0.01113148213089306</v>
       </c>
       <c r="H1133">
-        <v>0.01073760325709976</v>
+        <v>0.01083942080161871</v>
       </c>
       <c r="I1133">
-        <v>0.0542037723344011</v>
+        <v>0.10793867072565</v>
       </c>
       <c r="J1133">
-        <v>0.6635579559485695</v>
+        <v>0.6575809233882128</v>
       </c>
       <c r="K1133">
         <v>5.34</v>
@@ -59184,16 +59187,16 @@
         <v>7.62</v>
       </c>
       <c r="M1133">
-        <v>5.06</v>
+        <v>5.2</v>
       </c>
       <c r="N1133">
-        <v>7.38</v>
+        <v>7.42</v>
       </c>
       <c r="O1133">
         <v>1</v>
       </c>
       <c r="P1133" t="s">
-        <v>273</v>
+        <v>725</v>
       </c>
     </row>
     <row r="1134" spans="1:16">
@@ -59201,81 +59204,81 @@
         <v>0</v>
       </c>
       <c r="B1134" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C1134">
-        <v>3.565366250639179</v>
+        <v>4.153911162709241</v>
       </c>
       <c r="D1134" t="s">
-        <v>272</v>
+        <v>527</v>
       </c>
       <c r="E1134">
-        <v>4.092913099953997</v>
+        <v>4.044782405634466</v>
       </c>
       <c r="F1134">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1134">
-        <v>0.01061463374936082</v>
+        <v>0.01108608883729076</v>
       </c>
       <c r="H1134">
-        <v>0.010787086900046</v>
+        <v>0.01079521759436553</v>
       </c>
       <c r="I1134">
-        <v>0.5275468493148185</v>
+        <v>0.1091287570747745</v>
       </c>
       <c r="J1134">
-        <v>0.6575809233882128</v>
+        <v>0.6490803066087565</v>
       </c>
       <c r="K1134">
-        <v>5.36</v>
+        <v>5.34</v>
       </c>
       <c r="L1134">
-        <v>7.09</v>
+        <v>7.62</v>
       </c>
       <c r="M1134">
-        <v>5.09</v>
+        <v>5.2</v>
       </c>
       <c r="N1134">
-        <v>7.44</v>
+        <v>7.42</v>
       </c>
       <c r="O1134">
         <v>1</v>
       </c>
       <c r="P1134" t="s">
-        <v>724</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1135" spans="1:16">
       <c r="A1135" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1135" t="s">
         <v>274</v>
       </c>
       <c r="C1135">
-        <v>4.108517869106944</v>
+        <v>4.153205933412959</v>
       </c>
       <c r="D1135" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E1135">
-        <v>4.052640527655644</v>
+        <v>4.044095665495765</v>
       </c>
       <c r="F1135">
         <v>-1</v>
       </c>
       <c r="G1135">
-        <v>0.01113148213089306</v>
+        <v>0.01108679406658704</v>
       </c>
       <c r="H1135">
-        <v>0.01070735947234436</v>
+        <v>0.01079590433450424</v>
       </c>
       <c r="I1135">
-        <v>0.05587734145129986</v>
+        <v>0.1091102679171945</v>
       </c>
       <c r="J1135">
-        <v>0.6575809233882128</v>
+        <v>0.6492123720200452</v>
       </c>
       <c r="K1135">
         <v>5.34</v>
@@ -59284,16 +59287,16 @@
         <v>7.62</v>
       </c>
       <c r="M1135">
-        <v>5.06</v>
+        <v>5.2</v>
       </c>
       <c r="N1135">
-        <v>7.38</v>
+        <v>7.42</v>
       </c>
       <c r="O1135">
         <v>1</v>
       </c>
       <c r="P1135" t="s">
-        <v>724</v>
+        <v>521</v>
       </c>
     </row>
     <row r="1136" spans="1:16">
@@ -59301,148 +59304,48 @@
         <v>0</v>
       </c>
       <c r="B1136" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C1136">
-        <v>4.153911162709241</v>
+        <v>4.065515479958699</v>
       </c>
       <c r="D1136" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E1136">
-        <v>4.095653648559692</v>
+        <v>4.166446888282731</v>
       </c>
       <c r="F1136">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1136">
-        <v>0.01108608883729076</v>
+        <v>0.0110144845200413</v>
       </c>
       <c r="H1136">
-        <v>0.01066434635144031</v>
+        <v>0.01063355311171727</v>
       </c>
       <c r="I1136">
-        <v>0.05825751414954894</v>
+        <v>0.1009314083240325</v>
       </c>
       <c r="J1136">
-        <v>0.6490803066087565</v>
+        <v>0.6340300219053469</v>
       </c>
       <c r="K1136">
-        <v>5.34</v>
+        <v>5.48</v>
       </c>
       <c r="L1136">
-        <v>7.62</v>
+        <v>7.54</v>
       </c>
       <c r="M1136">
-        <v>5.06</v>
+        <v>5.1</v>
       </c>
       <c r="N1136">
-        <v>7.38</v>
+        <v>7.4</v>
       </c>
       <c r="O1136">
         <v>1</v>
       </c>
       <c r="P1136" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="1137" spans="1:16">
-      <c r="A1137" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>274</v>
-      </c>
-      <c r="C1137">
-        <v>4.153205933412959</v>
-      </c>
-      <c r="D1137" t="s">
-        <v>526</v>
-      </c>
-      <c r="E1137">
-        <v>4.094985397578571</v>
-      </c>
-      <c r="F1137">
-        <v>-1</v>
-      </c>
-      <c r="G1137">
-        <v>0.01108679406658704</v>
-      </c>
-      <c r="H1137">
-        <v>0.01066501460242143</v>
-      </c>
-      <c r="I1137">
-        <v>0.05822053583438791</v>
-      </c>
-      <c r="J1137">
-        <v>0.6492123720200452</v>
-      </c>
-      <c r="K1137">
-        <v>5.34</v>
-      </c>
-      <c r="L1137">
-        <v>7.62</v>
-      </c>
-      <c r="M1137">
-        <v>5.06</v>
-      </c>
-      <c r="N1137">
-        <v>7.38</v>
-      </c>
-      <c r="O1137">
-        <v>1</v>
-      </c>
-      <c r="P1137" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="1138" spans="1:16">
-      <c r="A1138" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>277</v>
-      </c>
-      <c r="C1138">
-        <v>4.065515479958699</v>
-      </c>
-      <c r="D1138" t="s">
-        <v>525</v>
-      </c>
-      <c r="E1138">
-        <v>4.166446888282731</v>
-      </c>
-      <c r="F1138">
-        <v>1</v>
-      </c>
-      <c r="G1138">
-        <v>0.0110144845200413</v>
-      </c>
-      <c r="H1138">
-        <v>0.01063355311171727</v>
-      </c>
-      <c r="I1138">
-        <v>0.1009314083240325</v>
-      </c>
-      <c r="J1138">
-        <v>0.6340300219053469</v>
-      </c>
-      <c r="K1138">
-        <v>5.48</v>
-      </c>
-      <c r="L1138">
-        <v>7.54</v>
-      </c>
-      <c r="M1138">
-        <v>5.1</v>
-      </c>
-      <c r="N1138">
-        <v>7.4</v>
-      </c>
-      <c r="O1138">
-        <v>1</v>
-      </c>
-      <c r="P1138" t="s">
         <v>271</v>
       </c>
     </row>
